--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="1404">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -2772,6 +2772,1473 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology</t>
+  </si>
+  <si>
+    <t>Md Abdur Rahman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consultant </t>
+  </si>
+  <si>
+    <t>I’m Md Abdur Rahman, a higher-study consultant for Engineering &amp; Technology. I know this path from the inside: I won the Erasmus Mundus Joint Master’s (EMJM) scholarship for my master’s, and a Marie Skłodowska-Curie Actions (MSCA) fellowship for my PhD. Through UNIPILOT GLOBAL, I help students find the right scholarship, write a stronger SOP and CV, and prepare for the visa and the move abroad.</t>
+  </si>
+  <si>
+    <t>Fariha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was worried my SOP didn’t show my story clearly. Unipilot Global gave me detailed feedback on it. After the review, my SOP was much stronger, and I also won the EMJM scholarship. </t>
+  </si>
+  <si>
+    <t>I joined the free seminar. They explained all the details clearly.</t>
+  </si>
+  <si>
+    <t>Seminar</t>
+  </si>
+  <si>
+    <t>Esha</t>
+  </si>
+  <si>
+    <t>Mohammed Abbas</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>CV and SOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I took one to one session. It was very helpful for me. </t>
+  </si>
+  <si>
+    <t>Edith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Africa </t>
+  </si>
+  <si>
+    <t>Interview Prep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The session was really help me to win a full funded scholarship. </t>
+  </si>
+  <si>
+    <t>Upcoming</t>
+  </si>
+  <si>
+    <t>Higher Study Abroad</t>
+  </si>
+  <si>
+    <t>iccr-atal-bihari-vajpayee-general-scholarship-bachelor</t>
+  </si>
+  <si>
+    <t>ICCR Atal Bihari Vajpayee General Scholarship Scheme</t>
+  </si>
+  <si>
+    <t>Indian Council for Cultural Relations (ICCR) — Govt. of India</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Tuition, Hostel Accommodation, ₹18,000/mo Stipend, Annual Contingent Grant, Return Airfare)</t>
+  </si>
+  <si>
+    <t>Feb 27 – Apr 22 (Annual cycle via A2A Portal)</t>
+  </si>
+  <si>
+    <t>International students worldwide; age 18–35; high school diploma (10+2) with strong grades (PCM mandatory for B.E./B.Tech); 500-word English essay required.</t>
+  </si>
+  <si>
+    <t>Medium: Online Application to 5 Empanelled Indian Universities + 500-Word English Essay + Transcripts + Medical Form</t>
+  </si>
+  <si>
+    <t>International Undergraduates Seeking Fully Funded Degrees at Indian Public Universities</t>
+  </si>
+  <si>
+    <t>Administered by the Indian Council for Cultural Relations (ICCR) under the Ministry of External Affairs, this flagship scheme offers 625+ fully funded slots annually across central and state public universities in India (including Delhi University, JNU, BHU, and NITs) across engineering, sciences, humanities, commerce, and performing arts.</t>
+  </si>
+  <si>
+    <t>Official Transcripts: Certified copies of Grade 10 and Grade 12 (10+2 equivalent) mark sheets translated into English (Physics, Chemistry, and Mathematics mandatory for B.E./B.Tech). | English Essay &amp; Proficiency: A 500-word essay in English written directly on the A2A portal (or IELTS/TOEFL score reports if available). | Letters of Recommendation: 2 character/academic reference letters from high school principals or teachers. | Medical &amp; Identity Documents: Official ICCR Physical Fitness Certificate signed by a registered physician, valid Passport (minimum 2 years validity), and colour passport photo.</t>
+  </si>
+  <si>
+    <t>University Scrutiny of Academic Eligibility across up to 5 Selected Universities → Indian Embassy/High Commission Allocation of Scholarship Slots Based on Merit and Country Quotas.</t>
+  </si>
+  <si>
+    <t>Disciplined high school graduates who select a balanced list of 5 central/state Indian universities and submit clean, English-translated transcripts early in March.</t>
+  </si>
+  <si>
+    <t>https://a2ascholarships.iccr.gov.in</t>
+  </si>
+  <si>
+    <t>iccr-suborno-jayanti-scholarship-bangladesh-master</t>
+  </si>
+  <si>
+    <t>ICCR Suborno Jayanti Scholarship Scheme (Bangladesh Track)</t>
+  </si>
+  <si>
+    <t>Indian Council for Cultural Relations (ICCR) &amp; High Commission of India, Dhaka</t>
+  </si>
+  <si>
+    <t>Bachelor, Master, PhD</t>
+  </si>
+  <si>
+    <t>Full Ride (500 Dedicated Slots: 100% Tuition, Hostel, ₹18,000–₹22,000/mo Stipend, Contingent Grant, Travel)</t>
+  </si>
+  <si>
+    <t>Citizens of Bangladesh; age 18–35 for Bachelor/Master and under 40 for PhD; minimum 60% marks or GPA 3.0+; all non-medical disciplines at Indian public universities.</t>
+  </si>
+  <si>
+    <t>Medium: A2A Portal Application + 500-Word Essay + SSC/HSC/Bachelor Transcripts + Research Synopsis (for PhD)</t>
+  </si>
+  <si>
+    <t>Bangladeshi Students Pursuing Bachelor’s, Master’s, or PhDs at Premier Indian Institutes</t>
+  </si>
+  <si>
+    <t>Dedicated exclusively to citizens of Bangladesh, the Suborno Jayanti Scholarship Scheme provides 500 fully funded ICCR scholarships each year to study at premier public universities and institutes across India in Engineering, IT, Science, Economics, Humanities, and Performing Arts.</t>
+  </si>
+  <si>
+    <t>Academic Transcripts: Certified copies of SSC, HSC, and Bachelor’s/Master’s mark sheets and certificates. | Personal Essay / Research Synopsis: 500-word English essay for UG/PG applicants; full PhD Research Synopsis focusing on India-based or theoretical research for Doctoral candidates. | Recommendation Letters: 2 academic reference letters uploaded to the A2A portal. | Identity &amp; Medical Proof: Valid Bangladeshi passport (at least 2 years validity), National ID/Birth Certificate, and signed ICCR Medical Fitness Form.</t>
+  </si>
+  <si>
+    <t>Host University Provisional Admission Confirmation on the A2A Portal → High Commission of India (Dhaka, Chattogram, Rajshahi, Khulna, Sylhet) Final Merit Selection.</t>
+  </si>
+  <si>
+    <t>Meritorious Bangladeshi students with strong HSC or Bachelor’s GPAs who apply early in February/March and select both top-tier metro and specialized central universities.</t>
+  </si>
+  <si>
+    <t>https://sjsdhaka.gov.in</t>
+  </si>
+  <si>
+    <t>study-in-india-sii-partner-institute-scholarship-bachelor</t>
+  </si>
+  <si>
+    <t>Study in India (SII) Partner Institute Scholarship</t>
+  </si>
+  <si>
+    <t>Ministry of Education, Government of India</t>
+  </si>
+  <si>
+    <t>Bachelor, Master</t>
+  </si>
+  <si>
+    <t>Up to 100% Tuition Fee Waiver (G1: 100%, G2: 50%, G3: 25% tuition waiver across 160+ premier Indian institutes)</t>
+  </si>
+  <si>
+    <t>Apr – Jun (Annual admission &amp; counselling cycle)</t>
+  </si>
+  <si>
+    <t>International students (including SAARC, ASEAN, Africa, Middle East); strong high school (10+2) or Bachelor’s GPA; admitted via the Study in India portal.</t>
+  </si>
+  <si>
+    <t>Low–Medium: Single SII Portal Application + Academic Transcripts + Passport Copy</t>
+  </si>
+  <si>
+    <t>International Students Seeking Direct Tuition Waivers at Top NIRF-Ranked Indian Colleges</t>
+  </si>
+  <si>
+    <t>A flagship initiative of the Ministry of Education, Government of India, Study in India (SII) partners with 160+ NAAC/NIRF-accredited Indian institutions (including IITs, NITs, IIITs, and top private/public universities) to offer streamlined single-window admissions and merit-based tuition waivers to international students from Asia and Africa.</t>
+  </si>
+  <si>
+    <t>Academic Transcripts: High school (10th and 12th grade) transcripts for Undergraduate applicants; Bachelor’s degree transcripts for Master’s applicants. | Identity Proof: Valid passport bio-data page and recent passport-sized photograph. | Choice Filling Form: Ranked preference list of courses and partner institutes submitted on the SII portal.</t>
+  </si>
+  <si>
+    <t>Academic Merit Evaluation &amp; Institute Cutoffs → Centralized SII Counselling &amp; Seat/Tuition Waiver Allocation (G1/G2/G3 tiers).</t>
+  </si>
+  <si>
+    <t>International applicants from Bangladesh, Nepal, Sri Lanka, and Africa with 75%+ high school or undergraduate marks who complete choice-filling across multiple partner institutes.</t>
+  </si>
+  <si>
+    <t>https://www.studyinindia.gov.in</t>
+  </si>
+  <si>
+    <t>nalanda-university-bimstec-international-scholarship-master</t>
+  </si>
+  <si>
+    <t>Nalanda University BIMSTEC &amp; International Master’s Scholarships</t>
+  </si>
+  <si>
+    <t>Nalanda University &amp; Ministry of External Affairs, India</t>
+  </si>
+  <si>
+    <t>Social Sciences &amp; Humanities, Environment, Water &amp; Energy, Business, Economics &amp; Management</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Tuition, Admission Fee, On-Campus Residence, Meals, ₹20,000/mo Stipend, Return Airfare)</t>
+  </si>
+  <si>
+    <t>Mar 18 – May 31 (Annual intake deadline)</t>
+  </si>
+  <si>
+    <t>Citizens of BIMSTEC nations (Bangladesh, Bhutan, Myanmar, Nepal, Sri Lanka, Thailand) and developing countries; Bachelor’s degree with minimum 55% or 2.8+ GPA.</t>
+  </si>
+  <si>
+    <t>Medium: Online University Application + Statement of Purpose + Academic Transcripts + Online Interview</t>
+  </si>
+  <si>
+    <t>South &amp; Southeast Asian Graduates in Ecology, International Relations, Sustainable MBA &amp; Humanities</t>
+  </si>
+  <si>
+    <t>Established as an International Institution of National Importance in Rajgir, Bihar, Nalanda University offers fully funded BIMSTEC, ASEAN, and International Merit Scholarships for 2-year Master’s and MBA programs in Ecology &amp; Environment Studies, Historical Studies, Buddhist/Hindu Studies, International Relations, and Sustainable Development Management.</t>
+  </si>
+  <si>
+    <t>Official Transcripts: Bachelor’s degree certificate and full academic transcripts (minimum 55% or CGPA 2.8/4.0). | Statement of Purpose &amp; Self-Introduction: Written Statement of Purpose (300–500 words) detailing academic motivation and regional impact. | Letters of Recommendation: 2 academic or professional reference letters. | Language &amp; ID Proof: Valid Passport and proof of English proficiency (or certificate of English medium instruction).</t>
+  </si>
+  <si>
+    <t>Application &amp; SOP Screening by School Faculty → Online Admission &amp; Scholarship Panel Interview → Ministry/University Scholarship Allocation.</t>
+  </si>
+  <si>
+    <t>Graduates from Bangladesh, Bhutan, Nepal, and Southeast Asia passionate about environmental sustainability, Asian diplomacy, or heritage studies.</t>
+  </si>
+  <si>
+    <t>https://nalandauniv.edu.in/scholarship-info/</t>
+  </si>
+  <si>
+    <t>prime-minister-s-research-fellowship-pmrf-india-phd</t>
+  </si>
+  <si>
+    <t>Prime Minister’s Research Fellowship (PMRF)</t>
+  </si>
+  <si>
+    <t>Ministry of Education, Government of India (IITs, IISc, IISERs, NITs)</t>
+  </si>
+  <si>
+    <t>Full Ride + Elite Stipend (₹70,000–₹80,000/mo Fellowship + ₹2,00,000/yr Research Contingency Grant for 4–5 years)</t>
+  </si>
+  <si>
+    <t>May / Dec (Aligned with Direct &amp; Lateral Entry PhD cycles)</t>
+  </si>
+  <si>
+    <t>Final-year B.Tech/Integrated M.Sc. or M.Tech graduates in India with CGPA ≥ 8.0 (or GATE ≥ 650) pursuing a PhD in STEM at IITs, IISc, IISERs, or central universities.</t>
+  </si>
+  <si>
+    <t>Very High: PhD Admission at PMRF Granting Institute + Rigorous Research Proposal + Technical Panel Interview</t>
+  </si>
+  <si>
+    <t>Top-Tier Indian STEM Graduates Pursuing Doctoral Research at IITs &amp; IISc</t>
+  </si>
+  <si>
+    <t>India’s highest-paying domestic doctoral fellowship, the Prime Minister’s Research Fellowship (PMRF) is designed to attract the brightest engineering and science talent into doctoral research at 38+ premier Indian institutions (including all IITs, IISc Bengaluru, IISERs, NITs, and top central universities) through Direct Entry and Lateral Entry tracks.</t>
+  </si>
+  <si>
+    <t>Academic Credentials: B.Tech / Integrated M.Sc. / M.Tech transcripts showing CGPA ≥ 8.0 (and GATE score ≥ 650 where applicable) or completed PhD coursework transcripts with CGPA ≥ 8.5 for Lateral Entry. | Research Proposal &amp; Abstract: Detailed doctoral research proposal (problem formulation, methodology, national/industrial relevance) endorsed by the host PhD supervisor. | Recommendation Letters: Strong recommendation from the host institute nodal officer and doctoral advisor. | Publications / Pre-prints: Copies of prior conference papers, journal publications, or undergraduate thesis projects.</t>
+  </si>
+  <si>
+    <t>Host Institute Nodal Screening &amp; Nomination → National Subject-Panel Evaluation of Research Proposal, Prior Technical Output, and Live Technical Interview.</t>
+  </si>
+  <si>
+    <t>IIT, NIT, and IISER graduates with 8.5+ CGPA, prior IEEE/ACM/science publications, and a well-defined deep-tech or fundamental science research problem.</t>
+  </si>
+  <si>
+    <t>https://www.pmrf.in</t>
+  </si>
+  <si>
+    <t>reliance-foundation-undergraduate-postgraduate-scholarship</t>
+  </si>
+  <si>
+    <t>Reliance Foundation Undergraduate &amp; Postgraduate Scholarships</t>
+  </si>
+  <si>
+    <t>Reliance Foundation — India</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Computer Science, Data &amp; AI, Mathematics &amp; Natural Sciences, All fields</t>
+  </si>
+  <si>
+    <t>Up to ₹2,00,000 (Undergrad) or ₹6,00,000 (Postgrad in AI, CS, Renewables &amp; Life Sciences) + Alumni Network</t>
+  </si>
+  <si>
+    <t>Oct 6 – Dec 15 (Annual cycle)</t>
+  </si>
+  <si>
+    <t>Resident Indian citizens enrolled in Year 1 of any undergraduate degree (household income &lt; ₹15 Lakh) or postgraduate STEM/AI degree with top entrance ranks.</t>
+  </si>
+  <si>
+    <t>Medium: Online Aptitude Test + Personal &amp; Leadership Essays + 2 Reference Letters + Income Proof</t>
+  </si>
+  <si>
+    <t>First-Year Indian Undergraduate &amp; Postgraduate Students in AI, Engineering &amp; General Degrees</t>
+  </si>
+  <si>
+    <t>Awarding 5,000 undergraduate merit-cum-means scholarships and 100 elite postgraduate STEM scholarships annually, the Reliance Foundation supports high-potential Indian students across all streams at the Bachelor’s level and future-ready fields (AI, Computer Science, Mathematics, Renewable Energy, Life Sciences) at the Master’s level.</t>
+  </si>
+  <si>
+    <t>Academic &amp; Entrance Records: Class 12 mark sheet and First-Year College Enrollment Proof (plus GATE score or Undergraduate CGPA ≥ 7.5 for Postgraduate applicants). | Online Aptitude Test: Mandatory 60-minute proctored aptitude test covering verbal, analytical, and numerical ability. | Essays &amp; References: 2 personal/leadership essays and 2 reference letters (required for Postgraduate track). | Financial Need Proof: Official family income certificate (household income under ₹15 Lakh for Undergrad; preference for &lt; ₹2.5 Lakh).</t>
+  </si>
+  <si>
+    <t>Aptitude Test Score &amp; Academic Merit (60%), Financial Need Assessment for UG / Research &amp; Leadership Essays for PG (40%).</t>
+  </si>
+  <si>
+    <t>High-scoring first-year Indian college students from modest socio-economic backgrounds and top GATE/CGPA graduates entering M.Tech/M.Sc. in AI or Clean Energy.</t>
+  </si>
+  <si>
+    <t>https://www.scholarships.reliancefoundation.org</t>
+  </si>
+  <si>
+    <t>STEM, Need-based</t>
+  </si>
+  <si>
+    <t>inlaks-shivdasani-foundation-overseas-scholarship-master</t>
+  </si>
+  <si>
+    <t>Inlaks Shivdasani Foundation Overseas Scholarship</t>
+  </si>
+  <si>
+    <t>Inlaks Shivdasani Foundation — India</t>
+  </si>
+  <si>
+    <t>United Kingdom, United States</t>
+  </si>
+  <si>
+    <t>Up to USD 120,000 (Covers Full Tuition, Living Stipend, One-Way Airfare, Visa Fees &amp; Health Allowance)</t>
+  </si>
+  <si>
+    <t>Mar 31 (Closes 12:00 PM IST annually)</t>
+  </si>
+  <si>
+    <t>Indian citizens resident in India; age under 30; holding an unconditional/conditional Master’s admission offer from a top-tier university in the UK, Europe, or USA.</t>
+  </si>
+  <si>
+    <t>High: Confirmed Overseas Admission Offer + Portfolio/SOP + 2 Reference Letters + 2-Stage Mumbai Interviews</t>
+  </si>
+  <si>
+    <t>Exceptional Young Indian Graduates Admitted to Top US, UK &amp; European Universities</t>
+  </si>
+  <si>
+    <t>One of India’s oldest and most prestigious private overseas scholarships, the Inlaks Shivdasani Foundation funds exceptional young Indian citizens under age 30 to pursue full-time Master’s degrees across the Humanities, Social Sciences, Fine Arts, Law, Architecture, and Natural Sciences at leading institutions in the UK, Europe, and North America.</t>
+  </si>
+  <si>
+    <t>Proof of Admission: Unconditional or conditional admission offer letter for the upcoming Fall intake at a top-ranked foreign university (plus complete breakdown of tuition and fee waivers). | Academic Transcripts: Official Indian Bachelor’s degree transcripts (minimum 65% for Humanities/Law/Arts; 70% for STEM/Environment). | Portfolio &amp; Writing Samples: Creative portfolio (mandatory for Architecture, Fine Arts, Design, and Film applicants) and personal statement. | Letters of Recommendation: 2 confidential reference letters submitted via the online portal.</t>
+  </si>
+  <si>
+    <t>Application &amp; Admission Offer Review in April → Online Preliminary Interview in May → Final In-Person Panel Interview in Mumbai.</t>
+  </si>
+  <si>
+    <t>Well-rounded Indian graduates with admission to Oxford, Cambridge, LSE, Columbia, or top European conservatories/universities who demonstrate originality and social commitment.</t>
+  </si>
+  <si>
+    <t>https://www.inlaksfoundation.org/scholarships/</t>
+  </si>
+  <si>
+    <t>jn-tata-endowment-higher-education-loan-scholarship-master</t>
+  </si>
+  <si>
+    <t>J.N. Tata Endowment for the Higher Education of Indians</t>
+  </si>
+  <si>
+    <t>Tata Trusts — India</t>
+  </si>
+  <si>
+    <t>United States, United Kingdom, Germany</t>
+  </si>
+  <si>
+    <t>Master, PhD</t>
+  </si>
+  <si>
+    <t>₹1,00,000 to ₹10,00,000 Low-Interest Loan Scholarship + Up to ₹7,50,000 Gift Award &amp; ₹50,000 Travel Grant</t>
+  </si>
+  <si>
+    <t>Mar 15 – Mar 23 (Annual spring application window)</t>
+  </si>
+  <si>
+    <t>Indian citizens holding a Bachelor’s degree with minimum 60% marks; admitted to or applying for a recognized postgraduate/PhD program overseas.</t>
+  </si>
+  <si>
+    <t>High: Statement of Purpose + Online Cognitive/Thinking Assessment + Technical Subject Interview</t>
+  </si>
+  <si>
+    <t>Indian Graduates Pursuing Master’s or PhDs Abroad Needing Flexible Funding</t>
+  </si>
+  <si>
+    <t>Founded by Jamsetji Nusserwanji Tata in 1892, the J.N. Tata Endowment awards merit-based loan scholarships (carrying a nominal 2% simple interest, often waived upon timely repayment) paired with partial travel grants and gift awards of up to ₹7.5 Lakh for Indian students heading to top global universities for Master’s, PhD, or Postdoctoral studies.</t>
+  </si>
+  <si>
+    <t>Academic Transcripts &amp; Test Scores: Undergraduate/Postgraduate mark sheets (minimum 60% average) and GRE/GMAT/IELTS/TOEFL scorecards. | Statement of Purpose: Structured SOP (up to 800 words) detailing academic pedigree, research/career trajectory, and choice of overseas university. | Letter of Recommendation &amp; Admission Letter: 1–2 academic/employer recommendations and overseas university admission offer. | Financial &amp; Identity Documents: PAN Card, Aadhaar, Passport, and candidate/guarantor income statements.</t>
+  </si>
+  <si>
+    <t>Phase 1 Academic &amp; SOP Screening → Phase 2 Online Cognitive Test → Phase 3 Technical Subject-Matter Expert Interview (April–June).</t>
+  </si>
+  <si>
+    <t>Ambitious Indian engineers, scientists, lawyers, and policy scholars admitted to top-50 global universities who perform strongly in the technical subject interview.</t>
+  </si>
+  <si>
+    <t>https://www.jntataendowment.org</t>
+  </si>
+  <si>
+    <t>asian-university-for-women-auw-scholarship-bachelor</t>
+  </si>
+  <si>
+    <t>Asian University for Women (AUW) Undergraduate Scholarships</t>
+  </si>
+  <si>
+    <t>Asian University for Women — Chittagong, Bangladesh</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Tuition, On-Campus Room &amp; Board, Healthcare, Course Supplies, Return Graduation Airfare)</t>
+  </si>
+  <si>
+    <t>Mar – May (Rolling deadlines for Fall/Summer intakes)</t>
+  </si>
+  <si>
+    <t>Female applicants from Bangladesh and across South/Southeast Asia &amp; the Middle East; strong secondary school record; demonstrated financial need; non-transfer students.</t>
+  </si>
+  <si>
+    <t>Medium: Admission Application + Self-Assessment Financial Aid Form + Family Income Proofs + Written/Interview Assessment</t>
+  </si>
+  <si>
+    <t>Talented Young Women from Bangladesh &amp; Asia Seeking Liberal Arts or STEM Degrees</t>
+  </si>
+  <si>
+    <t>Located in Chattagong, Bangladesh, the Asian University for Women (AUW) is an international liberal arts and sciences university dedicated to educating future female leaders across South and Southeast Asia. Over 85% of admitted students receive full or partial need-and-merit scholarships covering tuition, residential boarding, books, and healthcare.</t>
+  </si>
+  <si>
+    <t>Academic Transcripts: SSC and HSC (or O-Level / A-Level / Grade 12 equivalent) mark sheets and certificates. | Financial Aid Self-Assessment Form (SAF): Completed SAF accompanied by family bank statements, tax returns, or salary certificates proving financial need. | Personal Essays &amp; Application Form: Short personal essays demonstrating leadership, resilience, and community service.</t>
+  </si>
+  <si>
+    <t>Academic Readiness Review (Direct Undergraduate vs. Pathways for Promise Access Academy) + Written English/Math Assessment + Financial Aid Committee Need Verification.</t>
+  </si>
+  <si>
+    <t>First-generation and low-to-middle-income female high school graduates from Bangladesh, Pakistan, India, Afghanistan, Myanmar, and Nepal with strong leadership drive.</t>
+  </si>
+  <si>
+    <t>https://asian-university.org/admissions/financial-aid/</t>
+  </si>
+  <si>
+    <t>Women, Need-based</t>
+  </si>
+  <si>
+    <t>iut-oic-full-partial-scholarships-bangladesh-bachelor</t>
+  </si>
+  <si>
+    <t>IUT OIC Full &amp; Partial Scholarships (Bachelor’s Track)</t>
+  </si>
+  <si>
+    <t>Islamic University of Technology (IUT) &amp; Organisation of Islamic Cooperation</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Computer Science, Data &amp; AI</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Tuition, Campus Dormitory, Monthly Pocket Allowance, Medical Care, Books &amp; Return Airfare)</t>
+  </si>
+  <si>
+    <t>Feb – Apr (Annual admission &amp; OIC Focal Point nomination window)</t>
+  </si>
+  <si>
+    <t>Citizens of Bangladesh and 57 OIC member states; High School (HSC / A-Level) in Physics, Chemistry &amp; Mathematics with strong grades; passes IUT admission/nomination.</t>
+  </si>
+  <si>
+    <t>High: Competitive Engineering Entrance Test (Host Country) or OIC Ministry Nomination (International)</t>
+  </si>
+  <si>
+    <t>Top Engineering &amp; CS High School Graduates from Bangladesh and OIC Countries</t>
+  </si>
+  <si>
+    <t>Operated by the Organisation of Islamic Cooperation (OIC) in Gazipur, Bangladesh, the Islamic University of Technology (IUT) awards full and partial OIC scholarships to top-ranked Bangladeshi students (via the combined engineering admission merit list) and nominated international students from 57 OIC member states in Mechanical, Electrical, Civil, Computer Science, and Industrial Engineering.</t>
+  </si>
+  <si>
+    <t>Academic Certificates: SSC/O-Level and HSC/A-Level transcripts with top grades in Physics, Chemistry, Mathematics, and English. | OIC Nomination / Admission Test Receipt: Official nomination from the home country OIC Focal Point Ministry (for international applicants) or IUT Admission Test scorecard (for Bangladeshi applicants). | Medical &amp; Identity Documents: Valid Passport/National ID and medical fitness certificate.</t>
+  </si>
+  <si>
+    <t>Combined Engineering Admission Test Merit Rank (for Bangladeshi host-country slots) or OIC Member State Demographic Quota &amp; Academic Screening (for international slots).</t>
+  </si>
+  <si>
+    <t>High-scoring HSC/A-Level science students in Bangladesh and OIC member states with exceptional math and physics scores.</t>
+  </si>
+  <si>
+    <t>https://admission.iutoic-dhaka.edu/information/scholarship</t>
+  </si>
+  <si>
+    <t>bangladesh-government-mbbs-bds-scholarship-bachelor</t>
+  </si>
+  <si>
+    <t>Bangladesh Government MBBS &amp; BDS Scholarships for Foreign Students</t>
+  </si>
+  <si>
+    <t>Ministry of Education &amp; Ministry of Foreign Affairs, Bangladesh</t>
+  </si>
+  <si>
+    <t>Full Public Medical Tuition Waiver + Free Hostel Seat + Monthly Living Stipend at Government Medical Colleges</t>
+  </si>
+  <si>
+    <t>Jan – Feb 22 (Annual online portal &amp; embassy submission)</t>
+  </si>
+  <si>
+    <t>International students from SAARC and developing partner countries (outside Bangladesh); High School/A-Level with Biology, Chemistry &amp; Physics (minimum GPA 3.5–4.0).</t>
+  </si>
+  <si>
+    <t>Medium: Online DGME Application + Apostilled/Attested SSC &amp; HSC Equivalency Transcripts + Embassy Submission</t>
+  </si>
+  <si>
+    <t>International Pre-Med Students (SAARC &amp; Developing Nations) Seeking Public MBBS/BDS Degrees</t>
+  </si>
+  <si>
+    <t>Each academic year, the Government of the People's Republic of Bangladesh allocates fully funded and subsidized quota seats at premier public medical and dental colleges (including Dhaka Medical College, Sir Salimullah Medical College, and Chittagong Medical College) to meritorious international students from SAARC and friendly developing countries.</t>
+  </si>
+  <si>
+    <t>Attested Academic Transcripts: Grade 10 (SSC/O-Level) and Grade 12 (HSC/A-Level) mark sheets with Biology, Chemistry, and Physics, attested by the applicant's Ministry of Education, Ministry of Foreign Affairs, and the Bangladesh Embassy/High Commission. | DGME Online Application: Printed copy of the online foreign student medical admission application form. | Identity &amp; Financial Documents: Valid Passport copy, birth certificate, medical fitness report, and passport-sized photographs.</t>
+  </si>
+  <si>
+    <t>Equivalency Calculation of Grade 10 &amp; Grade 12 Biology/Science GPA by DGME Dhaka → Country-Quota Merit Allocation by the Central Scholarship Committee.</t>
+  </si>
+  <si>
+    <t>High-GPA pre-medical students from Nepal, Bhutan, India, Palestine, and African nations who complete document attestation at their local Bangladesh Mission before February.</t>
+  </si>
+  <si>
+    <t>https://www.dgme.gov.bd</t>
+  </si>
+  <si>
+    <t>iut-oic-postgraduate-scholarships-bangladesh-master-phd</t>
+  </si>
+  <si>
+    <t>IUT OIC Postgraduate Scholarships (M.Sc. &amp; PhD Track)</t>
+  </si>
+  <si>
+    <t>Islamic University of Technology (IUT) — Gazipur, Bangladesh</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Computer Science, Data &amp; AI, Education</t>
+  </si>
+  <si>
+    <t>Full Tuition Waiver + Residential &amp; Research Support (Full OIC Scholarship for M.Sc./PhD in Technical Education &amp; Engineering)</t>
+  </si>
+  <si>
+    <t>Feb – Apr (Annual 2026/2027 postgraduate call)</t>
+  </si>
+  <si>
+    <t>Citizens of Bangladesh and OIC member states holding a B.Sc. (for Master’s) or M.Sc. (for PhD) in Engineering, Computer Science, or Technical Education.</t>
+  </si>
+  <si>
+    <t>Medium–High: Online Application + Statement of Motivation + CV + 2 Reference Letters + English Proficiency</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technical Education Graduates from Bangladesh and OIC Nations</t>
+  </si>
+  <si>
+    <t>The Islamic University of Technology (IUT) in Gazipur offers full OIC scholarships and 100% departmental tuition waivers for Master’s and Doctoral candidates in Civil, Mechanical, Electrical, Computer Science, Chemical Engineering, and Technical &amp; Vocational Education (TVE).</t>
+  </si>
+  <si>
+    <t>University Degrees &amp; Transcripts: Certified copies of B.Sc. Engineering/CS degree (and M.Sc. degree for PhD applicants) with complete academic transcripts. | Motivation &amp; Research Plan: Letter of Motivation and preliminary research outline aligned with IUT engineering departments. | Letters of Recommendation: 2 academic recommendation letters (mandatory for PhD candidates) plus updated CV and English proficiency proof.</t>
+  </si>
+  <si>
+    <t>Departmental Academic Committee Review of GPA, Research Alignment, and OIC Member State Representation.</t>
+  </si>
+  <si>
+    <t>B.Sc. and M.Sc. engineering graduates and junior university faculty from Bangladesh and OIC countries seeking English-medium postgraduate research.</t>
+  </si>
+  <si>
+    <t>https://admission.iutoic-dhaka.edu/international-students/general-information</t>
+  </si>
+  <si>
+    <t>prime-minister-s-fellowship-bangladesh-master-phd</t>
+  </si>
+  <si>
+    <t>Prime Minister’s Fellowship Bangladesh (Master’s &amp; PhD Track)</t>
+  </si>
+  <si>
+    <t>Governance Innovation Unit (GIU), Prime Minister’s Office — Bangladesh</t>
+  </si>
+  <si>
+    <t>United Kingdom, United States, Australia</t>
+  </si>
+  <si>
+    <t>Full Ride Overseas (100% Tuition at Global Top-100/300 Universities, Living Stipend, Airfare, Health Insurance)</t>
+  </si>
+  <si>
+    <t>Mar – May (Annual call by GIU Bangladesh)</t>
+  </si>
+  <si>
+    <t>Bangladeshi citizens (BCS Cadre, Non-Cadre Govt. Officials, and Open/Private Sector Track); unconditional admission offer from a global top-ranked university; IELTS ≥ 6.5.</t>
+  </si>
+  <si>
+    <t>Very High: Unconditional Offer from Top-100/300 Global Univ + National Development Essay + IELTS 6.5+ + Viva</t>
+  </si>
+  <si>
+    <t>Bangladeshi Professionals, Academics &amp; Civil Servants Admitted to Top Global Universities</t>
+  </si>
+  <si>
+    <t>Administered by the Governance Innovation Unit (GIU) of the Prime Minister’s Office of Bangladesh, this flagship national fellowship funds Bangladeshi citizens across three quotas (BCS Cadre, Non-Cadre Government, and Open/Non-Government Citizens) to complete Master’s and PhD degrees at the world’s top-ranked universities (QS/THE Top 100–300).</t>
+  </si>
+  <si>
+    <t>Unconditional Admission Offer: Valid unconditional offer letter from a QS/Times Higher Education top-ranked international university. | Language Score: Valid IELTS overall score of 6.5+ (no band below 6.0) or TOEFL iBT equivalent. | Statement of Purpose &amp; Development Linkage: Detailed proposal demonstrating how the degree directly advances Bangladesh’s national development priorities, plus PhD Research Proposal.</t>
+  </si>
+  <si>
+    <t>University Global Ranking Score + Academic Track Record + Alignment with National Development Goals + High-Level Oral Viva in Dhaka.</t>
+  </si>
+  <si>
+    <t>Bangladeshi development practitioners, university lecturers, engineers, and civil servants holding unconditional offers from top UK, US, Australian, or European universities.</t>
+  </si>
+  <si>
+    <t>https://pmfellowship.pmo.gov.bd</t>
+  </si>
+  <si>
+    <t>Work experience, Research</t>
+  </si>
+  <si>
+    <t>bangabandhu-science-technology-nst-fellowship-bangladesh-phd</t>
+  </si>
+  <si>
+    <t>Bangabandhu Science &amp; Technology Fellowship (BSTFT) / NST Fellowship</t>
+  </si>
+  <si>
+    <t>Ministry of Science and Technology, Government of Bangladesh</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Mathematics &amp; Natural Sciences, Health &amp; Life Sciences, Agriculture &amp; Food Security</t>
+  </si>
+  <si>
+    <t>Full Domestic &amp; Overseas Research Grants (Monthly M.S./M.Phil/PhD Stipend + Full Tuition &amp; Thesis Grant)</t>
+  </si>
+  <si>
+    <t>Apr – Jun (NST Domestic) / Sep – Nov (Doctoral Grants)</t>
+  </si>
+  <si>
+    <t>Bangladeshi citizens enrolled in M.S., M.Phil, or PhD programs in Science, Engineering, Agriculture, or Biological/Medical Sciences at public universities in Bangladesh or abroad.</t>
+  </si>
+  <si>
+    <t>Medium–High: Supervisor-Endorsed Thesis/Research Proposal + University Enrollment Proof + Academic Transcripts</t>
+  </si>
+  <si>
+    <t>Bangladeshi M.S., M.Phil &amp; PhD STEM Researchers at Public Universities</t>
+  </si>
+  <si>
+    <t>Funded by the Ministry of Science and Technology (MoST) of the Government of Bangladesh, the NST Fellowship and Science &amp; Technology Fellowship Trust support thousands of Bangladeshi M.S., M.Phil, and PhD thesis students at public universities (such as BUET, Dhaka University, BAU, RU, CU, SUST, and JU) as well as doctoral scholars abroad.</t>
+  </si>
+  <si>
+    <t>Enrollment &amp; Supervisor Endorsement: Official certificate of enrollment in an M.S. (Thesis track), M.Phil, or PhD program at a recognized public university, signed by the thesis supervisor and department chair. | Research Synopsis: Approved thesis proposal detailing scientific methodology and expected national impact. | Academic Transcripts &amp; NID: SSC, HSC, Bachelor’s, and Master’s transcripts along with Bangladeshi National ID (NID).</t>
+  </si>
+  <si>
+    <t>Ministry Expert Committee Evaluation of Academic CGPA, Thesis Supervisor Endorsement, and Scientific Merit of the Research Synopsis.</t>
+  </si>
+  <si>
+    <t>Bangladeshi M.S. thesis and PhD researchers in agriculture, biotechnology, engineering, physics, and environmental sciences at public universities across Bangladesh.</t>
+  </si>
+  <si>
+    <t>https://most.gov.bd</t>
+  </si>
+  <si>
+    <t>msca-doctoral-networks-marie-sklodowska-curie-actions-phd</t>
+  </si>
+  <si>
+    <t>Marie Skłodowska-Curie Actions (MSCA) Doctoral Networks</t>
+  </si>
+  <si>
+    <t>European Commission (Horizon Europe) — EU &amp; Associated Countries</t>
+  </si>
+  <si>
+    <t>Germany, Netherlands, France, Spain, Italy, Belgium, Sweden, Denmark</t>
+  </si>
+  <si>
+    <t>Full Employment Contract (€3,400/mo Living Allowance + €600/mo Mobility Allowance + €660/mo Family Allowance + Full Research/Tuition Costs)</t>
+  </si>
+  <si>
+    <t>Year-round rolling vacancies on EURAXESS (Peak recruitment: Oct – May)</t>
+  </si>
+  <si>
+    <t>Open to all nationalities worldwide; holds a Master’s degree; must not have resided/worked in the recruiting host country for more than 12 months in the last 36 months (MSCA Mobility Rule); not yet awarded a PhD.</t>
+  </si>
+  <si>
+    <t>High: Tailored Cover Letter + Academic CV + Master’s Thesis Abstract + 2–3 Referees + Technical Panel Interview</t>
+  </si>
+  <si>
+    <t>Research-Focused Master’s Graduates Seeking Salaried European PhD Positions</t>
+  </si>
+  <si>
+    <t>Funded under the European Union’s Horizon Europe framework, MSCA Doctoral Networks recruit international doctoral candidates into high-impact research consortia comprising top European universities, research institutes, and industrial partners. Unlike traditional scholarships, MSCA fellows are hired as full-time salaried researchers for 36 to 48 months with full social security, pension, health coverage, and mandatory international/industrial secondments.</t>
+  </si>
+  <si>
+    <t>Curriculum Vitae: Detailed academic CV highlighting laboratory skills, thesis work, publications, and coding/experimental competencies. | Motivation Letter: Custom cover letter tailored to the specific Individual Research Project (IRP) advertised on EURAXESS. | Academic Transcripts &amp; Certificates: Certified Bachelor’s and Master’s degree certificates and full grade transcripts (plus Master’s thesis PDF or summary). | Mobility Declaration &amp; Referees: Signed declaration confirming compliance with the MSCA 12-in-36-month mobility rule, plus 2–3 academic reference letters.</t>
+  </si>
+  <si>
+    <t>Compliance with MSCA Mobility &amp; Doctoral Eligibility Rules (Pass/Fail) → Academic &amp; Technical Fit with the Specific Project (40%) → Research Experience &amp; Master’s Thesis Quality (30%) → Scientific Presentation &amp; Panel Interview (30%).</t>
+  </si>
+  <si>
+    <t>Proactive Master’s graduates who monitor EURAXESS daily, apply to specific 3-year project calls matching their exact experimental or computational background, and deliver a sharp 10-minute presentation of their Master’s thesis during the consortium interview.</t>
+  </si>
+  <si>
+    <t>https://euraxess.ec.europa.eu/jobs/search</t>
+  </si>
+  <si>
+    <t>chevening-scholarships-uk-government-global-programme-master</t>
+  </si>
+  <si>
+    <t>Chevening Scholarships (UK)</t>
+  </si>
+  <si>
+    <t>UK Foreign, Commonwealth &amp; Development Office (FCDO)</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Full Ride (100% UK Tuition Fees, Monthly Living Stipend, Return Economy Flights, Visa &amp; TB Test Costs, Arrival/Departure Allowances)</t>
+  </si>
+  <si>
+    <t>Aug – Nov 5 (Annual cycle; closes early November at 12:00 UTC)</t>
+  </si>
+  <si>
+    <t>Citizen of a Chevening-eligible country (including India, Bangladesh, Pakistan, and 160+ nations); Bachelor’s degree; minimum 2 years (2,800 hours) of work experience (full-time, part-time, or voluntary/internships); return to home country for 2 years post-study.</t>
+  </si>
+  <si>
+    <t>Very High: 4 Core Essays (Leadership, Networking, Studying in the UK, Career Plan) + 3 Unconditional UK University Choices + Embassy Interview</t>
+  </si>
+  <si>
+    <t>Emerging Leaders &amp; Mid-Career Professionals with 2+ Years of Work/Voluntary Experience</t>
+  </si>
+  <si>
+    <t>Chevening is the UK Government’s flagship international awards programme funded by the Foreign, Commonwealth and Development Office (FCDO) and partner organizations. It offers future leaders and influencers from over 160 countries a fully funded opportunity to complete any eligible 1-year taught Master’s degree at any UK university while joining an influential global network of 57,000+ alumni.</t>
+  </si>
+  <si>
+    <t>Four 500-Word Chevening Essays: Structured essays demonstrating (1) Leadership &amp; Influence, (2) Relationship-Building &amp; Networking, (3) Why Study in the UK (linking 3 chosen Master’s courses), and (4) Post-Study Career Plan aligned with UK/home-country priorities. | Work Experience Breakdown: Verifiable log of at least 2,800 hours (2 years) of full-time, part-time, or voluntary work completed after graduation. | Academic Transcripts &amp; 2 References: Official undergraduate degree transcripts and 2 reference letters uploaded before the interview stage. | Unconditional UK University Offer: At least 1 unconditional offer from one of your 3 selected UK Master’s programs by the mid-July deadline.</t>
+  </si>
+  <si>
+    <t>Automated Eligibility &amp; Work-Hours Filter → Independent Reading Committee Evaluation of the 4 Essays → Shortlisting for In-Person/Virtual British High Commission Panel Interview (Feb–Apr) → Unconditional UK Offer Verification (July).</t>
+  </si>
+  <si>
+    <t>Professionals, NGO founders, researchers, and policy advocates who use the STAR method (Situation, Task, Action, Result) in all four essays and connect their 3 UK Master’s choices directly to measurable national impact upon returning home.</t>
+  </si>
+  <si>
+    <t>https://www.chevening.org/scholarships/</t>
+  </si>
+  <si>
+    <t>commonwealth-phd-scholarships-low-middle-income-uk-phd</t>
+  </si>
+  <si>
+    <t>Commonwealth PhD Scholarships (UK)</t>
+  </si>
+  <si>
+    <t>UK Foreign, Commonwealth &amp; Development Office (FCDO) &amp; CSC</t>
+  </si>
+  <si>
+    <t>Full Ride (100% UK Tuition, £1,378–£1,690/mo Living Stipend, Return Flights, Study Travel Grant, Fieldwork Grant &amp; Family Allowances)</t>
+  </si>
+  <si>
+    <t>Sep – Oct 15 (Annual CSC portal + National Nominating Agency deadline)</t>
+  </si>
+  <si>
+    <t>Citizen or permanent resident of an eligible low- or middle-income Commonwealth country (including Bangladesh, Pakistan, India for Split-Site, Nigeria, Kenya, Ghana); holds a First Class or Upper Second Class (2:1) Bachelor’s and Master’s degree; unable to afford UK study without funding.</t>
+  </si>
+  <si>
+    <t>Very High: UK Doctoral Supervisor Support Statement + Development Impact Statement + CSC Application + National Agency Nomination</t>
+  </si>
+  <si>
+    <t>Commonwealth Doctoral Candidates Pursuing Development-Oriented PhDs in the UK</t>
+  </si>
+  <si>
+    <t>Administered by the Commonwealth Scholarship Commission (CSC) in the UK, Commonwealth PhD Scholarships (and Commonwealth Split-Site PhD Scholarships for candidates registered at home-country universities in countries like India, Bangladesh, and Pakistan) fund 3-year doctoral research (or 12-month split-site UK lab residencies) across six CSC development themes: Science &amp; Technology for Development, Health Systems, Global Prosperity, Peace &amp; Governance, Resilience/Climate Crisis, and Inclusion.</t>
+  </si>
+  <si>
+    <t>Supervisor Support Statement: Mandatory supporting statement from a prospective PhD supervisor at at least one UK university confirming research fit. | Development Impact Statement (4-Part): Detailed explanation of how the doctoral research addresses global/national development goals at local, national, and global scales, and how impact will be measured. | Research Proposal &amp; Methodology: Rigorous doctoral research plan written for both specialist and non-specialist reviewers. | Academic Transcripts &amp; 2 References: Certified Bachelor’s and Master’s transcripts plus 2 academic reference letters submitted via the CSC Central Application System, alongside National Nominating Agency application (e.g., UGC/MoE in Bangladesh, HEC in Pakistan, MoE in India).</t>
+  </si>
+  <si>
+    <t>Academic Merit of the Candidate (30%) + Quality of Research Proposal &amp; UK Supervisor Alignment (30%) + Potential Development Impact on the Home Country (40%), vetted jointly by the Home Country Nominating Agency and UK CSC Advisers.</t>
+  </si>
+  <si>
+    <t>Doctoral researchers who secure early backing from a UK professor before September and frame their PhD thesis around solving a concrete agricultural, climate, public health, or engineering bottleneck in their home Commonwealth nation.</t>
+  </si>
+  <si>
+    <t>https://cscuk.fcdo.gov.uk/scholarships/</t>
+  </si>
+  <si>
+    <t>STEM, Research, Need-based</t>
+  </si>
+  <si>
+    <t>gates-cambridge-scholarship-university-of-cambridge-master-phd</t>
+  </si>
+  <si>
+    <t>Gates Cambridge Scholarship</t>
+  </si>
+  <si>
+    <t>Bill &amp; Melinda Gates Foundation &amp; University of Cambridge, UK</t>
+  </si>
+  <si>
+    <t>Full Ride (100% University Composition Fee, £21,000/yr Stipend for up to 4 yrs, Economy Airfare, Visa &amp; IHS Health Surcharge, Academic &amp; Family Grants)</t>
+  </si>
+  <si>
+    <t>Oct 15 (US citizens) / Dec 3 or Jan 7 (International round — varies by Cambridge course)</t>
+  </si>
+  <si>
+    <t>Citizen of any country outside the United Kingdom; applying to pursue a full-time PhD, MLitt, or 1-year postgraduate course at the University of Cambridge; outstanding intellectual ability, leadership capacity, and commitment to improving the lives of others.</t>
+  </si>
+  <si>
+    <t>Very High: Cambridge Admission Dossier + Gates Cambridge 500-Word Personal Statement + PhD Research Proposal +Gates Reference Letter + Panel Interview</t>
+  </si>
+  <si>
+    <t>Top-1% Global Master’s &amp; PhD Applicants with Proven Social Leadership</t>
+  </si>
+  <si>
+    <t>Established in 2000 by a $210 million donation from the Bill and Melinda Gates Foundation to the University of Cambridge, the Gates Cambridge Scholarship is one of the most selective international postgraduate scholarships in the world. It awards roughly 80 full-cost scholarships each year to outstanding applicants from outside the UK to pursue a postgraduate degree in any subject available at Cambridge.</t>
+  </si>
+  <si>
+    <t>Gates Cambridge Statement (3,000 characters / ~500 words): Dedicated essay explaining why you are applying for a Gates Cambridge Scholarship, how you meet the four selection criteria, and how your work at Cambridge will improve the lives of others. | Research Proposal (PhD applicants): Detailed doctoral research proposal and confirmation of contact with a Cambridge supervisor. | Gates Cambridge Reference: A third, dedicated reference letter specifically addressing your leadership potential and social commitment (in addition to 2 standard academic references). | Academic Transcripts &amp; CV: Official university transcripts showing First Class / top-decile standing and a comprehensive CV.</t>
+  </si>
+  <si>
+    <t>Four Equally Weighted Pillars: (1) Outstanding Intellectual Ability (Departmental Ranking), (2) Reasons for Choice of Course (Academic Fit), (3) Commitment to Improving the Lives of Others, and (4) Leadership Potential — culminating in a 25-minute panel interview in March.</t>
+  </si>
+  <si>
+    <t>Scholars who combine top-ranked departmental academic credentials (publications, valedictorian GPAs) with an authentic, long-standing track record of civic, scientific, or humanitarian leadership.</t>
+  </si>
+  <si>
+    <t>https://www.gatescambridge.org/apply/</t>
+  </si>
+  <si>
+    <t>clarendon-fund-scholarships-university-of-oxford-master-phd</t>
+  </si>
+  <si>
+    <t>Clarendon Fund Scholarships (University of Oxford)</t>
+  </si>
+  <si>
+    <t>University of Oxford &amp; Oxford University Press, UK</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Oxford Course Fees + £19,237+/yr Living Grant for full period of fee liability)</t>
+  </si>
+  <si>
+    <t>Dec 3 – Jan 9 (Automatic consideration upon applying by your Oxford course’s Dec/Jan deadline)</t>
+  </si>
+  <si>
+    <t>Open to all nationalities worldwide; applying for any new full-time or part-time Master’s or DPhil (PhD) course at the University of Oxford; exceptional academic merit and research potential (typically GPA ≥ 3.7/4.0 or First Class Honours).</t>
+  </si>
+  <si>
+    <t>High: No Separate Scholarship Form Required (Evaluated via Oxford Graduate Admission Application, Statement of Purpose, Writing Sample/Proposal &amp; 3 References)</t>
+  </si>
+  <si>
+    <t>First-Class Master’s &amp; DPhil Applicants Applying to the University of Oxford</t>
+  </si>
+  <si>
+    <t>The Clarendon Fund is the University of Oxford’s flagship graduate scholarship scheme, awarding over 200 new, fully funded scholarships every year across all academic divisions (Medical Sciences, Mathematical, Physical &amp; Life Sciences, Humanities, and Social Sciences). Every international applicant who submits their Oxford graduate application by the December or January deadline is automatically considered without needing any separate scholarship application.</t>
+  </si>
+  <si>
+    <t>Oxford Graduate Application Form: Submitted prior to the specific course's December or January deadline. | Official Academic Transcripts: University transcripts demonstrating First Class Honours or top-tier GPA. | Statement of Purpose / DPhil Research Proposal: Course-specific personal statement or rigorous DPhil research proposal. | Three Academic Letters of Recommendation: 3 strong academic references testifying to your standing at the top of your cohort.</t>
+  </si>
+  <si>
+    <t>Pure Academic Excellence &amp; Future Potential: Oxford academic departments nominate their top-ranked admitted applicants based on GPA, research proposal originality, publications, and academic references → Divisional Funding Panels allocate awards in Feb–April.</t>
+  </si>
+  <si>
+    <t>Top-ranked applicants in each Oxford department whose academic transcripts, publications, and research proposals place them in the top 2–5% of their admitted graduate cohort.</t>
+  </si>
+  <si>
+    <t>https://www.ox.ac.uk/clarendon</t>
+  </si>
+  <si>
+    <t>international-max-planck-research-schools-imprs-germany-phd</t>
+  </si>
+  <si>
+    <t>International Max Planck Research Schools (IMPRS) PhD Fellowships</t>
+  </si>
+  <si>
+    <t>Max Planck Society (Max-Planck-Gesellschaft) &amp; Partner German Universities</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Computer Science, Data &amp; AI, Mathematics &amp; Natural Sciences, Health &amp; Life Sciences, Social Sciences &amp; Humanities</t>
+  </si>
+  <si>
+    <t>Full Salaried PhD Support (~€2,200–€2,700/mo net via TVöD E13 65% Contract, Zero Tuition, Full Health/Social Security, Conference Travel Grants)</t>
+  </si>
+  <si>
+    <t>Sep – Jan (Main annual calls; select IMPRS schools also recruit in Spring)</t>
+  </si>
+  <si>
+    <t>Open to all nationalities worldwide; holding (or about to complete) a Master’s degree (or exceptional 4-year B.Sc. Honours for fast-track programs) with top grades; strong English proficiency (no German required).</t>
+  </si>
+  <si>
+    <t>High: Online IMPRS Portal Application + Motivation Letter + Master’s Thesis Summary + 2–3 Referee Reports + Multi-Stage Symposium Interview</t>
+  </si>
+  <si>
+    <t>International STEM, AI, Life Sciences &amp; Social Science Graduates Seeking English-Taught PhDs in Germany</t>
+  </si>
+  <si>
+    <t>Operating 65+ specialized graduate schools across Germany in partnership with leading German universities (such as LMU Munich, TU Munich, Heidelberg, Göttingen, Leipzig, and ETH/EPFL partners), the International Max Planck Research Schools (IMPRS) provide world-class structured PhD training entirely in English. Admitted doctoral researchers receive standard German public-sector employment contracts (TVöD E13) or generous tax-free fellowships for 3 to 4 years.</t>
+  </si>
+  <si>
+    <t>Academic Transcripts &amp; Certificates: Bachelor’s and Master’s transcripts and degree certificates. | Letter of Motivation &amp; Lab Preferences: Statement detailing your scientific background and ranking your top 3 prospective Max Planck Principal Investigators (PIs). | Master’s Thesis Abstract &amp; CV: 1–2 page summary of your Master’s research project and full academic CV. | Confidential Reference Letters: 2 to 3 letters uploaded directly by referees to the IMPRS portal.</t>
+  </si>
+  <si>
+    <t>Scientific Committee Screening of Academic Record &amp; Research Experience → Online Pre-Interview → 2-to-3-Day Selection Symposium (Research Talk, 1-on-1 Interviews with Max Planck Directors/PIs, and Lab Rotations/Discussions).</t>
+  </si>
+  <si>
+    <t>Hands-on experimental and computational Master’s graduates who articulate a deep understanding of the specific Max Planck lab's recent papers and excel during the interactive selection symposium.</t>
+  </si>
+  <si>
+    <t>https://www.mpg.de/en/imprs</t>
+  </si>
+  <si>
+    <t>swedish-institute-scholarships-for-global-professionals-sisgp-master</t>
+  </si>
+  <si>
+    <t>Swedish Institute Scholarships for Global Professionals (SISGP)</t>
+  </si>
+  <si>
+    <t>Swedish Institute (SI) — Government of Sweden</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Tuition Paid Directly to University, SEK 12,000/mo Living Stipend, SEK 15,000 Travel Grant, Health Insurance)</t>
+  </si>
+  <si>
+    <t>Jan 15 (UniversityAdmissions.se deadline) / Feb 10 – Feb 26 (SI Scholarship portal window)</t>
+  </si>
+  <si>
+    <t>Citizens of 33+ eligible SISGP countries (including Bangladesh, Pakistan, Nepal, Indonesia, Kenya, Nigeria, Ghana, etc.); Bachelor’s degree; minimum 3,000 hours of demonstrated work experience AND leadership experience; admitted to one of 700+ eligible English-taught Swedish Master’s programs.</t>
+  </si>
+  <si>
+    <t>High: UniversityAdmissions.se Application + Official SI Templates for CV, Work &amp; Leadership Proof (3,000+ hrs) + 2 Reference Letters</t>
+  </si>
+  <si>
+    <t>Professionals from Developing Countries Seeking 1- or 2-Year Master’s in Sweden</t>
+  </si>
+  <si>
+    <t>Funded by the Swedish Ministry for Foreign Affairs and administered by the Swedish Institute (SI), SISGP awards around 350–400 full-ride Master’s scholarships annually to ambitious global professionals committed to the UN 2030 Agenda for Sustainable Development. It covers full tuition, living expenses, travel, and membership in the SI Network for Future Global Leaders (NFGL).</t>
+  </si>
+  <si>
+    <t>University Admissions Receipt: Proof of timely application to up to 4 eligible Master’s programs on UniversityAdmissions.se by mid-January. | SI Standardized Proof of Work &amp; Leadership Experience: Mandatory SI template forms signed and stamped by employers/organizations verifying at least 3,000 hours of work experience and leadership roles. | SI Standardized Curriculum Vitae: Completed strictly on the official Swedish Institute CV template. | Two Letters of Recommendation: Completed on the official SI reference template (1 professional, 1 academic/civil society).</t>
+  </si>
+  <si>
+    <t>Step 1: Strict Verification of 3,000 Work Hours, Leadership Proof &amp; SI Document Templates → Step 2: Evaluation of Academic Qualifications, Leadership Track Record, and Contribution to UN Sustainable Development Goals → Step 3: Confirmation of First-Choice Admission at a Swedish University in March/April.</t>
+  </si>
+  <si>
+    <t>Detail-oriented professionals who strictly follow the Swedish Institute's exact document templates, stamps, and page limits, and rank an SISGP-eligible Master’s program as their #1 priority on UniversityAdmissions.se.</t>
+  </si>
+  <si>
+    <t>https://si.se/en/apply/scholarships/swedish-institute-scholarships-for-global-professionals/</t>
+  </si>
+  <si>
+    <t>italian-government-maeci-invest-your-talent-in-italy-master-phd</t>
+  </si>
+  <si>
+    <t>Italian Government MAECI &amp; Invest Your Talent in Italy (IYT) Scholarships</t>
+  </si>
+  <si>
+    <t>Ministry of Foreign Affairs and International Cooperation (MAECI) — Italy</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Architecture, Arts &amp; Design, Business, Economics &amp; Management, All fields</t>
+  </si>
+  <si>
+    <t>Full Tuition Exemption + €900–€1,000/mo Stipend + Health Insurance + Mandatory Corporate Internship (IYT Track)</t>
+  </si>
+  <si>
+    <t>Feb – Mar (Invest Your Talent in Italy) / May – June (MAECI Study in Italy Call)</t>
+  </si>
+  <si>
+    <t>International students from eligible partner countries (including India, Bangladesh, Pakistan, African &amp; Asian nations); age under 28 (for Master’s) or under 30 (for PhD); Bachelor’s/Master’s degree; B2 English proficiency.</t>
+  </si>
+  <si>
+    <t>Medium: Study in Italy / IYT Portal Application + 1-Minute Video Essay (for IYT) + Statement of Purpose + Transcripts</t>
+  </si>
+  <si>
+    <t>Engineering, Architecture, Design, Economics &amp; Research Graduates Targeting Top Italian Universities</t>
+  </si>
+  <si>
+    <t>The Italian Ministry of Foreign Affairs (MAECI) operates two flagship merit scholarship tracks: the general MAECI Grants for Foreign Citizens (covering Master’s, AFAM Arts/Music, and PhD research across all Italian public universities) and the specialized 'Invest Your Talent in Italy' (IYT) program (combining English-taught Master’s degrees in Engineering, Architecture/Design, and Economics at Politecnico di Milano, Politecnico di Torino, Sapienza, Bologna, and Padua with a mandatory 3-month internship at a leading Italian company).</t>
+  </si>
+  <si>
+    <t>Academic Transcripts &amp; Diploma: Official Bachelor’s or Master’s degree certificate and transcripts. | 1-Minute Motivation Video &amp; Essay: Mandatory 60-second video motivation pitch (for IYT track) plus written Statement of Purpose. | Language Certificate: IELTS, TOEFL, or official Medium of Instruction (MOI) certificate confirming B2+ English proficiency. | Passport &amp; CV: Valid passport copy and Europass CV.</t>
+  </si>
+  <si>
+    <t>Academic GPA &amp; University Fit (50%), Motivation Video/Statement &amp; Professional Potential (30%), Italian Embassy Interview / Country Quota Allocation (20%).</t>
+  </si>
+  <si>
+    <t>Graduates in engineering, sustainable architecture, data science, and management who secure early pre-admission letters from Politecnico di Milano, Sapienza, or University of Bologna and submit a compelling motivation video.</t>
+  </si>
+  <si>
+    <t>https://studyinitaly.esteri.it</t>
+  </si>
+  <si>
+    <t>italy-dsu-regional-need-based-scholarship-bachelor-master-phd</t>
+  </si>
+  <si>
+    <t>Italian Regional DSU Need-Based Scholarships (EDISU / ER.GO / LazioDisco)</t>
+  </si>
+  <si>
+    <t>Italian Regional Right to University Study Agencies (DSU Toscana, EDISU Piemonte, ER.GO, LazioDisco)</t>
+  </si>
+  <si>
+    <t>Full Need-Based Support (100% Tuition Waiver, Free Dormitory Housing, Free Daily Canteen Meals + €6,500–€7,900/yr Cash Stipend)</t>
+  </si>
+  <si>
+    <t>July – September (Annual regional calls aligned with Italian university enrollment)</t>
+  </si>
+  <si>
+    <t>International and domestic students admitted to any public university in Italy (Bachelor’s, Master’s, or PhD) whose family economic status (ISEE Parificato) falls below the regional threshold (~€24,000–€27,000/yr; nearly all developing-country families qualify).</t>
+  </si>
+  <si>
+    <t>Medium: No Essay or GPA Cutoff in Year 1 (Requires Legalized/Apostilled Family Income, Bank, Property &amp; Family Composition Documents)</t>
+  </si>
+  <si>
+    <t>Students from South Asia, Africa &amp; Developing Nations Seeking Guaranteed Need-Based Funding in Italy</t>
+  </si>
+  <si>
+    <t>Guaranteed under Article 34 of the Italian Constitution ('Diritto allo Studio Universitario' — DSU), every region in Italy (Lombardy, Piedmont/EDISU, Emilia-Romagna/ER.GO, Tuscany/DSU, Lazio/LazioDisco, Veneto) provides comprehensive need-based scholarships to international students admitted to Italian public universities. First-year awards are determined strictly by family economic indicators (ISEE Parificato), while renewal in Year 2+ requires earning a set number of university ECTS credits (typically 20–25 CFU in Year 1).</t>
+  </si>
+  <si>
+    <t>University Pre-Admission / Universitaly Summary: Admission letter from an Italian public university and Universitaly pre-enrollment receipt. | Legalized Family Composition &amp; Income Certificates: Official municipal certificate listing all family members, previous calendar year annual household income certificate, property/real estate square-meter certificate, and Dec 31 bank balance statements. | Apostille / Consular Legalization &amp; Italian Translation: All financial documents must be translated into Italian and Apostilled (or legalized by the Italian Embassy) to generate the 'ISEE Parificato' certificate via an Italian CAF office.</t>
+  </si>
+  <si>
+    <t>100% Objective Economic Ranking in Year 1 based on the calculated ISEE Parificato score (students from low-income developing countries receive maximum priority points) + Academic Credit (CFU) threshold for Year 2 renewal.</t>
+  </si>
+  <si>
+    <t>Organized applicants from Bangladesh, India, Pakistan, and Africa who prepare, translate, and legalize their family income and property documents in May/June so they never miss the strict July/August regional DSU upload deadline.</t>
+  </si>
+  <si>
+    <t>https://www.uni-italia.it</t>
+  </si>
+  <si>
+    <t>vlir-uos-icp-connect-scholarships-belgium-master</t>
+  </si>
+  <si>
+    <t>VLIR-UOS ICP Connect Scholarships (Belgium)</t>
+  </si>
+  <si>
+    <t>VLIR-UOS &amp; Belgian Directorate-General for Development Cooperation (DGD)</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Agriculture &amp; Food Security, Environment, Water &amp; Energy, Health &amp; Life Sciences, Engineering &amp; Technology, Social Sciences &amp; Humanities</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Tuition Waiver, €1,400/mo All-Inclusive Stipend, International Flights, Health/Liability Insurance &amp; Logistics Allowance)</t>
+  </si>
+  <si>
+    <t>Jan 31 – Feb 28 (Varies across the 15 accredited Flemish Master’s programs at KU Leuven, UGent, UAntwerp, VUB, UHasselt)</t>
+  </si>
+  <si>
+    <t>National and current resident of one of the 29 eligible VLIR-UOS partner countries in Africa, Asia, and Latin America; age under 35 (for initial Master’s) or under 45 (for advanced Master’s); relevant professional/research experience in sustainable development.</t>
+  </si>
+  <si>
+    <t>High: University Master’s Application + VLIR-UOS Motivation &amp; Social Change Statement + Employer Support + 2 References</t>
+  </si>
+  <si>
+    <t>Development-Focused Professionals Pursuing English-Taught Master’s at KU Leuven, Ghent, or Antwerp</t>
+  </si>
+  <si>
+    <t>VLIR-UOS funds scholarships for international students from 29 developing countries in Africa, Asia, and Latin America to attend one of 15 accredited English-taught International Master’s Programmes (ICP Connect) at Flemish universities in Belgium (KU Leuven, Ghent University, University of Antwerp, Vrije Universiteit Brussel, and Hasselt University) covering fields such as Water Resources Engineering, Food Technology, Marine/Lacustrine Science, Epidemiology, Rural Development, and Transportation Sciences.</t>
+  </si>
+  <si>
+    <t>University Admission Application: Complete application for one of the 15 VLIR-UOS accredited ICP Master’s programs. | VLIR-UOS Motivation &amp; Change-Maker Statement: Essay explaining how you will act as an agent of change in your home institution or country upon graduation. | Professional Experience &amp; Employer Endorsement: Proof of employment in a higher education institution, research institute, government body, or social NGO. | Academic Transcripts &amp; 2 References: Certified Bachelor’s transcripts, IELTS/TOEFL score, and 2 reference letters.</t>
+  </si>
+  <si>
+    <t>Academic Merit &amp; Research Potential (30%), Professional Experience &amp; Likelihood of Knowledge Transfer / Multiplier Effect in Home Country (40%), Gender &amp; Regional Equity Balance (30%).</t>
+  </si>
+  <si>
+    <t>Researchers, agronomists, public health officers, and water/environmental engineers employed at universities or NGOs who demonstrate how Belgian technical training will immediately scale a project in their home country.</t>
+  </si>
+  <si>
+    <t>https://www.vliruos.be/get-funded/calls/icp-connect-scholarships</t>
+  </si>
+  <si>
+    <t>stipendium-hungaricum-postgraduate-track-master-phd</t>
+  </si>
+  <si>
+    <t>Stipendium Hungaricum (Master’s &amp; PhD Track)</t>
+  </si>
+  <si>
+    <t>Government of Hungary &amp; Tempus Public Foundation</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Tuition Waiver, Free Dormitory or HUF 40,000/mo Housing Grant, HUF 43,700–180,000/mo Stipend, Medical Insurance)</t>
+  </si>
+  <si>
+    <t>January 15 (Annual cycle on DreamApply + Home Country Sending Partner portal)</t>
+  </si>
+  <si>
+    <t>Citizens of 90+ Sending Partner countries (including Bangladesh, Pakistan, India, Nigeria, Kenya, etc.); Bachelor’s degree (for Master’s) or Master’s degree (for PhD); doctoral applicants must upload a Statement of Supervisor Acceptance from a Hungarian professor.</t>
+  </si>
+  <si>
+    <t>High: Dual Application (Tempus DreamApply Portal + Home Country Ministry/HEC/UGC Portal) + Research Plan + Supervisor Letter (PhD) + Oral Exam</t>
+  </si>
+  <si>
+    <t>Graduates Seeking English-Taught Master’s &amp; PhDs in Central Europe with Bilateral Quotas</t>
+  </si>
+  <si>
+    <t>Hungary’s flagship bilateral state scholarship supports thousands of international Master’s and Doctoral students across 30+ Hungarian universities (including ELTE Budapest, BME, University of Debrecen, University of Szeged, and University of Pécs) in over 800 English-taught degree programs. PhD scholars receive an increased monthly stipend (HUF 140,000/mo in Years 1–2 and HUF 180,000/mo in Years 3–4) alongside free tuition and housing.</t>
+  </si>
+  <si>
+    <t>Dual Portal Submissions: Application submitted both on the Hungarian DreamApply portal AND the applicant's home country Sending Partner portal (e.g., Ministry of Education in Bangladesh, HEC in Pakistan, MoE in India). | Research Plan &amp; Supervisor Statement (Mandatory for PhD): 2-page doctoral research proposal plus a signed Statement of Supervisor Acceptance from an accredited Hungarian doctoral school professor (via doktori.hu). | Academic Transcripts &amp; Motivation Letter: Bachelor’s/Master’s transcripts and a 1–2 page motivation letter addressed to the chosen Hungarian universities. | Language &amp; Medical Certificates: Proof of English proficiency and medical certificate.</t>
+  </si>
+  <si>
+    <t>Stage 1: Nomination by Home Country Sending Partner (HEC/Ministry/UGC exam or merit list) → Stage 2: University Entrance Exam &amp; Skype/Zoom Technical Interview in Hungary (March–May) → Stage 3: Tempus Public Foundation Award Allocation.</t>
+  </si>
+  <si>
+    <t>Master’s and PhD applicants who submit both the Hungarian and home-ministry applications before January 15 and (for PhD) contact Hungarian professors on doktori.hu in November to secure their mandatory supervisor acceptance letter.</t>
+  </si>
+  <si>
+    <t>https://stipendiumhungaricum.hu</t>
+  </si>
+  <si>
+    <t>turkiye-burslari-graduate-scholarship-master-phd</t>
+  </si>
+  <si>
+    <t>Türkiye Bursları Graduate Scholarship (Master’s &amp; PhD Track)</t>
+  </si>
+  <si>
+    <t>Presidency for Turks Abroad and Related Communities (YTB) — Government of Turkey</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Tuition + University Placement + Free Dormitory + Monthly Stipend + 1-Yr Turkish Language Course + Health Insurance + Return Flights)</t>
+  </si>
+  <si>
+    <t>Jan 10 – Feb 20 (Annual cycle)</t>
+  </si>
+  <si>
+    <t>International students worldwide; age under 30 for Master’s and under 35 for PhD; minimum 75% academic GPA in Bachelor’s/Master’s degrees.</t>
+  </si>
+  <si>
+    <t>High: Comprehensive TBBS Portal Application + Research Proposal (3,000-char sections) + Letter of Intent + 2 References + In-Person Embassy Interview</t>
+  </si>
+  <si>
+    <t>Master’s &amp; PhD Candidates Under 30/35 Seeking Full State Sponsorship &amp; University Placement in Turkey</t>
+  </si>
+  <si>
+    <t>Administered by the Republic of Turkey (YTB), Türkiye Bursları simultaneously places and funds international graduate students at top Turkish public and foundation universities (such as METU/ODTÜ, Boğaziçi, ITU, Bilkent, Koç, Hacettepe, and Ankara University). Unlike most scholarships, a single application on the TBBS portal handles both university admission across up to 12 selected programs and full scholarship funding.</t>
+  </si>
+  <si>
+    <t>Academic Diplomas &amp; Transcripts: Certified Bachelor’s (and Master’s for PhD) degree certificates and transcripts showing at least 75% cumulative grade average. | Structured Research Proposal (Master’s &amp; PhD): Detailed answers in the TBBS portal covering Research Title, Problem Analysis, Methodology, Literature Review, and Expected Contribution. | Letter of Intent &amp; 2 References: Statement of academic/career purpose and 2 academic recommendation letters. | International Test Scores (if required by English-medium universities): GRE/GMAT and TOEFL/IELTS for English-taught programs at METU, ITU, or Boğaziçi.</t>
+  </si>
+  <si>
+    <t>Academic GPA, Publications &amp; Research Proposal Review (50%) + 12-University Preference Alignment (20%) + In-Person Panel Interview at the Turkish Embassy/Consulate (30%).</t>
+  </si>
+  <si>
+    <t>Postgraduate candidates with 80%+ GPAs who write an original, literature-backed research proposal inside the TBBS portal and bring published papers or thesis samples to their in-person Turkish Embassy interview.</t>
+  </si>
+  <si>
+    <t>https://www.turkiyeburslari.gov.tr</t>
+  </si>
+  <si>
+    <t>hec-allama-iqbal-tap-scholarship-foreign-students-pakistan</t>
+  </si>
+  <si>
+    <t>HEC Allama Iqbal &amp; Technical Assistance Programme (TAP) Scholarships</t>
+  </si>
+  <si>
+    <t>Higher Education Commission (HEC) &amp; Ministry of Foreign Affairs, Government of Pakistan</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Health &amp; Life Sciences, Computer Science, Data &amp; AI, Agriculture &amp; Food Security, All fields</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Tuition Waiver, Free University Hostel, Monthly Living Stipend, Annual Book Allowance &amp; Return Airfare)</t>
+  </si>
+  <si>
+    <t>Mar – Jun (Annual cycle via HEC Portal &amp; Pakistan Embassies/High Commissions)</t>
+  </si>
+  <si>
+    <t>International students from South/Central Asia, Sri Lanka, Nepal, Afghanistan, Commonwealth, OIC, and developing partner countries; age 17–22 for Bachelor’s, under 30 for Master’s, and under 35 for PhD; strong academic standing.</t>
+  </si>
+  <si>
+    <t>Medium: Online HEC Scholarship Application + Attested Academic Transcripts + Written/Online Aptitude Test + Embassy Interview</t>
+  </si>
+  <si>
+    <t>International Students Seeking Fully Funded MBBS, BDS, Engineering, CS, or Postgraduate Degrees at Top Pakistani Universities</t>
+  </si>
+  <si>
+    <t>Funded by the Government of Pakistan through the Higher Education Commission (HEC) and the Ministry of Economic Affairs (Technical Assistance Programme / Allama Iqbal Scholarship Scheme), this flagship program awards hundreds of fully funded scholarships each year to international students from Asia, Africa, the Commonwealth, and OIC states to pursue Bachelor’s (including MBBS, BDS, B.Sc. Engineering, and BS CS), Master’s, and PhD degrees at Pakistan’s premier universities (NUST, Quaid-i-Azam University, UET, King Edward Medical University, Dow, LUMS, COMSATS, and UAF).</t>
+  </si>
+  <si>
+    <t>Academic Transcripts &amp; Certificates: Certified Grade 10 (SSC/O-Level) and Grade 12 (HSSC/A-Level) mark sheets for Undergraduates; Bachelor’s/Master’s transcripts for Postgraduate applicants. | HEC Online Application &amp; Embassy Endorsement: Completed HEC e-portal form and nomination through the Pakistan High Commission/Embassy in the home country. | Research Proposal (for MS/PhD): 2–3 page statement of research objectives. | Medical &amp; Identity Documents: Valid Passport, Birth Certificate, and Physical Fitness Certificate.</t>
+  </si>
+  <si>
+    <t>HEC Written/Online Academic Aptitude Test + Academic GPA Evaluation + Bilateral Country-Quota Interview conducted by HEC and the local Pakistan High Commission.</t>
+  </si>
+  <si>
+    <t>High-GPA science, pre-medical, and engineering students from South Asia, Central Asia, and Africa who apply early through both the HEC portal and their local Pakistan Mission.</t>
+  </si>
+  <si>
+    <t>https://www.hec.gov.pk/english/scholarshipsgrants/</t>
+  </si>
+  <si>
+    <t>comstech-oic-consortium-of-excellence-fellowships-pakistan-master-phd</t>
+  </si>
+  <si>
+    <t>COMSTECH-OIC Consortium of Excellence Fellowships (Pakistan)</t>
+  </si>
+  <si>
+    <t>OIC Standing Committee on Scientific &amp; Technological Cooperation (COMSTECH) — Islamabad, Pakistan</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Computer Science, Data &amp; AI, Mathematics &amp; Natural Sciences, Health &amp; Life Sciences, Agriculture &amp; Food Security</t>
+  </si>
+  <si>
+    <t>Full Fellowship (100% Tuition Waiver, Free Campus Accommodation, Monthly Living Stipend &amp; Round-Trip Economy Airfare)</t>
+  </si>
+  <si>
+    <t>Mar – May (Annual cycle across COMSTECH Fellowship tracks)</t>
+  </si>
+  <si>
+    <t>Citizens of any of the 57 OIC Member States (including Bangladesh, Pakistan, Malaysia, Indonesia, Egypt, Nigeria, Uganda, etc.); age under 35 (Master’s) or under 40 (PhD); B.Sc. or M.Sc. in STEM, Health, or Agricultural Sciences.</t>
+  </si>
+  <si>
+    <t>Medium: COMSTECH Application Form + Host Institute Acceptance/Endorsement + Research Plan + 2 Reference Letters</t>
+  </si>
+  <si>
+    <t>Researchers &amp; Graduate Students from OIC Member States (Including Bangladesh &amp; Pakistan) in STEM, Virology, Chemistry &amp; AI</t>
+  </si>
+  <si>
+    <t>Headquartered in Islamabad, Pakistan, COMSTECH (the Ministerial Standing Committee on Scientific and Technological Cooperation of the OIC) partners with Pakistan’s top research centers—including the International Center for Chemical and Biological Sciences (ICCBS Karachi), COMSATS University Islamabad, NUST, Quaid-i-Azam University, University of Agriculture Faisalabad (UAF), and University of Lahore—to provide fully funded MS, PhD, and Postdoctoral fellowships to young scientists from across the 57 OIC countries.</t>
+  </si>
+  <si>
+    <t>Academic Degrees &amp; Transcripts: Certified copies of Bachelor’s and/or Master’s degrees in relevant STEM or life science fields. | Research Proposal &amp; CV: Detailed research plan aligned with a COMSTECH Consortium of Excellence host laboratory in Pakistan, plus full CV and list of publications. | Letters of Recommendation &amp; Endorsement: 2 academic reference letters and endorsement from the applicant's home university or research institute. | Passport Copy: Valid passport bio-data page from an OIC member state.</t>
+  </si>
+  <si>
+    <t>Technical Review by COMSTECH Expert Panel in Islamabad + Host University/Institute Supervisor Evaluation of Research Feasibility + Regional OIC Distribution.</t>
+  </si>
+  <si>
+    <t>Young chemists, biotechnologists, agricultural scientists, and computer scientists from OIC countries (especially Bangladesh, Sub-Saharan Africa, and Central Asia) seeking intensive laboratory training in Pakistan.</t>
+  </si>
+  <si>
+    <t>https://comstech.org/fellowships/</t>
+  </si>
+  <si>
+    <t>lums-national-outreach-programme-nop-saarc-scholarship-pakistan-bachelor</t>
+  </si>
+  <si>
+    <t>LUMS National Outreach Programme (NOP) &amp; International Scholarships</t>
+  </si>
+  <si>
+    <t>Lahore University of Management Sciences (LUMS) — Lahore, Pakistan</t>
+  </si>
+  <si>
+    <t>Business, Economics &amp; Management, Computer Science, Data &amp; AI, Engineering &amp; Technology, Law, Governance &amp; Public Policy, Social Sciences &amp; Humanities</t>
+  </si>
+  <si>
+    <t>Full Ride (100% Tuition &amp; Registration Fee Waiver, Free Hostel Accommodation, Monthly Living &amp; Book Stipend, Free Summer Coaching Session)</t>
+  </si>
+  <si>
+    <t>Feb – Mar (NOP Undergraduate Summer Coaching Track) / Jan – Apr (Direct Graduate &amp; SAARC Scholarship Track)</t>
+  </si>
+  <si>
+    <t>High-achieving students from Pakistan (and SAARC/international applicants under LUMS Merit &amp; Shamim Khan Scholarships) with minimum 80% marks in Matric/O-Level; demonstrated high financial need for NOP.</t>
+  </si>
+  <si>
+    <t>High: Financial Need Dossier + 2-Week LUMS Summer Coaching Session (for NOP) + SAT/LCAT Entrance Exam + Admission Application</t>
+  </si>
+  <si>
+    <t>Brilliant Low-Income Pakistani &amp; South Asian Students Targeting Pakistan’s #1 Private Research University</t>
+  </si>
+  <si>
+    <t>Launched in 2001 by the Lahore University of Management Sciences (LUMS), the National Outreach Programme (NOP)—alongside LUMS Graduate Merit Waivers and Regional Scholarships—provides 100% full-ride scholarships to exceptionally talented students who cannot afford an elite university education. Shortlisted Matric/F.Sc. students are invited to a fully paid 2-week Summer Coaching Session at the LUMS campus in Lahore, have their LCAT/SAT registration fees covered, and receive full financial support through graduation.</t>
+  </si>
+  <si>
+    <t>Academic Mark Sheets: Matriculation (SSC / O-Level) mark sheet showing at least 80% marks, plus Intermediate (F.Sc. / A-Level) or Bachelor’s transcripts. | Financial Need Verification: Comprehensive household income, utility bills, asset declarations, and parent tax/income certificates. | Entrance Exam Scores: LCAT (LUMS Common Admission Test), SAT, or LGAT/GRE scores for graduate tracks. | Personal Statement &amp; Awards: Essay detailing personal resilience, academic ambition, and extracurricular achievements.</t>
+  </si>
+  <si>
+    <t>Stage 1: Academic Merit (80%+ Matric) &amp; Financial Need Audit → Stage 2: Evaluation during the 2-Week Residential Summer Coaching Session at LUMS → Stage 3: Performance in LCAT/SAT &amp; Holistic Admission Committee Review.</t>
+  </si>
+  <si>
+    <t>High-scoring F.Sc. and A-Level students from small towns and modest backgrounds across Pakistan who apply in Year 1 of Intermediate (F.Sc. Part-I) and excel in the LUMS Summer Coaching Session.</t>
+  </si>
+  <si>
+    <t>https://nop.lums.edu.pk</t>
+  </si>
+  <si>
+    <t>aga-khan-university-aku-financial-assistance-scholarships-pakistan</t>
+  </si>
+  <si>
+    <t>Aga Khan University (AKU) Financial Assistance &amp; Merit Scholarships</t>
+  </si>
+  <si>
+    <t>Aga Khan University &amp; Aga Khan Development Network — Karachi, Pakistan</t>
+  </si>
+  <si>
+    <t>Health &amp; Life Sciences, Education</t>
+  </si>
+  <si>
+    <t>Up to 100% Need-Blind Financial Assistance (Grant-in-Aid Tuition Coverage + Interest-Free Student Loan + Hostel &amp; Stipend Support)</t>
+  </si>
+  <si>
+    <t>May – Jul (AKU Admission Test Cycle; Financial Aid applications open upon admission shortlisting)</t>
+  </si>
+  <si>
+    <t>Pakistani and international students admitted on pure academic merit to AKU Karachi programs (MBBS, B.Sc. Nursing, M.Ed., Master of Public Health, Health Data Science, or PhD in Health Sciences) who demonstrate financial need.</t>
+  </si>
+  <si>
+    <t>Very High: Rigorous AKU Admission Test (Science/Math Reasoning) + Multiple Mini Interviews (MMIs) + Comprehensive Household Financial Audit</t>
+  </si>
+  <si>
+    <t>Top Pre-Medical, Nursing, Public Health &amp; Education Students Seeking Need-Blind Admission at AKU Karachi</t>
+  </si>
+  <si>
+    <t>Operating on a strictly need-blind admissions policy, Aga Khan University (AKU) in Karachi admits students solely on academic testing and interviews, and subsequently guarantees that no admitted student is turned away due to inability to pay. Through a blend of non-repayable Grants-in-Aid, merit awards, and interest-free student loans, AKU funds over 65% of its student body across Medicine (MBBS), Nursing &amp; Midwifery, Educational Development, and Graduate Health Sciences.</t>
+  </si>
+  <si>
+    <t>Academic Credentials: SSC/O-Level and HSSC/A-Level (Pre-Medical) transcripts for MBBS/BScN; Bachelor’s/Master’s transcripts for postgraduate tracks. | AKU Entrance Exam &amp; MMI Dossier: Passing scorecard in the international AKU Admission Test and 2 structured faculty interviews. | Financial Assistance Application Package: Detailed family income tax returns, bank statements, property valuation, utility bills, and third-party verification forms.</t>
+  </si>
+  <si>
+    <t>Step 1: Strictly Merit-Based Admission (AKU Written Test in Biology, Chemistry, Physics, Science/Math Reasoning + 2 Independent Interviews) → Step 2: Independent Financial Assistance Committee Verification of Family Need.</t>
+  </si>
+  <si>
+    <t>Brilliant pre-medical and healthcare students who master the AKU Admission Test's analytical science reasoning section and provide transparent, well-documented family financial records after receiving their admission offer.</t>
+  </si>
+  <si>
+    <t>https://www.aku.edu/admissions/fees-and-funding/Pages/home.aspx</t>
+  </si>
+  <si>
+    <t>hec-overseas-scholarships-us-pakistan-knowledge-corridor-master-phd</t>
+  </si>
+  <si>
+    <t>HEC Overseas Scholarships &amp; US-Pakistan Knowledge Corridor (Master’s &amp; PhD)</t>
+  </si>
+  <si>
+    <t>Higher Education Commission (HEC), Government of Pakistan</t>
+  </si>
+  <si>
+    <t>United States, United Kingdom, Germany, China</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Computer Science, Data &amp; AI, Mathematics &amp; Natural Sciences, Agriculture &amp; Food Security, All fields</t>
+  </si>
+  <si>
+    <t>Full Ride Overseas (100% Tuition or Top-300 Global Partner Placement, Monthly Living Stipend, Return Airfare, Health Insurance &amp; Settlement Grant)</t>
+  </si>
+  <si>
+    <t>Staggered annual windows (Typically Mar – Jun &amp; Sep – Nov on HEC e-portal)</t>
+  </si>
+  <si>
+    <t>Pakistani/AJK citizens; age under 35 (or under 40 for regular public university faculty/researchers); minimum 16–18 years of education (BS/MS/MPhil) with CGPA ≥ 3.0/4.0 or First Division; valid HAT or GRE score (≥ 60% / 300+).</t>
+  </si>
+  <si>
+    <t>Very High: HEC Online Application + HAT/GRE Score + Admission Offer from QS/THE Top-200/300 Global University + Legal Surety Bond to Return to Pakistan</t>
+  </si>
+  <si>
+    <t>Pakistani Graduates &amp; Junior Faculty Pursuing Fully Funded PhDs at Top US, UK, German, or Chinese Universities</t>
+  </si>
+  <si>
+    <t>The Higher Education Commission (HEC) of Pakistan operates two major overseas doctoral engines for Pakistani citizens: (1) Overseas Scholarships for MS/MPhil leading to PhD in Selected Fields (Phase-III) at the world’s top-ranked universities, and (2) the US-Pakistan Knowledge Corridor PhD Scholarship Program (funding 1,000+ Pakistani scholars at leading US R1 universities). Scholars receive full living stipends, health insurance, return airfare, and tuition coverage in exchange for a national service bond in Pakistan upon graduation.</t>
+  </si>
+  <si>
+    <t>Academic Degrees &amp; HEC-Attested Transcripts: BS (4-year) and MS/MPhil transcripts showing First Division and no Third Division across the entire academic career. | Standardized Test Scores: Valid HEC Aptitude Test (HAT) score ≥ 60% or GRE General Score ≥ 300 (plus IELTS/TOEFL). | Foreign University Admission / Supervisor Acceptance: Unconditional admission offer from a QS/Times Higher Education top-ranked university or HEC Tuition-Free partner university in Germany, France, China, UK, or the USA. | Surety Bond &amp; NOC: Legal deed of agreement/bond committing to serve in Pakistan post-PhD, plus No Objection Certificate (NOC) if currently employed in the public sector.</t>
+  </si>
+  <si>
+    <t>Academic Career Score (SSC to MS/MPhil CGPA) + HAT/GRE Test Score + QS/THE Global Ranking of Host Foreign University (applicants holding tuition-waived PhD offers from US R1 or European universities receive priority fast-track awards).</t>
+  </si>
+  <si>
+    <t>Pakistani BS/MS graduates who score 70+ in the HEC HAT (or 310+ on the GRE) and secure a tuition-waived PhD acceptance from a top US R1 university or a German/European partner institution.</t>
+  </si>
+  <si>
+    <t>usefp-fulbright-degree-program-pakistan-master-phd</t>
+  </si>
+  <si>
+    <t>USEFP Fulbright Master’s &amp; PhD Scholarship Program (Pakistan Track)</t>
+  </si>
+  <si>
+    <t>United States Educational Foundation in Pakistan (USEFP), HEC &amp; US Dept. of State</t>
+  </si>
+  <si>
+    <t>Full Ride (100% US Tuition, Monthly Living Stipend, Textbooks, Return Airfare, Health Insurance &amp; J-1 Visa Sponsorship)</t>
+  </si>
+  <si>
+    <t>Feb – Apr (Annual cycle via USEFP Islamabad portal)</t>
+  </si>
+  <si>
+    <t>Pakistani citizens residing in Pakistan; 16 years of education (4-year BS or BSc+MSc) for Master’s or 18 years (MS/MPhil) for PhD; GRE General Test required; all non-clinical fields (Energy, Water, Agriculture, Public Health, Education, Social Sciences, STEM).</t>
+  </si>
+  <si>
+    <t>Very High: GRE General Exam + 2 Detailed Essays (Study Objectives &amp; Personal Statement) + 3 Reference Letters + PhD Writing Sample + USEFP Interview</t>
+  </si>
+  <si>
+    <t>Pakistani Graduates &amp; Professionals Seeking Fully Funded Master’s or PhDs at Top US Universities</t>
+  </si>
+  <si>
+    <t>Jointly funded by the US Government and the Higher Education Commission (HEC) of Pakistan, the USEFP Fulbright Student Program in Pakistan is one of the largest Fulbright binational programs in the world, awarding 100–150 fully funded Master’s and PhD scholarships every year. It supports Pakistani scholars across all disciplines (except clinical medicine) to study at accredited US universities and return to contribute to Pakistan’s socio-economic development.</t>
+  </si>
+  <si>
+    <t>Standardized Test Scores: Official GRE General score report (mandatory at the time of application; TOEFL/Duolingo is only required after initial shortlisting). | Two Core Fulbright Essays: (1) Statement of Study/Research Objectives (explaining your exact academic specialization and why it matters to Pakistan) and (2) Personal Statement (tracing your life trajectory and leadership). | Academic Transcripts &amp; 3 References: Attested university degree transcripts and 3 online letters of recommendation. | Research Proposal / Writing Sample: Mandatory for PhD applicants.</t>
+  </si>
+  <si>
+    <t>Holistic Review of Academic Record, GRE Score &amp; Essay Depth (50%) + Regional/Gender Diversity across all Pakistani Provinces (20%) + In-Person Panel Interview in Islamabad/Karachi/Lahore (30%).</t>
+  </si>
+  <si>
+    <t>Authentic Pakistani applicants—especially women and candidates from underserved regions of Punjab, Sindh, KP, Balochistan, GB, and AJK—who pair a competitive GRE score with a clear, non-generic vision for solving a real development challenge in Pakistan.</t>
+  </si>
+  <si>
+    <t>https://www.usefp.org/scholarships/fulbright-degree.cfm</t>
+  </si>
+  <si>
+    <t>hec-indigenous-5000-phd-fellowship-program-pakistan-phd</t>
+  </si>
+  <si>
+    <t>HEC Indigenous PhD Fellowship Program (Pakistan)</t>
+  </si>
+  <si>
+    <t>Full Domestic PhD Funding (100% Pakistani University Tuition + Lab Bench Fees + Monthly Stipend + Book/Thesis Grant + 6-Mo Overseas IRSIP Split-Site Eligibility)</t>
+  </si>
+  <si>
+    <t>Periodic batch calls via HEC e-portal</t>
+  </si>
+  <si>
+    <t>Pakistani/AJK nationals; age under 35 (or under 40 for public-sector university faculty/researchers); minimum CGPA 3.0/4.0 in MS/MPhil/18-year degree; valid HEC HAT score ≥ 60%.</t>
+  </si>
+  <si>
+    <t>High: HEC e-Portal Application + HAT Qualifying Score + PhD Admission at an HEC-Recognized Pakistani University</t>
+  </si>
+  <si>
+    <t>Pakistani Researchers Pursuing Fully Funded Domestic PhDs with 6-Month Overseas Lab Placement (IRSIP)</t>
+  </si>
+  <si>
+    <t>The HEC Indigenous 5000 PhD Fellowship Program is Pakistan’s premier domestic doctoral funding scheme. It covers full university tuition, laboratory bench fees, monthly living stipends, book allowances, and thesis typing costs at HEC-recognized public and private universities across Pakistan, and makes scholars eligible for the HEC International Research Support Initiative Program (IRSIP)—a fully funded 6-month research residency at a top foreign laboratory in the US, Europe, UK, or Australia.</t>
+  </si>
+  <si>
+    <t>Academic Credentials: Matric, Intermediate, BS, and MS/MPhil degree certificates and transcripts with no Third Division. | HEC Aptitude Test (HAT): Official scorecard showing at least 60% marks in the relevant HAT category. | PhD Admission Letter: Proof of enrollment or admission into a PhD program at an HEC-recognized Pakistani university under an HEC-approved PhD Supervisor. | Legal Bond: Undertaking to complete the PhD and serve in Pakistan.</t>
+  </si>
+  <si>
+    <t>Composite Merit Formula combining Academic Record (SSC to MS/MPhil) and HAT Test Score, allocated according to Federal and Provincial/Regional quotas across Pakistan.</t>
+  </si>
+  <si>
+    <t>Diligent Pakistani MS/MPhil graduates who clear the HEC HAT exam with 65%+ marks, enroll with an HEC-approved PhD supervisor at NUST, QAU, PIEAS, UET, COMSATS, or Punjab University, and later leverage IRSIP for a 6-month international lab visit.</t>
+  </si>
+  <si>
+    <t>https://www.hec.gov.pk/english/scholarshipsgrants/Indigenous/</t>
+  </si>
+  <si>
+    <t>british-council-pakistan-scottish-scholarship-scheme-master</t>
+  </si>
+  <si>
+    <t>British Council Pakistan Scottish Scholarship Scheme</t>
+  </si>
+  <si>
+    <t>Scottish Government &amp; British Council Pakistan</t>
+  </si>
+  <si>
+    <t>Education, Environment, Water &amp; Energy, Agriculture &amp; Food Security, Health &amp; Life Sciences, Engineering &amp; Technology</t>
+  </si>
+  <si>
+    <t>Full Domestic Master’s Grant (100% Tuition Fees, University Hostel Accommodation, Travel To/From Home twice a year &amp; Study Materials)</t>
+  </si>
+  <si>
+    <t>Mar – Apr (Annual call via British Council Pakistan)</t>
+  </si>
+  <si>
+    <t>Female Pakistani citizens currently residing in Pakistan; holding a confirmed admission offer for a 1- or 2-year Master’s/MPhil degree at an HEC-recognized university in Pakistan in STEM, Education, Sustainable Energy, Food Security/Agriculture, or Health Sciences.</t>
+  </si>
+  <si>
+    <t>Medium: Online British Council Application + Pakistani University Admission Offer + Financial Need Proof + Personal Statement</t>
+  </si>
+  <si>
+    <t>Pakistani Women Pursuing Master’s/MPhil Degrees in STEM, Health, Education, or Climate/Agriculture in Pakistan</t>
+  </si>
+  <si>
+    <t>Funded by the Scottish Government and administered by the British Council in Pakistan, the Pakistan Scottish Scholarship Scheme supports talented young Pakistani women from underprivileged and minority backgrounds to complete a full Master’s or MPhil degree at any HEC-recognized university across Pakistan in priority fields driving gender equality and climate resilience.</t>
+  </si>
+  <si>
+    <t>University Admission Proof: Copy of official admission offer or enrollment letter for an eligible Master’s/MPhil program at an HEC-recognized Pakistani university. | Academic Transcripts: Certified Bachelor’s degree transcripts and certificate. | Financial Need Documentation: Proof of parent/guardian income, salary slips, or financial hardship declaration. | Personal Statement: Short motivation essay outlining career goals and community impact for women in Pakistan.</t>
+  </si>
+  <si>
+    <t>Academic Merit in Bachelor’s Degree (35%) + Demonstrated Financial Need &amp; Rural/Minority Representation (40%) + Alignment with Scottish Government Priority Fields &amp; Leadership Motivation (25%).</t>
+  </si>
+  <si>
+    <t>Ambitious female graduates from across Pakistan—with special encouragement for candidates from rural areas, minority communities, and persons with disabilities—admitted to Master’s programs in renewable energy, STEM, public health, or education.</t>
+  </si>
+  <si>
+    <t>https://www.britishcouncil.pk/programmes/education/scholarships</t>
   </si>
 </sst>
 </file>
@@ -2827,7 +4294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2840,6 +4307,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8880,278 +10348,2544 @@
       </c>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA82" s="5"/>
-      <c r="AB82" s="5"/>
+      <c r="A82" t="s">
+        <v>934</v>
+      </c>
+      <c r="B82" t="s">
+        <v>51</v>
+      </c>
+      <c r="D82" t="s">
+        <v>52</v>
+      </c>
+      <c r="E82" t="s">
+        <v>935</v>
+      </c>
+      <c r="F82" t="s">
+        <v>936</v>
+      </c>
+      <c r="G82" t="s">
+        <v>238</v>
+      </c>
+      <c r="H82" t="s">
+        <v>937</v>
+      </c>
+      <c r="I82" t="s">
+        <v>57</v>
+      </c>
+      <c r="J82" t="s">
+        <v>58</v>
+      </c>
+      <c r="K82" t="s">
+        <v>59</v>
+      </c>
+      <c r="L82" t="s">
+        <v>938</v>
+      </c>
+      <c r="M82" t="s">
+        <v>939</v>
+      </c>
+      <c r="N82" t="s">
+        <v>940</v>
+      </c>
+      <c r="O82" t="s">
+        <v>941</v>
+      </c>
+      <c r="P82" t="s">
+        <v>942</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>943</v>
+      </c>
+      <c r="R82" t="s">
+        <v>944</v>
+      </c>
+      <c r="S82" t="s">
+        <v>945</v>
+      </c>
+      <c r="T82" t="s">
+        <v>946</v>
+      </c>
+      <c r="V82" t="s">
+        <v>947</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA82" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB82" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC82" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA83" s="5"/>
-      <c r="AB83" s="5"/>
+      <c r="A83" t="s">
+        <v>948</v>
+      </c>
+      <c r="B83" t="s">
+        <v>51</v>
+      </c>
+      <c r="D83" t="s">
+        <v>52</v>
+      </c>
+      <c r="E83" t="s">
+        <v>949</v>
+      </c>
+      <c r="F83" t="s">
+        <v>950</v>
+      </c>
+      <c r="G83" t="s">
+        <v>238</v>
+      </c>
+      <c r="H83" t="s">
+        <v>937</v>
+      </c>
+      <c r="I83" t="s">
+        <v>951</v>
+      </c>
+      <c r="J83" t="s">
+        <v>58</v>
+      </c>
+      <c r="K83" t="s">
+        <v>59</v>
+      </c>
+      <c r="L83" t="s">
+        <v>952</v>
+      </c>
+      <c r="M83" t="s">
+        <v>939</v>
+      </c>
+      <c r="N83" t="s">
+        <v>953</v>
+      </c>
+      <c r="O83" t="s">
+        <v>954</v>
+      </c>
+      <c r="P83" t="s">
+        <v>955</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>956</v>
+      </c>
+      <c r="R83" t="s">
+        <v>957</v>
+      </c>
+      <c r="S83" t="s">
+        <v>958</v>
+      </c>
+      <c r="T83" t="s">
+        <v>959</v>
+      </c>
+      <c r="V83" t="s">
+        <v>960</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA83" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB83" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC83" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA84" s="5"/>
-      <c r="AB84" s="5"/>
+      <c r="A84" t="s">
+        <v>961</v>
+      </c>
+      <c r="B84" t="s">
+        <v>51</v>
+      </c>
+      <c r="D84" t="s">
+        <v>52</v>
+      </c>
+      <c r="E84" t="s">
+        <v>962</v>
+      </c>
+      <c r="F84" t="s">
+        <v>963</v>
+      </c>
+      <c r="G84" t="s">
+        <v>238</v>
+      </c>
+      <c r="H84" t="s">
+        <v>937</v>
+      </c>
+      <c r="I84" t="s">
+        <v>964</v>
+      </c>
+      <c r="J84" t="s">
+        <v>58</v>
+      </c>
+      <c r="K84" t="s">
+        <v>59</v>
+      </c>
+      <c r="L84" t="s">
+        <v>965</v>
+      </c>
+      <c r="M84" t="s">
+        <v>966</v>
+      </c>
+      <c r="N84" t="s">
+        <v>967</v>
+      </c>
+      <c r="O84" t="s">
+        <v>968</v>
+      </c>
+      <c r="P84" t="s">
+        <v>969</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>970</v>
+      </c>
+      <c r="R84" t="s">
+        <v>971</v>
+      </c>
+      <c r="S84" t="s">
+        <v>972</v>
+      </c>
+      <c r="T84" t="s">
+        <v>973</v>
+      </c>
+      <c r="V84" t="s">
+        <v>974</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA84" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB84" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC84" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA85" s="5"/>
-      <c r="AB85" s="5"/>
+      <c r="A85" t="s">
+        <v>975</v>
+      </c>
+      <c r="B85" t="s">
+        <v>51</v>
+      </c>
+      <c r="D85" t="s">
+        <v>52</v>
+      </c>
+      <c r="E85" t="s">
+        <v>976</v>
+      </c>
+      <c r="F85" t="s">
+        <v>977</v>
+      </c>
+      <c r="G85" t="s">
+        <v>238</v>
+      </c>
+      <c r="H85" t="s">
+        <v>937</v>
+      </c>
+      <c r="I85" t="s">
+        <v>118</v>
+      </c>
+      <c r="J85" t="s">
+        <v>978</v>
+      </c>
+      <c r="K85" t="s">
+        <v>59</v>
+      </c>
+      <c r="L85" t="s">
+        <v>979</v>
+      </c>
+      <c r="M85" t="s">
+        <v>980</v>
+      </c>
+      <c r="N85" t="s">
+        <v>981</v>
+      </c>
+      <c r="O85" t="s">
+        <v>982</v>
+      </c>
+      <c r="P85" t="s">
+        <v>983</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>984</v>
+      </c>
+      <c r="R85" t="s">
+        <v>985</v>
+      </c>
+      <c r="S85" t="s">
+        <v>986</v>
+      </c>
+      <c r="T85" t="s">
+        <v>987</v>
+      </c>
+      <c r="V85" t="s">
+        <v>988</v>
+      </c>
+      <c r="AA85" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB85" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC85" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA86" s="5"/>
-      <c r="AB86" s="5"/>
+      <c r="A86" t="s">
+        <v>989</v>
+      </c>
+      <c r="B86" t="s">
+        <v>51</v>
+      </c>
+      <c r="D86" t="s">
+        <v>52</v>
+      </c>
+      <c r="E86" t="s">
+        <v>990</v>
+      </c>
+      <c r="F86" t="s">
+        <v>991</v>
+      </c>
+      <c r="G86" t="s">
+        <v>238</v>
+      </c>
+      <c r="H86" t="s">
+        <v>937</v>
+      </c>
+      <c r="I86" t="s">
+        <v>194</v>
+      </c>
+      <c r="J86" t="s">
+        <v>158</v>
+      </c>
+      <c r="K86" t="s">
+        <v>59</v>
+      </c>
+      <c r="L86" t="s">
+        <v>992</v>
+      </c>
+      <c r="M86" t="s">
+        <v>993</v>
+      </c>
+      <c r="N86" t="s">
+        <v>994</v>
+      </c>
+      <c r="O86" t="s">
+        <v>995</v>
+      </c>
+      <c r="P86" t="s">
+        <v>996</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>997</v>
+      </c>
+      <c r="R86" t="s">
+        <v>998</v>
+      </c>
+      <c r="S86" t="s">
+        <v>999</v>
+      </c>
+      <c r="T86" t="s">
+        <v>1000</v>
+      </c>
+      <c r="V86" t="s">
+        <v>1001</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA86" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB86" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC86" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA87" s="5"/>
-      <c r="AB87" s="5"/>
+      <c r="A87" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B87" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" t="s">
+        <v>52</v>
+      </c>
+      <c r="E87" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F87" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G87" t="s">
+        <v>238</v>
+      </c>
+      <c r="H87" t="s">
+        <v>937</v>
+      </c>
+      <c r="I87" t="s">
+        <v>964</v>
+      </c>
+      <c r="J87" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K87" t="s">
+        <v>107</v>
+      </c>
+      <c r="L87" t="s">
+        <v>1006</v>
+      </c>
+      <c r="M87" t="s">
+        <v>1007</v>
+      </c>
+      <c r="N87" t="s">
+        <v>1008</v>
+      </c>
+      <c r="O87" t="s">
+        <v>1009</v>
+      </c>
+      <c r="P87" t="s">
+        <v>1010</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>1011</v>
+      </c>
+      <c r="R87" t="s">
+        <v>1012</v>
+      </c>
+      <c r="S87" t="s">
+        <v>1013</v>
+      </c>
+      <c r="T87" t="s">
+        <v>1014</v>
+      </c>
+      <c r="V87" t="s">
+        <v>1015</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>1016</v>
+      </c>
+      <c r="AA87" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB87" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC87" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA88" s="5"/>
-      <c r="AB88" s="5"/>
+      <c r="A88" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B88" t="s">
+        <v>51</v>
+      </c>
+      <c r="D88" t="s">
+        <v>52</v>
+      </c>
+      <c r="E88" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F88" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G88" t="s">
+        <v>238</v>
+      </c>
+      <c r="H88" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I88" t="s">
+        <v>118</v>
+      </c>
+      <c r="J88" t="s">
+        <v>58</v>
+      </c>
+      <c r="K88" t="s">
+        <v>59</v>
+      </c>
+      <c r="L88" t="s">
+        <v>1021</v>
+      </c>
+      <c r="M88" t="s">
+        <v>1022</v>
+      </c>
+      <c r="N88" t="s">
+        <v>1023</v>
+      </c>
+      <c r="O88" t="s">
+        <v>1024</v>
+      </c>
+      <c r="P88" t="s">
+        <v>1025</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>1026</v>
+      </c>
+      <c r="R88" t="s">
+        <v>1027</v>
+      </c>
+      <c r="S88" t="s">
+        <v>1028</v>
+      </c>
+      <c r="T88" t="s">
+        <v>1029</v>
+      </c>
+      <c r="V88" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AA88" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB88" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC88" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA89" s="5"/>
-      <c r="AB89" s="5"/>
+      <c r="A89" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B89" t="s">
+        <v>51</v>
+      </c>
+      <c r="D89" t="s">
+        <v>52</v>
+      </c>
+      <c r="E89" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F89" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G89" t="s">
+        <v>238</v>
+      </c>
+      <c r="H89" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I89" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J89" t="s">
+        <v>58</v>
+      </c>
+      <c r="K89" t="s">
+        <v>107</v>
+      </c>
+      <c r="L89" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M89" t="s">
+        <v>1037</v>
+      </c>
+      <c r="N89" t="s">
+        <v>1038</v>
+      </c>
+      <c r="O89" t="s">
+        <v>1039</v>
+      </c>
+      <c r="P89" t="s">
+        <v>1040</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>1041</v>
+      </c>
+      <c r="R89" t="s">
+        <v>1042</v>
+      </c>
+      <c r="S89" t="s">
+        <v>1043</v>
+      </c>
+      <c r="T89" t="s">
+        <v>1044</v>
+      </c>
+      <c r="V89" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AA89" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB89" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC89" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA90" s="5"/>
-      <c r="AB90" s="5"/>
+      <c r="A90" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B90" t="s">
+        <v>51</v>
+      </c>
+      <c r="D90" t="s">
+        <v>52</v>
+      </c>
+      <c r="E90" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F90" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G90" t="s">
+        <v>238</v>
+      </c>
+      <c r="H90" t="s">
+        <v>911</v>
+      </c>
+      <c r="I90" t="s">
+        <v>57</v>
+      </c>
+      <c r="J90" t="s">
+        <v>58</v>
+      </c>
+      <c r="K90" t="s">
+        <v>59</v>
+      </c>
+      <c r="L90" t="s">
+        <v>1049</v>
+      </c>
+      <c r="M90" t="s">
+        <v>1050</v>
+      </c>
+      <c r="N90" t="s">
+        <v>1051</v>
+      </c>
+      <c r="O90" t="s">
+        <v>1052</v>
+      </c>
+      <c r="P90" t="s">
+        <v>1053</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R90" t="s">
+        <v>1055</v>
+      </c>
+      <c r="S90" t="s">
+        <v>1056</v>
+      </c>
+      <c r="T90" t="s">
+        <v>1057</v>
+      </c>
+      <c r="V90" t="s">
+        <v>1058</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AA90" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB90" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC90" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA91" s="5"/>
-      <c r="AB91" s="5"/>
+      <c r="A91" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B91" t="s">
+        <v>51</v>
+      </c>
+      <c r="D91" t="s">
+        <v>52</v>
+      </c>
+      <c r="E91" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F91" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G91" t="s">
+        <v>238</v>
+      </c>
+      <c r="H91" t="s">
+        <v>911</v>
+      </c>
+      <c r="I91" t="s">
+        <v>57</v>
+      </c>
+      <c r="J91" t="s">
+        <v>1063</v>
+      </c>
+      <c r="K91" t="s">
+        <v>59</v>
+      </c>
+      <c r="L91" t="s">
+        <v>1064</v>
+      </c>
+      <c r="M91" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N91" t="s">
+        <v>1066</v>
+      </c>
+      <c r="O91" t="s">
+        <v>1067</v>
+      </c>
+      <c r="P91" t="s">
+        <v>1068</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R91" t="s">
+        <v>1070</v>
+      </c>
+      <c r="S91" t="s">
+        <v>1071</v>
+      </c>
+      <c r="T91" t="s">
+        <v>1072</v>
+      </c>
+      <c r="V91" t="s">
+        <v>1073</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA91" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB91" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC91" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA92" s="5"/>
-      <c r="AB92" s="5"/>
+      <c r="A92" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B92" t="s">
+        <v>51</v>
+      </c>
+      <c r="D92" t="s">
+        <v>52</v>
+      </c>
+      <c r="E92" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F92" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G92" t="s">
+        <v>238</v>
+      </c>
+      <c r="H92" t="s">
+        <v>911</v>
+      </c>
+      <c r="I92" t="s">
+        <v>57</v>
+      </c>
+      <c r="J92" t="s">
+        <v>378</v>
+      </c>
+      <c r="K92" t="s">
+        <v>59</v>
+      </c>
+      <c r="L92" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M92" t="s">
+        <v>1078</v>
+      </c>
+      <c r="N92" t="s">
+        <v>1079</v>
+      </c>
+      <c r="O92" t="s">
+        <v>1080</v>
+      </c>
+      <c r="P92" t="s">
+        <v>1081</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>1082</v>
+      </c>
+      <c r="R92" t="s">
+        <v>1083</v>
+      </c>
+      <c r="S92" t="s">
+        <v>1084</v>
+      </c>
+      <c r="T92" t="s">
+        <v>1085</v>
+      </c>
+      <c r="V92" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AA92" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB92" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC92" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA93" s="5"/>
-      <c r="AB93" s="5"/>
+      <c r="A93" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B93" t="s">
+        <v>51</v>
+      </c>
+      <c r="D93" t="s">
+        <v>52</v>
+      </c>
+      <c r="E93" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F93" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G93" t="s">
+        <v>238</v>
+      </c>
+      <c r="H93" t="s">
+        <v>911</v>
+      </c>
+      <c r="I93" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J93" t="s">
+        <v>1090</v>
+      </c>
+      <c r="K93" t="s">
+        <v>59</v>
+      </c>
+      <c r="L93" t="s">
+        <v>1091</v>
+      </c>
+      <c r="M93" t="s">
+        <v>1092</v>
+      </c>
+      <c r="N93" t="s">
+        <v>1093</v>
+      </c>
+      <c r="O93" t="s">
+        <v>1094</v>
+      </c>
+      <c r="P93" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>1096</v>
+      </c>
+      <c r="R93" t="s">
+        <v>1097</v>
+      </c>
+      <c r="S93" t="s">
+        <v>1098</v>
+      </c>
+      <c r="T93" t="s">
+        <v>1099</v>
+      </c>
+      <c r="V93" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA93" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB93" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC93" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA94" s="5"/>
-      <c r="AB94" s="5"/>
+      <c r="A94" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B94" t="s">
+        <v>51</v>
+      </c>
+      <c r="D94" t="s">
+        <v>52</v>
+      </c>
+      <c r="E94" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F94" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G94" t="s">
+        <v>238</v>
+      </c>
+      <c r="H94" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I94" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J94" t="s">
+        <v>58</v>
+      </c>
+      <c r="K94" t="s">
+        <v>59</v>
+      </c>
+      <c r="L94" t="s">
+        <v>1105</v>
+      </c>
+      <c r="M94" t="s">
+        <v>1106</v>
+      </c>
+      <c r="N94" t="s">
+        <v>1107</v>
+      </c>
+      <c r="O94" t="s">
+        <v>1108</v>
+      </c>
+      <c r="P94" t="s">
+        <v>1109</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>1110</v>
+      </c>
+      <c r="R94" t="s">
+        <v>1111</v>
+      </c>
+      <c r="S94" t="s">
+        <v>1112</v>
+      </c>
+      <c r="T94" t="s">
+        <v>1113</v>
+      </c>
+      <c r="V94" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AA94" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB94" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC94" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA95" s="5"/>
-      <c r="AB95" s="5"/>
+      <c r="A95" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B95" t="s">
+        <v>51</v>
+      </c>
+      <c r="D95" t="s">
+        <v>52</v>
+      </c>
+      <c r="E95" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F95" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G95" t="s">
+        <v>238</v>
+      </c>
+      <c r="H95" t="s">
+        <v>911</v>
+      </c>
+      <c r="I95" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J95" t="s">
+        <v>1119</v>
+      </c>
+      <c r="K95" t="s">
+        <v>59</v>
+      </c>
+      <c r="L95" t="s">
+        <v>1120</v>
+      </c>
+      <c r="M95" t="s">
+        <v>1121</v>
+      </c>
+      <c r="N95" t="s">
+        <v>1122</v>
+      </c>
+      <c r="O95" t="s">
+        <v>1123</v>
+      </c>
+      <c r="P95" t="s">
+        <v>1124</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>1125</v>
+      </c>
+      <c r="R95" t="s">
+        <v>1126</v>
+      </c>
+      <c r="S95" t="s">
+        <v>1127</v>
+      </c>
+      <c r="T95" t="s">
+        <v>1128</v>
+      </c>
+      <c r="V95" t="s">
+        <v>1129</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA95" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB95" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC95" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA96" s="5"/>
-      <c r="AB96" s="5"/>
+      <c r="A96" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B96" t="s">
+        <v>51</v>
+      </c>
+      <c r="D96" t="s">
+        <v>52</v>
+      </c>
+      <c r="E96" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G96" t="s">
+        <v>366</v>
+      </c>
+      <c r="H96" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I96" t="s">
+        <v>194</v>
+      </c>
+      <c r="J96" t="s">
+        <v>58</v>
+      </c>
+      <c r="K96" t="s">
+        <v>59</v>
+      </c>
+      <c r="L96" t="s">
+        <v>1134</v>
+      </c>
+      <c r="M96" t="s">
+        <v>1135</v>
+      </c>
+      <c r="N96" t="s">
+        <v>1136</v>
+      </c>
+      <c r="O96" t="s">
+        <v>1137</v>
+      </c>
+      <c r="P96" t="s">
+        <v>1138</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>1139</v>
+      </c>
+      <c r="R96" t="s">
+        <v>1140</v>
+      </c>
+      <c r="S96" t="s">
+        <v>1141</v>
+      </c>
+      <c r="T96" t="s">
+        <v>1142</v>
+      </c>
+      <c r="V96" t="s">
+        <v>1143</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA96" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB96" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC96" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="97" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA97" s="5"/>
-      <c r="AB97" s="5"/>
+    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B97" t="s">
+        <v>51</v>
+      </c>
+      <c r="D97" t="s">
+        <v>52</v>
+      </c>
+      <c r="E97" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F97" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G97" t="s">
+        <v>366</v>
+      </c>
+      <c r="H97" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I97" t="s">
+        <v>118</v>
+      </c>
+      <c r="J97" t="s">
+        <v>58</v>
+      </c>
+      <c r="K97" t="s">
+        <v>59</v>
+      </c>
+      <c r="L97" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M97" t="s">
+        <v>1149</v>
+      </c>
+      <c r="N97" t="s">
+        <v>1150</v>
+      </c>
+      <c r="O97" t="s">
+        <v>1151</v>
+      </c>
+      <c r="P97" t="s">
+        <v>1152</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>1153</v>
+      </c>
+      <c r="R97" t="s">
+        <v>1154</v>
+      </c>
+      <c r="S97" t="s">
+        <v>1155</v>
+      </c>
+      <c r="T97" t="s">
+        <v>1156</v>
+      </c>
+      <c r="V97" t="s">
+        <v>1157</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>434</v>
+      </c>
+      <c r="AA97" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB97" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC97" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA98" s="5"/>
-      <c r="AB98" s="5"/>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B98" t="s">
+        <v>51</v>
+      </c>
+      <c r="D98" t="s">
+        <v>52</v>
+      </c>
+      <c r="E98" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F98" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G98" t="s">
+        <v>366</v>
+      </c>
+      <c r="H98" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I98" t="s">
+        <v>194</v>
+      </c>
+      <c r="J98" t="s">
+        <v>58</v>
+      </c>
+      <c r="K98" t="s">
+        <v>59</v>
+      </c>
+      <c r="L98" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M98" t="s">
+        <v>1162</v>
+      </c>
+      <c r="N98" t="s">
+        <v>1163</v>
+      </c>
+      <c r="O98" t="s">
+        <v>1164</v>
+      </c>
+      <c r="P98" t="s">
+        <v>1165</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>1166</v>
+      </c>
+      <c r="R98" t="s">
+        <v>1167</v>
+      </c>
+      <c r="S98" t="s">
+        <v>1168</v>
+      </c>
+      <c r="T98" t="s">
+        <v>1169</v>
+      </c>
+      <c r="V98" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AA98" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB98" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="99" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA99" s="5"/>
-      <c r="AB99" s="5"/>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B99" t="s">
+        <v>51</v>
+      </c>
+      <c r="D99" t="s">
+        <v>52</v>
+      </c>
+      <c r="E99" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F99" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G99" t="s">
+        <v>366</v>
+      </c>
+      <c r="H99" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I99" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J99" t="s">
+        <v>58</v>
+      </c>
+      <c r="K99" t="s">
+        <v>59</v>
+      </c>
+      <c r="L99" t="s">
+        <v>1175</v>
+      </c>
+      <c r="M99" t="s">
+        <v>1176</v>
+      </c>
+      <c r="N99" t="s">
+        <v>1177</v>
+      </c>
+      <c r="O99" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P99" t="s">
+        <v>1179</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>1180</v>
+      </c>
+      <c r="R99" t="s">
+        <v>1181</v>
+      </c>
+      <c r="S99" t="s">
+        <v>1182</v>
+      </c>
+      <c r="T99" t="s">
+        <v>1183</v>
+      </c>
+      <c r="V99" t="s">
+        <v>1184</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>295</v>
+      </c>
+      <c r="AA99" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB99" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="100" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA100" s="5"/>
-      <c r="AB100" s="5"/>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B100" t="s">
+        <v>51</v>
+      </c>
+      <c r="D100" t="s">
+        <v>52</v>
+      </c>
+      <c r="E100" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F100" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G100" t="s">
+        <v>366</v>
+      </c>
+      <c r="H100" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I100" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J100" t="s">
+        <v>58</v>
+      </c>
+      <c r="K100" t="s">
+        <v>59</v>
+      </c>
+      <c r="L100" t="s">
+        <v>1188</v>
+      </c>
+      <c r="M100" t="s">
+        <v>1189</v>
+      </c>
+      <c r="N100" t="s">
+        <v>1190</v>
+      </c>
+      <c r="O100" t="s">
+        <v>1191</v>
+      </c>
+      <c r="P100" t="s">
+        <v>1192</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>1193</v>
+      </c>
+      <c r="R100" t="s">
+        <v>1194</v>
+      </c>
+      <c r="S100" t="s">
+        <v>1195</v>
+      </c>
+      <c r="T100" t="s">
+        <v>1196</v>
+      </c>
+      <c r="V100" t="s">
+        <v>1197</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>295</v>
+      </c>
+      <c r="AA100" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB100" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC100" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="101" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA101" s="5"/>
-      <c r="AB101" s="5"/>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B101" t="s">
+        <v>51</v>
+      </c>
+      <c r="D101" t="s">
+        <v>52</v>
+      </c>
+      <c r="E101" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F101" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G101" t="s">
+        <v>366</v>
+      </c>
+      <c r="H101" t="s">
+        <v>209</v>
+      </c>
+      <c r="I101" t="s">
+        <v>194</v>
+      </c>
+      <c r="J101" t="s">
+        <v>1201</v>
+      </c>
+      <c r="K101" t="s">
+        <v>59</v>
+      </c>
+      <c r="L101" t="s">
+        <v>1202</v>
+      </c>
+      <c r="M101" t="s">
+        <v>1203</v>
+      </c>
+      <c r="N101" t="s">
+        <v>1204</v>
+      </c>
+      <c r="O101" t="s">
+        <v>1205</v>
+      </c>
+      <c r="P101" t="s">
+        <v>1206</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>1207</v>
+      </c>
+      <c r="R101" t="s">
+        <v>1208</v>
+      </c>
+      <c r="S101" t="s">
+        <v>1209</v>
+      </c>
+      <c r="T101" t="s">
+        <v>1210</v>
+      </c>
+      <c r="V101" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA101" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB101" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC101" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="102" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA102" s="5"/>
-      <c r="AB102" s="5"/>
+    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B102" t="s">
+        <v>51</v>
+      </c>
+      <c r="D102" t="s">
+        <v>52</v>
+      </c>
+      <c r="E102" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F102" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G102" t="s">
+        <v>366</v>
+      </c>
+      <c r="H102" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I102" t="s">
+        <v>118</v>
+      </c>
+      <c r="J102" t="s">
+        <v>58</v>
+      </c>
+      <c r="K102" t="s">
+        <v>59</v>
+      </c>
+      <c r="L102" t="s">
+        <v>1216</v>
+      </c>
+      <c r="M102" t="s">
+        <v>1217</v>
+      </c>
+      <c r="N102" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O102" t="s">
+        <v>1219</v>
+      </c>
+      <c r="P102" t="s">
+        <v>1220</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>1221</v>
+      </c>
+      <c r="R102" t="s">
+        <v>1222</v>
+      </c>
+      <c r="S102" t="s">
+        <v>1223</v>
+      </c>
+      <c r="T102" t="s">
+        <v>1224</v>
+      </c>
+      <c r="V102" t="s">
+        <v>1225</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>434</v>
+      </c>
+      <c r="AA102" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB102" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC102" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="103" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA103" s="5"/>
-      <c r="AB103" s="5"/>
+    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B103" t="s">
+        <v>51</v>
+      </c>
+      <c r="D103" t="s">
+        <v>52</v>
+      </c>
+      <c r="E103" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F103" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G103" t="s">
+        <v>366</v>
+      </c>
+      <c r="H103" t="s">
+        <v>1229</v>
+      </c>
+      <c r="I103" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J103" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K103" t="s">
+        <v>59</v>
+      </c>
+      <c r="L103" t="s">
+        <v>1231</v>
+      </c>
+      <c r="M103" t="s">
+        <v>1232</v>
+      </c>
+      <c r="N103" t="s">
+        <v>1233</v>
+      </c>
+      <c r="O103" t="s">
+        <v>1234</v>
+      </c>
+      <c r="P103" t="s">
+        <v>1235</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>1236</v>
+      </c>
+      <c r="R103" t="s">
+        <v>1237</v>
+      </c>
+      <c r="S103" t="s">
+        <v>1238</v>
+      </c>
+      <c r="T103" t="s">
+        <v>1239</v>
+      </c>
+      <c r="V103" t="s">
+        <v>1240</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA103" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB103" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC103" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="104" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA104" s="5"/>
-      <c r="AB104" s="5"/>
+    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B104" t="s">
+        <v>51</v>
+      </c>
+      <c r="D104" t="s">
+        <v>52</v>
+      </c>
+      <c r="E104" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F104" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G104" t="s">
+        <v>366</v>
+      </c>
+      <c r="H104" t="s">
+        <v>1229</v>
+      </c>
+      <c r="I104" t="s">
+        <v>951</v>
+      </c>
+      <c r="J104" t="s">
+        <v>58</v>
+      </c>
+      <c r="K104" t="s">
+        <v>59</v>
+      </c>
+      <c r="L104" t="s">
+        <v>1244</v>
+      </c>
+      <c r="M104" t="s">
+        <v>1245</v>
+      </c>
+      <c r="N104" t="s">
+        <v>1246</v>
+      </c>
+      <c r="O104" t="s">
+        <v>1247</v>
+      </c>
+      <c r="P104" t="s">
+        <v>1248</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>1249</v>
+      </c>
+      <c r="R104" t="s">
+        <v>1250</v>
+      </c>
+      <c r="S104" t="s">
+        <v>1251</v>
+      </c>
+      <c r="T104" t="s">
+        <v>1252</v>
+      </c>
+      <c r="V104" t="s">
+        <v>1253</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA104" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB104" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC104" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="105" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA105" s="5"/>
-      <c r="AB105" s="5"/>
+    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B105" t="s">
+        <v>51</v>
+      </c>
+      <c r="D105" t="s">
+        <v>52</v>
+      </c>
+      <c r="E105" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F105" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G105" t="s">
+        <v>366</v>
+      </c>
+      <c r="H105" t="s">
+        <v>1257</v>
+      </c>
+      <c r="I105" t="s">
+        <v>118</v>
+      </c>
+      <c r="J105" t="s">
+        <v>1258</v>
+      </c>
+      <c r="K105" t="s">
+        <v>59</v>
+      </c>
+      <c r="L105" t="s">
+        <v>1259</v>
+      </c>
+      <c r="M105" t="s">
+        <v>1260</v>
+      </c>
+      <c r="N105" t="s">
+        <v>1261</v>
+      </c>
+      <c r="O105" t="s">
+        <v>1262</v>
+      </c>
+      <c r="P105" t="s">
+        <v>1263</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R105" t="s">
+        <v>1265</v>
+      </c>
+      <c r="S105" t="s">
+        <v>1266</v>
+      </c>
+      <c r="T105" t="s">
+        <v>1267</v>
+      </c>
+      <c r="V105" t="s">
+        <v>1268</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA105" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB105" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC105" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="106" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA106" s="5"/>
-      <c r="AB106" s="5"/>
+    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B106" t="s">
+        <v>51</v>
+      </c>
+      <c r="D106" t="s">
+        <v>52</v>
+      </c>
+      <c r="E106" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F106" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G106" t="s">
+        <v>366</v>
+      </c>
+      <c r="H106" t="s">
+        <v>367</v>
+      </c>
+      <c r="I106" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J106" t="s">
+        <v>58</v>
+      </c>
+      <c r="K106" t="s">
+        <v>59</v>
+      </c>
+      <c r="L106" t="s">
+        <v>1272</v>
+      </c>
+      <c r="M106" t="s">
+        <v>1273</v>
+      </c>
+      <c r="N106" t="s">
+        <v>1274</v>
+      </c>
+      <c r="O106" t="s">
+        <v>1275</v>
+      </c>
+      <c r="P106" t="s">
+        <v>1276</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>1277</v>
+      </c>
+      <c r="R106" t="s">
+        <v>1278</v>
+      </c>
+      <c r="S106" t="s">
+        <v>1279</v>
+      </c>
+      <c r="T106" t="s">
+        <v>1280</v>
+      </c>
+      <c r="V106" t="s">
+        <v>1281</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA106" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB106" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC106" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="107" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA107" s="5"/>
-      <c r="AB107" s="5"/>
+    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B107" t="s">
+        <v>51</v>
+      </c>
+      <c r="D107" t="s">
+        <v>52</v>
+      </c>
+      <c r="E107" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F107" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G107" t="s">
+        <v>366</v>
+      </c>
+      <c r="H107" t="s">
+        <v>377</v>
+      </c>
+      <c r="I107" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J107" t="s">
+        <v>58</v>
+      </c>
+      <c r="K107" t="s">
+        <v>59</v>
+      </c>
+      <c r="L107" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M107" t="s">
+        <v>1286</v>
+      </c>
+      <c r="N107" t="s">
+        <v>1287</v>
+      </c>
+      <c r="O107" t="s">
+        <v>1288</v>
+      </c>
+      <c r="P107" t="s">
+        <v>1289</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>1290</v>
+      </c>
+      <c r="R107" t="s">
+        <v>1291</v>
+      </c>
+      <c r="S107" t="s">
+        <v>1292</v>
+      </c>
+      <c r="T107" t="s">
+        <v>1293</v>
+      </c>
+      <c r="V107" t="s">
+        <v>1294</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>295</v>
+      </c>
+      <c r="AA107" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB107" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC107" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="108" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA108" s="5"/>
-      <c r="AB108" s="5"/>
+    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B108" t="s">
+        <v>51</v>
+      </c>
+      <c r="D108" t="s">
+        <v>52</v>
+      </c>
+      <c r="E108" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F108" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G108" t="s">
+        <v>238</v>
+      </c>
+      <c r="H108" t="s">
+        <v>925</v>
+      </c>
+      <c r="I108" t="s">
+        <v>951</v>
+      </c>
+      <c r="J108" t="s">
+        <v>1298</v>
+      </c>
+      <c r="K108" t="s">
+        <v>59</v>
+      </c>
+      <c r="L108" t="s">
+        <v>1299</v>
+      </c>
+      <c r="M108" t="s">
+        <v>1300</v>
+      </c>
+      <c r="N108" t="s">
+        <v>1301</v>
+      </c>
+      <c r="O108" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P108" t="s">
+        <v>1303</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>1304</v>
+      </c>
+      <c r="R108" t="s">
+        <v>1305</v>
+      </c>
+      <c r="S108" t="s">
+        <v>1306</v>
+      </c>
+      <c r="T108" t="s">
+        <v>1307</v>
+      </c>
+      <c r="V108" t="s">
+        <v>1308</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA108" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB108" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="109" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA109" s="5"/>
-      <c r="AB109" s="5"/>
+    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B109" t="s">
+        <v>51</v>
+      </c>
+      <c r="D109" t="s">
+        <v>52</v>
+      </c>
+      <c r="E109" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F109" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G109" t="s">
+        <v>238</v>
+      </c>
+      <c r="H109" t="s">
+        <v>925</v>
+      </c>
+      <c r="I109" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J109" t="s">
+        <v>1312</v>
+      </c>
+      <c r="K109" t="s">
+        <v>59</v>
+      </c>
+      <c r="L109" t="s">
+        <v>1313</v>
+      </c>
+      <c r="M109" t="s">
+        <v>1314</v>
+      </c>
+      <c r="N109" t="s">
+        <v>1315</v>
+      </c>
+      <c r="O109" t="s">
+        <v>1316</v>
+      </c>
+      <c r="P109" t="s">
+        <v>1317</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>1318</v>
+      </c>
+      <c r="R109" t="s">
+        <v>1319</v>
+      </c>
+      <c r="S109" t="s">
+        <v>1320</v>
+      </c>
+      <c r="T109" t="s">
+        <v>1321</v>
+      </c>
+      <c r="V109" t="s">
+        <v>1322</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA109" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB109" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC109" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="110" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA110" s="5"/>
-      <c r="AB110" s="5"/>
+    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B110" t="s">
+        <v>51</v>
+      </c>
+      <c r="D110" t="s">
+        <v>52</v>
+      </c>
+      <c r="E110" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F110" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G110" t="s">
+        <v>238</v>
+      </c>
+      <c r="H110" t="s">
+        <v>925</v>
+      </c>
+      <c r="I110" t="s">
+        <v>964</v>
+      </c>
+      <c r="J110" t="s">
+        <v>1326</v>
+      </c>
+      <c r="K110" t="s">
+        <v>59</v>
+      </c>
+      <c r="L110" t="s">
+        <v>1327</v>
+      </c>
+      <c r="M110" t="s">
+        <v>1328</v>
+      </c>
+      <c r="N110" t="s">
+        <v>1329</v>
+      </c>
+      <c r="O110" t="s">
+        <v>1330</v>
+      </c>
+      <c r="P110" t="s">
+        <v>1331</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>1332</v>
+      </c>
+      <c r="R110" t="s">
+        <v>1333</v>
+      </c>
+      <c r="S110" t="s">
+        <v>1334</v>
+      </c>
+      <c r="T110" t="s">
+        <v>1335</v>
+      </c>
+      <c r="V110" t="s">
+        <v>1336</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>1016</v>
+      </c>
+      <c r="AA110" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB110" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC110" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="111" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA111" s="5"/>
-      <c r="AB111" s="5"/>
+    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B111" t="s">
+        <v>51</v>
+      </c>
+      <c r="D111" t="s">
+        <v>52</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F111" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G111" t="s">
+        <v>238</v>
+      </c>
+      <c r="H111" t="s">
+        <v>925</v>
+      </c>
+      <c r="I111" t="s">
+        <v>951</v>
+      </c>
+      <c r="J111" t="s">
+        <v>1340</v>
+      </c>
+      <c r="K111" t="s">
+        <v>59</v>
+      </c>
+      <c r="L111" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M111" t="s">
+        <v>1342</v>
+      </c>
+      <c r="N111" t="s">
+        <v>1343</v>
+      </c>
+      <c r="O111" t="s">
+        <v>1344</v>
+      </c>
+      <c r="P111" t="s">
+        <v>1345</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>1346</v>
+      </c>
+      <c r="R111" t="s">
+        <v>1347</v>
+      </c>
+      <c r="S111" t="s">
+        <v>1348</v>
+      </c>
+      <c r="T111" t="s">
+        <v>1349</v>
+      </c>
+      <c r="V111" t="s">
+        <v>1350</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA111" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB111" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="112" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA112" s="5"/>
-      <c r="AB112" s="5"/>
+    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B112" t="s">
+        <v>51</v>
+      </c>
+      <c r="D112" t="s">
+        <v>52</v>
+      </c>
+      <c r="E112" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F112" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G112" t="s">
+        <v>238</v>
+      </c>
+      <c r="H112" t="s">
+        <v>1354</v>
+      </c>
+      <c r="I112" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J112" t="s">
+        <v>1355</v>
+      </c>
+      <c r="K112" t="s">
+        <v>59</v>
+      </c>
+      <c r="L112" t="s">
+        <v>1356</v>
+      </c>
+      <c r="M112" t="s">
+        <v>1357</v>
+      </c>
+      <c r="N112" t="s">
+        <v>1358</v>
+      </c>
+      <c r="O112" t="s">
+        <v>1359</v>
+      </c>
+      <c r="P112" t="s">
+        <v>1360</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>1361</v>
+      </c>
+      <c r="R112" t="s">
+        <v>1362</v>
+      </c>
+      <c r="S112" t="s">
+        <v>1363</v>
+      </c>
+      <c r="T112" t="s">
+        <v>1364</v>
+      </c>
+      <c r="V112" t="s">
+        <v>1308</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA112" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB112" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC112" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="113" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA113" s="5"/>
-      <c r="AB113" s="5"/>
+    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B113" t="s">
+        <v>51</v>
+      </c>
+      <c r="D113" t="s">
+        <v>52</v>
+      </c>
+      <c r="E113" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F113" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G113" t="s">
+        <v>238</v>
+      </c>
+      <c r="H113" t="s">
+        <v>515</v>
+      </c>
+      <c r="I113" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J113" t="s">
+        <v>58</v>
+      </c>
+      <c r="K113" t="s">
+        <v>59</v>
+      </c>
+      <c r="L113" t="s">
+        <v>1368</v>
+      </c>
+      <c r="M113" t="s">
+        <v>1369</v>
+      </c>
+      <c r="N113" t="s">
+        <v>1370</v>
+      </c>
+      <c r="O113" t="s">
+        <v>1371</v>
+      </c>
+      <c r="P113" t="s">
+        <v>1372</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>1373</v>
+      </c>
+      <c r="R113" t="s">
+        <v>1374</v>
+      </c>
+      <c r="S113" t="s">
+        <v>1375</v>
+      </c>
+      <c r="T113" t="s">
+        <v>1376</v>
+      </c>
+      <c r="V113" t="s">
+        <v>1377</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA113" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB113" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC113" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="114" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA114" s="5"/>
-      <c r="AB114" s="5"/>
+    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B114" t="s">
+        <v>51</v>
+      </c>
+      <c r="D114" t="s">
+        <v>52</v>
+      </c>
+      <c r="E114" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F114" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G114" t="s">
+        <v>238</v>
+      </c>
+      <c r="H114" t="s">
+        <v>925</v>
+      </c>
+      <c r="I114" t="s">
+        <v>194</v>
+      </c>
+      <c r="J114" t="s">
+        <v>58</v>
+      </c>
+      <c r="K114" t="s">
+        <v>59</v>
+      </c>
+      <c r="L114" t="s">
+        <v>1380</v>
+      </c>
+      <c r="M114" t="s">
+        <v>1381</v>
+      </c>
+      <c r="N114" t="s">
+        <v>1382</v>
+      </c>
+      <c r="O114" t="s">
+        <v>1383</v>
+      </c>
+      <c r="P114" t="s">
+        <v>1384</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>1385</v>
+      </c>
+      <c r="R114" t="s">
+        <v>1386</v>
+      </c>
+      <c r="S114" t="s">
+        <v>1387</v>
+      </c>
+      <c r="T114" t="s">
+        <v>1388</v>
+      </c>
+      <c r="V114" t="s">
+        <v>1389</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA114" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB114" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC114" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA115" s="5"/>
-      <c r="AB115" s="5"/>
+    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B115" t="s">
+        <v>51</v>
+      </c>
+      <c r="D115" t="s">
+        <v>52</v>
+      </c>
+      <c r="E115" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F115" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G115" t="s">
+        <v>238</v>
+      </c>
+      <c r="H115" t="s">
+        <v>925</v>
+      </c>
+      <c r="I115" t="s">
+        <v>118</v>
+      </c>
+      <c r="J115" t="s">
+        <v>1393</v>
+      </c>
+      <c r="K115" t="s">
+        <v>59</v>
+      </c>
+      <c r="L115" t="s">
+        <v>1394</v>
+      </c>
+      <c r="M115" t="s">
+        <v>1395</v>
+      </c>
+      <c r="N115" t="s">
+        <v>1396</v>
+      </c>
+      <c r="O115" t="s">
+        <v>1397</v>
+      </c>
+      <c r="P115" t="s">
+        <v>1398</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>1399</v>
+      </c>
+      <c r="R115" t="s">
+        <v>1400</v>
+      </c>
+      <c r="S115" t="s">
+        <v>1401</v>
+      </c>
+      <c r="T115" t="s">
+        <v>1402</v>
+      </c>
+      <c r="V115" t="s">
+        <v>1403</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA115" s="5">
+        <v>46312</v>
+      </c>
+      <c r="AB115" s="5">
+        <v>46312</v>
+      </c>
       <c r="AC115" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA116" s="5"/>
       <c r="AB116" s="5"/>
       <c r="AC116" t="str">
@@ -9159,7 +12893,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA117" s="5"/>
       <c r="AB117" s="5"/>
       <c r="AC117" t="str">
@@ -9167,7 +12901,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA118" s="5"/>
       <c r="AB118" s="5"/>
       <c r="AC118" t="str">
@@ -9175,7 +12909,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA119" s="5"/>
       <c r="AB119" s="5"/>
       <c r="AC119" t="str">
@@ -9183,7 +12917,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA120" s="5"/>
       <c r="AB120" s="5"/>
       <c r="AC120" t="str">
@@ -9191,7 +12925,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA121" s="5"/>
       <c r="AB121" s="5"/>
       <c r="AC121" t="str">
@@ -9199,7 +12933,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA122" s="5"/>
       <c r="AB122" s="5"/>
       <c r="AC122" t="str">
@@ -9207,7 +12941,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA123" s="5"/>
       <c r="AB123" s="5"/>
       <c r="AC123" t="str">
@@ -9215,7 +12949,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA124" s="5"/>
       <c r="AB124" s="5"/>
       <c r="AC124" t="str">
@@ -9223,7 +12957,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA125" s="5"/>
       <c r="AB125" s="5"/>
       <c r="AC125" t="str">
@@ -9231,7 +12965,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA126" s="5"/>
       <c r="AB126" s="5"/>
       <c r="AC126" t="str">
@@ -9239,7 +12973,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA127" s="5"/>
       <c r="AB127" s="5"/>
       <c r="AC127" t="str">
@@ -9247,7 +12981,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA128" s="5"/>
       <c r="AB128" s="5"/>
       <c r="AC128" t="str">
@@ -11460,7 +15194,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.44140625" customWidth="1"/>
@@ -11528,6 +15262,17 @@
       </c>
       <c r="J2" t="s">
         <v>876</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <v>46341</v>
+      </c>
+      <c r="D3" t="s">
+        <v>932</v>
+      </c>
+      <c r="E3" t="s">
+        <v>933</v>
       </c>
     </row>
   </sheetData>
@@ -11604,7 +15349,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -11656,6 +15401,80 @@
         <v>914</v>
       </c>
     </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>919</v>
+      </c>
+      <c r="B3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C3" t="s">
+        <v>912</v>
+      </c>
+      <c r="D3" t="s">
+        <v>920</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>923</v>
+      </c>
+      <c r="B4" t="s">
+        <v>911</v>
+      </c>
+      <c r="C4" t="s">
+        <v>922</v>
+      </c>
+      <c r="D4" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>924</v>
+      </c>
+      <c r="B5" t="s">
+        <v>925</v>
+      </c>
+      <c r="C5" t="s">
+        <v>926</v>
+      </c>
+      <c r="D5" t="s">
+        <v>927</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>928</v>
+      </c>
+      <c r="B6" t="s">
+        <v>929</v>
+      </c>
+      <c r="C6" t="s">
+        <v>930</v>
+      </c>
+      <c r="D6" t="s">
+        <v>931</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>914</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11663,7 +15482,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -11687,6 +15506,20 @@
       </c>
       <c r="E1" s="2" t="s">
         <v>885</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>915</v>
+      </c>
+      <c r="B2" t="s">
+        <v>916</v>
+      </c>
+      <c r="C2" t="s">
+        <v>917</v>
+      </c>
+      <c r="D2" t="s">
+        <v>918</v>
       </c>
     </row>
   </sheetData>
@@ -11772,6 +15605,9 @@
       <c r="A3" t="s">
         <v>899</v>
       </c>
+      <c r="B3">
+        <v>20</v>
+      </c>
       <c r="C3" t="s">
         <v>900</v>
       </c>

--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -6426,9 +6426,6 @@
     <t>2026-11-21</t>
   </si>
   <si>
-    <t>ar1.jpg</t>
-  </si>
-  <si>
     <t>2026-10-18</t>
   </si>
   <si>
@@ -6490,6 +6487,9 @@
   </si>
   <si>
     <t>7:00 PM (BD time)</t>
+  </si>
+  <si>
+    <t>ar1.JPEG</t>
   </si>
 </sst>
 </file>
@@ -6512,12 +6512,14 @@
       <sz val="16"/>
       <color rgb="FF0B1B34"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -21092,7 +21094,7 @@
         <v>2131</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="D3" t="s">
         <v>1352</v>
@@ -21143,34 +21145,34 @@
     </row>
     <row r="2" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>2133</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>2134</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>2135</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>2136</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>2137</v>
       </c>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>1352</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>2138</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>2139</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>1211</v>
@@ -21179,71 +21181,71 @@
     </row>
     <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>1352</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>2140</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>2141</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>2142</v>
       </c>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>2143</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>2144</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>2145</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>2146</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>2147</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>2148</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>2149</v>
       </c>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>2150</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>2151</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>2152</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="F7" s="7"/>
     </row>
@@ -21577,7 +21579,7 @@
         <v>1398</v>
       </c>
       <c r="E2" t="s">
-        <v>2132</v>
+        <v>2153</v>
       </c>
     </row>
   </sheetData>

--- a/content.xlsx
+++ b/content.xlsx
@@ -6489,7 +6489,7 @@
     <t>7:00 PM (BD time)</t>
   </si>
   <si>
-    <t>ar1.JPEG</t>
+    <t>ar1.jpeg</t>
   </si>
 </sst>
 </file>

--- a/content.xlsx
+++ b/content.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3421" uniqueCount="2180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3421" uniqueCount="2179">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -6484,9 +6484,6 @@
   </si>
   <si>
     <t>BSc, Your University | MSc, Your University</t>
-  </si>
-  <si>
-    <t>Won DAAD for a Master in Germany | Helped 30 students with SOPs</t>
   </si>
   <si>
     <t>English | Bangla</t>
@@ -7112,70 +7109,70 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2162</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>2163</v>
-      </c>
       <c r="C1" s="2" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="B2">
         <v>3000</v>
       </c>
       <c r="C2" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C4" t="s">
         <v>2168</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2169</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B5" t="s">
         <v>2170</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>2171</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2172</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C6" t="s">
         <v>2173</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C7" t="s">
         <v>2175</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2176</v>
       </c>
     </row>
   </sheetData>
@@ -21713,16 +21710,16 @@
         <v>2144</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>2176</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>2177</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>2152</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>2153</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>2154</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -21748,19 +21745,19 @@
         <v>2151</v>
       </c>
       <c r="I3" t="s">
+        <v>2177</v>
+      </c>
+      <c r="J3" t="s">
+        <v>2152</v>
+      </c>
+      <c r="K3" t="s">
         <v>2178</v>
       </c>
-      <c r="J3" t="s">
-        <v>2153</v>
-      </c>
-      <c r="K3" t="s">
-        <v>2179</v>
-      </c>
       <c r="L3" t="s">
+        <v>2154</v>
+      </c>
+      <c r="N3" t="s">
         <v>2155</v>
-      </c>
-      <c r="N3" t="s">
-        <v>2156</v>
       </c>
     </row>
   </sheetData>
@@ -21792,22 +21789,22 @@
         <v>2095</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2157</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2158</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2159</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2160</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>2161</v>
       </c>
     </row>
   </sheetData>

--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3421" uniqueCount="2179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="2304">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -6565,6 +6565,381 @@
   </si>
   <si>
     <t>Leipzig, Germany</t>
+  </si>
+  <si>
+    <t>KAUST Fellowship (Master’s &amp; PhD)</t>
+  </si>
+  <si>
+    <t>King Abdullah University of Science and Technology (KAUST), Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Fellowship for admitted full-time students: tuition and fees covered, monthly stipend, accommodation, health insurance and relocation support. No separate fellowship application</t>
+  </si>
+  <si>
+    <t>Fall 2027 (MS, MS/PhD, PhD): 3 Jan 2027. Annual cycle</t>
+  </si>
+  <si>
+    <t>International applicants are welcome. A relevant Bachelor’s degree for Master’s programmes and a relevant Master’s degree for PhD programmes, in KAUST’s STEM fields</t>
+  </si>
+  <si>
+    <t>High: Online KAUST admissions application + transcripts + CV + statement + recommendation letters + English proficiency</t>
+  </si>
+  <si>
+    <t>STEM graduates seeking a fully funded research Master’s or PhD in Saudi Arabia</t>
+  </si>
+  <si>
+    <t>KAUST funds every admitted full-time graduate student through the KAUST Fellowship. You apply once for admission and are automatically considered for the fellowship. Spring entry is for PhD applicants only, and its 2027 round has already closed. MS/PhD and PhD applicants can name the faculty members they would like to work with.</t>
+  </si>
+  <si>
+    <t>Academic transcripts and degree certificates | CV | Statement of purpose | Recommendation letters | English proficiency score if required</t>
+  </si>
+  <si>
+    <t>Name specific KAUST faculty whose research matches yours | Check the programme page for its own requirements before you apply</t>
+  </si>
+  <si>
+    <t>https://admissions.kaust.edu.sa/</t>
+  </si>
+  <si>
+    <t>MBZUAI Graduate Scholarship (Master’s &amp; PhD)</t>
+  </si>
+  <si>
+    <t>Mohamed bin Zayed University of Artificial Intelligence (MBZUAI), Abu Dhabi</t>
+  </si>
+  <si>
+    <t>United Arab Emirates</t>
+  </si>
+  <si>
+    <t>Computer Science, Data &amp; AI</t>
+  </si>
+  <si>
+    <t>PhD: funded study with a monthly stipend, tuition and health insurance as published by MBZUAI. Master’s: funding is not automatic with admission, so check the official page for the current model</t>
+  </si>
+  <si>
+    <t>2027 intake: 15 Dec 2026</t>
+  </si>
+  <si>
+    <t>International applicants are welcome. A relevant Bachelor’s degree for Master’s programmes and a Master’s degree for PhD programmes</t>
+  </si>
+  <si>
+    <t>High: Online application + transcripts + referee recommendations (2 for Master’s, 3 for PhD) + research statement for PhD</t>
+  </si>
+  <si>
+    <t>Computer science and AI graduates targeting research-focused AI study in the UAE</t>
+  </si>
+  <si>
+    <t>MBZUAI is a graduate university focused on artificial intelligence in Abu Dhabi. The 2027 graduate application opened in September 2026 and closes on 15 December 2026. Decisions are expected by the end of March 2027 and programmes start in August 2027. Funding differs between PhD and Master’s programmes.</t>
+  </si>
+  <si>
+    <t>Official transcripts and degree certificates | Recommendation letters | Research statement (PhD) | CV | English proficiency score</t>
+  </si>
+  <si>
+    <t>Check which Master’s tracks come with funding before you apply | For the PhD, connect your research statement to a specific faculty group</t>
+  </si>
+  <si>
+    <t>https://mbzuai.ac.ae/</t>
+  </si>
+  <si>
+    <t>Khalifa University Graduate Scholarships (Master’s &amp; PhD)</t>
+  </si>
+  <si>
+    <t>Khalifa University of Science and Technology, Abu Dhabi</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Mathematics &amp; Natural Sciences, Computer Science, Data &amp; AI, Environment, Water &amp; Energy</t>
+  </si>
+  <si>
+    <t>Merit-based tiers with a monthly stipend. PhD scholarships include a full tuition fee waiver. Medical insurance and UAE visa fee coverage for full-time international students. Free housing for eligible full-time students</t>
+  </si>
+  <si>
+    <t>Varies by intake (Fall and Spring). Check the graduate admissions page</t>
+  </si>
+  <si>
+    <t>International and UAE national students admitted to full-time graduate programmes. Scholarship tiers depend on academic merit. PhD scholarships are reviewed every year</t>
+  </si>
+  <si>
+    <t>High: Online graduate application + transcripts + references + research statement for PhD</t>
+  </si>
+  <si>
+    <t>Engineering and science graduates seeking funded Master’s or PhD study in Abu Dhabi</t>
+  </si>
+  <si>
+    <t>Khalifa University offers merit-based graduate scholarships to full-time students. Applicants are considered when they apply for admission, and the scholarship tier depends on academic merit and the university’s priorities.</t>
+  </si>
+  <si>
+    <t>Apply as early as possible: tiers are set by merit and ranking | Reread the scholarship conditions on the official page because tiers can change</t>
+  </si>
+  <si>
+    <t>https://www.ku.ac.ae/admissions/graduate-admissions/</t>
+  </si>
+  <si>
+    <t>HBKU Graduate Scholarships (Master’s &amp; PhD)</t>
+  </si>
+  <si>
+    <t>Hamad Bin Khalifa University (HBKU), Doha</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>Law, Governance &amp; Public Policy, Social Sciences &amp; Humanities, Engineering &amp; Technology, Health &amp; Life Sciences, Environment, Water &amp; Energy</t>
+  </si>
+  <si>
+    <t>Scholarship considered during graduate admission. Monthly stipend for selected students (selected international PhD students can receive it for up to 45 months). Other support such as housing or airfare depends on the programme. Funding is not guaranteed to every applicant</t>
+  </si>
+  <si>
+    <t>International applicants: 1 Feb 2027</t>
+  </si>
+  <si>
+    <t>International students admitted to an HBKU graduate programme. A relevant Bachelor’s degree for Master’s and a Master’s degree for PhD. No separate scholarship application</t>
+  </si>
+  <si>
+    <t>High: Online graduate application + transcripts + statement of purpose + 2 recommendation letters + CV + English proficiency</t>
+  </si>
+  <si>
+    <t>Graduates in law, policy, sciences and engineering seeking funded study in Qatar</t>
+  </si>
+  <si>
+    <t>Hamad Bin Khalifa University in Doha offers Master’s, PhD and law programmes. Scholarship consideration takes place within the admission process, so you do not submit a second application.</t>
+  </si>
+  <si>
+    <t>Submit well before 1 Feb 2027 because funding decisions follow admission | Read the programme page for any extra tests or interviews</t>
+  </si>
+  <si>
+    <t>https://www.hbku.edu.qa</t>
+  </si>
+  <si>
+    <t>NYU Abu Dhabi Undergraduate Financial Aid</t>
+  </si>
+  <si>
+    <t>New York University Abu Dhabi</t>
+  </si>
+  <si>
+    <t>Need-based financial aid. Awards vary with demonstrated financial need and can be large, often including housing, meals, insurance and travel</t>
+  </si>
+  <si>
+    <t>Follows the undergraduate admission deadlines. Submit the CSS Profile by the published aid deadline</t>
+  </si>
+  <si>
+    <t>Applicants to NYU Abu Dhabi undergraduate programmes from any country. Aid is based on demonstrated financial need and requires the CSS Profile and financial documents</t>
+  </si>
+  <si>
+    <t>Very High: Highly selective undergraduate application + CSS Profile + financial documents</t>
+  </si>
+  <si>
+    <t>High-achieving undergraduates with financial need who want a liberal arts degree in Abu Dhabi</t>
+  </si>
+  <si>
+    <t>NYU Abu Dhabi accepts financial aid applications from students of any citizenship. Need-based aid is decided from the financial documents you submit, so late or missing documents are the most common problem.</t>
+  </si>
+  <si>
+    <t>Undergraduate application | CSS Profile | Financial documents requested by the university | Academic transcripts | English proficiency score</t>
+  </si>
+  <si>
+    <t>Start the CSS Profile early because financial documents take time to collect | Keep the numbers consistent across every form</t>
+  </si>
+  <si>
+    <t>https://nyuad.nyu.edu/en/apply/undergraduate/scholarships-and-financial-aid.html</t>
+  </si>
+  <si>
+    <t>Islamic University of Madinah International Scholarships</t>
+  </si>
+  <si>
+    <t>Islamic University of Madinah, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Social Sciences &amp; Humanities, Law, Governance &amp; Public Policy</t>
+  </si>
+  <si>
+    <t>Full scholarships can include tuition-free study, university housing and healthcare. The university also lists partial scholarships without a stipend. Benefits differ by type, so read the current admission guide</t>
+  </si>
+  <si>
+    <t>Annual cycle through the university portal and the Study in Saudi platform. Check the current admission guide</t>
+  </si>
+  <si>
+    <t>International students. The university is a men’s institution and guides list Muslim male applicants, so confirm the current rules. Undergraduate applicants need a secondary school certificate. Postgraduate applicants need the relevant earlier degree</t>
+  </si>
+  <si>
+    <t>Medium: Online application + academic certificates + passport copy</t>
+  </si>
+  <si>
+    <t>Muslim male students seeking free study in Islamic and Arabic studies in Madinah</t>
+  </si>
+  <si>
+    <t>The Islamic University of Madinah offers scholarships to international students for undergraduate and postgraduate study. Many applicants apply through the Study in Saudi platform, which is run by the Saudi Ministry of Education.</t>
+  </si>
+  <si>
+    <t>Academic certificates and transcripts | Passport copy | Application form | Other documents listed in the admission guide</t>
+  </si>
+  <si>
+    <t>Read the admission guide for the scholarship type first because full and partial scholarships differ | Apply early in the cycle</t>
+  </si>
+  <si>
+    <t>https://iu.edu.sa/</t>
+  </si>
+  <si>
+    <t>Study in Saudi: Saudi Government Scholarships for International Students</t>
+  </si>
+  <si>
+    <t>Ministry of Education, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Government-funded external scholarships at participating Saudi universities. Benefits differ by university and programme, so check each listing on the platform</t>
+  </si>
+  <si>
+    <t>Annual cycles set by each university. Check the Study in Saudi platform</t>
+  </si>
+  <si>
+    <t>International students who meet the entry requirements of the chosen Saudi university</t>
+  </si>
+  <si>
+    <t>Medium: Application through the Study in Saudi platform or the university portal + academic documents</t>
+  </si>
+  <si>
+    <t>Students who want to compare funded study options at Saudi universities</t>
+  </si>
+  <si>
+    <t>Study in Saudi is the Saudi Ministry of Education platform where international students apply for external scholarships at Saudi universities. Each university sets its own programmes, deadlines and benefits.</t>
+  </si>
+  <si>
+    <t>Academic certificates and transcripts | Passport copy | Language proficiency evidence if requested</t>
+  </si>
+  <si>
+    <t>Shortlist two or three universities and compare their benefits before applying</t>
+  </si>
+  <si>
+    <t>https://studyinsaudi.moe.gov.sa/</t>
+  </si>
+  <si>
+    <t>UNHCR DAFI Scholarship (Refugee Undergraduate Scholarships)</t>
+  </si>
+  <si>
+    <t>UNHCR, funded by the German government</t>
+  </si>
+  <si>
+    <t>Jordan, Lebanon, Egypt, Iraq, Syria, Yemen, Morocco, Algeria, Mauritania</t>
+  </si>
+  <si>
+    <t>Scholarship for refugee undergraduates in their country of asylum. Can cover tuition and study materials and, depending on the country programme, food, transport and accommodation, in full or in part</t>
+  </si>
+  <si>
+    <t>Set by each country programme. Contact the UNHCR office in your country of asylum</t>
+  </si>
+  <si>
+    <t>Recognised refugees (not asylum seekers) who completed secondary school to a high standard and have no other means to pay for university. No other family member may hold a DAFI scholarship. Courses lead to employment and last up to about four years</t>
+  </si>
+  <si>
+    <t>Medium: Country-specific application form through the UNHCR office or partner. Do not send it to UNHCR headquarters</t>
+  </si>
+  <si>
+    <t>Refugee students who need support to study in their country of asylum</t>
+  </si>
+  <si>
+    <t>DAFI is the Albert Einstein German Academic Refugee Initiative. It helps refugee students earn an undergraduate degree in their country of asylum, with extra support such as mentoring and academic preparation.</t>
+  </si>
+  <si>
+    <t>Proof of refugee status | Secondary school certificates | Application form from the UNHCR office | Identity documents</t>
+  </si>
+  <si>
+    <t>Ask the UNHCR office or its partner about the next call because timing differs by country</t>
+  </si>
+  <si>
+    <t>https://www.unhcr.org/</t>
+  </si>
+  <si>
+    <t>Need-based, Refugee / displaced</t>
+  </si>
+  <si>
+    <t>Weizmann Institute Feinberg Graduate School (MSc &amp; PhD)</t>
+  </si>
+  <si>
+    <t>Weizmann Institute of Science, Rehovot</t>
+  </si>
+  <si>
+    <t>Mathematics &amp; Natural Sciences, Health &amp; Life Sciences, Computer Science, Data &amp; AI</t>
+  </si>
+  <si>
+    <t>No tuition fees. Students receive fellowships so they can devote their time to research. MSc students receive a monthly fellowship for 24 months</t>
+  </si>
+  <si>
+    <t>Varies by track. Check the Feinberg Graduate School admissions page</t>
+  </si>
+  <si>
+    <t>Admission is based on academic excellence and integrity. Classes are taught in English and international applicants are accepted</t>
+  </si>
+  <si>
+    <t>Very High: Highly selective application with transcripts and recommendation letters</t>
+  </si>
+  <si>
+    <t>Top science graduates seeking funded research degrees in Israel</t>
+  </si>
+  <si>
+    <t>The Feinberg Graduate School of the Weizmann Institute offers research-focused MSc and PhD study. All students are directly involved in the Institute’s research and receive fellowships.</t>
+  </si>
+  <si>
+    <t>Academic transcripts and degree certificates | CV | Recommendation letters | Statement of purpose | English proficiency evidence if required</t>
+  </si>
+  <si>
+    <t>Check the track’s own deadline early because tracks differ | Read the research of two or three groups before you write your statement</t>
+  </si>
+  <si>
+    <t>https://www.weizmann.ac.il/feinberg/admissions</t>
+  </si>
+  <si>
+    <t>MBZUAI Undergraduate Research Internship Program (UGRIP)</t>
+  </si>
+  <si>
+    <t>Four-week summer research internship. Recent calls covered a stipend, accommodation, airfare, visa support and health insurance</t>
+  </si>
+  <si>
+    <t>Annual summer programme. Recent calls closed around late February. Check the official page for 2027 dates</t>
+  </si>
+  <si>
+    <t>STEM undergraduates in the 3rd or 4th year with a strong GPA (recent calls listed CGPA 3.5/4.0) and English proficiency (recent calls listed TOEFL 90 or IELTS 6.5). Open to all nationalities</t>
+  </si>
+  <si>
+    <t>High: Online application + transcripts + CV + English score</t>
+  </si>
+  <si>
+    <t>Strong STEM undergraduates who want hands-on AI research experience</t>
+  </si>
+  <si>
+    <t>MBZUAI’s summer programme lets undergraduates work on research projects with faculty and graduate students in Abu Dhabi. Recent calls listed machine learning, computer vision and natural language processing.</t>
+  </si>
+  <si>
+    <t>Academic transcripts | CV | English proficiency score | Application form</t>
+  </si>
+  <si>
+    <t>Apply in January or early February and read the posted research areas first | Show a small project or code sample if you can</t>
+  </si>
+  <si>
+    <t>kaust-fellowship-master-s-phd</t>
+  </si>
+  <si>
+    <t>mbzuai-graduate-scholarship-master-s-phd</t>
+  </si>
+  <si>
+    <t>khalifa-university-graduate-scholarships-master-s-phd</t>
+  </si>
+  <si>
+    <t>hbku-graduate-scholarships-master-s-phd</t>
+  </si>
+  <si>
+    <t>nyu-abu-dhabi-undergraduate-financial-aid</t>
+  </si>
+  <si>
+    <t>islamic-university-of-madinah-international-scholarships</t>
+  </si>
+  <si>
+    <t>study-in-saudi-saudi-government-scholarships-for-internation</t>
+  </si>
+  <si>
+    <t>unhcr-dafi-scholarship-refugee-undergraduate-scholarships</t>
+  </si>
+  <si>
+    <t>weizmann-institute-feinberg-graduate-school-msc-phd</t>
+  </si>
+  <si>
+    <t>mbzuai-undergraduate-research-internship-program-ugrip</t>
   </si>
 </sst>
 </file>
@@ -19214,7 +19589,69 @@
       </c>
     </row>
     <row r="168" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA168" s="4"/>
+      <c r="A168" s="5" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>2179</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>2180</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>1662</v>
+      </c>
+      <c r="I168" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="J168" s="5" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K168" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L168" s="5" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M168" s="5" t="s">
+        <v>2182</v>
+      </c>
+      <c r="N168" s="5" t="s">
+        <v>2183</v>
+      </c>
+      <c r="O168" s="5" t="s">
+        <v>2184</v>
+      </c>
+      <c r="P168" s="5" t="s">
+        <v>2185</v>
+      </c>
+      <c r="Q168" s="5" t="s">
+        <v>2186</v>
+      </c>
+      <c r="R168" s="5" t="s">
+        <v>2187</v>
+      </c>
+      <c r="U168" s="5" t="s">
+        <v>2188</v>
+      </c>
+      <c r="V168" s="5" t="s">
+        <v>2189</v>
+      </c>
+      <c r="Z168" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA168" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB168" s="4"/>
       <c r="AC168" t="str">
         <f t="shared" si="2"/>
@@ -19222,7 +19659,69 @@
       </c>
     </row>
     <row r="169" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA169" s="4"/>
+      <c r="A169" s="5" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>2190</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>2191</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I169" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="J169" s="5" t="s">
+        <v>2193</v>
+      </c>
+      <c r="K169" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="L169" s="5" t="s">
+        <v>2194</v>
+      </c>
+      <c r="M169" s="5" t="s">
+        <v>2195</v>
+      </c>
+      <c r="N169" s="5" t="s">
+        <v>2196</v>
+      </c>
+      <c r="O169" s="5" t="s">
+        <v>2197</v>
+      </c>
+      <c r="P169" s="5" t="s">
+        <v>2198</v>
+      </c>
+      <c r="Q169" s="5" t="s">
+        <v>2199</v>
+      </c>
+      <c r="R169" s="5" t="s">
+        <v>2200</v>
+      </c>
+      <c r="U169" s="5" t="s">
+        <v>2201</v>
+      </c>
+      <c r="V169" s="5" t="s">
+        <v>2202</v>
+      </c>
+      <c r="Z169" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA169" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB169" s="4"/>
       <c r="AC169" t="str">
         <f t="shared" si="2"/>
@@ -19230,7 +19729,69 @@
       </c>
     </row>
     <row r="170" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA170" s="4"/>
+      <c r="A170" s="5" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>2203</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>2204</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H170" s="5" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I170" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="J170" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="K170" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="L170" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="M170" s="5" t="s">
+        <v>2207</v>
+      </c>
+      <c r="N170" s="5" t="s">
+        <v>2208</v>
+      </c>
+      <c r="O170" s="5" t="s">
+        <v>2209</v>
+      </c>
+      <c r="P170" s="5" t="s">
+        <v>2210</v>
+      </c>
+      <c r="Q170" s="5" t="s">
+        <v>2211</v>
+      </c>
+      <c r="R170" s="5" t="s">
+        <v>2187</v>
+      </c>
+      <c r="U170" s="5" t="s">
+        <v>2212</v>
+      </c>
+      <c r="V170" s="5" t="s">
+        <v>2213</v>
+      </c>
+      <c r="Z170" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA170" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB170" s="4"/>
       <c r="AC170" t="str">
         <f t="shared" si="2"/>
@@ -19238,7 +19799,69 @@
       </c>
     </row>
     <row r="171" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA171" s="4"/>
+      <c r="A171" s="5" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>2214</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>2215</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H171" s="5" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I171" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="J171" s="5" t="s">
+        <v>2217</v>
+      </c>
+      <c r="K171" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="L171" s="5" t="s">
+        <v>2218</v>
+      </c>
+      <c r="M171" s="5" t="s">
+        <v>2219</v>
+      </c>
+      <c r="N171" s="5" t="s">
+        <v>2220</v>
+      </c>
+      <c r="O171" s="5" t="s">
+        <v>2221</v>
+      </c>
+      <c r="P171" s="5" t="s">
+        <v>2222</v>
+      </c>
+      <c r="Q171" s="5" t="s">
+        <v>2223</v>
+      </c>
+      <c r="R171" s="5" t="s">
+        <v>2187</v>
+      </c>
+      <c r="U171" s="5" t="s">
+        <v>2224</v>
+      </c>
+      <c r="V171" s="5" t="s">
+        <v>2225</v>
+      </c>
+      <c r="Z171" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA171" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB171" s="4"/>
       <c r="AC171" t="str">
         <f t="shared" si="2"/>
@@ -19246,7 +19869,69 @@
       </c>
     </row>
     <row r="172" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA172" s="4"/>
+      <c r="A172" s="5" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>2226</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>2227</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I172" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J172" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K172" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L172" s="5" t="s">
+        <v>2228</v>
+      </c>
+      <c r="M172" s="5" t="s">
+        <v>2229</v>
+      </c>
+      <c r="N172" s="5" t="s">
+        <v>2230</v>
+      </c>
+      <c r="O172" s="5" t="s">
+        <v>2231</v>
+      </c>
+      <c r="P172" s="5" t="s">
+        <v>2232</v>
+      </c>
+      <c r="Q172" s="5" t="s">
+        <v>2233</v>
+      </c>
+      <c r="R172" s="5" t="s">
+        <v>2234</v>
+      </c>
+      <c r="U172" s="5" t="s">
+        <v>2235</v>
+      </c>
+      <c r="V172" s="5" t="s">
+        <v>2236</v>
+      </c>
+      <c r="Z172" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA172" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB172" s="4"/>
       <c r="AC172" t="str">
         <f t="shared" si="2"/>
@@ -19254,7 +19939,66 @@
       </c>
     </row>
     <row r="173" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA173" s="4"/>
+      <c r="A173" s="5" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>2237</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>1662</v>
+      </c>
+      <c r="I173" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="J173" s="5" t="s">
+        <v>2239</v>
+      </c>
+      <c r="K173" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L173" s="5" t="s">
+        <v>2240</v>
+      </c>
+      <c r="M173" s="5" t="s">
+        <v>2241</v>
+      </c>
+      <c r="N173" s="5" t="s">
+        <v>2242</v>
+      </c>
+      <c r="O173" s="5" t="s">
+        <v>2243</v>
+      </c>
+      <c r="P173" s="5" t="s">
+        <v>2244</v>
+      </c>
+      <c r="Q173" s="5" t="s">
+        <v>2245</v>
+      </c>
+      <c r="R173" s="5" t="s">
+        <v>2246</v>
+      </c>
+      <c r="U173" s="5" t="s">
+        <v>2247</v>
+      </c>
+      <c r="V173" s="5" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AA173" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB173" s="4"/>
       <c r="AC173" t="str">
         <f t="shared" si="2"/>
@@ -19262,7 +20006,66 @@
       </c>
     </row>
     <row r="174" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA174" s="4"/>
+      <c r="A174" s="5" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>2249</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>2250</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H174" s="5" t="s">
+        <v>1662</v>
+      </c>
+      <c r="I174" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="J174" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K174" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L174" s="5" t="s">
+        <v>2251</v>
+      </c>
+      <c r="M174" s="5" t="s">
+        <v>2252</v>
+      </c>
+      <c r="N174" s="5" t="s">
+        <v>2253</v>
+      </c>
+      <c r="O174" s="5" t="s">
+        <v>2254</v>
+      </c>
+      <c r="P174" s="5" t="s">
+        <v>2255</v>
+      </c>
+      <c r="Q174" s="5" t="s">
+        <v>2256</v>
+      </c>
+      <c r="R174" s="5" t="s">
+        <v>2257</v>
+      </c>
+      <c r="U174" s="5" t="s">
+        <v>2258</v>
+      </c>
+      <c r="V174" s="5" t="s">
+        <v>2259</v>
+      </c>
+      <c r="AA174" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB174" s="4"/>
       <c r="AC174" t="str">
         <f t="shared" si="2"/>
@@ -19270,7 +20073,69 @@
       </c>
     </row>
     <row r="175" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA175" s="4"/>
+      <c r="A175" s="5" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>2260</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>2261</v>
+      </c>
+      <c r="G175" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I175" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J175" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K175" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L175" s="5" t="s">
+        <v>2263</v>
+      </c>
+      <c r="M175" s="5" t="s">
+        <v>2264</v>
+      </c>
+      <c r="N175" s="5" t="s">
+        <v>2265</v>
+      </c>
+      <c r="O175" s="5" t="s">
+        <v>2266</v>
+      </c>
+      <c r="P175" s="5" t="s">
+        <v>2267</v>
+      </c>
+      <c r="Q175" s="5" t="s">
+        <v>2268</v>
+      </c>
+      <c r="R175" s="5" t="s">
+        <v>2269</v>
+      </c>
+      <c r="U175" s="5" t="s">
+        <v>2270</v>
+      </c>
+      <c r="V175" s="5" t="s">
+        <v>2271</v>
+      </c>
+      <c r="Z175" s="5" t="s">
+        <v>2272</v>
+      </c>
+      <c r="AA175" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB175" s="4"/>
       <c r="AC175" t="str">
         <f t="shared" si="2"/>
@@ -19278,22 +20143,146 @@
       </c>
     </row>
     <row r="176" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA176" s="4"/>
+      <c r="A176" s="5" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>2273</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>2039</v>
+      </c>
+      <c r="I176" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="J176" s="5" t="s">
+        <v>2275</v>
+      </c>
+      <c r="K176" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L176" s="5" t="s">
+        <v>2276</v>
+      </c>
+      <c r="M176" s="5" t="s">
+        <v>2277</v>
+      </c>
+      <c r="N176" s="5" t="s">
+        <v>2278</v>
+      </c>
+      <c r="O176" s="5" t="s">
+        <v>2279</v>
+      </c>
+      <c r="P176" s="5" t="s">
+        <v>2280</v>
+      </c>
+      <c r="Q176" s="5" t="s">
+        <v>2281</v>
+      </c>
+      <c r="R176" s="5" t="s">
+        <v>2282</v>
+      </c>
+      <c r="U176" s="5" t="s">
+        <v>2283</v>
+      </c>
+      <c r="V176" s="5" t="s">
+        <v>2284</v>
+      </c>
+      <c r="Z176" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA176" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB176" s="4"/>
       <c r="AC176" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="177" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA177" s="4"/>
+    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A177" s="5" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>2285</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>2191</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H177" s="5" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I177" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J177" s="5" t="s">
+        <v>1356</v>
+      </c>
+      <c r="K177" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L177" s="5" t="s">
+        <v>2286</v>
+      </c>
+      <c r="M177" s="5" t="s">
+        <v>2287</v>
+      </c>
+      <c r="N177" s="5" t="s">
+        <v>2288</v>
+      </c>
+      <c r="O177" s="5" t="s">
+        <v>2289</v>
+      </c>
+      <c r="P177" s="5" t="s">
+        <v>2290</v>
+      </c>
+      <c r="Q177" s="5" t="s">
+        <v>2291</v>
+      </c>
+      <c r="R177" s="5" t="s">
+        <v>2292</v>
+      </c>
+      <c r="U177" s="5" t="s">
+        <v>2293</v>
+      </c>
+      <c r="V177" s="5" t="s">
+        <v>2202</v>
+      </c>
+      <c r="Z177" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA177" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB177" s="4"/>
       <c r="AC177" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="178" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA178" s="4"/>
       <c r="AB178" s="4"/>
       <c r="AC178" t="str">
@@ -19301,7 +20290,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA179" s="4"/>
       <c r="AB179" s="4"/>
       <c r="AC179" t="str">
@@ -19309,7 +20298,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA180" s="4"/>
       <c r="AB180" s="4"/>
       <c r="AC180" t="str">
@@ -19317,7 +20306,7 @@
         <v/>
       </c>
     </row>
-    <row r="181" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA181" s="4"/>
       <c r="AB181" s="4"/>
       <c r="AC181" t="str">
@@ -19325,7 +20314,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA182" s="4"/>
       <c r="AB182" s="4"/>
       <c r="AC182" t="str">
@@ -19333,7 +20322,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA183" s="4"/>
       <c r="AB183" s="4"/>
       <c r="AC183" t="str">
@@ -19341,7 +20330,7 @@
         <v/>
       </c>
     </row>
-    <row r="184" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA184" s="4"/>
       <c r="AB184" s="4"/>
       <c r="AC184" t="str">
@@ -19349,7 +20338,7 @@
         <v/>
       </c>
     </row>
-    <row r="185" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA185" s="4"/>
       <c r="AB185" s="4"/>
       <c r="AC185" t="str">
@@ -19357,7 +20346,7 @@
         <v/>
       </c>
     </row>
-    <row r="186" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA186" s="4"/>
       <c r="AB186" s="4"/>
       <c r="AC186" t="str">
@@ -19365,7 +20354,7 @@
         <v/>
       </c>
     </row>
-    <row r="187" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA187" s="4"/>
       <c r="AB187" s="4"/>
       <c r="AC187" t="str">
@@ -19373,7 +20362,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA188" s="4"/>
       <c r="AB188" s="4"/>
       <c r="AC188" t="str">
@@ -19381,7 +20370,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA189" s="4"/>
       <c r="AB189" s="4"/>
       <c r="AC189" t="str">
@@ -19389,7 +20378,7 @@
         <v/>
       </c>
     </row>
-    <row r="190" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA190" s="4"/>
       <c r="AB190" s="4"/>
       <c r="AC190" t="str">
@@ -19397,7 +20386,7 @@
         <v/>
       </c>
     </row>
-    <row r="191" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA191" s="4"/>
       <c r="AB191" s="4"/>
       <c r="AC191" t="str">
@@ -19405,7 +20394,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="27:29" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA192" s="4"/>
       <c r="AB192" s="4"/>
       <c r="AC192" t="str">

--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -22173,7 +22173,7 @@
         <v>2067</v>
       </c>
       <c r="D3" t="s">
-        <v>2068</v>
+        <v>2061</v>
       </c>
       <c r="E3" t="s">
         <v>2069</v>

--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="2304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4409" uniqueCount="2881">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -6940,6 +6940,1737 @@
   </si>
   <si>
     <t>mbzuai-undergraduate-research-internship-program-ugrip</t>
+  </si>
+  <si>
+    <t>Czech Government Scholarships for Developing Countries</t>
+  </si>
+  <si>
+    <t>Government of the Czech Republic (Ministry of Education, Youth and Sports)</t>
+  </si>
+  <si>
+    <t>Czech Republic</t>
+  </si>
+  <si>
+    <t>Tuition paid by the government plus a monthly stipend (about CZK 16,000 for follow-up Master, about CZK 24,960 for PhD)</t>
+  </si>
+  <si>
+    <t>Sep 30 (annual, for the next academic year)</t>
+  </si>
+  <si>
+    <t>Adult citizens of a limited list of developing countries that changes each year. Applications go through the Czech embassy or the national UNESCO commission in your country.</t>
+  </si>
+  <si>
+    <t>High: embassy application + legalised diploma with sworn translation</t>
+  </si>
+  <si>
+    <t>Graduates from the listed countries who want a funded Master or PhD in English or Czech</t>
+  </si>
+  <si>
+    <t>The Czech government funds studies at public universities as part of its foreign development assistance. Programmes can be taught in English or Czech, and Czech-taught tracks include a preparatory year.</t>
+  </si>
+  <si>
+    <t>Application form | Signed declaration of the terms | Legalised copy of your diploma with sworn Czech translation | Passport copy | University admission or application proof</t>
+  </si>
+  <si>
+    <t>Competitive selection of applications received through embassies and UNESCO commissions</t>
+  </si>
+  <si>
+    <t>https://studyin.gov.cz/scholarships/scholarship-detail?id=340</t>
+  </si>
+  <si>
+    <t>Lithuanian State Scholarships for Full-Time Master Studies</t>
+  </si>
+  <si>
+    <t>Ministry of Education, Science and Sport of Lithuania</t>
+  </si>
+  <si>
+    <t>Lithuania</t>
+  </si>
+  <si>
+    <t>Monthly stipend and, for some nationalities, tuition coverage at Lithuanian universities (amounts vary by call)</t>
+  </si>
+  <si>
+    <t>May (annual call, check the yearly dates)</t>
+  </si>
+  <si>
+    <t>Citizens of countries listed in each yearly call only (past calls included Armenia, Azerbaijan, Belarus, China, Georgia, Israel, Japan, South Korea, Moldova and Ukraine). No application fee.</t>
+  </si>
+  <si>
+    <t>Medium: online application + university admission</t>
+  </si>
+  <si>
+    <t>Students from the listed countries aiming for a Master in the Baltics</t>
+  </si>
+  <si>
+    <t>Lithuania offers state scholarships for full-time Master studies to selected nationalities. Always read the current call, because eligible countries and benefits change.</t>
+  </si>
+  <si>
+    <t>Application form | Passport copy | Bachelor diploma and transcript | Motivation letter | Language proof (check the call for the exact list)</t>
+  </si>
+  <si>
+    <t>Competitive selection run by the ministry, in rounds</t>
+  </si>
+  <si>
+    <t>https://studyin.lt/scholarships/full-time-master-degree-studies/</t>
+  </si>
+  <si>
+    <t>Estonian Government Scholarship for Degree and Exchange Study</t>
+  </si>
+  <si>
+    <t>Estonian Ministry of Education and Research and Harno (Education and Youth Board)</t>
+  </si>
+  <si>
+    <t>Estonia</t>
+  </si>
+  <si>
+    <t>Monthly stipend of EUR 350 (Master) or EUR 660 (PhD). Tuition and other costs are not covered.</t>
+  </si>
+  <si>
+    <t>Sep 1 - Oct 1 (annual call)</t>
+  </si>
+  <si>
+    <t>Students from countries listed by the Ministry. You need an admission or confirmation letter from an Estonian university. Bachelor level is only for Estonian language and culture fields.</t>
+  </si>
+  <si>
+    <t>Medium: online application + admission letter</t>
+  </si>
+  <si>
+    <t>Master and PhD students who already have, or are applying for, a place at an Estonian university</t>
+  </si>
+  <si>
+    <t>A government stipend for foreign students in degree or exchange studies at Estonian universities. It supports living costs and works well together with a tuition waiver from a university.</t>
+  </si>
+  <si>
+    <t>Application form | Motivation letter | Passport or ID copy | Admission or confirmation letter from an Estonian university</t>
+  </si>
+  <si>
+    <t>Evaluated by a scholarship commission; results announced by December</t>
+  </si>
+  <si>
+    <t>https://www.harno.ee/en/scholarships-and-grants/scholarships-studying-and-working-estonia/scholarships-international</t>
+  </si>
+  <si>
+    <t>National Scholarship Programme of the Slovak Republic (NSP)</t>
+  </si>
+  <si>
+    <t>Ministry of Education, Science, Research and Sport of Slovakia (run by SAIA)</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
+  </si>
+  <si>
+    <t>Monthly stipend of EUR 620 (Master) or about EUR 1,025 (PhD) for a study or research stay of 1-2 semesters (Master) or 1-10 months (PhD)</t>
+  </si>
+  <si>
+    <t>Apr 30 (annual, for the next academic year)</t>
+  </si>
+  <si>
+    <t>Open to citizens of any country except Slovakia. Master applicants must be enrolled abroad with at least 2.5 years completed. You need an invitation letter from a Slovak host university. This is a mobility stay, not a full degree.</t>
+  </si>
+  <si>
+    <t>Medium: online application + invitation letter</t>
+  </si>
+  <si>
+    <t>Master and PhD students who want a funded exchange or research stay in Central Europe</t>
+  </si>
+  <si>
+    <t>Slovakia funds incoming study and research stays for students from any country. You arrange an invitation from a Slovak university and then apply online through SAIA.</t>
+  </si>
+  <si>
+    <t>Online application | Invitation or acceptance letter from the Slovak host institution | Study or research plan | CV | Transcript</t>
+  </si>
+  <si>
+    <t>SAIA checks formal requirements, then an expert committee selects</t>
+  </si>
+  <si>
+    <t>https://www.scholarships.sk/</t>
+  </si>
+  <si>
+    <t>Russian Government Scholarship (Quota)</t>
+  </si>
+  <si>
+    <t>Government of the Russian Federation (Rossotrudnichestvo)</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>Free tuition plus a small monthly stipend, with an optional preparatory year paid by the state</t>
+  </si>
+  <si>
+    <t>Oct - Jan (annual, dates differ by country)</t>
+  </si>
+  <si>
+    <t>Foreign citizens. Apply on the Education in Russia portal, then go through selection by the Russian embassy or Rossotrudnichestvo office in your country. Some universities set entrance tests.</t>
+  </si>
+  <si>
+    <t>High: online application + embassy selection + possible entrance test</t>
+  </si>
+  <si>
+    <t>Students who want a state-funded degree and are open to studying in Russian or English</t>
+  </si>
+  <si>
+    <t>Russia allocates a yearly quota of state-funded places to foreign students. You choose up to six universities in the portal. Check your own government travel advice before you plan.</t>
+  </si>
+  <si>
+    <t>Online application form | Photo | Passport scan with notarised translation | Education certificate and transcript | Consent form for personal data</t>
+  </si>
+  <si>
+    <t>Competitive selection in your home country, then university admission</t>
+  </si>
+  <si>
+    <t>https://education-in-russia.com/</t>
+  </si>
+  <si>
+    <t>Kemitraan Negara Berkembang (KNB) Indonesian Government Scholarship</t>
+  </si>
+  <si>
+    <t>Ministry of Higher Education, Science and Technology of Indonesia</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Tuition, monthly living allowance, settlement allowance, health insurance, round-trip airfare and an Indonesian language course</t>
+  </si>
+  <si>
+    <t>Mar (annual; 2025 call ran Mar 3-21)</t>
+  </si>
+  <si>
+    <t>Citizens of developing countries. You need a recommendation or nomination letter from the Indonesian embassy. Master degree holders cannot apply for the Master track.</t>
+  </si>
+  <si>
+    <t>High: embassy letter + medical statement + online application</t>
+  </si>
+  <si>
+    <t>Students from developing countries who want a fully funded degree in Southeast Asia</t>
+  </si>
+  <si>
+    <t>Indonesia offers about 200 awards a year through its Developing Countries Partnership scholarship. Awardees study at one of the host universities and begin with Indonesian language study.</t>
+  </si>
+  <si>
+    <t>Online application | Recommendation letter from the Indonesian embassy | Proof of citizenship | Official medical statement | Offer or invitation letter from a university | Recommendation from your employer or supervisor</t>
+  </si>
+  <si>
+    <t>Selected by the Indonesian ministry from applications received online</t>
+  </si>
+  <si>
+    <t>https://knb.kemdiktisaintek.go.id/</t>
+  </si>
+  <si>
+    <t>MBZUAI Graduate Scholarships (Abu Dhabi)</t>
+  </si>
+  <si>
+    <t>Mohamed bin Zayed University of Artificial Intelligence, funded by the UAE government</t>
+  </si>
+  <si>
+    <t>100% tuition, monthly stipend, health insurance, on-campus housing and annual return flight</t>
+  </si>
+  <si>
+    <t>Feb (annual, for the August intake)</t>
+  </si>
+  <si>
+    <t>All nationalities. Bachelor degree in computer science, engineering, mathematics or a related field for the MSc, and usually a Master degree for the PhD. The scholarship comes automatically with admission.</t>
+  </si>
+  <si>
+    <t>High: strong academic record + references + (PhD) research statement</t>
+  </si>
+  <si>
+    <t>Strong STEM graduates interested in artificial intelligence</t>
+  </si>
+  <si>
+    <t>MBZUAI is a graduate university focused only on artificial intelligence, and it funds every full-time student it admits. Programmes include machine learning, computer vision and natural language processing.</t>
+  </si>
+  <si>
+    <t>Online application | Transcripts and degree certificates | CV | Research statement (PhD) | Two recommendation letters for MSc, three for PhD | English test score</t>
+  </si>
+  <si>
+    <t>University admission decision includes the scholarship</t>
+  </si>
+  <si>
+    <t>Hamad Bin Khalifa University (HBKU) Graduate Scholarship (Qatar)</t>
+  </si>
+  <si>
+    <t>Hamad Bin Khalifa University, Education City, Doha</t>
+  </si>
+  <si>
+    <t>Tuition waiver, monthly stipend (about QAR 5,000 for Master and QAR 7,500 for PhD), housing or housing allowance, health insurance and annual return flight</t>
+  </si>
+  <si>
+    <t>Feb 1 (annual, international applicants)</t>
+  </si>
+  <si>
+    <t>Open to all nationalities. There is no separate application: you are considered for the scholarship when you apply for graduate admission. PhD applicants usually need a Master degree.</t>
+  </si>
+  <si>
+    <t>High: admission application + references + statement of purpose</t>
+  </si>
+  <si>
+    <t>Graduates interested in programmes such as public policy, data science, sustainability, law or Islamic studies</t>
+  </si>
+  <si>
+    <t>HBKU is a research university in Qatar that funds admitted graduate students at the Master and PhD level. Applications for graduate admission open around October.</t>
+  </si>
+  <si>
+    <t>Application form | Transcripts | Standardised test or English score | Two recommendation letters | Personal statement and statement of purpose | CV | Passport copy | Research proposal (if applicable)</t>
+  </si>
+  <si>
+    <t>Admission and scholarship decided together</t>
+  </si>
+  <si>
+    <t>https://www.hbku.edu.qa/</t>
+  </si>
+  <si>
+    <t>Banach NAWA Scholarship Programme (Poland)</t>
+  </si>
+  <si>
+    <t>NAWA (Polish National Agency for Academic Exchange) with the Ministry of Foreign Affairs of Poland</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Tuition-free Master at public universities, monthly scholarship of PLN 2,500, one-time mobility allowance and an optional preparatory course for Polish-taught studies</t>
+  </si>
+  <si>
+    <t>May (spring call; an autumn call also runs, dates vary)</t>
+  </si>
+  <si>
+    <t>Citizens of countries on the programme list only. Bachelor graduates or final-semester students, with no previous Master degree. You apply to NAWA and to a Polish university at the same time.</t>
+  </si>
+  <si>
+    <t>High: NAWA online application + university admission</t>
+  </si>
+  <si>
+    <t>Bachelor graduates from eligible developing countries who want a funded Master in Europe</t>
+  </si>
+  <si>
+    <t>A Polish development-cooperation scholarship for Master studies in English or Polish. The 2026 spring call closed on 8 May 2026, so prepare early for the next call.</t>
+  </si>
+  <si>
+    <t>CV | Bachelor diploma or proof of final semester | Language proof | Motivation letter | University application documents</t>
+  </si>
+  <si>
+    <t>Competitive selection by NAWA</t>
+  </si>
+  <si>
+    <t>https://nawa.gov.pl/en/students/foreign-students/the-banach-scholarship-programme</t>
+  </si>
+  <si>
+    <t>barbados-national-development-scholarship-2026</t>
+  </si>
+  <si>
+    <t>Barbados National Development Scholarship</t>
+  </si>
+  <si>
+    <t>Government of Barbados — Ministry of Education, Technological and Vocational Training</t>
+  </si>
+  <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
+    <t>United States, Canada, United Kingdom, Other accredited destinations</t>
+  </si>
+  <si>
+    <t>National development priority fields</t>
+  </si>
+  <si>
+    <t>Tuition, return airfare, book allowance and living allowance (amount depends on destination)</t>
+  </si>
+  <si>
+    <t>2026 cycle closed; official page listed 17 June 2026. Check ministry for next call.</t>
+  </si>
+  <si>
+    <t>Barbadian citizens aged 18–40 accepted by an internationally accredited university; return-to-Barbados service bond applies.</t>
+  </si>
+  <si>
+    <t>High: official application and supporting academic/acceptance documents; check current form.</t>
+  </si>
+  <si>
+    <t>Barbadian citizens pursuing priority undergraduate or postgraduate study abroad</t>
+  </si>
+  <si>
+    <t>Government scholarship for eligible Barbadian citizens at undergraduate and postgraduate levels. Award terms and priority fields are defined in the annual official notice.</t>
+  </si>
+  <si>
+    <t>Use the current ministry application form and official notice for the exact document checklist.</t>
+  </si>
+  <si>
+    <t>Subject to the ministry’s annual criteria and available awards.</t>
+  </si>
+  <si>
+    <t>Do not advertise as currently accepting applications; the 2026 deadline has passed. Recheck the official page before changing status.</t>
+  </si>
+  <si>
+    <t>https://education.gov.bb/national-development-scholarship-2026/</t>
+  </si>
+  <si>
+    <t>Barbados, Government, Undergraduate, Postgraduate</t>
+  </si>
+  <si>
+    <t>barbados-errol-walton-barrow-scholarships-2026</t>
+  </si>
+  <si>
+    <t>Errol Walton Barrow Scholarships</t>
+  </si>
+  <si>
+    <t>United States, Canada, United Kingdom</t>
+  </si>
+  <si>
+    <t>Marine Studies, Aeronautics, Culinary Arts (as listed in 2026 notice)</t>
+  </si>
+  <si>
+    <t>Tuition, return airfare and destination-based living allowance</t>
+  </si>
+  <si>
+    <t>2026 cycle closed; official notice listed 6 August 2026. Check ministry for next call.</t>
+  </si>
+  <si>
+    <t>Barbadian citizens accepted at an accredited institution; specific eligibility may depend on the award stream and school background.</t>
+  </si>
+  <si>
+    <t>High: application form and supporting documents; follow current notice.</t>
+  </si>
+  <si>
+    <t>Eligible Barbadian students in the stated fields</t>
+  </si>
+  <si>
+    <t>Scholarship scheme administered by the Barbados ministry. The 2026 notice names Marine Studies, Aeronautics and Culinary Arts for the specified award stream.</t>
+  </si>
+  <si>
+    <t>Refer to the official annual application form and notice; do not assume a fixed list across cycles.</t>
+  </si>
+  <si>
+    <t>As stated in the current ministry notice.</t>
+  </si>
+  <si>
+    <t>Keep marked Closed until a new official call is published.</t>
+  </si>
+  <si>
+    <t>https://education.gov.bb/2026-errol-walton-barrow-scholarships/</t>
+  </si>
+  <si>
+    <t>Barbados, Government, Marine Studies, Aeronautics, Culinary Arts</t>
+  </si>
+  <si>
+    <t>benin-university-allowances-2026-2027</t>
+  </si>
+  <si>
+    <t>Benin Public University Study Allowances (Allocations universitaires) 2026–2027</t>
+  </si>
+  <si>
+    <t>Direction des Bourses et Aides Universitaires (DBAU), Government of Benin</t>
+  </si>
+  <si>
+    <t>Benin</t>
+  </si>
+  <si>
+    <t>Public university programmes; specific rules set by the call</t>
+  </si>
+  <si>
+    <t>University study allowance; amount and category depend on official rules</t>
+  </si>
+  <si>
+    <t>5 February 2027 (official portal notice for 2026–2027)</t>
+  </si>
+  <si>
+    <t>Applicants seeking university allowances at Benin public universities who meet the official academic and administrative criteria; check the French-language call for eligible applicant categories.</t>
+  </si>
+  <si>
+    <t>Medium: online application through the official government scholarship service.</t>
+  </si>
+  <si>
+    <t>Students applying to public universities in Benin</t>
+  </si>
+  <si>
+    <t>The official DBAU portal announced online applications for study allowances at public universities in Benin for the 2026–2027 academic year, with a stated closing date of 5 February 2027.</t>
+  </si>
+  <si>
+    <t>Follow the official online application instructions; requirements vary by allowance category.</t>
+  </si>
+  <si>
+    <t>Government eligibility and academic criteria described in the official call.</t>
+  </si>
+  <si>
+    <t>Portal information is in French. Confirm the applicant category and required documents on the application site.</t>
+  </si>
+  <si>
+    <t>https://bourses.enseignementsuperieur.gouv.bj/</t>
+  </si>
+  <si>
+    <t>Benin, Public University, Study Allowance, 2026-2027</t>
+  </si>
+  <si>
+    <t>bhutan-rcsc-pre-service-scholarship-2026-2027</t>
+  </si>
+  <si>
+    <t>Bhutan Royal Civil Service Commission Pre-Service Scholarship</t>
+  </si>
+  <si>
+    <t>Royal Civil Service Commission (RCSC), Bhutan</t>
+  </si>
+  <si>
+    <t>Bhutan, overseas destinations as specified in call</t>
+  </si>
+  <si>
+    <t>Priority fields listed in annual announcement</t>
+  </si>
+  <si>
+    <t>Government scholarship; exact benefits and eligible courses are in the annual announcement</t>
+  </si>
+  <si>
+    <t>2026–2027 call announced in January 2026; verify whether any new round is open.</t>
+  </si>
+  <si>
+    <t>Class XII graduates meeting the RCSC’s criteria; the 2026–2027 notice referred to Class XII graduates of 2025, excluding repeaters.</t>
+  </si>
+  <si>
+    <t>Medium: online application through Bhutan Citizen Services when the call is open.</t>
+  </si>
+  <si>
+    <t>Eligible Bhutanese school-leavers seeking government-sponsored study</t>
+  </si>
+  <si>
+    <t>RCSC announced pre-service scholarship slots for the 2026–2027 academic session. Eligibility is tied to the specific annual announcement and applicant cohort.</t>
+  </si>
+  <si>
+    <t>The official portal announcement lists the required identity, academic and security-clearance documents.</t>
+  </si>
+  <si>
+    <t>According to RCSC scholarship criteria and the published call.</t>
+  </si>
+  <si>
+    <t>This is a cohort-specific call, not a permanent open application. Check RCSC for the next intake.</t>
+  </si>
+  <si>
+    <t>https://rcsc.gov.bt/2026/01/pre-service-scholarship-announcement/</t>
+  </si>
+  <si>
+    <t>Bhutan, RCSC, Government Scholarship</t>
+  </si>
+  <si>
+    <t>bhutan-kings-scholarship-2026</t>
+  </si>
+  <si>
+    <t>Bhutan King’s Scholarship</t>
+  </si>
+  <si>
+    <t>Bhutan, as specified by the annual award</t>
+  </si>
+  <si>
+    <t>Priority fields according to annual call</t>
+  </si>
+  <si>
+    <t>Government scholarship; consult official notice for award terms</t>
+  </si>
+  <si>
+    <t>2026 call announced in January 2026; verify next cycle with RCSC.</t>
+  </si>
+  <si>
+    <t>The 2026 announcement targeted Class XII graduates of 2025 who sat the BHSEC examination, excluding repeaters, and met the stated criteria.</t>
+  </si>
+  <si>
+    <t>Medium: apply through Bhutan Citizen Services when a call is open.</t>
+  </si>
+  <si>
+    <t>Eligible Bhutanese Class XII graduates</t>
+  </si>
+  <si>
+    <t>RCSC announced five King’s Scholarship slots for the 2026 academic session. Eligibility is specific to the published annual notice.</t>
+  </si>
+  <si>
+    <t>Use the current RCSC announcement and online portal checklist.</t>
+  </si>
+  <si>
+    <t>As set out in the RCSC notice.</t>
+  </si>
+  <si>
+    <t>Keep closed until a new cohort and deadline are announced.</t>
+  </si>
+  <si>
+    <t>https://rcsc.gov.bt/2026/01/kings-scholarship-announcement-3/</t>
+  </si>
+  <si>
+    <t>Bhutan, King’s Scholarship, Government</t>
+  </si>
+  <si>
+    <t>botswana-tertiary-education-students-sponsorship</t>
+  </si>
+  <si>
+    <t>Botswana Tertiary Education Students Sponsorship</t>
+  </si>
+  <si>
+    <t>Government of Botswana — Placement Division</t>
+  </si>
+  <si>
+    <t>Botswana, approved regional and overseas institutions</t>
+  </si>
+  <si>
+    <t>Bachelor, Diploma</t>
+  </si>
+  <si>
+    <t>Programmes approved under government sponsorship</t>
+  </si>
+  <si>
+    <t>Government sponsorship; coverage depends on approved programme and current rules</t>
+  </si>
+  <si>
+    <t>No verified current deadline; marked Closed until an active official call is confirmed.</t>
+  </si>
+  <si>
+    <t>Botswana citizens who are not gainfully employed; new students generally must be able to complete study before age 35. Published academic cutoffs and exceptions apply.</t>
+  </si>
+  <si>
+    <t>Medium–High: check programme approval, academic cutoff and application process.</t>
+  </si>
+  <si>
+    <t>Eligible Botswana citizens entering approved tertiary programmes</t>
+  </si>
+  <si>
+    <t>The Government of Botswana’s Placement Division administers sponsorship for local public/private tertiary institutions and approved external institutions.</t>
+  </si>
+  <si>
+    <t>Follow the current government application instructions; eligibility and evidence requirements may differ by applicant category.</t>
+  </si>
+  <si>
+    <t>Placement Division applies the official criteria, including academic results and programme/institution approval.</t>
+  </si>
+  <si>
+    <t>Do not state a fixed award value without checking the current sponsorship rules. Keep Closed until a new official call or application window is confirmed.</t>
+  </si>
+  <si>
+    <t>https://www.gov.bw/taxonomy/term/110?page=0</t>
+  </si>
+  <si>
+    <t>Botswana, Government Sponsorship, Tertiary Education</t>
+  </si>
+  <si>
+    <t>botswana-india-africa-maitri-iccr-scholarship-2026-2027</t>
+  </si>
+  <si>
+    <t>India–Africa Maitri Scholarship Scheme (ICCR) — Botswana Notice</t>
+  </si>
+  <si>
+    <t>Indian Council for Cultural Relations (ICCR); Government of Botswana notice</t>
+  </si>
+  <si>
+    <t>Africa, Asia</t>
+  </si>
+  <si>
+    <t>Programmes listed in the ICCR scholarship catalogue</t>
+  </si>
+  <si>
+    <t>ICCR scholarship benefits vary by scheme and programme; consult official call.</t>
+  </si>
+  <si>
+    <t>2026–2027 notice published by Botswana government on 2 July 2026; confirm the deadline in the linked notice.</t>
+  </si>
+  <si>
+    <t>Applicants from Botswana who meet ICCR scheme, academic, age and course requirements in the official notice.</t>
+  </si>
+  <si>
+    <t>Medium–High: online ICCR application and required academic/identity documents.</t>
+  </si>
+  <si>
+    <t>Botswana applicants interested in studying in India</t>
+  </si>
+  <si>
+    <t>The Government of Botswana published an official notice for ICCR scholarships under the India–Africa Maitri Scholarship Scheme for academic year 2026–2027.</t>
+  </si>
+  <si>
+    <t>Follow the official ICCR call and the Botswana government notice for the applicable checklist.</t>
+  </si>
+  <si>
+    <t>ICCR and the applicable nomination/application process.</t>
+  </si>
+  <si>
+    <t>Use the linked official notice to confirm deadline, eligible courses and exact funding before publishing an active status.</t>
+  </si>
+  <si>
+    <t>https://www.gov.bw/node/1415</t>
+  </si>
+  <si>
+    <t>Botswana, India, ICCR, International Scholarship</t>
+  </si>
+  <si>
+    <t>brunei-government-scholarship-foreign-students-2026-2027</t>
+  </si>
+  <si>
+    <t>Government of Brunei Darussalam Scholarship for Foreign Students (BDGS) 2026–2027</t>
+  </si>
+  <si>
+    <t>Ministry of Foreign Affairs, Brunei Darussalam</t>
+  </si>
+  <si>
+    <t>Brunei Darussalam</t>
+  </si>
+  <si>
+    <t>Diploma, Bachelor, Master</t>
+  </si>
+  <si>
+    <t>Participating programmes at designated institutions</t>
+  </si>
+  <si>
+    <t>Government scholarship; consult the official 2026–2027 terms for tuition, allowances, travel and other benefits.</t>
+  </si>
+  <si>
+    <t>2026–2027 cycle announcement published; check official notice for deadline and current status.</t>
+  </si>
+  <si>
+    <t>Foreign students who satisfy the nationality, age, academic, health and language requirements in the official BDGS call. Eligible nationalities and programme restrictions must be checked.</t>
+  </si>
+  <si>
+    <t>Medium–High: online application and academic/identity documentation.</t>
+  </si>
+  <si>
+    <t>International students seeking study at participating institutions in Brunei</t>
+  </si>
+  <si>
+    <t>Brunei’s Ministry of Foreign Affairs lists the Government of Brunei Darussalam Scholarship for Foreign Students for the 2026–2027 academic session.</t>
+  </si>
+  <si>
+    <t>Follow the current official application form and call; do not rely on third-party summaries for the document checklist.</t>
+  </si>
+  <si>
+    <t>Government and host-institution assessment under the annual scheme rules.</t>
+  </si>
+  <si>
+    <t>Do not assume every nationality or course is eligible. Confirm the current deadline on the official page.</t>
+  </si>
+  <si>
+    <t>https://www.mfa.gov.bn/Pages/online-bdgs.aspx</t>
+  </si>
+  <si>
+    <t>Brunei, International Students, Government Scholarship, BDGS</t>
+  </si>
+  <si>
+    <t>bosnia-herzegovina-fulbright-foreign-student-program</t>
+  </si>
+  <si>
+    <t>Fulbright Foreign Student Program — Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>U.S. Department of State; U.S. Embassy in Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>Europe, North America</t>
+  </si>
+  <si>
+    <t>Master, PhD, Research</t>
+  </si>
+  <si>
+    <t>Various academic fields; subject restrictions may apply by cycle</t>
+  </si>
+  <si>
+    <t>Funding and eligible costs depend on the current country-specific Fulbright call.</t>
+  </si>
+  <si>
+    <t>2026 call dates have passed or current cycle not confirmed; check official source for next call.</t>
+  </si>
+  <si>
+    <t>Applicants from Bosnia and Herzegovina meeting the country-specific academic, language and professional requirements.</t>
+  </si>
+  <si>
+    <t>High: competitive application, academic records, essays and references as required by the call.</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina applicants pursuing graduate study or research in the United States</t>
+  </si>
+  <si>
+    <t>The Bosnia and Herzegovina authorities reported a 2026 U.S. Government scholarship call including the Fulbright Foreign Student Program. Availability and dates are country-cycle specific.</t>
+  </si>
+  <si>
+    <t>Use the official U.S. Embassy call for the current document checklist.</t>
+  </si>
+  <si>
+    <t>Competitive country-specific selection and review.</t>
+  </si>
+  <si>
+    <t>Link directly to the country-specific embassy call rather than promising a universal deadline or award package. Keep Closed until a new official call or application window is confirmed.</t>
+  </si>
+  <si>
+    <t>https://fmks.gov.ba/en/open-calls-announced-for-prestigious-u-s-government-scholarship-programs/</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina, Fulbright, United States, Graduate Study</t>
+  </si>
+  <si>
+    <t>bosnia-herzegovina-chevening-scholarship</t>
+  </si>
+  <si>
+    <t>Chevening Scholarship — Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>All fields, subject to course and programme rules</t>
+  </si>
+  <si>
+    <t>Typically covers eligible tuition, travel and living costs under the current Chevening terms.</t>
+  </si>
+  <si>
+    <t>Applicants who meet Chevening’s global criteria and Bosnia and Herzegovina country-specific rules, including work experience and eligible course requirements.</t>
+  </si>
+  <si>
+    <t>High: competitive application, leadership examples, course choices and references.</t>
+  </si>
+  <si>
+    <t>Early- and mid-career professionals from Bosnia and Herzegovina seeking a UK master’s degree</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina’s Ministry of Civil Affairs published information on UK-funded scholarship opportunities for its citizens, including Chevening.</t>
+  </si>
+  <si>
+    <t>Follow the current Chevening application guidance and country page.</t>
+  </si>
+  <si>
+    <t>Competitive application review under current Chevening rules.</t>
+  </si>
+  <si>
+    <t>Verify country availability and the opening/closing dates on Chevening’s official country page before marking the call open. Keep Closed until a new official call or application window is confirmed.</t>
+  </si>
+  <si>
+    <t>https://mcp.gov.ba/bs/portal/objava/informacija-o-stipendijama-ujedinjenog-kraljevstva-koje-su-dostupne-studentima-iz-bosne-i-hercegovine-1772005076004</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina, Chevening, United Kingdom, Master</t>
+  </si>
+  <si>
+    <t>burkina-faso-government-scholarships-study-aid</t>
+  </si>
+  <si>
+    <t>Burkina Faso Government Scholarships, Study Grants and Training Aid</t>
+  </si>
+  <si>
+    <t>Government of Burkina Faso — Ministry responsible for higher education</t>
+  </si>
+  <si>
+    <t>Burkina Faso and destinations specified in official calls</t>
+  </si>
+  <si>
+    <t>Bachelor, Master, PhD, Research</t>
+  </si>
+  <si>
+    <t>Fields prioritized under current government rules</t>
+  </si>
+  <si>
+    <t>Varies</t>
+  </si>
+  <si>
+    <t>Scholarships, study grants, loans or training aid according to the relevant scheme</t>
+  </si>
+  <si>
+    <t>Variable; check the official public-service page and annual calls.</t>
+  </si>
+  <si>
+    <t>Applicants meeting the current academic average, age and complete-application requirements; rules vary by award category.</t>
+  </si>
+  <si>
+    <t>Medium–High: follow the specific scheme and submit the required dossier.</t>
+  </si>
+  <si>
+    <t>Students, researchers and eligible workers seeking government study or training support</t>
+  </si>
+  <si>
+    <t>Burkina Faso’s official public-service portal describes the procedure for awarding and renewing scholarships, study loans and aid, including study and training support.</t>
+  </si>
+  <si>
+    <t>The exact checklist depends on the current scholarship or training-aid procedure.</t>
+  </si>
+  <si>
+    <t>Under current national rules and annual quotas; consult the latest decree/call.</t>
+  </si>
+  <si>
+    <t>French-language government resource. Avoid stating that all categories are open to foreign applicants.</t>
+  </si>
+  <si>
+    <t>https://service-public.gov.bf/thematiques/education-recherche/octroi-et-renouvellement-des-bourses-d-etudes</t>
+  </si>
+  <si>
+    <t>Burkina Faso, Government, Study Grant, Training</t>
+  </si>
+  <si>
+    <t>burkina-faso-national-internship-portal</t>
+  </si>
+  <si>
+    <t>Burkina Faso National Internship Opportunities Portal</t>
+  </si>
+  <si>
+    <t>Ministry of Sports, Youth and Employment — Burkina Faso</t>
+  </si>
+  <si>
+    <t>Burkina Faso</t>
+  </si>
+  <si>
+    <t>Secondary, Diploma, Bachelor</t>
+  </si>
+  <si>
+    <t>Public administration, trades, construction, services, agriculture and other listed placements</t>
+  </si>
+  <si>
+    <t>Placement details, duration and any allowance are shown in individual listings.</t>
+  </si>
+  <si>
+    <t>Varies by vacancy; individual offers display start and end dates.</t>
+  </si>
+  <si>
+    <t>Applicants meeting the education, skills and location requirements in each published internship listing.</t>
+  </si>
+  <si>
+    <t>Low–Medium: register and apply to a specific listing through the official portal.</t>
+  </si>
+  <si>
+    <t>Young people seeking practical work experience in Burkina Faso</t>
+  </si>
+  <si>
+    <t>The Ministry’s national platform publishes internship opportunities and training placements through the relevant employment directorates.</t>
+  </si>
+  <si>
+    <t>Follow the requirements of each listing; CV and evidence of qualifications may be requested.</t>
+  </si>
+  <si>
+    <t>Employer or responsible directorate selection based on each listing.</t>
+  </si>
+  <si>
+    <t>This is a live listings portal, not one single internship award. Check vacancy dates before sharing individual placements.</t>
+  </si>
+  <si>
+    <t>https://stage.jeunesse.gov.bf/</t>
+  </si>
+  <si>
+    <t>Burkina Faso, Internship, Youth Employment, Local Opportunities</t>
+  </si>
+  <si>
+    <t>erasmus-mundus-joint-masters-global-scholarship</t>
+  </si>
+  <si>
+    <t>Erasmus Mundus Joint Masters Scholarships</t>
+  </si>
+  <si>
+    <t>European Union — Erasmus+; participating university consortia</t>
+  </si>
+  <si>
+    <t>Europe, Worldwide</t>
+  </si>
+  <si>
+    <t>Participating European and partner countries</t>
+  </si>
+  <si>
+    <t>Varies by joint master programme</t>
+  </si>
+  <si>
+    <t>Selected scholarships cover participation costs and contribute to travel, visa and living expenses.</t>
+  </si>
+  <si>
+    <t>Programme-specific; many courses accept applications between October and January for the following academic year.</t>
+  </si>
+  <si>
+    <t>Students worldwide may apply, subject to the chosen master’s admission criteria and any country-specific restrictions.</t>
+  </si>
+  <si>
+    <t>High: apply directly to each consortium; documents and selection criteria vary.</t>
+  </si>
+  <si>
+    <t>International applicants seeking a joint master’s degree across multiple universities</t>
+  </si>
+  <si>
+    <t>Erasmus Mundus Joint Masters are integrated programmes delivered by international university consortia. Selected programmes offer competitive scholarships to applicants from around the world.</t>
+  </si>
+  <si>
+    <t>Usually academic transcripts and degree certificate, CV, motivation statement, language evidence and references; check the individual programme.</t>
+  </si>
+  <si>
+    <t>Each consortium runs its own admissions and scholarship selection.</t>
+  </si>
+  <si>
+    <t>Use the official catalogue and link to the exact programme. Do not use one universal deadline for all courses.</t>
+  </si>
+  <si>
+    <t>https://erasmus-plus.ec.europa.eu/opportunities/individuals/students/erasmus-mundus-joint-masters</t>
+  </si>
+  <si>
+    <t>International, Europe, Master, Full Scholarship, Erasmus Mundus</t>
+  </si>
+  <si>
+    <t>unesco-internship-programme-global</t>
+  </si>
+  <si>
+    <t>UNESCO Internship Programme</t>
+  </si>
+  <si>
+    <t>United Nations Educational, Scientific and Cultural Organization (UNESCO)</t>
+  </si>
+  <si>
+    <t>Worldwide</t>
+  </si>
+  <si>
+    <t>UNESCO offices and participating locations</t>
+  </si>
+  <si>
+    <t>Bachelor, Master, PhD, Technical/Vocational</t>
+  </si>
+  <si>
+    <t>Education, culture, science, communication, administration and other advertised areas</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Learning placement; applicants should check the official terms for insurance, travel and living costs.</t>
+  </si>
+  <si>
+    <t>No single deadline; vacancies are posted periodically on the official careers site.</t>
+  </si>
+  <si>
+    <t>Generally age 20 or older; applicants must meet the enrolment or recent-graduate criteria in UNESCO’s current internship rules.</t>
+  </si>
+  <si>
+    <t>Medium–High: apply to a posted opening and provide the required application materials.</t>
+  </si>
+  <si>
+    <t>Students and recent graduates interested in international development, culture, education or science</t>
+  </si>
+  <si>
+    <t>UNESCO’s internship programme offers practical learning assignments to eligible students and recent graduates. Eligibility and openings are governed by current official rules.</t>
+  </si>
+  <si>
+    <t>Apply through the official careers portal; prepare CV and any supporting documents requested by the vacancy.</t>
+  </si>
+  <si>
+    <t>Vacancy-specific competitive review.</t>
+  </si>
+  <si>
+    <t>Confirm the exact opening and whether costs are covered; do not describe it as a paid internship unless the official posting says so.</t>
+  </si>
+  <si>
+    <t>https://careers.unesco.org/content/Internship-Programme/</t>
+  </si>
+  <si>
+    <t>International, UNESCO, Internship, Unpaid, Students</t>
+  </si>
+  <si>
+    <t>united-nations-secretariat-internship-global</t>
+  </si>
+  <si>
+    <t>United Nations Secretariat Internship Programme</t>
+  </si>
+  <si>
+    <t>United Nations Secretariat</t>
+  </si>
+  <si>
+    <t>United Nations duty stations as advertised</t>
+  </si>
+  <si>
+    <t>Varies by vacancy: policy, communications, economics, law, administration, languages and more</t>
+  </si>
+  <si>
+    <t>Internship experience; the Secretariat internship programme is generally unpaid and costs are normally the intern’s responsibility.</t>
+  </si>
+  <si>
+    <t>No single deadline; apply to individual internship vacancies on UN Careers.</t>
+  </si>
+  <si>
+    <t>Generally enrolled in the final year of a first university degree, enrolled in a graduate programme, or graduated within the period stated in the vacancy. Language and other requirements vary.</t>
+  </si>
+  <si>
+    <t>Medium–High: online profile, application/cover letter and vacancy-specific information.</t>
+  </si>
+  <si>
+    <t>University students and recent graduates seeking UN experience</t>
+  </si>
+  <si>
+    <t>The UN Secretariat advertises internships through UN Careers. Applicants must meet the eligibility conditions in each vacancy; internship terms and location are specified in the posting.</t>
+  </si>
+  <si>
+    <t>Typically CV/profile and cover letter; follow the application instructions in the individual vacancy.</t>
+  </si>
+  <si>
+    <t>Vacancy-specific screening and selection.</t>
+  </si>
+  <si>
+    <t>Do not imply that the UN internship is paid. Check each vacancy for country, language, duration and cost conditions.</t>
+  </si>
+  <si>
+    <t>https://careers.un.org/internship?language=en</t>
+  </si>
+  <si>
+    <t>International, United Nations, Internship, Unpaid, Students</t>
+  </si>
+  <si>
+    <t>benin-public-university-allowances-2026-2027</t>
+  </si>
+  <si>
+    <t>Benin Public University Study Scholarships and Allowances 2026–2027</t>
+  </si>
+  <si>
+    <t>Direction des Bourses et Aides Universitaires (DBAU), Ministry of Higher Education and Scientific Research, Benin</t>
+  </si>
+  <si>
+    <t>Undergraduate, Master, Doctoral (check current call)</t>
+  </si>
+  <si>
+    <t>Public university programmes; subject to official award rules</t>
+  </si>
+  <si>
+    <t>Partial / varies by award category</t>
+  </si>
+  <si>
+    <t>Government university study allowance or scholarship; amount depends on award category</t>
+  </si>
+  <si>
+    <t>Applicants seeking university study at public universities in Benin; individual award criteria apply</t>
+  </si>
+  <si>
+    <t>Medium: online application and supporting documents</t>
+  </si>
+  <si>
+    <t>DBAU has opened applications for university study allowances at public universities for the 2026–2027 academic year. The portal also lists bilateral scholarship calls with separate requirements.</t>
+  </si>
+  <si>
+    <t>Follow the current online application instructions.</t>
+  </si>
+  <si>
+    <t>Selection managed by DBAU and the National Commission for University Scholarships and Assistance, subject to eligibility and available funding.</t>
+  </si>
+  <si>
+    <t>Verify the deadline and award category on the official portal before applying. Do not describe all allowances as full scholarships.</t>
+  </si>
+  <si>
+    <t>Benin; government scholarship; university allowance; 2026-2027</t>
+  </si>
+  <si>
+    <t>belize-nich-archaeology-cultural-heritage-internship</t>
+  </si>
+  <si>
+    <t>National Institute of Culture and History Internship — Archaeology and Heritage</t>
+  </si>
+  <si>
+    <t>National Institute of Culture and History (NICH), Belize</t>
+  </si>
+  <si>
+    <t>Central America</t>
+  </si>
+  <si>
+    <t>Belize</t>
+  </si>
+  <si>
+    <t>Student placements; confirm with NICH</t>
+  </si>
+  <si>
+    <t>Archaeology; cultural heritage; research; exploration; archaeological monitoring</t>
+  </si>
+  <si>
+    <t>Not stated</t>
+  </si>
+  <si>
+    <t>Placement; stipend and duration not stated</t>
+  </si>
+  <si>
+    <t>No general deadline published</t>
+  </si>
+  <si>
+    <t>Applicants must complete NICH internship documentation; under-18 applicants are limited to office duties according to the official page</t>
+  </si>
+  <si>
+    <t>Medium: submit documentation and coordinate with NICH</t>
+  </si>
+  <si>
+    <t>Students interested in archaeology, research and Belizean heritage</t>
+  </si>
+  <si>
+    <t>NICH provides internship documentation for placements related to archaeology, research, exploration and monitoring archaeological features. Availability, stipend and intake dates must be confirmed directly.</t>
+  </si>
+  <si>
+    <t>NICH internship documentation form and additional documents requested by NICH.</t>
+  </si>
+  <si>
+    <t>Placement availability and duties confirmed by NICH.</t>
+  </si>
+  <si>
+    <t>List as a placement pathway, not a guaranteed paid internship. Confirm dates, supervision, insurance and travel costs.</t>
+  </si>
+  <si>
+    <t>https://nichbelize.org/internship-documentation-form/</t>
+  </si>
+  <si>
+    <t>Belize; internship; archaeology; heritage; research</t>
+  </si>
+  <si>
+    <t>Barbados National Development Scholarship 2026</t>
+  </si>
+  <si>
+    <t>Government of Barbados, Ministry of Education Transformation</t>
+  </si>
+  <si>
+    <t>International; eligible accredited universities</t>
+  </si>
+  <si>
+    <t>Undergraduate, Postgraduate</t>
+  </si>
+  <si>
+    <t>Climate change; renewable energy; biotechnology; AI; robotics; cybersecurity; data science; health and other listed priority fields</t>
+  </si>
+  <si>
+    <t>Full; according to official award terms</t>
+  </si>
+  <si>
+    <t>Tuition; return economy airfare; book allowance; eligible clothing allowance; destination-based living allowance</t>
+  </si>
+  <si>
+    <t>17 June 2026; closed</t>
+  </si>
+  <si>
+    <t>Barbadian citizens aged 18–40 with admission to an internationally accredited university; other call conditions apply</t>
+  </si>
+  <si>
+    <t>High: admission evidence, academic records and official application</t>
+  </si>
+  <si>
+    <t>Barbadian students admitted to accredited programmes in priority fields</t>
+  </si>
+  <si>
+    <t>The Government of Barbados offers National Development Scholarships at undergraduate and postgraduate levels in designated priority fields. The 2026 application deadline has passed.</t>
+  </si>
+  <si>
+    <t>Official application form and supporting academic, citizenship and admission evidence as required by the Ministry.</t>
+  </si>
+  <si>
+    <t>Government review against citizenship, age, admission and priority-field criteria. Award holders must comply with the return-to-Barbados service bond.</t>
+  </si>
+  <si>
+    <t>Do not mark the 2026 round Open. Monitor the Ministry for the next call and verify award terms.</t>
+  </si>
+  <si>
+    <t>Barbados; government scholarship; undergraduate; postgraduate; closed 2026</t>
+  </si>
+  <si>
+    <t>barbados-errol-walton-barrow-scholarship-2026</t>
+  </si>
+  <si>
+    <t>Errol Walton Barrow Scholarships 2026</t>
+  </si>
+  <si>
+    <t>International; eligible institutions</t>
+  </si>
+  <si>
+    <t>Marine Studies; Aeronautics; Culinary Arts</t>
+  </si>
+  <si>
+    <t>Tuition; return economy airfare; annual living allowance according to destination</t>
+  </si>
+  <si>
+    <t>6 August 2026; closed</t>
+  </si>
+  <si>
+    <t>Barbadian citizens meeting the specified school and course requirements; admission to an accredited institution required</t>
+  </si>
+  <si>
+    <t>High: university acceptance and Ministry application requirements</t>
+  </si>
+  <si>
+    <t>Eligible Barbadian students pursuing marine studies, aeronautics or culinary arts</t>
+  </si>
+  <si>
+    <t>The Errol Walton Barrow Scholarships support eligible Barbadian students in specified fields. The 2026 call is closed.</t>
+  </si>
+  <si>
+    <t>Official scholarship application and supporting academic, citizenship and university-admission evidence.</t>
+  </si>
+  <si>
+    <t>Ministry review against citizenship, school and field requirements; return-to-Barbados service bond applies.</t>
+  </si>
+  <si>
+    <t>Use the latest Ministry notice for future dates. Confirm the eligible-school list and exact award conditions.</t>
+  </si>
+  <si>
+    <t>Barbados; scholarship; marine studies; aeronautics; culinary arts; closed 2026</t>
+  </si>
+  <si>
+    <t>belize-stipendium-hungaricum-2026-2027</t>
+  </si>
+  <si>
+    <t>Stipendium Hungaricum Scholarship Programme 2026–2027 — Belize Call</t>
+  </si>
+  <si>
+    <t>Government of Hungary / Tempus Public Foundation; announced by Belize Ministry of Education, Culture, Science and Technology</t>
+  </si>
+  <si>
+    <t>Undergraduate, Master, Doctoral; subject to Belize call</t>
+  </si>
+  <si>
+    <t>Eligible programmes in the official programme catalogue</t>
+  </si>
+  <si>
+    <t>Programme-defined</t>
+  </si>
+  <si>
+    <t>Tuition exemption and programme-defined stipend, accommodation contribution and medical insurance</t>
+  </si>
+  <si>
+    <t>2026–2027 call; verify exact dates in the official announcement</t>
+  </si>
+  <si>
+    <t>Belizean applicants meeting the Belize-specific nomination and Hungarian programme requirements</t>
+  </si>
+  <si>
+    <t>High: programme application and any required national nomination</t>
+  </si>
+  <si>
+    <t>Belizean students seeking degree study in Hungary</t>
+  </si>
+  <si>
+    <t>Belize's Ministry of Education published a call for the Stipendium Hungaricum programme for 2026–2027. Use the country-specific call to verify levels, nomination rules and deadlines.</t>
+  </si>
+  <si>
+    <t>Documents specified by the Belize call and selected programme.</t>
+  </si>
+  <si>
+    <t>National nomination where required, followed by university and scholarship selection.</t>
+  </si>
+  <si>
+    <t>Confirm whether a new 2027–2028 call has been published before changing the status.</t>
+  </si>
+  <si>
+    <t>https://www.moecst.gov.bz/call-for-applications-for-stipendium-hungaricum-programme-for-2026-2027/</t>
+  </si>
+  <si>
+    <t>Belize; Hungary; Stipendium Hungaricum; 2026-2027</t>
+  </si>
+  <si>
+    <t>burundi-scholarship-announcements-2026-27</t>
+  </si>
+  <si>
+    <t>Burundi Government Scholarship Announcements 2026–2027</t>
+  </si>
+  <si>
+    <t>Burundi Ministry of Foreign Affairs</t>
+  </si>
+  <si>
+    <t>To be confirmed</t>
+  </si>
+  <si>
+    <t>Deadline not confirmed; check official announcement</t>
+  </si>
+  <si>
+    <t>Eligibility, nationality, destination and academic requirements must be confirmed from the individual official scholarship notice.</t>
+  </si>
+  <si>
+    <t>Medium–High</t>
+  </si>
+  <si>
+    <t>Burundian students seeking government-supported study opportunities</t>
+  </si>
+  <si>
+    <t>Official announcement of scholarship opportunities for the 2026–2027 academic year. Verify the individual award conditions, application process and deadline before publishing it as an active opportunity.</t>
+  </si>
+  <si>
+    <t>As specified in the official notice</t>
+  </si>
+  <si>
+    <t>Confirm that applications are still accepted and identify the specific scholarship before marking this record Open.</t>
+  </si>
+  <si>
+    <t>https://www.mae.gov.bi/2026/02/20/offres-des-bourses-detudes-pour-lannee-academique-2026-2027/</t>
+  </si>
+  <si>
+    <t>cabo-verde-scholarship-brazil-2026</t>
+  </si>
+  <si>
+    <t>State Scholarships for Higher Education in Brazil 2026–2027</t>
+  </si>
+  <si>
+    <t>Government of Cabo Verde</t>
+  </si>
+  <si>
+    <t>Undergraduate; Integrated Master</t>
+  </si>
+  <si>
+    <t>Deadline not confirmed; consult the official notice</t>
+  </si>
+  <si>
+    <t>Cabo Verdean nationals enrolled in eligible undergraduate or integrated master's programmes for the continuation-of-study call; verify all conditions in the official announcement.</t>
+  </si>
+  <si>
+    <t>Cabo Verdean students seeking to continue higher education in Brazil</t>
+  </si>
+  <si>
+    <t>Official scholarship notice relating to higher education in Brazil for the 2026–2027 academic year. Confirm eligibility, funding coverage and whether applications remain open before publication.</t>
+  </si>
+  <si>
+    <t>Do not describe this as a fully funded scholarship until the award terms have been confirmed.</t>
+  </si>
+  <si>
+    <t>https://minedu.gov.cv/media/manuais/2026/03/18/Edital_Bolsa_Brasil_2026_1.pdf</t>
+  </si>
+  <si>
+    <t>colombia-icetex-labour-internship-fund-2026</t>
+  </si>
+  <si>
+    <t>ICETEX–Ministry of Labour Internship Support Programme</t>
+  </si>
+  <si>
+    <t>ICETEX and Colombia's Ministry of Labour</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Undergraduate students</t>
+  </si>
+  <si>
+    <t>Work placements; subject to programme conditions</t>
+  </si>
+  <si>
+    <t>Support for eligible internships; confirm the exact benefits in the official call</t>
+  </si>
+  <si>
+    <t>2026 call deadlines have passed according to the previously identified listings</t>
+  </si>
+  <si>
+    <t>Eligibility depends on the specific call and participating educational institutions or certified education secretariats. Intended for eligible students undertaking qualifying work placements in Colombia.</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Colombian students completing eligible professional or academic internships</t>
+  </si>
+  <si>
+    <t>Programme supporting eligible labour internships in Colombia. The identified 2026 application period has passed; monitor ICETEX for a new call and confirm the programme's current terms.</t>
+  </si>
+  <si>
+    <t>As specified in the official call</t>
+  </si>
+  <si>
+    <t>Do not advertise the 2026 call as accepting applications.</t>
+  </si>
+  <si>
+    <t>https://web.icetex.gov.co/-/fondo-programa-de-practicas-laborales-ministerio-del-trabajo</t>
+  </si>
+  <si>
+    <t>comoros-scholarships-morocco</t>
+  </si>
+  <si>
+    <t>Scholarships for Study in Morocco</t>
+  </si>
+  <si>
+    <t>Comoros Ministry of National Education</t>
+  </si>
+  <si>
+    <t>Indian Ocean</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>2026 application deadline and current status must be confirmed</t>
+  </si>
+  <si>
+    <t>Comorian applicants meeting the academic, nationality and documentation requirements specified in the official scholarship announcement.</t>
+  </si>
+  <si>
+    <t>Comorian students seeking higher education in Morocco</t>
+  </si>
+  <si>
+    <t>Official announcement concerning applications for scholarships to study in Morocco. Verify the academic year, eligible degree levels, funding coverage and deadline before listing it as open.</t>
+  </si>
+  <si>
+    <t>Check whether the registration period is still open before publishing an application invitation.</t>
+  </si>
+  <si>
+    <t>https://mineducomores.gouv.km/annonce-relative-a-linscription-aux-bourses-detudes-au-maroc/</t>
+  </si>
+  <si>
+    <t>croatia-government-bilateral-scholarships-2026-27</t>
+  </si>
+  <si>
+    <t>Croatian Government Bilateral Scholarships 2026–2027</t>
+  </si>
+  <si>
+    <t>Croatian Ministry of Science, Education and Youth; Agency for Mobility and EU Programmes</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Undergraduate; Master; PhD; Research</t>
+  </si>
+  <si>
+    <t>Study; academic exchange; research</t>
+  </si>
+  <si>
+    <t>Depends on the bilateral agreement and award terms</t>
+  </si>
+  <si>
+    <t>Foreign students, university teachers, scientists and researchers from countries covered by the relevant bilateral agreements; eligibility depends on nationality and the specific call.</t>
+  </si>
+  <si>
+    <t>Eligible international students, researchers and university teachers</t>
+  </si>
+  <si>
+    <t>Annual bilateral scholarship programme supporting eligible international study, academic exchange and research in Croatia. The 2026–2027 call closed on 10 April 2026. Check for a subsequent call before inviting applications.</t>
+  </si>
+  <si>
+    <t>Do not imply that citizens of all 11 countries are eligible; check the bilateral agreement for each nationality.</t>
+  </si>
+  <si>
+    <t>https://mzom.gov.hr/print.aspx?id=7588&amp;url=print</t>
+  </si>
+  <si>
+    <t>cyprus-state-scholarships-2025-26</t>
+  </si>
+  <si>
+    <t>Cyprus State Scholarship Scheme 2025–2026</t>
+  </si>
+  <si>
+    <t>Cyprus State Scholarship Foundation</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>Cyprus and eligible overseas destinations, depending on scheme</t>
+  </si>
+  <si>
+    <t>Undergraduate; Master; PhD</t>
+  </si>
+  <si>
+    <t>Various fields, subject to the scheme</t>
+  </si>
+  <si>
+    <t>Depends on the award and applicable scheme rules</t>
+  </si>
+  <si>
+    <t>The 2025–2026 general application window has closed. Nationality, residency, study level and programme requirements depend on the specific scheme.</t>
+  </si>
+  <si>
+    <t>Applicants eligible for Cyprus state scholarship awards</t>
+  </si>
+  <si>
+    <t>State scholarship programme administered through Cyprus's official scholarship framework. The previously identified 2025–2026 general application deadline was 8 April 2026. Check for a newer call and its eligibility conditions.</t>
+  </si>
+  <si>
+    <t>As specified in the official scheme</t>
+  </si>
+  <si>
+    <t>Do not reuse the expired deadline for a later award or claim that every international applicant qualifies.</t>
+  </si>
+  <si>
+    <t>https://www.gov.cy/en/service/apply-for-a-state-scholarship-for-studies-2/</t>
+  </si>
+  <si>
+    <t>dominica-cuba-government-scholarship-2025</t>
+  </si>
+  <si>
+    <t>Government of Cuba Scholarship Programme — Dominica Call</t>
+  </si>
+  <si>
+    <t>Government of Dominica; Ministry of Education, Human Resource Planning, Vocational Training and National Excellence</t>
+  </si>
+  <si>
+    <t>Cuba</t>
+  </si>
+  <si>
+    <t>Undergraduate</t>
+  </si>
+  <si>
+    <t>Subjects and programmes specified in the official call</t>
+  </si>
+  <si>
+    <t>Full; airfare not included</t>
+  </si>
+  <si>
+    <t>Varies by award</t>
+  </si>
+  <si>
+    <t>2025 call; closed</t>
+  </si>
+  <si>
+    <t>Applicants meeting the Dominica Ministry's academic, age and programme requirements</t>
+  </si>
+  <si>
+    <t>Medium: obtain the prescribed form and supporting documents</t>
+  </si>
+  <si>
+    <t>Eligible students from Dominica seeking undergraduate study in Cuba</t>
+  </si>
+  <si>
+    <t>The Government of Dominica publishes bilateral scholarship opportunities, including the Government of Cuba Scholarship Programme. This record refers to the 2025 call, not a confirmed current intake.</t>
+  </si>
+  <si>
+    <t>Ministry application form and supporting academic documents; confirm the exact list with the Ministry</t>
+  </si>
+  <si>
+    <t>Selection and award conditions determined by the Ministry and partner-country programme</t>
+  </si>
+  <si>
+    <t>Monitor the government portal for a new call. Do not reuse the 2025 deadline or assume the next award has identical conditions.</t>
+  </si>
+  <si>
+    <t>https://education.gov.dm/index.php/services/scholarships</t>
+  </si>
+  <si>
+    <t>Dominica; Cuba; government scholarship; closed</t>
+  </si>
+  <si>
+    <t>dominican-republic-mescyt-international-scholarships-2026</t>
+  </si>
+  <si>
+    <t>MESCyT International Scholarships 2026</t>
+  </si>
+  <si>
+    <t>Ministry of Higher Education, Science and Technology (MESCyT), Dominican Republic</t>
+  </si>
+  <si>
+    <t>Multiple international destinations</t>
+  </si>
+  <si>
+    <t>Undergraduate, Postgraduate; depends on published offer</t>
+  </si>
+  <si>
+    <t>Fields specified in each annual call</t>
+  </si>
+  <si>
+    <t>Varies by programme</t>
+  </si>
+  <si>
+    <t>Varies by host country and programme</t>
+  </si>
+  <si>
+    <t>2026 call; check official portal for any subsequent round</t>
+  </si>
+  <si>
+    <t>Dominican citizens meeting the applicable residency, academic performance, language and programme conditions</t>
+  </si>
+  <si>
+    <t>High: online application and academic documentation</t>
+  </si>
+  <si>
+    <t>Dominican students seeking eligible international degree programmes</t>
+  </si>
+  <si>
+    <t>MESCyT coordinates international scholarship offers with partner governments and institutions. Each offer has its own eligible fields, destination, requirements and deadline.</t>
+  </si>
+  <si>
+    <t>Academic transcripts; degree certificates where applicable; identity and passport documents; CV; language evidence and statement of purpose as required</t>
+  </si>
+  <si>
+    <t>Selection by the relevant scholarship provider and/or MESCyT process, as specified in the call</t>
+  </si>
+  <si>
+    <t>Do not advertise as open to all nationalities. Confirm the individual award and its application window.</t>
+  </si>
+  <si>
+    <t>https://mescyt.gob.do/becas/internacionales/</t>
+  </si>
+  <si>
+    <t>Dominican Republic; MESCyT; international scholarship; closed 2026</t>
+  </si>
+  <si>
+    <t>ecuador-jovenes-nuevo-ecuador-scholarship-2026</t>
+  </si>
+  <si>
+    <t>Jóvenes del Nuevo Ecuador National Scholarship 2026</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Superior, Ciencia, Tecnología e Innovación (SENESCYT), Ecuador</t>
+  </si>
+  <si>
+    <t>South America</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Technical, Technological, Undergraduate degree</t>
+  </si>
+  <si>
+    <t>Eligible third-level programmes at public or private Ecuadorian higher-education institutions</t>
+  </si>
+  <si>
+    <t>USD 828.97 one-time maintenance support for one academic period</t>
+  </si>
+  <si>
+    <t>28 June 2026; closed</t>
+  </si>
+  <si>
+    <t>Ecuadorian applicants aged 18–29 who meet citizenship-rights, current-enrolment and other official programme conditions</t>
+  </si>
+  <si>
+    <t>Medium: online application and proof of enrolment</t>
+  </si>
+  <si>
+    <t>Eligible Ecuadorian students who need maintenance support while studying</t>
+  </si>
+  <si>
+    <t>The 2026 programme provided a one-time partial maintenance grant to qualifying students enrolled in eligible third-level studies in Ecuador. The application deadline has passed.</t>
+  </si>
+  <si>
+    <t>Current enrolment certificate and documents required by the official programme guidelines</t>
+  </si>
+  <si>
+    <t>Eligibility screening and award assessment under SENESCYT rules</t>
+  </si>
+  <si>
+    <t>Keep the record closed until a new call is announced. This is a one-time maintenance grant, not a full tuition scholarship.</t>
+  </si>
+  <si>
+    <t>https://siau.senescyt.gob.ec/programa-de-becas-nacionales-jovenes-del-nuevo-ecuador-2026/</t>
+  </si>
+  <si>
+    <t>Ecuador; SENESCYT; maintenance grant; closed 2026</t>
+  </si>
+  <si>
+    <t>fiji-government-tertiary-scholarships-tsls-2026</t>
+  </si>
+  <si>
+    <t>Fiji Government Tertiary Scholarships and Study Funding 2026</t>
+  </si>
+  <si>
+    <t>Tertiary Scholarships and Loans Service (TSLS), Government of Fiji</t>
+  </si>
+  <si>
+    <t>Fiji</t>
+  </si>
+  <si>
+    <t>Undergraduate, Postgraduate and vocational/tertiary levels; scheme-dependent</t>
+  </si>
+  <si>
+    <t>Eligible programmes under the relevant TSLS scheme</t>
+  </si>
+  <si>
+    <t>Government-funded; varies by scheme</t>
+  </si>
+  <si>
+    <t>Scholarship, study loan or grant; benefits depend on eligibility and scheme</t>
+  </si>
+  <si>
+    <t>2026 intake; verify the next intake on the official portal</t>
+  </si>
+  <si>
+    <t>Eligibility depends on the scheme; government funding is primarily for eligible Fijian students</t>
+  </si>
+  <si>
+    <t>Medium to high: registration, institution offer and supporting personal, academic and financial information</t>
+  </si>
+  <si>
+    <t>Eligible Fijian students pursuing tertiary or vocational education</t>
+  </si>
+  <si>
+    <t>TSLS administers government-funded scholarships, study loans and grants. This entry refers to the 2026 intake, not a currently confirmed open application window.</t>
+  </si>
+  <si>
+    <t>Final institution offer and documents requested in the relevant TSLS application and policy handbook</t>
+  </si>
+  <si>
+    <t>Assessment against the current scheme's published eligibility and funding criteria</t>
+  </si>
+  <si>
+    <t>Do not describe all TSLS support as a full scholarship. Check the latest handbook for nationality, income, course and award conditions.</t>
+  </si>
+  <si>
+    <t>https://tsls.com.fj/</t>
+  </si>
+  <si>
+    <t>Fiji; TSLS; tertiary education; scholarship; study loan; closed 2026</t>
   </si>
 </sst>
 </file>
@@ -6997,7 +8728,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7011,6 +8742,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7557,7 +9290,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC400"/>
+  <dimension ref="A1:AC398"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" style="5" customWidth="1"/>
@@ -7739,7 +9472,7 @@
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
       <c r="AC2" s="6" t="str">
-        <f t="shared" ref="AC2:AC65" si="0">IF(AND(E2&lt;&gt;"",COUNTIF($E$2:$E$800,E2)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E2&lt;&gt;"",COUNTIF($E$2:$E$798,E2)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -7813,7 +9546,7 @@
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E3&lt;&gt;"",COUNTIF($E$2:$E$798,E3)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -7879,7 +9612,7 @@
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
       <c r="AC4" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E4&lt;&gt;"",COUNTIF($E$2:$E$798,E4)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -7945,7 +9678,7 @@
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E5&lt;&gt;"",COUNTIF($E$2:$E$798,E5)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8009,7 +9742,7 @@
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E6&lt;&gt;"",COUNTIF($E$2:$E$798,E6)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8085,7 +9818,7 @@
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E7&lt;&gt;"",COUNTIF($E$2:$E$798,E7)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8159,7 +9892,7 @@
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
       <c r="AC8" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E8&lt;&gt;"",COUNTIF($E$2:$E$798,E8)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8223,7 +9956,7 @@
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
       <c r="AC9" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E9&lt;&gt;"",COUNTIF($E$2:$E$798,E9)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8299,7 +10032,7 @@
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E10&lt;&gt;"",COUNTIF($E$2:$E$798,E10)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8365,7 +10098,7 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E11&lt;&gt;"",COUNTIF($E$2:$E$798,E11)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8431,7 +10164,7 @@
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E12&lt;&gt;"",COUNTIF($E$2:$E$798,E12)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8507,7 +10240,7 @@
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E13&lt;&gt;"",COUNTIF($E$2:$E$798,E13)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8573,7 +10306,7 @@
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E14&lt;&gt;"",COUNTIF($E$2:$E$798,E14)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8639,7 +10372,7 @@
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E15&lt;&gt;"",COUNTIF($E$2:$E$798,E15)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8703,7 +10436,7 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E16&lt;&gt;"",COUNTIF($E$2:$E$798,E16)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8779,7 +10512,7 @@
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E17&lt;&gt;"",COUNTIF($E$2:$E$798,E17)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8853,7 +10586,7 @@
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E18&lt;&gt;"",COUNTIF($E$2:$E$798,E18)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8917,7 +10650,7 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E19&lt;&gt;"",COUNTIF($E$2:$E$798,E19)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -8981,7 +10714,7 @@
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E20&lt;&gt;"",COUNTIF($E$2:$E$798,E20)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9055,7 +10788,7 @@
       <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E21&lt;&gt;"",COUNTIF($E$2:$E$798,E21)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9131,7 +10864,7 @@
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E22&lt;&gt;"",COUNTIF($E$2:$E$798,E22)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9197,7 +10930,7 @@
       <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E23&lt;&gt;"",COUNTIF($E$2:$E$798,E23)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9261,7 +10994,7 @@
       <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E24&lt;&gt;"",COUNTIF($E$2:$E$798,E24)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9325,7 +11058,7 @@
       <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E25&lt;&gt;"",COUNTIF($E$2:$E$798,E25)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9401,7 +11134,7 @@
       <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E26&lt;&gt;"",COUNTIF($E$2:$E$798,E26)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9467,7 +11200,7 @@
       <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E27&lt;&gt;"",COUNTIF($E$2:$E$798,E27)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9541,7 +11274,7 @@
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E28&lt;&gt;"",COUNTIF($E$2:$E$798,E28)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9607,7 +11340,7 @@
       <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E29&lt;&gt;"",COUNTIF($E$2:$E$798,E29)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9673,7 +11406,7 @@
       <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
       <c r="AC30" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E30&lt;&gt;"",COUNTIF($E$2:$E$798,E30)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9737,7 +11470,7 @@
       <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
       <c r="AC31" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E31&lt;&gt;"",COUNTIF($E$2:$E$798,E31)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9803,7 +11536,7 @@
       <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E32&lt;&gt;"",COUNTIF($E$2:$E$798,E32)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9875,7 +11608,7 @@
       <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E33&lt;&gt;"",COUNTIF($E$2:$E$798,E33)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9949,7 +11682,7 @@
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E34&lt;&gt;"",COUNTIF($E$2:$E$798,E34)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10025,7 +11758,7 @@
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E35&lt;&gt;"",COUNTIF($E$2:$E$798,E35)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10099,7 +11832,7 @@
       <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E36&lt;&gt;"",COUNTIF($E$2:$E$798,E36)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10163,7 +11896,7 @@
       <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E37&lt;&gt;"",COUNTIF($E$2:$E$798,E37)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10229,7 +11962,7 @@
       <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E38&lt;&gt;"",COUNTIF($E$2:$E$798,E38)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10303,7 +12036,7 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E39&lt;&gt;"",COUNTIF($E$2:$E$798,E39)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10377,7 +12110,7 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E40&lt;&gt;"",COUNTIF($E$2:$E$798,E40)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10443,7 +12176,7 @@
       <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
       <c r="AC41" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E41&lt;&gt;"",COUNTIF($E$2:$E$798,E41)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10517,7 +12250,7 @@
       <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
       <c r="AC42" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E42&lt;&gt;"",COUNTIF($E$2:$E$798,E42)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10583,7 +12316,7 @@
       <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
       <c r="AC43" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E43&lt;&gt;"",COUNTIF($E$2:$E$798,E43)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10649,7 +12382,7 @@
       <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
       <c r="AC44" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E44&lt;&gt;"",COUNTIF($E$2:$E$798,E44)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10713,7 +12446,7 @@
       <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
       <c r="AC45" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E45&lt;&gt;"",COUNTIF($E$2:$E$798,E45)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10787,7 +12520,7 @@
       <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E46&lt;&gt;"",COUNTIF($E$2:$E$798,E46)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10851,7 +12584,7 @@
       <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
       <c r="AC47" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E47&lt;&gt;"",COUNTIF($E$2:$E$798,E47)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10917,7 +12650,7 @@
       <c r="AA48" s="3"/>
       <c r="AB48" s="3"/>
       <c r="AC48" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E48&lt;&gt;"",COUNTIF($E$2:$E$798,E48)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10983,7 +12716,7 @@
       <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E49&lt;&gt;"",COUNTIF($E$2:$E$798,E49)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11059,7 +12792,7 @@
       <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
       <c r="AC50" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E50&lt;&gt;"",COUNTIF($E$2:$E$798,E50)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11125,7 +12858,7 @@
       <c r="AA51" s="3"/>
       <c r="AB51" s="3"/>
       <c r="AC51" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E51&lt;&gt;"",COUNTIF($E$2:$E$798,E51)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11191,7 +12924,7 @@
       <c r="AA52" s="3"/>
       <c r="AB52" s="3"/>
       <c r="AC52" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E52&lt;&gt;"",COUNTIF($E$2:$E$798,E52)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11257,7 +12990,7 @@
       <c r="AA53" s="3"/>
       <c r="AB53" s="3"/>
       <c r="AC53" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E53&lt;&gt;"",COUNTIF($E$2:$E$798,E53)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11321,7 +13054,7 @@
       <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
       <c r="AC54" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E54&lt;&gt;"",COUNTIF($E$2:$E$798,E54)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11387,7 +13120,7 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E55&lt;&gt;"",COUNTIF($E$2:$E$798,E55)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11459,7 +13192,7 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E56&lt;&gt;"",COUNTIF($E$2:$E$798,E56)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11533,7 +13266,7 @@
       <c r="AA57" s="3"/>
       <c r="AB57" s="3"/>
       <c r="AC57" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E57&lt;&gt;"",COUNTIF($E$2:$E$798,E57)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11597,7 +13330,7 @@
       <c r="AA58" s="3"/>
       <c r="AB58" s="3"/>
       <c r="AC58" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E58&lt;&gt;"",COUNTIF($E$2:$E$798,E58)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11661,7 +13394,7 @@
       <c r="AA59" s="3"/>
       <c r="AB59" s="3"/>
       <c r="AC59" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E59&lt;&gt;"",COUNTIF($E$2:$E$798,E59)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11727,7 +13460,7 @@
       <c r="AA60" s="3"/>
       <c r="AB60" s="3"/>
       <c r="AC60" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E60&lt;&gt;"",COUNTIF($E$2:$E$798,E60)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11803,7 +13536,7 @@
       <c r="AA61" s="3"/>
       <c r="AB61" s="3"/>
       <c r="AC61" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E61&lt;&gt;"",COUNTIF($E$2:$E$798,E61)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11867,7 +13600,7 @@
       <c r="AA62" s="3"/>
       <c r="AB62" s="3"/>
       <c r="AC62" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E62&lt;&gt;"",COUNTIF($E$2:$E$798,E62)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11941,7 +13674,7 @@
       <c r="AA63" s="3"/>
       <c r="AB63" s="3"/>
       <c r="AC63" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E63&lt;&gt;"",COUNTIF($E$2:$E$798,E63)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12005,7 +13738,7 @@
       <c r="AA64" s="3"/>
       <c r="AB64" s="3"/>
       <c r="AC64" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E64&lt;&gt;"",COUNTIF($E$2:$E$798,E64)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12069,7 +13802,7 @@
       <c r="AA65" s="3"/>
       <c r="AB65" s="3"/>
       <c r="AC65" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(E65&lt;&gt;"",COUNTIF($E$2:$E$798,E65)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12145,7 +13878,7 @@
       <c r="AA66" s="3"/>
       <c r="AB66" s="3"/>
       <c r="AC66" s="6" t="str">
-        <f t="shared" ref="AC66:AC129" si="1">IF(AND(E66&lt;&gt;"",COUNTIF($E$2:$E$800,E66)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E66&lt;&gt;"",COUNTIF($E$2:$E$798,E66)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12209,7 +13942,7 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E67&lt;&gt;"",COUNTIF($E$2:$E$798,E67)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12275,7 +14008,7 @@
       <c r="AA68" s="3"/>
       <c r="AB68" s="3"/>
       <c r="AC68" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E68&lt;&gt;"",COUNTIF($E$2:$E$798,E68)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12339,7 +14072,7 @@
       <c r="AA69" s="3"/>
       <c r="AB69" s="3"/>
       <c r="AC69" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E69&lt;&gt;"",COUNTIF($E$2:$E$798,E69)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12415,7 +14148,7 @@
       <c r="AA70" s="3"/>
       <c r="AB70" s="3"/>
       <c r="AC70" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E70&lt;&gt;"",COUNTIF($E$2:$E$798,E70)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12481,7 +14214,7 @@
       <c r="AA71" s="3"/>
       <c r="AB71" s="3"/>
       <c r="AC71" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E71&lt;&gt;"",COUNTIF($E$2:$E$798,E71)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12547,7 +14280,7 @@
       <c r="AA72" s="3"/>
       <c r="AB72" s="3"/>
       <c r="AC72" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E72&lt;&gt;"",COUNTIF($E$2:$E$798,E72)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12621,7 +14354,7 @@
       <c r="AA73" s="3"/>
       <c r="AB73" s="3"/>
       <c r="AC73" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E73&lt;&gt;"",COUNTIF($E$2:$E$798,E73)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12685,7 +14418,7 @@
       <c r="AA74" s="3"/>
       <c r="AB74" s="3"/>
       <c r="AC74" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E74&lt;&gt;"",COUNTIF($E$2:$E$798,E74)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12749,7 +14482,7 @@
       <c r="AA75" s="3"/>
       <c r="AB75" s="3"/>
       <c r="AC75" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E75&lt;&gt;"",COUNTIF($E$2:$E$798,E75)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12825,7 +14558,7 @@
       <c r="AA76" s="3"/>
       <c r="AB76" s="3"/>
       <c r="AC76" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E76&lt;&gt;"",COUNTIF($E$2:$E$798,E76)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12891,7 +14624,7 @@
       <c r="AA77" s="3"/>
       <c r="AB77" s="3"/>
       <c r="AC77" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E77&lt;&gt;"",COUNTIF($E$2:$E$798,E77)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12957,7 +14690,7 @@
       <c r="AA78" s="3"/>
       <c r="AB78" s="3"/>
       <c r="AC78" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E78&lt;&gt;"",COUNTIF($E$2:$E$798,E78)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13031,7 +14764,7 @@
       <c r="AA79" s="3"/>
       <c r="AB79" s="3"/>
       <c r="AC79" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E79&lt;&gt;"",COUNTIF($E$2:$E$798,E79)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13095,7 +14828,7 @@
       <c r="AA80" s="3"/>
       <c r="AB80" s="3"/>
       <c r="AC80" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E80&lt;&gt;"",COUNTIF($E$2:$E$798,E80)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13159,7 +14892,7 @@
       <c r="AA81" s="3"/>
       <c r="AB81" s="3"/>
       <c r="AC81" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E81&lt;&gt;"",COUNTIF($E$2:$E$798,E81)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13234,7 +14967,7 @@
         <v>46312</v>
       </c>
       <c r="AC82" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E82&lt;&gt;"",COUNTIF($E$2:$E$798,E82)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13309,7 +15042,7 @@
         <v>46312</v>
       </c>
       <c r="AC83" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E83&lt;&gt;"",COUNTIF($E$2:$E$798,E83)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13384,7 +15117,7 @@
         <v>46312</v>
       </c>
       <c r="AC84" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E84&lt;&gt;"",COUNTIF($E$2:$E$798,E84)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13456,7 +15189,7 @@
         <v>46312</v>
       </c>
       <c r="AC85" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E85&lt;&gt;"",COUNTIF($E$2:$E$798,E85)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13531,7 +15264,7 @@
         <v>46312</v>
       </c>
       <c r="AC86" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E86&lt;&gt;"",COUNTIF($E$2:$E$798,E86)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13606,7 +15339,7 @@
         <v>46312</v>
       </c>
       <c r="AC87" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E87&lt;&gt;"",COUNTIF($E$2:$E$798,E87)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13678,7 +15411,7 @@
         <v>46312</v>
       </c>
       <c r="AC88" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E88&lt;&gt;"",COUNTIF($E$2:$E$798,E88)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13750,7 +15483,7 @@
         <v>46312</v>
       </c>
       <c r="AC89" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E89&lt;&gt;"",COUNTIF($E$2:$E$798,E89)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13825,7 +15558,7 @@
         <v>46312</v>
       </c>
       <c r="AC90" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E90&lt;&gt;"",COUNTIF($E$2:$E$798,E90)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13900,7 +15633,7 @@
         <v>46312</v>
       </c>
       <c r="AC91" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E91&lt;&gt;"",COUNTIF($E$2:$E$798,E91)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13972,7 +15705,7 @@
         <v>46312</v>
       </c>
       <c r="AC92" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E92&lt;&gt;"",COUNTIF($E$2:$E$798,E92)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14047,7 +15780,7 @@
         <v>46312</v>
       </c>
       <c r="AC93" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E93&lt;&gt;"",COUNTIF($E$2:$E$798,E93)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14122,7 +15855,7 @@
         <v>46312</v>
       </c>
       <c r="AC94" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E94&lt;&gt;"",COUNTIF($E$2:$E$798,E94)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14197,7 +15930,7 @@
         <v>46312</v>
       </c>
       <c r="AC95" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E95&lt;&gt;"",COUNTIF($E$2:$E$798,E95)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14272,7 +16005,7 @@
         <v>46312</v>
       </c>
       <c r="AC96" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E96&lt;&gt;"",COUNTIF($E$2:$E$798,E96)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14347,7 +16080,7 @@
         <v>46312</v>
       </c>
       <c r="AC97" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E97&lt;&gt;"",COUNTIF($E$2:$E$798,E97)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14422,7 +16155,7 @@
         <v>46312</v>
       </c>
       <c r="AC98" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E98&lt;&gt;"",COUNTIF($E$2:$E$798,E98)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14497,7 +16230,7 @@
         <v>46312</v>
       </c>
       <c r="AC99" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E99&lt;&gt;"",COUNTIF($E$2:$E$798,E99)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14572,7 +16305,7 @@
         <v>46312</v>
       </c>
       <c r="AC100" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E100&lt;&gt;"",COUNTIF($E$2:$E$798,E100)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14647,7 +16380,7 @@
         <v>46312</v>
       </c>
       <c r="AC101" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E101&lt;&gt;"",COUNTIF($E$2:$E$798,E101)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14722,7 +16455,7 @@
         <v>46312</v>
       </c>
       <c r="AC102" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E102&lt;&gt;"",COUNTIF($E$2:$E$798,E102)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14797,7 +16530,7 @@
         <v>46312</v>
       </c>
       <c r="AC103" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E103&lt;&gt;"",COUNTIF($E$2:$E$798,E103)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14872,7 +16605,7 @@
         <v>46312</v>
       </c>
       <c r="AC104" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E104&lt;&gt;"",COUNTIF($E$2:$E$798,E104)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14947,7 +16680,7 @@
         <v>46312</v>
       </c>
       <c r="AC105" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E105&lt;&gt;"",COUNTIF($E$2:$E$798,E105)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15022,7 +16755,7 @@
         <v>46312</v>
       </c>
       <c r="AC106" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E106&lt;&gt;"",COUNTIF($E$2:$E$798,E106)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15097,7 +16830,7 @@
         <v>46312</v>
       </c>
       <c r="AC107" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E107&lt;&gt;"",COUNTIF($E$2:$E$798,E107)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15172,7 +16905,7 @@
         <v>46312</v>
       </c>
       <c r="AC108" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E108&lt;&gt;"",COUNTIF($E$2:$E$798,E108)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15247,7 +16980,7 @@
         <v>46312</v>
       </c>
       <c r="AC109" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E109&lt;&gt;"",COUNTIF($E$2:$E$798,E109)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15322,7 +17055,7 @@
         <v>46312</v>
       </c>
       <c r="AC110" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E110&lt;&gt;"",COUNTIF($E$2:$E$798,E110)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15397,7 +17130,7 @@
         <v>46312</v>
       </c>
       <c r="AC111" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E111&lt;&gt;"",COUNTIF($E$2:$E$798,E111)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15472,7 +17205,7 @@
         <v>46312</v>
       </c>
       <c r="AC112" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E112&lt;&gt;"",COUNTIF($E$2:$E$798,E112)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15547,7 +17280,7 @@
         <v>46312</v>
       </c>
       <c r="AC113" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E113&lt;&gt;"",COUNTIF($E$2:$E$798,E113)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15622,7 +17355,7 @@
         <v>46312</v>
       </c>
       <c r="AC114" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E114&lt;&gt;"",COUNTIF($E$2:$E$798,E114)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15697,7 +17430,7 @@
         <v>46312</v>
       </c>
       <c r="AC115" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E115&lt;&gt;"",COUNTIF($E$2:$E$798,E115)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15772,7 +17505,7 @@
         <v>46313</v>
       </c>
       <c r="AC116" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E116&lt;&gt;"",COUNTIF($E$2:$E$798,E116)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15847,7 +17580,7 @@
         <v>46313</v>
       </c>
       <c r="AC117" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E117&lt;&gt;"",COUNTIF($E$2:$E$798,E117)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15922,7 +17655,7 @@
         <v>46313</v>
       </c>
       <c r="AC118" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E118&lt;&gt;"",COUNTIF($E$2:$E$798,E118)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15997,7 +17730,7 @@
         <v>46313</v>
       </c>
       <c r="AC119" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E119&lt;&gt;"",COUNTIF($E$2:$E$798,E119)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16072,7 +17805,7 @@
         <v>46313</v>
       </c>
       <c r="AC120" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E120&lt;&gt;"",COUNTIF($E$2:$E$798,E120)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16147,7 +17880,7 @@
         <v>46313</v>
       </c>
       <c r="AC121" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E121&lt;&gt;"",COUNTIF($E$2:$E$798,E121)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16222,7 +17955,7 @@
         <v>46313</v>
       </c>
       <c r="AC122" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E122&lt;&gt;"",COUNTIF($E$2:$E$798,E122)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16297,7 +18030,7 @@
         <v>46313</v>
       </c>
       <c r="AC123" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E123&lt;&gt;"",COUNTIF($E$2:$E$798,E123)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16372,7 +18105,7 @@
         <v>46313</v>
       </c>
       <c r="AC124" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E124&lt;&gt;"",COUNTIF($E$2:$E$798,E124)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16447,7 +18180,7 @@
         <v>46313</v>
       </c>
       <c r="AC125" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E125&lt;&gt;"",COUNTIF($E$2:$E$798,E125)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16522,7 +18255,7 @@
         <v>46313</v>
       </c>
       <c r="AC126" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E126&lt;&gt;"",COUNTIF($E$2:$E$798,E126)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16597,7 +18330,7 @@
         <v>46313</v>
       </c>
       <c r="AC127" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E127&lt;&gt;"",COUNTIF($E$2:$E$798,E127)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16672,7 +18405,7 @@
         <v>46313</v>
       </c>
       <c r="AC128" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E128&lt;&gt;"",COUNTIF($E$2:$E$798,E128)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16747,7 +18480,7 @@
         <v>46313</v>
       </c>
       <c r="AC129" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AND(E129&lt;&gt;"",COUNTIF($E$2:$E$798,E129)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16822,7 +18555,7 @@
         <v>46313</v>
       </c>
       <c r="AC130" t="str">
-        <f t="shared" ref="AC130:AC193" si="2">IF(AND(E130&lt;&gt;"",COUNTIF($E$2:$E$800,E130)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E130&lt;&gt;"",COUNTIF($E$2:$E$798,E130)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16897,7 +18630,7 @@
         <v>46313</v>
       </c>
       <c r="AC131" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E131&lt;&gt;"",COUNTIF($E$2:$E$798,E131)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16972,7 +18705,7 @@
         <v>46313</v>
       </c>
       <c r="AC132" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E132&lt;&gt;"",COUNTIF($E$2:$E$798,E132)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17047,7 +18780,7 @@
         <v>46313</v>
       </c>
       <c r="AC133" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E133&lt;&gt;"",COUNTIF($E$2:$E$798,E133)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17122,7 +18855,7 @@
         <v>46313</v>
       </c>
       <c r="AC134" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E134&lt;&gt;"",COUNTIF($E$2:$E$798,E134)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17197,7 +18930,7 @@
         <v>46313</v>
       </c>
       <c r="AC135" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E135&lt;&gt;"",COUNTIF($E$2:$E$798,E135)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17272,7 +19005,7 @@
         <v>46313</v>
       </c>
       <c r="AC136" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E136&lt;&gt;"",COUNTIF($E$2:$E$798,E136)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17347,7 +19080,7 @@
         <v>46313</v>
       </c>
       <c r="AC137" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E137&lt;&gt;"",COUNTIF($E$2:$E$798,E137)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17422,7 +19155,7 @@
         <v>46313</v>
       </c>
       <c r="AC138" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E138&lt;&gt;"",COUNTIF($E$2:$E$798,E138)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17497,7 +19230,7 @@
         <v>46313</v>
       </c>
       <c r="AC139" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E139&lt;&gt;"",COUNTIF($E$2:$E$798,E139)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17572,7 +19305,7 @@
         <v>46313</v>
       </c>
       <c r="AC140" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E140&lt;&gt;"",COUNTIF($E$2:$E$798,E140)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17647,7 +19380,7 @@
         <v>46313</v>
       </c>
       <c r="AC141" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E141&lt;&gt;"",COUNTIF($E$2:$E$798,E141)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17722,7 +19455,7 @@
         <v>46313</v>
       </c>
       <c r="AC142" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E142&lt;&gt;"",COUNTIF($E$2:$E$798,E142)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17797,7 +19530,7 @@
         <v>46313</v>
       </c>
       <c r="AC143" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E143&lt;&gt;"",COUNTIF($E$2:$E$798,E143)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17872,7 +19605,7 @@
         <v>46313</v>
       </c>
       <c r="AC144" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E144&lt;&gt;"",COUNTIF($E$2:$E$798,E144)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17947,7 +19680,7 @@
         <v>46313</v>
       </c>
       <c r="AC145" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E145&lt;&gt;"",COUNTIF($E$2:$E$798,E145)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18022,7 +19755,7 @@
         <v>46313</v>
       </c>
       <c r="AC146" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E146&lt;&gt;"",COUNTIF($E$2:$E$798,E146)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18097,7 +19830,7 @@
         <v>46313</v>
       </c>
       <c r="AC147" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E147&lt;&gt;"",COUNTIF($E$2:$E$798,E147)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18172,7 +19905,7 @@
         <v>46313</v>
       </c>
       <c r="AC148" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E148&lt;&gt;"",COUNTIF($E$2:$E$798,E148)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18247,7 +19980,7 @@
         <v>46313</v>
       </c>
       <c r="AC149" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E149&lt;&gt;"",COUNTIF($E$2:$E$798,E149)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18322,7 +20055,7 @@
         <v>46313</v>
       </c>
       <c r="AC150" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E150&lt;&gt;"",COUNTIF($E$2:$E$798,E150)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18397,7 +20130,7 @@
         <v>46313</v>
       </c>
       <c r="AC151" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E151&lt;&gt;"",COUNTIF($E$2:$E$798,E151)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18472,7 +20205,7 @@
         <v>46313</v>
       </c>
       <c r="AC152" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E152&lt;&gt;"",COUNTIF($E$2:$E$798,E152)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18547,7 +20280,7 @@
         <v>46313</v>
       </c>
       <c r="AC153" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E153&lt;&gt;"",COUNTIF($E$2:$E$798,E153)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18622,7 +20355,7 @@
         <v>46313</v>
       </c>
       <c r="AC154" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E154&lt;&gt;"",COUNTIF($E$2:$E$798,E154)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18697,7 +20430,7 @@
         <v>46313</v>
       </c>
       <c r="AC155" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E155&lt;&gt;"",COUNTIF($E$2:$E$798,E155)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18772,7 +20505,7 @@
         <v>46313</v>
       </c>
       <c r="AC156" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E156&lt;&gt;"",COUNTIF($E$2:$E$798,E156)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18847,7 +20580,7 @@
         <v>46313</v>
       </c>
       <c r="AC157" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E157&lt;&gt;"",COUNTIF($E$2:$E$798,E157)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18922,7 +20655,7 @@
         <v>46313</v>
       </c>
       <c r="AC158" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E158&lt;&gt;"",COUNTIF($E$2:$E$798,E158)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18997,7 +20730,7 @@
         <v>46313</v>
       </c>
       <c r="AC159" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E159&lt;&gt;"",COUNTIF($E$2:$E$798,E159)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19072,7 +20805,7 @@
         <v>46313</v>
       </c>
       <c r="AC160" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E160&lt;&gt;"",COUNTIF($E$2:$E$798,E160)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19147,7 +20880,7 @@
         <v>46313</v>
       </c>
       <c r="AC161" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E161&lt;&gt;"",COUNTIF($E$2:$E$798,E161)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19222,7 +20955,7 @@
         <v>46313</v>
       </c>
       <c r="AC162" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E162&lt;&gt;"",COUNTIF($E$2:$E$798,E162)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19297,7 +21030,7 @@
         <v>46313</v>
       </c>
       <c r="AC163" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E163&lt;&gt;"",COUNTIF($E$2:$E$798,E163)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19372,7 +21105,7 @@
         <v>46313</v>
       </c>
       <c r="AC164" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E164&lt;&gt;"",COUNTIF($E$2:$E$798,E164)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19447,7 +21180,7 @@
         <v>46313</v>
       </c>
       <c r="AC165" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E165&lt;&gt;"",COUNTIF($E$2:$E$798,E165)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19522,7 +21255,7 @@
         <v>46313</v>
       </c>
       <c r="AC166" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E166&lt;&gt;"",COUNTIF($E$2:$E$798,E166)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19584,7 +21317,7 @@
       <c r="AA167" s="4"/>
       <c r="AB167" s="4"/>
       <c r="AC167" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E167&lt;&gt;"",COUNTIF($E$2:$E$798,E167)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19654,7 +21387,7 @@
       </c>
       <c r="AB168" s="4"/>
       <c r="AC168" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E168&lt;&gt;"",COUNTIF($E$2:$E$798,E168)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19724,7 +21457,7 @@
       </c>
       <c r="AB169" s="4"/>
       <c r="AC169" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E169&lt;&gt;"",COUNTIF($E$2:$E$798,E169)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19794,7 +21527,7 @@
       </c>
       <c r="AB170" s="4"/>
       <c r="AC170" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E170&lt;&gt;"",COUNTIF($E$2:$E$798,E170)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19864,7 +21597,7 @@
       </c>
       <c r="AB171" s="4"/>
       <c r="AC171" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E171&lt;&gt;"",COUNTIF($E$2:$E$798,E171)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19934,7 +21667,7 @@
       </c>
       <c r="AB172" s="4"/>
       <c r="AC172" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E172&lt;&gt;"",COUNTIF($E$2:$E$798,E172)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20001,7 +21734,7 @@
       </c>
       <c r="AB173" s="4"/>
       <c r="AC173" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E173&lt;&gt;"",COUNTIF($E$2:$E$798,E173)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20068,7 +21801,7 @@
       </c>
       <c r="AB174" s="4"/>
       <c r="AC174" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E174&lt;&gt;"",COUNTIF($E$2:$E$798,E174)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20138,7 +21871,7 @@
       </c>
       <c r="AB175" s="4"/>
       <c r="AC175" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E175&lt;&gt;"",COUNTIF($E$2:$E$798,E175)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20208,7 +21941,7 @@
       </c>
       <c r="AB176" s="4"/>
       <c r="AC176" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AND(E176&lt;&gt;"",COUNTIF($E$2:$E$798,E176)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20278,383 +22011,2911 @@
       </c>
       <c r="AB177" s="4"/>
       <c r="AC177" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA178" s="4"/>
-      <c r="AB178" s="4"/>
-      <c r="AC178" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA179" s="4"/>
-      <c r="AB179" s="4"/>
-      <c r="AC179" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA180" s="4"/>
-      <c r="AB180" s="4"/>
-      <c r="AC180" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA181" s="4"/>
-      <c r="AB181" s="4"/>
-      <c r="AC181" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA182" s="4"/>
-      <c r="AB182" s="4"/>
-      <c r="AC182" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA183" s="4"/>
-      <c r="AB183" s="4"/>
-      <c r="AC183" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA184" s="4"/>
-      <c r="AB184" s="4"/>
-      <c r="AC184" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA185" s="4"/>
-      <c r="AB185" s="4"/>
-      <c r="AC185" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA186" s="4"/>
-      <c r="AB186" s="4"/>
-      <c r="AC186" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA187" s="4"/>
-      <c r="AB187" s="4"/>
-      <c r="AC187" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA188" s="4"/>
-      <c r="AB188" s="4"/>
-      <c r="AC188" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA189" s="4"/>
-      <c r="AB189" s="4"/>
-      <c r="AC189" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA190" s="4"/>
-      <c r="AB190" s="4"/>
-      <c r="AC190" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA191" s="4"/>
-      <c r="AB191" s="4"/>
-      <c r="AC191" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA192" s="4"/>
-      <c r="AB192" s="4"/>
-      <c r="AC192" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA193" s="4"/>
-      <c r="AB193" s="4"/>
-      <c r="AC193" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA194" s="4"/>
-      <c r="AB194" s="4"/>
-      <c r="AC194" t="str">
-        <f t="shared" ref="AC194:AC257" si="3">IF(AND(E194&lt;&gt;"",COUNTIF($E$2:$E$800,E194)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA195" s="4"/>
-      <c r="AB195" s="4"/>
-      <c r="AC195" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA196" s="4"/>
-      <c r="AB196" s="4"/>
-      <c r="AC196" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA197" s="4"/>
-      <c r="AB197" s="4"/>
-      <c r="AC197" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA198" s="4"/>
-      <c r="AB198" s="4"/>
-      <c r="AC198" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA199" s="4"/>
-      <c r="AB199" s="4"/>
-      <c r="AC199" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA200" s="4"/>
-      <c r="AB200" s="4"/>
-      <c r="AC200" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA201" s="4"/>
-      <c r="AB201" s="4"/>
-      <c r="AC201" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA202" s="4"/>
-      <c r="AB202" s="4"/>
-      <c r="AC202" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA203" s="4"/>
-      <c r="AB203" s="4"/>
-      <c r="AC203" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA204" s="4"/>
-      <c r="AB204" s="4"/>
-      <c r="AC204" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA205" s="4"/>
-      <c r="AB205" s="4"/>
-      <c r="AC205" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA206" s="4"/>
-      <c r="AB206" s="4"/>
-      <c r="AC206" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E177&lt;&gt;"",COUNTIF($E$2:$E$798,E177)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="1:29" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A178" s="6"/>
+      <c r="B178" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C178" s="6"/>
+      <c r="D178" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G178" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>2306</v>
+      </c>
+      <c r="I178" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="J178" s="6"/>
+      <c r="K178" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L178" s="6" t="s">
+        <v>2307</v>
+      </c>
+      <c r="M178" s="6" t="s">
+        <v>2308</v>
+      </c>
+      <c r="N178" s="6" t="s">
+        <v>2309</v>
+      </c>
+      <c r="O178" s="6" t="s">
+        <v>2310</v>
+      </c>
+      <c r="P178" s="6" t="s">
+        <v>2311</v>
+      </c>
+      <c r="Q178" s="6" t="s">
+        <v>2312</v>
+      </c>
+      <c r="R178" s="6" t="s">
+        <v>2313</v>
+      </c>
+      <c r="S178" s="6" t="s">
+        <v>2314</v>
+      </c>
+      <c r="T178" s="6"/>
+      <c r="U178" s="6"/>
+      <c r="V178" s="6" t="s">
+        <v>2315</v>
+      </c>
+      <c r="W178" s="6"/>
+      <c r="X178" s="6"/>
+      <c r="Y178" s="6"/>
+      <c r="Z178" s="6"/>
+      <c r="AA178" s="6" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AB178" s="6"/>
+    </row>
+    <row r="179" spans="1:29" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A179" s="6"/>
+      <c r="B179" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C179" s="6"/>
+      <c r="D179" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>2316</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>2317</v>
+      </c>
+      <c r="G179" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>2318</v>
+      </c>
+      <c r="I179" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J179" s="6"/>
+      <c r="K179" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L179" s="6" t="s">
+        <v>2319</v>
+      </c>
+      <c r="M179" s="6" t="s">
+        <v>2320</v>
+      </c>
+      <c r="N179" s="6" t="s">
+        <v>2321</v>
+      </c>
+      <c r="O179" s="6" t="s">
+        <v>2322</v>
+      </c>
+      <c r="P179" s="6" t="s">
+        <v>2323</v>
+      </c>
+      <c r="Q179" s="6" t="s">
+        <v>2324</v>
+      </c>
+      <c r="R179" s="6" t="s">
+        <v>2325</v>
+      </c>
+      <c r="S179" s="6" t="s">
+        <v>2326</v>
+      </c>
+      <c r="T179" s="6"/>
+      <c r="U179" s="6"/>
+      <c r="V179" s="6" t="s">
+        <v>2327</v>
+      </c>
+      <c r="W179" s="6"/>
+      <c r="X179" s="6"/>
+      <c r="Y179" s="6"/>
+      <c r="Z179" s="6"/>
+      <c r="AA179" s="6" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AB179" s="6"/>
+    </row>
+    <row r="180" spans="1:29" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A180" s="6"/>
+      <c r="B180" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C180" s="6"/>
+      <c r="D180" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>2328</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G180" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H180" s="6" t="s">
+        <v>2330</v>
+      </c>
+      <c r="I180" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="J180" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K180" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="L180" s="6" t="s">
+        <v>2331</v>
+      </c>
+      <c r="M180" s="6" t="s">
+        <v>2332</v>
+      </c>
+      <c r="N180" s="6" t="s">
+        <v>2333</v>
+      </c>
+      <c r="O180" s="6" t="s">
+        <v>2334</v>
+      </c>
+      <c r="P180" s="6" t="s">
+        <v>2335</v>
+      </c>
+      <c r="Q180" s="6" t="s">
+        <v>2336</v>
+      </c>
+      <c r="R180" s="6" t="s">
+        <v>2337</v>
+      </c>
+      <c r="S180" s="6" t="s">
+        <v>2338</v>
+      </c>
+      <c r="T180" s="6"/>
+      <c r="U180" s="6"/>
+      <c r="V180" s="6" t="s">
+        <v>2339</v>
+      </c>
+      <c r="W180" s="6"/>
+      <c r="X180" s="6"/>
+      <c r="Y180" s="6"/>
+      <c r="Z180" s="6"/>
+      <c r="AA180" s="6" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AB180" s="6"/>
+    </row>
+    <row r="181" spans="1:29" s="5" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A181" s="6"/>
+      <c r="B181" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C181" s="6"/>
+      <c r="D181" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>2340</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>2341</v>
+      </c>
+      <c r="G181" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H181" s="6" t="s">
+        <v>2342</v>
+      </c>
+      <c r="I181" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="J181" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K181" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="L181" s="6" t="s">
+        <v>2343</v>
+      </c>
+      <c r="M181" s="6" t="s">
+        <v>2344</v>
+      </c>
+      <c r="N181" s="6" t="s">
+        <v>2345</v>
+      </c>
+      <c r="O181" s="6" t="s">
+        <v>2346</v>
+      </c>
+      <c r="P181" s="6" t="s">
+        <v>2347</v>
+      </c>
+      <c r="Q181" s="6" t="s">
+        <v>2348</v>
+      </c>
+      <c r="R181" s="6" t="s">
+        <v>2349</v>
+      </c>
+      <c r="S181" s="6" t="s">
+        <v>2350</v>
+      </c>
+      <c r="T181" s="6"/>
+      <c r="U181" s="6"/>
+      <c r="V181" s="6" t="s">
+        <v>2351</v>
+      </c>
+      <c r="W181" s="6"/>
+      <c r="X181" s="6"/>
+      <c r="Y181" s="6"/>
+      <c r="Z181" s="6"/>
+      <c r="AA181" s="6" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AB181" s="6"/>
+    </row>
+    <row r="182" spans="1:29" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A182" s="6"/>
+      <c r="B182" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C182" s="6"/>
+      <c r="D182" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>2353</v>
+      </c>
+      <c r="G182" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H182" s="6" t="s">
+        <v>2354</v>
+      </c>
+      <c r="I182" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="J182" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K182" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L182" s="6" t="s">
+        <v>2355</v>
+      </c>
+      <c r="M182" s="6" t="s">
+        <v>2356</v>
+      </c>
+      <c r="N182" s="6" t="s">
+        <v>2357</v>
+      </c>
+      <c r="O182" s="6" t="s">
+        <v>2358</v>
+      </c>
+      <c r="P182" s="6" t="s">
+        <v>2359</v>
+      </c>
+      <c r="Q182" s="6" t="s">
+        <v>2360</v>
+      </c>
+      <c r="R182" s="6" t="s">
+        <v>2361</v>
+      </c>
+      <c r="S182" s="6" t="s">
+        <v>2362</v>
+      </c>
+      <c r="T182" s="6"/>
+      <c r="U182" s="6"/>
+      <c r="V182" s="6" t="s">
+        <v>2363</v>
+      </c>
+      <c r="W182" s="6"/>
+      <c r="X182" s="6"/>
+      <c r="Y182" s="6"/>
+      <c r="Z182" s="6"/>
+      <c r="AA182" s="6" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AB182" s="6"/>
+    </row>
+    <row r="183" spans="1:29" s="5" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A183" s="6"/>
+      <c r="B183" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C183" s="6"/>
+      <c r="D183" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>2364</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>2365</v>
+      </c>
+      <c r="G183" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="H183" s="6" t="s">
+        <v>2366</v>
+      </c>
+      <c r="I183" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="J183" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K183" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L183" s="6" t="s">
+        <v>2367</v>
+      </c>
+      <c r="M183" s="6" t="s">
+        <v>2368</v>
+      </c>
+      <c r="N183" s="6" t="s">
+        <v>2369</v>
+      </c>
+      <c r="O183" s="6" t="s">
+        <v>2370</v>
+      </c>
+      <c r="P183" s="6" t="s">
+        <v>2371</v>
+      </c>
+      <c r="Q183" s="6" t="s">
+        <v>2372</v>
+      </c>
+      <c r="R183" s="6" t="s">
+        <v>2373</v>
+      </c>
+      <c r="S183" s="6" t="s">
+        <v>2374</v>
+      </c>
+      <c r="T183" s="6"/>
+      <c r="U183" s="6"/>
+      <c r="V183" s="6" t="s">
+        <v>2375</v>
+      </c>
+      <c r="W183" s="6"/>
+      <c r="X183" s="6"/>
+      <c r="Y183" s="6"/>
+      <c r="Z183" s="6"/>
+      <c r="AA183" s="6" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AB183" s="6"/>
+    </row>
+    <row r="184" spans="1:29" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A184" s="6"/>
+      <c r="B184" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C184" s="6"/>
+      <c r="D184" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>2376</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>2377</v>
+      </c>
+      <c r="G184" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="H184" s="6" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I184" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="J184" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="K184" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L184" s="6" t="s">
+        <v>2378</v>
+      </c>
+      <c r="M184" s="6" t="s">
+        <v>2379</v>
+      </c>
+      <c r="N184" s="6" t="s">
+        <v>2380</v>
+      </c>
+      <c r="O184" s="6" t="s">
+        <v>2381</v>
+      </c>
+      <c r="P184" s="6" t="s">
+        <v>2382</v>
+      </c>
+      <c r="Q184" s="6" t="s">
+        <v>2383</v>
+      </c>
+      <c r="R184" s="6" t="s">
+        <v>2384</v>
+      </c>
+      <c r="S184" s="6" t="s">
+        <v>2385</v>
+      </c>
+      <c r="T184" s="6"/>
+      <c r="U184" s="6"/>
+      <c r="V184" s="6" t="s">
+        <v>2202</v>
+      </c>
+      <c r="W184" s="6"/>
+      <c r="X184" s="6"/>
+      <c r="Y184" s="6"/>
+      <c r="Z184" s="6"/>
+      <c r="AA184" s="6" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AB184" s="6"/>
+    </row>
+    <row r="185" spans="1:29" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A185" s="6"/>
+      <c r="B185" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C185" s="6"/>
+      <c r="D185" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>2386</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>2387</v>
+      </c>
+      <c r="G185" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="H185" s="6" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I185" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="J185" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K185" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L185" s="6" t="s">
+        <v>2388</v>
+      </c>
+      <c r="M185" s="6" t="s">
+        <v>2389</v>
+      </c>
+      <c r="N185" s="6" t="s">
+        <v>2390</v>
+      </c>
+      <c r="O185" s="6" t="s">
+        <v>2391</v>
+      </c>
+      <c r="P185" s="6" t="s">
+        <v>2392</v>
+      </c>
+      <c r="Q185" s="6" t="s">
+        <v>2393</v>
+      </c>
+      <c r="R185" s="6" t="s">
+        <v>2394</v>
+      </c>
+      <c r="S185" s="6" t="s">
+        <v>2395</v>
+      </c>
+      <c r="T185" s="6"/>
+      <c r="U185" s="6"/>
+      <c r="V185" s="6" t="s">
+        <v>2396</v>
+      </c>
+      <c r="W185" s="6"/>
+      <c r="X185" s="6"/>
+      <c r="Y185" s="6"/>
+      <c r="Z185" s="6"/>
+      <c r="AA185" s="6" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AB185" s="6"/>
+    </row>
+    <row r="186" spans="1:29" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A186" s="6"/>
+      <c r="B186" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C186" s="6"/>
+      <c r="D186" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>2397</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>2398</v>
+      </c>
+      <c r="G186" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>2399</v>
+      </c>
+      <c r="I186" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J186" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K186" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L186" s="6" t="s">
+        <v>2400</v>
+      </c>
+      <c r="M186" s="6" t="s">
+        <v>2401</v>
+      </c>
+      <c r="N186" s="6" t="s">
+        <v>2402</v>
+      </c>
+      <c r="O186" s="6" t="s">
+        <v>2403</v>
+      </c>
+      <c r="P186" s="6" t="s">
+        <v>2404</v>
+      </c>
+      <c r="Q186" s="6" t="s">
+        <v>2405</v>
+      </c>
+      <c r="R186" s="6" t="s">
+        <v>2406</v>
+      </c>
+      <c r="S186" s="6" t="s">
+        <v>2407</v>
+      </c>
+      <c r="T186" s="6"/>
+      <c r="U186" s="6"/>
+      <c r="V186" s="6" t="s">
+        <v>2408</v>
+      </c>
+      <c r="W186" s="6"/>
+      <c r="X186" s="6"/>
+      <c r="Y186" s="6"/>
+      <c r="Z186" s="6"/>
+      <c r="AA186" s="6" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AB186" s="6"/>
+    </row>
+    <row r="187" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="6" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C187" s="6"/>
+      <c r="D187" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>2410</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>2411</v>
+      </c>
+      <c r="G187" s="6" t="s">
+        <v>2412</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>2413</v>
+      </c>
+      <c r="I187" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="J187" s="6" t="s">
+        <v>2414</v>
+      </c>
+      <c r="K187" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L187" s="6" t="s">
+        <v>2415</v>
+      </c>
+      <c r="M187" s="6" t="s">
+        <v>2416</v>
+      </c>
+      <c r="N187" s="6" t="s">
+        <v>2417</v>
+      </c>
+      <c r="O187" s="6" t="s">
+        <v>2418</v>
+      </c>
+      <c r="P187" s="6" t="s">
+        <v>2419</v>
+      </c>
+      <c r="Q187" s="6" t="s">
+        <v>2420</v>
+      </c>
+      <c r="R187" s="6" t="s">
+        <v>2421</v>
+      </c>
+      <c r="S187" s="6" t="s">
+        <v>2422</v>
+      </c>
+      <c r="T187" s="6"/>
+      <c r="U187" s="6" t="s">
+        <v>2423</v>
+      </c>
+      <c r="V187" s="6" t="s">
+        <v>2424</v>
+      </c>
+      <c r="W187" s="6"/>
+      <c r="X187" s="6"/>
+      <c r="Y187" s="6"/>
+      <c r="Z187" s="6" t="s">
+        <v>2425</v>
+      </c>
+      <c r="AA187" s="6"/>
+      <c r="AB187" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC187" s="6" t="str">
+        <f>IF(AND(E187&lt;&gt;"",COUNTIF($E$2:$E$798,E187)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="6" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C188" s="6"/>
+      <c r="D188" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>2427</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>2411</v>
+      </c>
+      <c r="G188" s="6" t="s">
+        <v>2412</v>
+      </c>
+      <c r="H188" s="6" t="s">
+        <v>2428</v>
+      </c>
+      <c r="I188" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="J188" s="6" t="s">
+        <v>2429</v>
+      </c>
+      <c r="K188" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L188" s="6" t="s">
+        <v>2430</v>
+      </c>
+      <c r="M188" s="6" t="s">
+        <v>2431</v>
+      </c>
+      <c r="N188" s="6" t="s">
+        <v>2432</v>
+      </c>
+      <c r="O188" s="6" t="s">
+        <v>2433</v>
+      </c>
+      <c r="P188" s="6" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q188" s="6" t="s">
+        <v>2435</v>
+      </c>
+      <c r="R188" s="6" t="s">
+        <v>2436</v>
+      </c>
+      <c r="S188" s="6" t="s">
+        <v>2437</v>
+      </c>
+      <c r="T188" s="6"/>
+      <c r="U188" s="6" t="s">
+        <v>2438</v>
+      </c>
+      <c r="V188" s="6" t="s">
+        <v>2439</v>
+      </c>
+      <c r="W188" s="6"/>
+      <c r="X188" s="6"/>
+      <c r="Y188" s="6"/>
+      <c r="Z188" s="6" t="s">
+        <v>2440</v>
+      </c>
+      <c r="AA188" s="6"/>
+      <c r="AB188" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC188" s="6" t="str">
+        <f>IF(AND(E188&lt;&gt;"",COUNTIF($E$2:$E$798,E188)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="6" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C189" s="6"/>
+      <c r="D189" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>2442</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>2443</v>
+      </c>
+      <c r="G189" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H189" s="6" t="s">
+        <v>2444</v>
+      </c>
+      <c r="I189" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="J189" s="6" t="s">
+        <v>2445</v>
+      </c>
+      <c r="K189" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L189" s="6" t="s">
+        <v>2446</v>
+      </c>
+      <c r="M189" s="6" t="s">
+        <v>2447</v>
+      </c>
+      <c r="N189" s="6" t="s">
+        <v>2448</v>
+      </c>
+      <c r="O189" s="6" t="s">
+        <v>2449</v>
+      </c>
+      <c r="P189" s="6" t="s">
+        <v>2450</v>
+      </c>
+      <c r="Q189" s="6" t="s">
+        <v>2451</v>
+      </c>
+      <c r="R189" s="6" t="s">
+        <v>2452</v>
+      </c>
+      <c r="S189" s="6" t="s">
+        <v>2453</v>
+      </c>
+      <c r="T189" s="6"/>
+      <c r="U189" s="6" t="s">
+        <v>2454</v>
+      </c>
+      <c r="V189" s="6" t="s">
+        <v>2455</v>
+      </c>
+      <c r="W189" s="6"/>
+      <c r="X189" s="6"/>
+      <c r="Y189" s="6"/>
+      <c r="Z189" s="6" t="s">
+        <v>2456</v>
+      </c>
+      <c r="AA189" s="6"/>
+      <c r="AB189" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC189" s="6" t="str">
+        <f>IF(AND(E189&lt;&gt;"",COUNTIF($E$2:$E$798,E189)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="6" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C190" s="6"/>
+      <c r="D190" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>2458</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>2459</v>
+      </c>
+      <c r="G190" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="H190" s="6" t="s">
+        <v>2460</v>
+      </c>
+      <c r="I190" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J190" s="6" t="s">
+        <v>2461</v>
+      </c>
+      <c r="K190" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L190" s="6" t="s">
+        <v>2462</v>
+      </c>
+      <c r="M190" s="6" t="s">
+        <v>2463</v>
+      </c>
+      <c r="N190" s="6" t="s">
+        <v>2464</v>
+      </c>
+      <c r="O190" s="6" t="s">
+        <v>2465</v>
+      </c>
+      <c r="P190" s="6" t="s">
+        <v>2466</v>
+      </c>
+      <c r="Q190" s="6" t="s">
+        <v>2467</v>
+      </c>
+      <c r="R190" s="6" t="s">
+        <v>2468</v>
+      </c>
+      <c r="S190" s="6" t="s">
+        <v>2469</v>
+      </c>
+      <c r="T190" s="6"/>
+      <c r="U190" s="6" t="s">
+        <v>2470</v>
+      </c>
+      <c r="V190" s="6" t="s">
+        <v>2471</v>
+      </c>
+      <c r="W190" s="6"/>
+      <c r="X190" s="6"/>
+      <c r="Y190" s="6"/>
+      <c r="Z190" s="6" t="s">
+        <v>2472</v>
+      </c>
+      <c r="AA190" s="6"/>
+      <c r="AB190" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC190" s="6" t="str">
+        <f>IF(AND(E190&lt;&gt;"",COUNTIF($E$2:$E$798,E190)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="6" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C191" s="6"/>
+      <c r="D191" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>2474</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>2459</v>
+      </c>
+      <c r="G191" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="H191" s="6" t="s">
+        <v>2475</v>
+      </c>
+      <c r="I191" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J191" s="6" t="s">
+        <v>2476</v>
+      </c>
+      <c r="K191" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L191" s="6" t="s">
+        <v>2477</v>
+      </c>
+      <c r="M191" s="6" t="s">
+        <v>2478</v>
+      </c>
+      <c r="N191" s="6" t="s">
+        <v>2479</v>
+      </c>
+      <c r="O191" s="6" t="s">
+        <v>2480</v>
+      </c>
+      <c r="P191" s="6" t="s">
+        <v>2481</v>
+      </c>
+      <c r="Q191" s="6" t="s">
+        <v>2482</v>
+      </c>
+      <c r="R191" s="6" t="s">
+        <v>2483</v>
+      </c>
+      <c r="S191" s="6" t="s">
+        <v>2484</v>
+      </c>
+      <c r="T191" s="6"/>
+      <c r="U191" s="6" t="s">
+        <v>2485</v>
+      </c>
+      <c r="V191" s="6" t="s">
+        <v>2486</v>
+      </c>
+      <c r="W191" s="6"/>
+      <c r="X191" s="6"/>
+      <c r="Y191" s="6"/>
+      <c r="Z191" s="6" t="s">
+        <v>2487</v>
+      </c>
+      <c r="AA191" s="6"/>
+      <c r="AB191" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC191" s="6" t="str">
+        <f>IF(AND(E191&lt;&gt;"",COUNTIF($E$2:$E$798,E191)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="6" t="s">
+        <v>2488</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C192" s="6"/>
+      <c r="D192" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>2489</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>2490</v>
+      </c>
+      <c r="G192" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>2491</v>
+      </c>
+      <c r="I192" s="6" t="s">
+        <v>2492</v>
+      </c>
+      <c r="J192" s="6" t="s">
+        <v>2493</v>
+      </c>
+      <c r="K192" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L192" s="6" t="s">
+        <v>2494</v>
+      </c>
+      <c r="M192" s="6" t="s">
+        <v>2495</v>
+      </c>
+      <c r="N192" s="6" t="s">
+        <v>2496</v>
+      </c>
+      <c r="O192" s="6" t="s">
+        <v>2497</v>
+      </c>
+      <c r="P192" s="6" t="s">
+        <v>2498</v>
+      </c>
+      <c r="Q192" s="6" t="s">
+        <v>2499</v>
+      </c>
+      <c r="R192" s="6" t="s">
+        <v>2500</v>
+      </c>
+      <c r="S192" s="6" t="s">
+        <v>2501</v>
+      </c>
+      <c r="T192" s="6"/>
+      <c r="U192" s="6" t="s">
+        <v>2502</v>
+      </c>
+      <c r="V192" s="6" t="s">
+        <v>2503</v>
+      </c>
+      <c r="W192" s="6"/>
+      <c r="X192" s="6"/>
+      <c r="Y192" s="6"/>
+      <c r="Z192" s="6" t="s">
+        <v>2504</v>
+      </c>
+      <c r="AA192" s="6"/>
+      <c r="AB192" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC192" s="6" t="str">
+        <f>IF(AND(E192&lt;&gt;"",COUNTIF($E$2:$E$798,E192)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="6" t="s">
+        <v>2505</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C193" s="6"/>
+      <c r="D193" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>2506</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>2507</v>
+      </c>
+      <c r="G193" s="6" t="s">
+        <v>2508</v>
+      </c>
+      <c r="H193" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="I193" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="J193" s="6" t="s">
+        <v>2509</v>
+      </c>
+      <c r="K193" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L193" s="6" t="s">
+        <v>2510</v>
+      </c>
+      <c r="M193" s="6" t="s">
+        <v>2511</v>
+      </c>
+      <c r="N193" s="6" t="s">
+        <v>2512</v>
+      </c>
+      <c r="O193" s="6" t="s">
+        <v>2513</v>
+      </c>
+      <c r="P193" s="6" t="s">
+        <v>2514</v>
+      </c>
+      <c r="Q193" s="6" t="s">
+        <v>2515</v>
+      </c>
+      <c r="R193" s="6" t="s">
+        <v>2516</v>
+      </c>
+      <c r="S193" s="6" t="s">
+        <v>2517</v>
+      </c>
+      <c r="T193" s="6"/>
+      <c r="U193" s="6" t="s">
+        <v>2518</v>
+      </c>
+      <c r="V193" s="6" t="s">
+        <v>2519</v>
+      </c>
+      <c r="W193" s="6"/>
+      <c r="X193" s="6"/>
+      <c r="Y193" s="6"/>
+      <c r="Z193" s="6" t="s">
+        <v>2520</v>
+      </c>
+      <c r="AA193" s="6"/>
+      <c r="AB193" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC193" s="6" t="str">
+        <f>IF(AND(E193&lt;&gt;"",COUNTIF($E$2:$E$798,E193)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="6" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C194" s="6"/>
+      <c r="D194" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>2522</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>2523</v>
+      </c>
+      <c r="G194" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="H194" s="6" t="s">
+        <v>2524</v>
+      </c>
+      <c r="I194" s="6" t="s">
+        <v>2525</v>
+      </c>
+      <c r="J194" s="6" t="s">
+        <v>2526</v>
+      </c>
+      <c r="K194" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L194" s="6" t="s">
+        <v>2527</v>
+      </c>
+      <c r="M194" s="6" t="s">
+        <v>2528</v>
+      </c>
+      <c r="N194" s="6" t="s">
+        <v>2529</v>
+      </c>
+      <c r="O194" s="6" t="s">
+        <v>2530</v>
+      </c>
+      <c r="P194" s="6" t="s">
+        <v>2531</v>
+      </c>
+      <c r="Q194" s="6" t="s">
+        <v>2532</v>
+      </c>
+      <c r="R194" s="6" t="s">
+        <v>2533</v>
+      </c>
+      <c r="S194" s="6" t="s">
+        <v>2534</v>
+      </c>
+      <c r="T194" s="6"/>
+      <c r="U194" s="6" t="s">
+        <v>2535</v>
+      </c>
+      <c r="V194" s="6" t="s">
+        <v>2536</v>
+      </c>
+      <c r="W194" s="6"/>
+      <c r="X194" s="6"/>
+      <c r="Y194" s="6"/>
+      <c r="Z194" s="6" t="s">
+        <v>2537</v>
+      </c>
+      <c r="AA194" s="6"/>
+      <c r="AB194" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC194" s="6" t="str">
+        <f>IF(AND(E194&lt;&gt;"",COUNTIF($E$2:$E$798,E194)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="6" t="s">
+        <v>2538</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C195" s="6"/>
+      <c r="D195" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F195" s="6" t="s">
+        <v>2540</v>
+      </c>
+      <c r="G195" s="6" t="s">
+        <v>2541</v>
+      </c>
+      <c r="H195" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="I195" s="6" t="s">
+        <v>2542</v>
+      </c>
+      <c r="J195" s="6" t="s">
+        <v>2543</v>
+      </c>
+      <c r="K195" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L195" s="6" t="s">
+        <v>2544</v>
+      </c>
+      <c r="M195" s="6" t="s">
+        <v>2545</v>
+      </c>
+      <c r="N195" s="6" t="s">
+        <v>2546</v>
+      </c>
+      <c r="O195" s="6" t="s">
+        <v>2547</v>
+      </c>
+      <c r="P195" s="6" t="s">
+        <v>2548</v>
+      </c>
+      <c r="Q195" s="6" t="s">
+        <v>2549</v>
+      </c>
+      <c r="R195" s="6" t="s">
+        <v>2550</v>
+      </c>
+      <c r="S195" s="6" t="s">
+        <v>2551</v>
+      </c>
+      <c r="T195" s="6"/>
+      <c r="U195" s="6" t="s">
+        <v>2552</v>
+      </c>
+      <c r="V195" s="6" t="s">
+        <v>2553</v>
+      </c>
+      <c r="W195" s="6"/>
+      <c r="X195" s="6"/>
+      <c r="Y195" s="6"/>
+      <c r="Z195" s="6" t="s">
+        <v>2554</v>
+      </c>
+      <c r="AA195" s="6"/>
+      <c r="AB195" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC195" s="6" t="str">
+        <f>IF(AND(E195&lt;&gt;"",COUNTIF($E$2:$E$798,E195)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="6" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C196" s="6"/>
+      <c r="D196" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E196" s="6" t="s">
+        <v>2556</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="G196" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H196" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I196" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J196" s="6" t="s">
+        <v>2557</v>
+      </c>
+      <c r="K196" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L196" s="6" t="s">
+        <v>2558</v>
+      </c>
+      <c r="M196" s="6" t="s">
+        <v>2545</v>
+      </c>
+      <c r="N196" s="6" t="s">
+        <v>2559</v>
+      </c>
+      <c r="O196" s="6" t="s">
+        <v>2560</v>
+      </c>
+      <c r="P196" s="6" t="s">
+        <v>2561</v>
+      </c>
+      <c r="Q196" s="6" t="s">
+        <v>2562</v>
+      </c>
+      <c r="R196" s="6" t="s">
+        <v>2563</v>
+      </c>
+      <c r="S196" s="6" t="s">
+        <v>2564</v>
+      </c>
+      <c r="T196" s="6"/>
+      <c r="U196" s="6" t="s">
+        <v>2565</v>
+      </c>
+      <c r="V196" s="6" t="s">
+        <v>2566</v>
+      </c>
+      <c r="W196" s="6"/>
+      <c r="X196" s="6"/>
+      <c r="Y196" s="6"/>
+      <c r="Z196" s="6" t="s">
+        <v>2567</v>
+      </c>
+      <c r="AA196" s="6"/>
+      <c r="AB196" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC196" s="6" t="str">
+        <f>IF(AND(E196&lt;&gt;"",COUNTIF($E$2:$E$798,E196)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="6" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C197" s="6"/>
+      <c r="D197" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>2569</v>
+      </c>
+      <c r="F197" s="6" t="s">
+        <v>2570</v>
+      </c>
+      <c r="G197" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H197" s="6" t="s">
+        <v>2571</v>
+      </c>
+      <c r="I197" s="6" t="s">
+        <v>2572</v>
+      </c>
+      <c r="J197" s="6" t="s">
+        <v>2573</v>
+      </c>
+      <c r="K197" s="6" t="s">
+        <v>2574</v>
+      </c>
+      <c r="L197" s="6" t="s">
+        <v>2575</v>
+      </c>
+      <c r="M197" s="6" t="s">
+        <v>2576</v>
+      </c>
+      <c r="N197" s="6" t="s">
+        <v>2577</v>
+      </c>
+      <c r="O197" s="6" t="s">
+        <v>2578</v>
+      </c>
+      <c r="P197" s="6" t="s">
+        <v>2579</v>
+      </c>
+      <c r="Q197" s="6" t="s">
+        <v>2580</v>
+      </c>
+      <c r="R197" s="6" t="s">
+        <v>2581</v>
+      </c>
+      <c r="S197" s="6" t="s">
+        <v>2582</v>
+      </c>
+      <c r="T197" s="6"/>
+      <c r="U197" s="6" t="s">
+        <v>2583</v>
+      </c>
+      <c r="V197" s="6" t="s">
+        <v>2584</v>
+      </c>
+      <c r="W197" s="6"/>
+      <c r="X197" s="6"/>
+      <c r="Y197" s="6"/>
+      <c r="Z197" s="6" t="s">
+        <v>2585</v>
+      </c>
+      <c r="AA197" s="6"/>
+      <c r="AB197" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC197" s="6" t="str">
+        <f>IF(AND(E197&lt;&gt;"",COUNTIF($E$2:$E$798,E197)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="6" t="s">
+        <v>2586</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C198" s="6"/>
+      <c r="D198" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E198" s="6" t="s">
+        <v>2587</v>
+      </c>
+      <c r="F198" s="6" t="s">
+        <v>2588</v>
+      </c>
+      <c r="G198" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H198" s="6" t="s">
+        <v>2589</v>
+      </c>
+      <c r="I198" s="6" t="s">
+        <v>2590</v>
+      </c>
+      <c r="J198" s="6" t="s">
+        <v>2591</v>
+      </c>
+      <c r="K198" s="6" t="s">
+        <v>2574</v>
+      </c>
+      <c r="L198" s="6" t="s">
+        <v>2592</v>
+      </c>
+      <c r="M198" s="6" t="s">
+        <v>2593</v>
+      </c>
+      <c r="N198" s="6" t="s">
+        <v>2594</v>
+      </c>
+      <c r="O198" s="6" t="s">
+        <v>2595</v>
+      </c>
+      <c r="P198" s="6" t="s">
+        <v>2596</v>
+      </c>
+      <c r="Q198" s="6" t="s">
+        <v>2597</v>
+      </c>
+      <c r="R198" s="6" t="s">
+        <v>2598</v>
+      </c>
+      <c r="S198" s="6" t="s">
+        <v>2599</v>
+      </c>
+      <c r="T198" s="6"/>
+      <c r="U198" s="6" t="s">
+        <v>2600</v>
+      </c>
+      <c r="V198" s="6" t="s">
+        <v>2601</v>
+      </c>
+      <c r="W198" s="6"/>
+      <c r="X198" s="6"/>
+      <c r="Y198" s="6"/>
+      <c r="Z198" s="6" t="s">
+        <v>2602</v>
+      </c>
+      <c r="AA198" s="6"/>
+      <c r="AB198" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC198" s="6" t="str">
+        <f>IF(AND(E198&lt;&gt;"",COUNTIF($E$2:$E$798,E198)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="6" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C199" s="6"/>
+      <c r="D199" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E199" s="6" t="s">
+        <v>2604</v>
+      </c>
+      <c r="F199" s="6" t="s">
+        <v>2605</v>
+      </c>
+      <c r="G199" s="6" t="s">
+        <v>2606</v>
+      </c>
+      <c r="H199" s="6" t="s">
+        <v>2607</v>
+      </c>
+      <c r="I199" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J199" s="6" t="s">
+        <v>2608</v>
+      </c>
+      <c r="K199" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L199" s="6" t="s">
+        <v>2609</v>
+      </c>
+      <c r="M199" s="6" t="s">
+        <v>2610</v>
+      </c>
+      <c r="N199" s="6" t="s">
+        <v>2611</v>
+      </c>
+      <c r="O199" s="6" t="s">
+        <v>2612</v>
+      </c>
+      <c r="P199" s="6" t="s">
+        <v>2613</v>
+      </c>
+      <c r="Q199" s="6" t="s">
+        <v>2614</v>
+      </c>
+      <c r="R199" s="6" t="s">
+        <v>2615</v>
+      </c>
+      <c r="S199" s="6" t="s">
+        <v>2616</v>
+      </c>
+      <c r="T199" s="6"/>
+      <c r="U199" s="6" t="s">
+        <v>2617</v>
+      </c>
+      <c r="V199" s="6" t="s">
+        <v>2618</v>
+      </c>
+      <c r="W199" s="6"/>
+      <c r="X199" s="6"/>
+      <c r="Y199" s="6"/>
+      <c r="Z199" s="6" t="s">
+        <v>2619</v>
+      </c>
+      <c r="AA199" s="6"/>
+      <c r="AB199" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC199" s="6" t="str">
+        <f>IF(AND(E199&lt;&gt;"",COUNTIF($E$2:$E$798,E199)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="6" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C200" s="6"/>
+      <c r="D200" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>2621</v>
+      </c>
+      <c r="F200" s="6" t="s">
+        <v>2622</v>
+      </c>
+      <c r="G200" s="6" t="s">
+        <v>2623</v>
+      </c>
+      <c r="H200" s="6" t="s">
+        <v>2624</v>
+      </c>
+      <c r="I200" s="6" t="s">
+        <v>2625</v>
+      </c>
+      <c r="J200" s="6" t="s">
+        <v>2626</v>
+      </c>
+      <c r="K200" s="6" t="s">
+        <v>2627</v>
+      </c>
+      <c r="L200" s="6" t="s">
+        <v>2628</v>
+      </c>
+      <c r="M200" s="6" t="s">
+        <v>2629</v>
+      </c>
+      <c r="N200" s="6" t="s">
+        <v>2630</v>
+      </c>
+      <c r="O200" s="6" t="s">
+        <v>2631</v>
+      </c>
+      <c r="P200" s="6" t="s">
+        <v>2632</v>
+      </c>
+      <c r="Q200" s="6" t="s">
+        <v>2633</v>
+      </c>
+      <c r="R200" s="6" t="s">
+        <v>2634</v>
+      </c>
+      <c r="S200" s="6" t="s">
+        <v>2635</v>
+      </c>
+      <c r="T200" s="6"/>
+      <c r="U200" s="6" t="s">
+        <v>2636</v>
+      </c>
+      <c r="V200" s="6" t="s">
+        <v>2637</v>
+      </c>
+      <c r="W200" s="6"/>
+      <c r="X200" s="6"/>
+      <c r="Y200" s="6"/>
+      <c r="Z200" s="6" t="s">
+        <v>2638</v>
+      </c>
+      <c r="AA200" s="6"/>
+      <c r="AB200" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC200" s="6" t="str">
+        <f>IF(AND(E200&lt;&gt;"",COUNTIF($E$2:$E$798,E200)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="6" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C201" s="6"/>
+      <c r="D201" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>2640</v>
+      </c>
+      <c r="F201" s="6" t="s">
+        <v>2641</v>
+      </c>
+      <c r="G201" s="6" t="s">
+        <v>2623</v>
+      </c>
+      <c r="H201" s="6" t="s">
+        <v>2642</v>
+      </c>
+      <c r="I201" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="J201" s="6" t="s">
+        <v>2643</v>
+      </c>
+      <c r="K201" s="6" t="s">
+        <v>2627</v>
+      </c>
+      <c r="L201" s="6" t="s">
+        <v>2644</v>
+      </c>
+      <c r="M201" s="6" t="s">
+        <v>2645</v>
+      </c>
+      <c r="N201" s="6" t="s">
+        <v>2646</v>
+      </c>
+      <c r="O201" s="6" t="s">
+        <v>2647</v>
+      </c>
+      <c r="P201" s="6" t="s">
+        <v>2648</v>
+      </c>
+      <c r="Q201" s="6" t="s">
+        <v>2649</v>
+      </c>
+      <c r="R201" s="6" t="s">
+        <v>2650</v>
+      </c>
+      <c r="S201" s="6" t="s">
+        <v>2651</v>
+      </c>
+      <c r="T201" s="6"/>
+      <c r="U201" s="6" t="s">
+        <v>2652</v>
+      </c>
+      <c r="V201" s="6" t="s">
+        <v>2653</v>
+      </c>
+      <c r="W201" s="6"/>
+      <c r="X201" s="6"/>
+      <c r="Y201" s="6"/>
+      <c r="Z201" s="6" t="s">
+        <v>2654</v>
+      </c>
+      <c r="AA201" s="6"/>
+      <c r="AB201" s="3">
+        <v>46313</v>
+      </c>
+      <c r="AC201" s="6" t="str">
+        <f>IF(AND(E201&lt;&gt;"",COUNTIF($E$2:$E$798,E201)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A202" s="5" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>2656</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>2657</v>
+      </c>
+      <c r="G202" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H202" s="5" t="s">
+        <v>2444</v>
+      </c>
+      <c r="I202" s="5" t="s">
+        <v>2658</v>
+      </c>
+      <c r="J202" s="5" t="s">
+        <v>2659</v>
+      </c>
+      <c r="K202" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="L202" s="5" t="s">
+        <v>2661</v>
+      </c>
+      <c r="M202" s="7">
+        <v>46423</v>
+      </c>
+      <c r="N202" s="5" t="s">
+        <v>2662</v>
+      </c>
+      <c r="O202" s="5" t="s">
+        <v>2663</v>
+      </c>
+      <c r="P202" s="5" t="s">
+        <v>2450</v>
+      </c>
+      <c r="Q202" s="5" t="s">
+        <v>2664</v>
+      </c>
+      <c r="R202" s="5" t="s">
+        <v>2665</v>
+      </c>
+      <c r="S202" s="5" t="s">
+        <v>2666</v>
+      </c>
+      <c r="U202" s="5" t="s">
+        <v>2667</v>
+      </c>
+      <c r="V202" s="5" t="s">
+        <v>2455</v>
+      </c>
+      <c r="Z202" s="5" t="s">
+        <v>2668</v>
+      </c>
+      <c r="AA202" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB202" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC202"/>
+    </row>
+    <row r="203" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A203" s="5" t="s">
+        <v>2669</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>2670</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G203" s="5" t="s">
+        <v>2672</v>
+      </c>
+      <c r="H203" s="5" t="s">
+        <v>2673</v>
+      </c>
+      <c r="I203" s="5" t="s">
+        <v>2674</v>
+      </c>
+      <c r="J203" s="5" t="s">
+        <v>2675</v>
+      </c>
+      <c r="K203" s="5" t="s">
+        <v>2676</v>
+      </c>
+      <c r="L203" s="5" t="s">
+        <v>2677</v>
+      </c>
+      <c r="M203" s="5" t="s">
+        <v>2678</v>
+      </c>
+      <c r="N203" s="5" t="s">
+        <v>2679</v>
+      </c>
+      <c r="O203" s="5" t="s">
+        <v>2680</v>
+      </c>
+      <c r="P203" s="5" t="s">
+        <v>2681</v>
+      </c>
+      <c r="Q203" s="5" t="s">
+        <v>2682</v>
+      </c>
+      <c r="R203" s="5" t="s">
+        <v>2683</v>
+      </c>
+      <c r="S203" s="5" t="s">
+        <v>2684</v>
+      </c>
+      <c r="U203" s="5" t="s">
+        <v>2685</v>
+      </c>
+      <c r="V203" s="5" t="s">
+        <v>2686</v>
+      </c>
+      <c r="Z203" s="5" t="s">
+        <v>2687</v>
+      </c>
+      <c r="AA203" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB203" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC203"/>
+    </row>
+    <row r="204" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A204" s="5" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E204" s="5" t="s">
+        <v>2688</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>2689</v>
+      </c>
+      <c r="G204" s="5" t="s">
+        <v>2412</v>
+      </c>
+      <c r="H204" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="I204" s="5" t="s">
+        <v>2691</v>
+      </c>
+      <c r="J204" s="5" t="s">
+        <v>2692</v>
+      </c>
+      <c r="K204" s="5" t="s">
+        <v>2693</v>
+      </c>
+      <c r="L204" s="5" t="s">
+        <v>2694</v>
+      </c>
+      <c r="M204" s="5" t="s">
+        <v>2695</v>
+      </c>
+      <c r="N204" s="5" t="s">
+        <v>2696</v>
+      </c>
+      <c r="O204" s="5" t="s">
+        <v>2697</v>
+      </c>
+      <c r="P204" s="5" t="s">
+        <v>2698</v>
+      </c>
+      <c r="Q204" s="5" t="s">
+        <v>2699</v>
+      </c>
+      <c r="R204" s="5" t="s">
+        <v>2700</v>
+      </c>
+      <c r="S204" s="5" t="s">
+        <v>2701</v>
+      </c>
+      <c r="U204" s="5" t="s">
+        <v>2702</v>
+      </c>
+      <c r="V204" s="5" t="s">
+        <v>2424</v>
+      </c>
+      <c r="Z204" s="5" t="s">
+        <v>2703</v>
+      </c>
+      <c r="AA204" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB204" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC204"/>
+    </row>
+    <row r="205" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A205" s="5" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E205" s="5" t="s">
+        <v>2705</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>2689</v>
+      </c>
+      <c r="G205" s="5" t="s">
+        <v>2412</v>
+      </c>
+      <c r="H205" s="5" t="s">
+        <v>2706</v>
+      </c>
+      <c r="I205" s="5" t="s">
+        <v>2691</v>
+      </c>
+      <c r="J205" s="5" t="s">
+        <v>2707</v>
+      </c>
+      <c r="K205" s="5" t="s">
+        <v>2693</v>
+      </c>
+      <c r="L205" s="5" t="s">
+        <v>2708</v>
+      </c>
+      <c r="M205" s="5" t="s">
+        <v>2709</v>
+      </c>
+      <c r="N205" s="5" t="s">
+        <v>2710</v>
+      </c>
+      <c r="O205" s="5" t="s">
+        <v>2711</v>
+      </c>
+      <c r="P205" s="5" t="s">
+        <v>2712</v>
+      </c>
+      <c r="Q205" s="5" t="s">
+        <v>2713</v>
+      </c>
+      <c r="R205" s="5" t="s">
+        <v>2714</v>
+      </c>
+      <c r="S205" s="5" t="s">
+        <v>2715</v>
+      </c>
+      <c r="U205" s="5" t="s">
+        <v>2716</v>
+      </c>
+      <c r="V205" s="5" t="s">
+        <v>2439</v>
+      </c>
+      <c r="Z205" s="5" t="s">
+        <v>2717</v>
+      </c>
+      <c r="AA205" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB205" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC205"/>
+    </row>
+    <row r="206" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A206" s="5" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E206" s="5" t="s">
+        <v>2719</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>2720</v>
+      </c>
+      <c r="G206" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H206" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="I206" s="5" t="s">
+        <v>2721</v>
+      </c>
+      <c r="J206" s="5" t="s">
+        <v>2722</v>
+      </c>
+      <c r="K206" s="5" t="s">
+        <v>2723</v>
+      </c>
+      <c r="L206" s="5" t="s">
+        <v>2724</v>
+      </c>
+      <c r="M206" s="5" t="s">
+        <v>2725</v>
+      </c>
+      <c r="N206" s="5" t="s">
+        <v>2726</v>
+      </c>
+      <c r="O206" s="5" t="s">
+        <v>2727</v>
+      </c>
+      <c r="P206" s="5" t="s">
+        <v>2728</v>
+      </c>
+      <c r="Q206" s="5" t="s">
+        <v>2729</v>
+      </c>
+      <c r="R206" s="5" t="s">
+        <v>2730</v>
+      </c>
+      <c r="S206" s="5" t="s">
+        <v>2731</v>
+      </c>
+      <c r="U206" s="5" t="s">
+        <v>2732</v>
+      </c>
+      <c r="V206" s="5" t="s">
+        <v>2733</v>
+      </c>
+      <c r="Z206" s="5" t="s">
+        <v>2734</v>
+      </c>
+      <c r="AA206" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB206" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC206"/>
+    </row>
+    <row r="207" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A207" s="5" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E207" s="5" t="s">
+        <v>2736</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>2737</v>
+      </c>
+      <c r="G207" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H207" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="I207" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="J207" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="K207" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="L207" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="M207" s="5" t="s">
+        <v>2739</v>
+      </c>
+      <c r="N207" s="5" t="s">
+        <v>2740</v>
+      </c>
+      <c r="O207" s="5" t="s">
+        <v>2741</v>
+      </c>
+      <c r="P207" s="5" t="s">
+        <v>2742</v>
+      </c>
+      <c r="Q207" s="5" t="s">
+        <v>2743</v>
+      </c>
+      <c r="R207" s="5" t="s">
+        <v>2744</v>
+      </c>
+      <c r="S207" s="5" t="s">
+        <v>2744</v>
+      </c>
+      <c r="U207" s="5" t="s">
+        <v>2745</v>
+      </c>
+      <c r="V207" s="5" t="s">
+        <v>2746</v>
+      </c>
       <c r="AA207" s="4"/>
-      <c r="AB207" s="4"/>
-      <c r="AC207" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="27:29" x14ac:dyDescent="0.3">
+      <c r="AB207" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC207" s="8">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="208" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A208" s="5" t="s">
+        <v>2747</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E208" s="5" t="s">
+        <v>2748</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>2749</v>
+      </c>
+      <c r="G208" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H208" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="I208" s="5" t="s">
+        <v>2750</v>
+      </c>
+      <c r="J208" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="K208" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="L208" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="M208" s="5" t="s">
+        <v>2751</v>
+      </c>
+      <c r="N208" s="5" t="s">
+        <v>2752</v>
+      </c>
+      <c r="O208" s="5" t="s">
+        <v>2741</v>
+      </c>
+      <c r="P208" s="5" t="s">
+        <v>2753</v>
+      </c>
+      <c r="Q208" s="5" t="s">
+        <v>2754</v>
+      </c>
+      <c r="R208" s="5" t="s">
+        <v>2744</v>
+      </c>
+      <c r="S208" s="5" t="s">
+        <v>2744</v>
+      </c>
+      <c r="U208" s="5" t="s">
+        <v>2755</v>
+      </c>
+      <c r="V208" s="5" t="s">
+        <v>2756</v>
+      </c>
       <c r="AA208" s="4"/>
-      <c r="AB208" s="4"/>
-      <c r="AC208" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="27:29" x14ac:dyDescent="0.3">
+      <c r="AB208" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC208" s="8">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="209" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A209" s="5" t="s">
+        <v>2757</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>2758</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>2759</v>
+      </c>
+      <c r="G209" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="H209" s="5" t="s">
+        <v>2760</v>
+      </c>
+      <c r="I209" s="5" t="s">
+        <v>2761</v>
+      </c>
+      <c r="J209" s="5" t="s">
+        <v>2762</v>
+      </c>
+      <c r="K209" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="L209" s="5" t="s">
+        <v>2763</v>
+      </c>
+      <c r="M209" s="5" t="s">
+        <v>2764</v>
+      </c>
+      <c r="N209" s="5" t="s">
+        <v>2765</v>
+      </c>
+      <c r="O209" s="5" t="s">
+        <v>2766</v>
+      </c>
+      <c r="P209" s="5" t="s">
+        <v>2767</v>
+      </c>
+      <c r="Q209" s="5" t="s">
+        <v>2768</v>
+      </c>
+      <c r="R209" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="S209" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="U209" s="5" t="s">
+        <v>2770</v>
+      </c>
+      <c r="V209" s="5" t="s">
+        <v>2771</v>
+      </c>
       <c r="AA209" s="4"/>
-      <c r="AB209" s="4"/>
-      <c r="AC209" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="27:29" x14ac:dyDescent="0.3">
+      <c r="AB209" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC209" s="8">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="210" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A210" s="5" t="s">
+        <v>2772</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E210" s="5" t="s">
+        <v>2773</v>
+      </c>
+      <c r="F210" s="5" t="s">
+        <v>2774</v>
+      </c>
+      <c r="G210" s="5" t="s">
+        <v>2775</v>
+      </c>
+      <c r="H210" s="5" t="s">
+        <v>2776</v>
+      </c>
+      <c r="I210" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="J210" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="K210" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="L210" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="M210" s="5" t="s">
+        <v>2777</v>
+      </c>
+      <c r="N210" s="5" t="s">
+        <v>2778</v>
+      </c>
+      <c r="O210" s="5" t="s">
+        <v>2741</v>
+      </c>
+      <c r="P210" s="5" t="s">
+        <v>2779</v>
+      </c>
+      <c r="Q210" s="5" t="s">
+        <v>2780</v>
+      </c>
+      <c r="R210" s="5" t="s">
+        <v>2744</v>
+      </c>
+      <c r="S210" s="5" t="s">
+        <v>2744</v>
+      </c>
+      <c r="U210" s="5" t="s">
+        <v>2781</v>
+      </c>
+      <c r="V210" s="5" t="s">
+        <v>2782</v>
+      </c>
       <c r="AA210" s="4"/>
-      <c r="AB210" s="4"/>
-      <c r="AC210" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="27:29" x14ac:dyDescent="0.3">
+      <c r="AB210" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC210" s="8">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="211" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A211" s="5" t="s">
+        <v>2783</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E211" s="5" t="s">
+        <v>2784</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>2785</v>
+      </c>
+      <c r="G211" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H211" s="5" t="s">
+        <v>2786</v>
+      </c>
+      <c r="I211" s="5" t="s">
+        <v>2787</v>
+      </c>
+      <c r="J211" s="5" t="s">
+        <v>2788</v>
+      </c>
+      <c r="K211" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="L211" s="5" t="s">
+        <v>2789</v>
+      </c>
+      <c r="M211" s="8">
+        <v>46122</v>
+      </c>
+      <c r="N211" s="5" t="s">
+        <v>2790</v>
+      </c>
+      <c r="O211" s="5" t="s">
+        <v>2741</v>
+      </c>
+      <c r="P211" s="5" t="s">
+        <v>2791</v>
+      </c>
+      <c r="Q211" s="5" t="s">
+        <v>2792</v>
+      </c>
+      <c r="R211" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="S211" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="U211" s="5" t="s">
+        <v>2793</v>
+      </c>
+      <c r="V211" s="5" t="s">
+        <v>2794</v>
+      </c>
       <c r="AA211" s="4"/>
-      <c r="AB211" s="4"/>
-      <c r="AC211" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="27:29" x14ac:dyDescent="0.3">
+      <c r="AB211" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC211" s="8">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="212" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A212" s="5" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E212" s="5" t="s">
+        <v>2796</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>2797</v>
+      </c>
+      <c r="G212" s="5" t="s">
+        <v>2798</v>
+      </c>
+      <c r="H212" s="5" t="s">
+        <v>2799</v>
+      </c>
+      <c r="I212" s="5" t="s">
+        <v>2800</v>
+      </c>
+      <c r="J212" s="5" t="s">
+        <v>2801</v>
+      </c>
+      <c r="K212" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="L212" s="5" t="s">
+        <v>2802</v>
+      </c>
+      <c r="M212" s="8">
+        <v>46120</v>
+      </c>
+      <c r="N212" s="5" t="s">
+        <v>2803</v>
+      </c>
+      <c r="O212" s="5" t="s">
+        <v>2741</v>
+      </c>
+      <c r="P212" s="5" t="s">
+        <v>2804</v>
+      </c>
+      <c r="Q212" s="5" t="s">
+        <v>2805</v>
+      </c>
+      <c r="R212" s="5" t="s">
+        <v>2806</v>
+      </c>
+      <c r="S212" s="5" t="s">
+        <v>2806</v>
+      </c>
+      <c r="U212" s="5" t="s">
+        <v>2807</v>
+      </c>
+      <c r="V212" s="5" t="s">
+        <v>2808</v>
+      </c>
       <c r="AA212" s="4"/>
-      <c r="AB212" s="4"/>
-      <c r="AC212" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA213" s="4"/>
-      <c r="AB213" s="4"/>
-      <c r="AC213" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA214" s="4"/>
-      <c r="AB214" s="4"/>
-      <c r="AC214" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA215" s="4"/>
-      <c r="AB215" s="4"/>
-      <c r="AC215" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA216" s="4"/>
-      <c r="AB216" s="4"/>
-      <c r="AC216" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="27:29" x14ac:dyDescent="0.3">
+      <c r="AB212" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC212" s="8">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A213" s="5" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D213" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E213" s="5" t="s">
+        <v>2810</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>2811</v>
+      </c>
+      <c r="G213" s="5" t="s">
+        <v>2412</v>
+      </c>
+      <c r="H213" s="5" t="s">
+        <v>2812</v>
+      </c>
+      <c r="I213" s="5" t="s">
+        <v>2813</v>
+      </c>
+      <c r="J213" s="5" t="s">
+        <v>2814</v>
+      </c>
+      <c r="K213" s="5" t="s">
+        <v>2815</v>
+      </c>
+      <c r="L213" s="5" t="s">
+        <v>2816</v>
+      </c>
+      <c r="M213" s="5" t="s">
+        <v>2817</v>
+      </c>
+      <c r="N213" s="5" t="s">
+        <v>2818</v>
+      </c>
+      <c r="O213" s="5" t="s">
+        <v>2819</v>
+      </c>
+      <c r="P213" s="5" t="s">
+        <v>2820</v>
+      </c>
+      <c r="Q213" s="5" t="s">
+        <v>2821</v>
+      </c>
+      <c r="R213" s="5" t="s">
+        <v>2822</v>
+      </c>
+      <c r="S213" s="5" t="s">
+        <v>2823</v>
+      </c>
+      <c r="U213" s="5" t="s">
+        <v>2824</v>
+      </c>
+      <c r="V213" s="5" t="s">
+        <v>2825</v>
+      </c>
+      <c r="Z213" s="5" t="s">
+        <v>2826</v>
+      </c>
+      <c r="AA213" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB213" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC213"/>
+    </row>
+    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A214" s="5" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E214" s="5" t="s">
+        <v>2828</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>2829</v>
+      </c>
+      <c r="G214" s="5" t="s">
+        <v>2412</v>
+      </c>
+      <c r="H214" s="5" t="s">
+        <v>2830</v>
+      </c>
+      <c r="I214" s="5" t="s">
+        <v>2831</v>
+      </c>
+      <c r="J214" s="5" t="s">
+        <v>2832</v>
+      </c>
+      <c r="K214" s="5" t="s">
+        <v>2833</v>
+      </c>
+      <c r="L214" s="5" t="s">
+        <v>2834</v>
+      </c>
+      <c r="M214" s="5" t="s">
+        <v>2835</v>
+      </c>
+      <c r="N214" s="5" t="s">
+        <v>2836</v>
+      </c>
+      <c r="O214" s="5" t="s">
+        <v>2837</v>
+      </c>
+      <c r="P214" s="5" t="s">
+        <v>2838</v>
+      </c>
+      <c r="Q214" s="5" t="s">
+        <v>2839</v>
+      </c>
+      <c r="R214" s="5" t="s">
+        <v>2840</v>
+      </c>
+      <c r="S214" s="5" t="s">
+        <v>2841</v>
+      </c>
+      <c r="U214" s="5" t="s">
+        <v>2842</v>
+      </c>
+      <c r="V214" s="5" t="s">
+        <v>2843</v>
+      </c>
+      <c r="Z214" s="5" t="s">
+        <v>2844</v>
+      </c>
+      <c r="AA214" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB214" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC214"/>
+    </row>
+    <row r="215" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A215" s="5" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D215" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E215" s="5" t="s">
+        <v>2846</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>2847</v>
+      </c>
+      <c r="G215" s="5" t="s">
+        <v>2848</v>
+      </c>
+      <c r="H215" s="5" t="s">
+        <v>2849</v>
+      </c>
+      <c r="I215" s="5" t="s">
+        <v>2850</v>
+      </c>
+      <c r="J215" s="5" t="s">
+        <v>2851</v>
+      </c>
+      <c r="K215" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L215" s="5" t="s">
+        <v>2852</v>
+      </c>
+      <c r="M215" s="5" t="s">
+        <v>2853</v>
+      </c>
+      <c r="N215" s="5" t="s">
+        <v>2854</v>
+      </c>
+      <c r="O215" s="5" t="s">
+        <v>2855</v>
+      </c>
+      <c r="P215" s="5" t="s">
+        <v>2856</v>
+      </c>
+      <c r="Q215" s="5" t="s">
+        <v>2857</v>
+      </c>
+      <c r="R215" s="5" t="s">
+        <v>2858</v>
+      </c>
+      <c r="S215" s="5" t="s">
+        <v>2859</v>
+      </c>
+      <c r="U215" s="5" t="s">
+        <v>2860</v>
+      </c>
+      <c r="V215" s="5" t="s">
+        <v>2861</v>
+      </c>
+      <c r="Z215" s="5" t="s">
+        <v>2862</v>
+      </c>
+      <c r="AA215" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB215" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC215"/>
+    </row>
+    <row r="216" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A216" s="5" t="s">
+        <v>2863</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E216" s="5" t="s">
+        <v>2864</v>
+      </c>
+      <c r="F216" s="5" t="s">
+        <v>2865</v>
+      </c>
+      <c r="G216" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="H216" s="5" t="s">
+        <v>2866</v>
+      </c>
+      <c r="I216" s="5" t="s">
+        <v>2867</v>
+      </c>
+      <c r="J216" s="5" t="s">
+        <v>2868</v>
+      </c>
+      <c r="K216" s="5" t="s">
+        <v>2869</v>
+      </c>
+      <c r="L216" s="5" t="s">
+        <v>2870</v>
+      </c>
+      <c r="M216" s="5" t="s">
+        <v>2871</v>
+      </c>
+      <c r="N216" s="5" t="s">
+        <v>2872</v>
+      </c>
+      <c r="O216" s="5" t="s">
+        <v>2873</v>
+      </c>
+      <c r="P216" s="5" t="s">
+        <v>2874</v>
+      </c>
+      <c r="Q216" s="5" t="s">
+        <v>2875</v>
+      </c>
+      <c r="R216" s="5" t="s">
+        <v>2876</v>
+      </c>
+      <c r="S216" s="5" t="s">
+        <v>2877</v>
+      </c>
+      <c r="U216" s="5" t="s">
+        <v>2878</v>
+      </c>
+      <c r="V216" s="5" t="s">
+        <v>2879</v>
+      </c>
+      <c r="Z216" s="5" t="s">
+        <v>2880</v>
+      </c>
+      <c r="AA216" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB216" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC216"/>
+    </row>
+    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA217" s="4"/>
       <c r="AB217" s="4"/>
       <c r="AC217" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E217&lt;&gt;"",COUNTIF($E$2:$E$798,E217)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA218" s="4"/>
       <c r="AB218" s="4"/>
       <c r="AC218" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E218&lt;&gt;"",COUNTIF($E$2:$E$798,E218)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA219" s="4"/>
       <c r="AB219" s="4"/>
       <c r="AC219" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E219&lt;&gt;"",COUNTIF($E$2:$E$798,E219)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA220" s="4"/>
       <c r="AB220" s="4"/>
       <c r="AC220" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E220&lt;&gt;"",COUNTIF($E$2:$E$798,E220)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA221" s="4"/>
       <c r="AB221" s="4"/>
       <c r="AC221" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E221&lt;&gt;"",COUNTIF($E$2:$E$798,E221)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA222" s="4"/>
       <c r="AB222" s="4"/>
       <c r="AC222" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E222&lt;&gt;"",COUNTIF($E$2:$E$798,E222)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA223" s="4"/>
       <c r="AB223" s="4"/>
       <c r="AC223" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E223&lt;&gt;"",COUNTIF($E$2:$E$798,E223)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA224" s="4"/>
       <c r="AB224" s="4"/>
       <c r="AC224" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E224&lt;&gt;"",COUNTIF($E$2:$E$798,E224)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20662,7 +24923,7 @@
       <c r="AA225" s="4"/>
       <c r="AB225" s="4"/>
       <c r="AC225" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E225&lt;&gt;"",COUNTIF($E$2:$E$798,E225)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20670,7 +24931,7 @@
       <c r="AA226" s="4"/>
       <c r="AB226" s="4"/>
       <c r="AC226" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E226&lt;&gt;"",COUNTIF($E$2:$E$798,E226)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20678,7 +24939,7 @@
       <c r="AA227" s="4"/>
       <c r="AB227" s="4"/>
       <c r="AC227" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E227&lt;&gt;"",COUNTIF($E$2:$E$798,E227)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20686,7 +24947,7 @@
       <c r="AA228" s="4"/>
       <c r="AB228" s="4"/>
       <c r="AC228" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E228&lt;&gt;"",COUNTIF($E$2:$E$798,E228)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20694,7 +24955,7 @@
       <c r="AA229" s="4"/>
       <c r="AB229" s="4"/>
       <c r="AC229" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E229&lt;&gt;"",COUNTIF($E$2:$E$798,E229)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20702,7 +24963,7 @@
       <c r="AA230" s="4"/>
       <c r="AB230" s="4"/>
       <c r="AC230" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E230&lt;&gt;"",COUNTIF($E$2:$E$798,E230)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20710,7 +24971,7 @@
       <c r="AA231" s="4"/>
       <c r="AB231" s="4"/>
       <c r="AC231" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E231&lt;&gt;"",COUNTIF($E$2:$E$798,E231)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20718,7 +24979,7 @@
       <c r="AA232" s="4"/>
       <c r="AB232" s="4"/>
       <c r="AC232" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E232&lt;&gt;"",COUNTIF($E$2:$E$798,E232)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20726,7 +24987,7 @@
       <c r="AA233" s="4"/>
       <c r="AB233" s="4"/>
       <c r="AC233" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E233&lt;&gt;"",COUNTIF($E$2:$E$798,E233)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20734,7 +24995,7 @@
       <c r="AA234" s="4"/>
       <c r="AB234" s="4"/>
       <c r="AC234" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E234&lt;&gt;"",COUNTIF($E$2:$E$798,E234)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20742,7 +25003,7 @@
       <c r="AA235" s="4"/>
       <c r="AB235" s="4"/>
       <c r="AC235" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E235&lt;&gt;"",COUNTIF($E$2:$E$798,E235)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20750,7 +25011,7 @@
       <c r="AA236" s="4"/>
       <c r="AB236" s="4"/>
       <c r="AC236" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E236&lt;&gt;"",COUNTIF($E$2:$E$798,E236)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20758,7 +25019,7 @@
       <c r="AA237" s="4"/>
       <c r="AB237" s="4"/>
       <c r="AC237" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E237&lt;&gt;"",COUNTIF($E$2:$E$798,E237)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20766,7 +25027,7 @@
       <c r="AA238" s="4"/>
       <c r="AB238" s="4"/>
       <c r="AC238" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E238&lt;&gt;"",COUNTIF($E$2:$E$798,E238)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20774,7 +25035,7 @@
       <c r="AA239" s="4"/>
       <c r="AB239" s="4"/>
       <c r="AC239" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E239&lt;&gt;"",COUNTIF($E$2:$E$798,E239)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20782,7 +25043,7 @@
       <c r="AA240" s="4"/>
       <c r="AB240" s="4"/>
       <c r="AC240" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E240&lt;&gt;"",COUNTIF($E$2:$E$798,E240)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20790,7 +25051,7 @@
       <c r="AA241" s="4"/>
       <c r="AB241" s="4"/>
       <c r="AC241" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E241&lt;&gt;"",COUNTIF($E$2:$E$798,E241)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20798,7 +25059,7 @@
       <c r="AA242" s="4"/>
       <c r="AB242" s="4"/>
       <c r="AC242" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E242&lt;&gt;"",COUNTIF($E$2:$E$798,E242)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20806,7 +25067,7 @@
       <c r="AA243" s="4"/>
       <c r="AB243" s="4"/>
       <c r="AC243" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E243&lt;&gt;"",COUNTIF($E$2:$E$798,E243)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20814,7 +25075,7 @@
       <c r="AA244" s="4"/>
       <c r="AB244" s="4"/>
       <c r="AC244" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E244&lt;&gt;"",COUNTIF($E$2:$E$798,E244)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20822,7 +25083,7 @@
       <c r="AA245" s="4"/>
       <c r="AB245" s="4"/>
       <c r="AC245" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E245&lt;&gt;"",COUNTIF($E$2:$E$798,E245)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20830,7 +25091,7 @@
       <c r="AA246" s="4"/>
       <c r="AB246" s="4"/>
       <c r="AC246" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E246&lt;&gt;"",COUNTIF($E$2:$E$798,E246)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20838,7 +25099,7 @@
       <c r="AA247" s="4"/>
       <c r="AB247" s="4"/>
       <c r="AC247" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E247&lt;&gt;"",COUNTIF($E$2:$E$798,E247)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20846,7 +25107,7 @@
       <c r="AA248" s="4"/>
       <c r="AB248" s="4"/>
       <c r="AC248" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E248&lt;&gt;"",COUNTIF($E$2:$E$798,E248)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20854,7 +25115,7 @@
       <c r="AA249" s="4"/>
       <c r="AB249" s="4"/>
       <c r="AC249" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E249&lt;&gt;"",COUNTIF($E$2:$E$798,E249)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20862,7 +25123,7 @@
       <c r="AA250" s="4"/>
       <c r="AB250" s="4"/>
       <c r="AC250" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E250&lt;&gt;"",COUNTIF($E$2:$E$798,E250)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20870,7 +25131,7 @@
       <c r="AA251" s="4"/>
       <c r="AB251" s="4"/>
       <c r="AC251" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E251&lt;&gt;"",COUNTIF($E$2:$E$798,E251)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20878,7 +25139,7 @@
       <c r="AA252" s="4"/>
       <c r="AB252" s="4"/>
       <c r="AC252" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E252&lt;&gt;"",COUNTIF($E$2:$E$798,E252)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20886,7 +25147,7 @@
       <c r="AA253" s="4"/>
       <c r="AB253" s="4"/>
       <c r="AC253" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E253&lt;&gt;"",COUNTIF($E$2:$E$798,E253)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20894,7 +25155,7 @@
       <c r="AA254" s="4"/>
       <c r="AB254" s="4"/>
       <c r="AC254" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E254&lt;&gt;"",COUNTIF($E$2:$E$798,E254)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20902,7 +25163,7 @@
       <c r="AA255" s="4"/>
       <c r="AB255" s="4"/>
       <c r="AC255" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E255&lt;&gt;"",COUNTIF($E$2:$E$798,E255)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20910,7 +25171,7 @@
       <c r="AA256" s="4"/>
       <c r="AB256" s="4"/>
       <c r="AC256" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E256&lt;&gt;"",COUNTIF($E$2:$E$798,E256)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20918,7 +25179,7 @@
       <c r="AA257" s="4"/>
       <c r="AB257" s="4"/>
       <c r="AC257" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(E257&lt;&gt;"",COUNTIF($E$2:$E$798,E257)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20926,7 +25187,7 @@
       <c r="AA258" s="4"/>
       <c r="AB258" s="4"/>
       <c r="AC258" t="str">
-        <f t="shared" ref="AC258:AC321" si="4">IF(AND(E258&lt;&gt;"",COUNTIF($E$2:$E$800,E258)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E258&lt;&gt;"",COUNTIF($E$2:$E$798,E258)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20934,7 +25195,7 @@
       <c r="AA259" s="4"/>
       <c r="AB259" s="4"/>
       <c r="AC259" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E259&lt;&gt;"",COUNTIF($E$2:$E$798,E259)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20942,7 +25203,7 @@
       <c r="AA260" s="4"/>
       <c r="AB260" s="4"/>
       <c r="AC260" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E260&lt;&gt;"",COUNTIF($E$2:$E$798,E260)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20950,7 +25211,7 @@
       <c r="AA261" s="4"/>
       <c r="AB261" s="4"/>
       <c r="AC261" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E261&lt;&gt;"",COUNTIF($E$2:$E$798,E261)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20958,7 +25219,7 @@
       <c r="AA262" s="4"/>
       <c r="AB262" s="4"/>
       <c r="AC262" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E262&lt;&gt;"",COUNTIF($E$2:$E$798,E262)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20966,7 +25227,7 @@
       <c r="AA263" s="4"/>
       <c r="AB263" s="4"/>
       <c r="AC263" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E263&lt;&gt;"",COUNTIF($E$2:$E$798,E263)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20974,7 +25235,7 @@
       <c r="AA264" s="4"/>
       <c r="AB264" s="4"/>
       <c r="AC264" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E264&lt;&gt;"",COUNTIF($E$2:$E$798,E264)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20982,7 +25243,7 @@
       <c r="AA265" s="4"/>
       <c r="AB265" s="4"/>
       <c r="AC265" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E265&lt;&gt;"",COUNTIF($E$2:$E$798,E265)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20990,7 +25251,7 @@
       <c r="AA266" s="4"/>
       <c r="AB266" s="4"/>
       <c r="AC266" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E266&lt;&gt;"",COUNTIF($E$2:$E$798,E266)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20998,7 +25259,7 @@
       <c r="AA267" s="4"/>
       <c r="AB267" s="4"/>
       <c r="AC267" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E267&lt;&gt;"",COUNTIF($E$2:$E$798,E267)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21006,7 +25267,7 @@
       <c r="AA268" s="4"/>
       <c r="AB268" s="4"/>
       <c r="AC268" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E268&lt;&gt;"",COUNTIF($E$2:$E$798,E268)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21014,7 +25275,7 @@
       <c r="AA269" s="4"/>
       <c r="AB269" s="4"/>
       <c r="AC269" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E269&lt;&gt;"",COUNTIF($E$2:$E$798,E269)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21022,7 +25283,7 @@
       <c r="AA270" s="4"/>
       <c r="AB270" s="4"/>
       <c r="AC270" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E270&lt;&gt;"",COUNTIF($E$2:$E$798,E270)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21030,7 +25291,7 @@
       <c r="AA271" s="4"/>
       <c r="AB271" s="4"/>
       <c r="AC271" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E271&lt;&gt;"",COUNTIF($E$2:$E$798,E271)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21038,7 +25299,7 @@
       <c r="AA272" s="4"/>
       <c r="AB272" s="4"/>
       <c r="AC272" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E272&lt;&gt;"",COUNTIF($E$2:$E$798,E272)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21046,7 +25307,7 @@
       <c r="AA273" s="4"/>
       <c r="AB273" s="4"/>
       <c r="AC273" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E273&lt;&gt;"",COUNTIF($E$2:$E$798,E273)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21054,7 +25315,7 @@
       <c r="AA274" s="4"/>
       <c r="AB274" s="4"/>
       <c r="AC274" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E274&lt;&gt;"",COUNTIF($E$2:$E$798,E274)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21062,7 +25323,7 @@
       <c r="AA275" s="4"/>
       <c r="AB275" s="4"/>
       <c r="AC275" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E275&lt;&gt;"",COUNTIF($E$2:$E$798,E275)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21070,7 +25331,7 @@
       <c r="AA276" s="4"/>
       <c r="AB276" s="4"/>
       <c r="AC276" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E276&lt;&gt;"",COUNTIF($E$2:$E$798,E276)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21078,7 +25339,7 @@
       <c r="AA277" s="4"/>
       <c r="AB277" s="4"/>
       <c r="AC277" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E277&lt;&gt;"",COUNTIF($E$2:$E$798,E277)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21086,7 +25347,7 @@
       <c r="AA278" s="4"/>
       <c r="AB278" s="4"/>
       <c r="AC278" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E278&lt;&gt;"",COUNTIF($E$2:$E$798,E278)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21094,7 +25355,7 @@
       <c r="AA279" s="4"/>
       <c r="AB279" s="4"/>
       <c r="AC279" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E279&lt;&gt;"",COUNTIF($E$2:$E$798,E279)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21102,7 +25363,7 @@
       <c r="AA280" s="4"/>
       <c r="AB280" s="4"/>
       <c r="AC280" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E280&lt;&gt;"",COUNTIF($E$2:$E$798,E280)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21110,7 +25371,7 @@
       <c r="AA281" s="4"/>
       <c r="AB281" s="4"/>
       <c r="AC281" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E281&lt;&gt;"",COUNTIF($E$2:$E$798,E281)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21118,7 +25379,7 @@
       <c r="AA282" s="4"/>
       <c r="AB282" s="4"/>
       <c r="AC282" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E282&lt;&gt;"",COUNTIF($E$2:$E$798,E282)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21126,7 +25387,7 @@
       <c r="AA283" s="4"/>
       <c r="AB283" s="4"/>
       <c r="AC283" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E283&lt;&gt;"",COUNTIF($E$2:$E$798,E283)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21134,7 +25395,7 @@
       <c r="AA284" s="4"/>
       <c r="AB284" s="4"/>
       <c r="AC284" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E284&lt;&gt;"",COUNTIF($E$2:$E$798,E284)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21142,7 +25403,7 @@
       <c r="AA285" s="4"/>
       <c r="AB285" s="4"/>
       <c r="AC285" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E285&lt;&gt;"",COUNTIF($E$2:$E$798,E285)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21150,7 +25411,7 @@
       <c r="AA286" s="4"/>
       <c r="AB286" s="4"/>
       <c r="AC286" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E286&lt;&gt;"",COUNTIF($E$2:$E$798,E286)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21158,7 +25419,7 @@
       <c r="AA287" s="4"/>
       <c r="AB287" s="4"/>
       <c r="AC287" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E287&lt;&gt;"",COUNTIF($E$2:$E$798,E287)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21166,7 +25427,7 @@
       <c r="AA288" s="4"/>
       <c r="AB288" s="4"/>
       <c r="AC288" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E288&lt;&gt;"",COUNTIF($E$2:$E$798,E288)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21174,7 +25435,7 @@
       <c r="AA289" s="4"/>
       <c r="AB289" s="4"/>
       <c r="AC289" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E289&lt;&gt;"",COUNTIF($E$2:$E$798,E289)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21182,7 +25443,7 @@
       <c r="AA290" s="4"/>
       <c r="AB290" s="4"/>
       <c r="AC290" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E290&lt;&gt;"",COUNTIF($E$2:$E$798,E290)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21190,7 +25451,7 @@
       <c r="AA291" s="4"/>
       <c r="AB291" s="4"/>
       <c r="AC291" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E291&lt;&gt;"",COUNTIF($E$2:$E$798,E291)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21198,7 +25459,7 @@
       <c r="AA292" s="4"/>
       <c r="AB292" s="4"/>
       <c r="AC292" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E292&lt;&gt;"",COUNTIF($E$2:$E$798,E292)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21206,7 +25467,7 @@
       <c r="AA293" s="4"/>
       <c r="AB293" s="4"/>
       <c r="AC293" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E293&lt;&gt;"",COUNTIF($E$2:$E$798,E293)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21214,7 +25475,7 @@
       <c r="AA294" s="4"/>
       <c r="AB294" s="4"/>
       <c r="AC294" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E294&lt;&gt;"",COUNTIF($E$2:$E$798,E294)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21222,7 +25483,7 @@
       <c r="AA295" s="4"/>
       <c r="AB295" s="4"/>
       <c r="AC295" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E295&lt;&gt;"",COUNTIF($E$2:$E$798,E295)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21230,7 +25491,7 @@
       <c r="AA296" s="4"/>
       <c r="AB296" s="4"/>
       <c r="AC296" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E296&lt;&gt;"",COUNTIF($E$2:$E$798,E296)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21238,7 +25499,7 @@
       <c r="AA297" s="4"/>
       <c r="AB297" s="4"/>
       <c r="AC297" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E297&lt;&gt;"",COUNTIF($E$2:$E$798,E297)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21246,7 +25507,7 @@
       <c r="AA298" s="4"/>
       <c r="AB298" s="4"/>
       <c r="AC298" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E298&lt;&gt;"",COUNTIF($E$2:$E$798,E298)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21254,7 +25515,7 @@
       <c r="AA299" s="4"/>
       <c r="AB299" s="4"/>
       <c r="AC299" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E299&lt;&gt;"",COUNTIF($E$2:$E$798,E299)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21262,7 +25523,7 @@
       <c r="AA300" s="4"/>
       <c r="AB300" s="4"/>
       <c r="AC300" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E300&lt;&gt;"",COUNTIF($E$2:$E$798,E300)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21270,7 +25531,7 @@
       <c r="AA301" s="4"/>
       <c r="AB301" s="4"/>
       <c r="AC301" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E301&lt;&gt;"",COUNTIF($E$2:$E$798,E301)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21278,7 +25539,7 @@
       <c r="AA302" s="4"/>
       <c r="AB302" s="4"/>
       <c r="AC302" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E302&lt;&gt;"",COUNTIF($E$2:$E$798,E302)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21286,7 +25547,7 @@
       <c r="AA303" s="4"/>
       <c r="AB303" s="4"/>
       <c r="AC303" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E303&lt;&gt;"",COUNTIF($E$2:$E$798,E303)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21294,7 +25555,7 @@
       <c r="AA304" s="4"/>
       <c r="AB304" s="4"/>
       <c r="AC304" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E304&lt;&gt;"",COUNTIF($E$2:$E$798,E304)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21302,7 +25563,7 @@
       <c r="AA305" s="4"/>
       <c r="AB305" s="4"/>
       <c r="AC305" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E305&lt;&gt;"",COUNTIF($E$2:$E$798,E305)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21310,7 +25571,7 @@
       <c r="AA306" s="4"/>
       <c r="AB306" s="4"/>
       <c r="AC306" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E306&lt;&gt;"",COUNTIF($E$2:$E$798,E306)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21318,7 +25579,7 @@
       <c r="AA307" s="4"/>
       <c r="AB307" s="4"/>
       <c r="AC307" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E307&lt;&gt;"",COUNTIF($E$2:$E$798,E307)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21326,7 +25587,7 @@
       <c r="AA308" s="4"/>
       <c r="AB308" s="4"/>
       <c r="AC308" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E308&lt;&gt;"",COUNTIF($E$2:$E$798,E308)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21334,7 +25595,7 @@
       <c r="AA309" s="4"/>
       <c r="AB309" s="4"/>
       <c r="AC309" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E309&lt;&gt;"",COUNTIF($E$2:$E$798,E309)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21342,7 +25603,7 @@
       <c r="AA310" s="4"/>
       <c r="AB310" s="4"/>
       <c r="AC310" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E310&lt;&gt;"",COUNTIF($E$2:$E$798,E310)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21350,7 +25611,7 @@
       <c r="AA311" s="4"/>
       <c r="AB311" s="4"/>
       <c r="AC311" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E311&lt;&gt;"",COUNTIF($E$2:$E$798,E311)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21358,7 +25619,7 @@
       <c r="AA312" s="4"/>
       <c r="AB312" s="4"/>
       <c r="AC312" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E312&lt;&gt;"",COUNTIF($E$2:$E$798,E312)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21366,7 +25627,7 @@
       <c r="AA313" s="4"/>
       <c r="AB313" s="4"/>
       <c r="AC313" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E313&lt;&gt;"",COUNTIF($E$2:$E$798,E313)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21374,7 +25635,7 @@
       <c r="AA314" s="4"/>
       <c r="AB314" s="4"/>
       <c r="AC314" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E314&lt;&gt;"",COUNTIF($E$2:$E$798,E314)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21382,7 +25643,7 @@
       <c r="AA315" s="4"/>
       <c r="AB315" s="4"/>
       <c r="AC315" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E315&lt;&gt;"",COUNTIF($E$2:$E$798,E315)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21390,7 +25651,7 @@
       <c r="AA316" s="4"/>
       <c r="AB316" s="4"/>
       <c r="AC316" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E316&lt;&gt;"",COUNTIF($E$2:$E$798,E316)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21398,7 +25659,7 @@
       <c r="AA317" s="4"/>
       <c r="AB317" s="4"/>
       <c r="AC317" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E317&lt;&gt;"",COUNTIF($E$2:$E$798,E317)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21406,7 +25667,7 @@
       <c r="AA318" s="4"/>
       <c r="AB318" s="4"/>
       <c r="AC318" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E318&lt;&gt;"",COUNTIF($E$2:$E$798,E318)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21414,7 +25675,7 @@
       <c r="AA319" s="4"/>
       <c r="AB319" s="4"/>
       <c r="AC319" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E319&lt;&gt;"",COUNTIF($E$2:$E$798,E319)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21422,7 +25683,7 @@
       <c r="AA320" s="4"/>
       <c r="AB320" s="4"/>
       <c r="AC320" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E320&lt;&gt;"",COUNTIF($E$2:$E$798,E320)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21430,7 +25691,7 @@
       <c r="AA321" s="4"/>
       <c r="AB321" s="4"/>
       <c r="AC321" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(E321&lt;&gt;"",COUNTIF($E$2:$E$798,E321)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21438,7 +25699,7 @@
       <c r="AA322" s="4"/>
       <c r="AB322" s="4"/>
       <c r="AC322" t="str">
-        <f t="shared" ref="AC322:AC385" si="5">IF(AND(E322&lt;&gt;"",COUNTIF($E$2:$E$800,E322)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E322&lt;&gt;"",COUNTIF($E$2:$E$798,E322)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21446,7 +25707,7 @@
       <c r="AA323" s="4"/>
       <c r="AB323" s="4"/>
       <c r="AC323" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E323&lt;&gt;"",COUNTIF($E$2:$E$798,E323)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21454,7 +25715,7 @@
       <c r="AA324" s="4"/>
       <c r="AB324" s="4"/>
       <c r="AC324" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E324&lt;&gt;"",COUNTIF($E$2:$E$798,E324)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21462,7 +25723,7 @@
       <c r="AA325" s="4"/>
       <c r="AB325" s="4"/>
       <c r="AC325" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E325&lt;&gt;"",COUNTIF($E$2:$E$798,E325)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21470,7 +25731,7 @@
       <c r="AA326" s="4"/>
       <c r="AB326" s="4"/>
       <c r="AC326" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E326&lt;&gt;"",COUNTIF($E$2:$E$798,E326)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21478,7 +25739,7 @@
       <c r="AA327" s="4"/>
       <c r="AB327" s="4"/>
       <c r="AC327" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E327&lt;&gt;"",COUNTIF($E$2:$E$798,E327)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21486,7 +25747,7 @@
       <c r="AA328" s="4"/>
       <c r="AB328" s="4"/>
       <c r="AC328" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E328&lt;&gt;"",COUNTIF($E$2:$E$798,E328)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21494,7 +25755,7 @@
       <c r="AA329" s="4"/>
       <c r="AB329" s="4"/>
       <c r="AC329" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E329&lt;&gt;"",COUNTIF($E$2:$E$798,E329)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21502,7 +25763,7 @@
       <c r="AA330" s="4"/>
       <c r="AB330" s="4"/>
       <c r="AC330" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E330&lt;&gt;"",COUNTIF($E$2:$E$798,E330)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21510,7 +25771,7 @@
       <c r="AA331" s="4"/>
       <c r="AB331" s="4"/>
       <c r="AC331" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E331&lt;&gt;"",COUNTIF($E$2:$E$798,E331)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21518,7 +25779,7 @@
       <c r="AA332" s="4"/>
       <c r="AB332" s="4"/>
       <c r="AC332" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E332&lt;&gt;"",COUNTIF($E$2:$E$798,E332)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21526,7 +25787,7 @@
       <c r="AA333" s="4"/>
       <c r="AB333" s="4"/>
       <c r="AC333" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E333&lt;&gt;"",COUNTIF($E$2:$E$798,E333)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21534,7 +25795,7 @@
       <c r="AA334" s="4"/>
       <c r="AB334" s="4"/>
       <c r="AC334" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E334&lt;&gt;"",COUNTIF($E$2:$E$798,E334)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21542,7 +25803,7 @@
       <c r="AA335" s="4"/>
       <c r="AB335" s="4"/>
       <c r="AC335" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E335&lt;&gt;"",COUNTIF($E$2:$E$798,E335)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21550,7 +25811,7 @@
       <c r="AA336" s="4"/>
       <c r="AB336" s="4"/>
       <c r="AC336" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E336&lt;&gt;"",COUNTIF($E$2:$E$798,E336)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21558,7 +25819,7 @@
       <c r="AA337" s="4"/>
       <c r="AB337" s="4"/>
       <c r="AC337" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E337&lt;&gt;"",COUNTIF($E$2:$E$798,E337)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21566,7 +25827,7 @@
       <c r="AA338" s="4"/>
       <c r="AB338" s="4"/>
       <c r="AC338" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E338&lt;&gt;"",COUNTIF($E$2:$E$798,E338)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21574,7 +25835,7 @@
       <c r="AA339" s="4"/>
       <c r="AB339" s="4"/>
       <c r="AC339" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E339&lt;&gt;"",COUNTIF($E$2:$E$798,E339)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21582,7 +25843,7 @@
       <c r="AA340" s="4"/>
       <c r="AB340" s="4"/>
       <c r="AC340" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E340&lt;&gt;"",COUNTIF($E$2:$E$798,E340)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21590,7 +25851,7 @@
       <c r="AA341" s="4"/>
       <c r="AB341" s="4"/>
       <c r="AC341" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E341&lt;&gt;"",COUNTIF($E$2:$E$798,E341)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21598,7 +25859,7 @@
       <c r="AA342" s="4"/>
       <c r="AB342" s="4"/>
       <c r="AC342" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E342&lt;&gt;"",COUNTIF($E$2:$E$798,E342)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21606,7 +25867,7 @@
       <c r="AA343" s="4"/>
       <c r="AB343" s="4"/>
       <c r="AC343" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E343&lt;&gt;"",COUNTIF($E$2:$E$798,E343)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21614,7 +25875,7 @@
       <c r="AA344" s="4"/>
       <c r="AB344" s="4"/>
       <c r="AC344" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E344&lt;&gt;"",COUNTIF($E$2:$E$798,E344)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21622,7 +25883,7 @@
       <c r="AA345" s="4"/>
       <c r="AB345" s="4"/>
       <c r="AC345" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E345&lt;&gt;"",COUNTIF($E$2:$E$798,E345)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21630,7 +25891,7 @@
       <c r="AA346" s="4"/>
       <c r="AB346" s="4"/>
       <c r="AC346" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E346&lt;&gt;"",COUNTIF($E$2:$E$798,E346)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21638,7 +25899,7 @@
       <c r="AA347" s="4"/>
       <c r="AB347" s="4"/>
       <c r="AC347" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E347&lt;&gt;"",COUNTIF($E$2:$E$798,E347)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21646,7 +25907,7 @@
       <c r="AA348" s="4"/>
       <c r="AB348" s="4"/>
       <c r="AC348" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E348&lt;&gt;"",COUNTIF($E$2:$E$798,E348)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21654,7 +25915,7 @@
       <c r="AA349" s="4"/>
       <c r="AB349" s="4"/>
       <c r="AC349" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E349&lt;&gt;"",COUNTIF($E$2:$E$798,E349)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21662,7 +25923,7 @@
       <c r="AA350" s="4"/>
       <c r="AB350" s="4"/>
       <c r="AC350" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E350&lt;&gt;"",COUNTIF($E$2:$E$798,E350)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21670,7 +25931,7 @@
       <c r="AA351" s="4"/>
       <c r="AB351" s="4"/>
       <c r="AC351" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E351&lt;&gt;"",COUNTIF($E$2:$E$798,E351)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21678,7 +25939,7 @@
       <c r="AA352" s="4"/>
       <c r="AB352" s="4"/>
       <c r="AC352" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E352&lt;&gt;"",COUNTIF($E$2:$E$798,E352)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21686,7 +25947,7 @@
       <c r="AA353" s="4"/>
       <c r="AB353" s="4"/>
       <c r="AC353" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E353&lt;&gt;"",COUNTIF($E$2:$E$798,E353)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21694,7 +25955,7 @@
       <c r="AA354" s="4"/>
       <c r="AB354" s="4"/>
       <c r="AC354" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E354&lt;&gt;"",COUNTIF($E$2:$E$798,E354)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21702,7 +25963,7 @@
       <c r="AA355" s="4"/>
       <c r="AB355" s="4"/>
       <c r="AC355" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E355&lt;&gt;"",COUNTIF($E$2:$E$798,E355)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21710,7 +25971,7 @@
       <c r="AA356" s="4"/>
       <c r="AB356" s="4"/>
       <c r="AC356" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E356&lt;&gt;"",COUNTIF($E$2:$E$798,E356)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21718,7 +25979,7 @@
       <c r="AA357" s="4"/>
       <c r="AB357" s="4"/>
       <c r="AC357" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E357&lt;&gt;"",COUNTIF($E$2:$E$798,E357)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21726,7 +25987,7 @@
       <c r="AA358" s="4"/>
       <c r="AB358" s="4"/>
       <c r="AC358" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E358&lt;&gt;"",COUNTIF($E$2:$E$798,E358)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21734,7 +25995,7 @@
       <c r="AA359" s="4"/>
       <c r="AB359" s="4"/>
       <c r="AC359" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E359&lt;&gt;"",COUNTIF($E$2:$E$798,E359)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21742,7 +26003,7 @@
       <c r="AA360" s="4"/>
       <c r="AB360" s="4"/>
       <c r="AC360" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E360&lt;&gt;"",COUNTIF($E$2:$E$798,E360)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21750,7 +26011,7 @@
       <c r="AA361" s="4"/>
       <c r="AB361" s="4"/>
       <c r="AC361" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E361&lt;&gt;"",COUNTIF($E$2:$E$798,E361)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21758,7 +26019,7 @@
       <c r="AA362" s="4"/>
       <c r="AB362" s="4"/>
       <c r="AC362" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E362&lt;&gt;"",COUNTIF($E$2:$E$798,E362)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21766,7 +26027,7 @@
       <c r="AA363" s="4"/>
       <c r="AB363" s="4"/>
       <c r="AC363" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E363&lt;&gt;"",COUNTIF($E$2:$E$798,E363)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21774,7 +26035,7 @@
       <c r="AA364" s="4"/>
       <c r="AB364" s="4"/>
       <c r="AC364" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E364&lt;&gt;"",COUNTIF($E$2:$E$798,E364)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21782,7 +26043,7 @@
       <c r="AA365" s="4"/>
       <c r="AB365" s="4"/>
       <c r="AC365" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E365&lt;&gt;"",COUNTIF($E$2:$E$798,E365)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21790,7 +26051,7 @@
       <c r="AA366" s="4"/>
       <c r="AB366" s="4"/>
       <c r="AC366" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E366&lt;&gt;"",COUNTIF($E$2:$E$798,E366)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21798,7 +26059,7 @@
       <c r="AA367" s="4"/>
       <c r="AB367" s="4"/>
       <c r="AC367" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E367&lt;&gt;"",COUNTIF($E$2:$E$798,E367)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21806,7 +26067,7 @@
       <c r="AA368" s="4"/>
       <c r="AB368" s="4"/>
       <c r="AC368" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E368&lt;&gt;"",COUNTIF($E$2:$E$798,E368)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21814,7 +26075,7 @@
       <c r="AA369" s="4"/>
       <c r="AB369" s="4"/>
       <c r="AC369" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E369&lt;&gt;"",COUNTIF($E$2:$E$798,E369)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21822,7 +26083,7 @@
       <c r="AA370" s="4"/>
       <c r="AB370" s="4"/>
       <c r="AC370" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E370&lt;&gt;"",COUNTIF($E$2:$E$798,E370)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21830,7 +26091,7 @@
       <c r="AA371" s="4"/>
       <c r="AB371" s="4"/>
       <c r="AC371" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E371&lt;&gt;"",COUNTIF($E$2:$E$798,E371)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21838,7 +26099,7 @@
       <c r="AA372" s="4"/>
       <c r="AB372" s="4"/>
       <c r="AC372" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E372&lt;&gt;"",COUNTIF($E$2:$E$798,E372)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21846,7 +26107,7 @@
       <c r="AA373" s="4"/>
       <c r="AB373" s="4"/>
       <c r="AC373" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E373&lt;&gt;"",COUNTIF($E$2:$E$798,E373)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21854,7 +26115,7 @@
       <c r="AA374" s="4"/>
       <c r="AB374" s="4"/>
       <c r="AC374" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E374&lt;&gt;"",COUNTIF($E$2:$E$798,E374)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21862,7 +26123,7 @@
       <c r="AA375" s="4"/>
       <c r="AB375" s="4"/>
       <c r="AC375" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E375&lt;&gt;"",COUNTIF($E$2:$E$798,E375)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21870,7 +26131,7 @@
       <c r="AA376" s="4"/>
       <c r="AB376" s="4"/>
       <c r="AC376" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E376&lt;&gt;"",COUNTIF($E$2:$E$798,E376)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21878,7 +26139,7 @@
       <c r="AA377" s="4"/>
       <c r="AB377" s="4"/>
       <c r="AC377" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E377&lt;&gt;"",COUNTIF($E$2:$E$798,E377)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21886,7 +26147,7 @@
       <c r="AA378" s="4"/>
       <c r="AB378" s="4"/>
       <c r="AC378" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E378&lt;&gt;"",COUNTIF($E$2:$E$798,E378)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21894,7 +26155,7 @@
       <c r="AA379" s="4"/>
       <c r="AB379" s="4"/>
       <c r="AC379" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E379&lt;&gt;"",COUNTIF($E$2:$E$798,E379)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21902,7 +26163,7 @@
       <c r="AA380" s="4"/>
       <c r="AB380" s="4"/>
       <c r="AC380" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E380&lt;&gt;"",COUNTIF($E$2:$E$798,E380)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21910,7 +26171,7 @@
       <c r="AA381" s="4"/>
       <c r="AB381" s="4"/>
       <c r="AC381" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E381&lt;&gt;"",COUNTIF($E$2:$E$798,E381)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21918,7 +26179,7 @@
       <c r="AA382" s="4"/>
       <c r="AB382" s="4"/>
       <c r="AC382" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E382&lt;&gt;"",COUNTIF($E$2:$E$798,E382)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21926,7 +26187,7 @@
       <c r="AA383" s="4"/>
       <c r="AB383" s="4"/>
       <c r="AC383" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E383&lt;&gt;"",COUNTIF($E$2:$E$798,E383)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21934,7 +26195,7 @@
       <c r="AA384" s="4"/>
       <c r="AB384" s="4"/>
       <c r="AC384" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E384&lt;&gt;"",COUNTIF($E$2:$E$798,E384)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21942,7 +26203,7 @@
       <c r="AA385" s="4"/>
       <c r="AB385" s="4"/>
       <c r="AC385" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(AND(E385&lt;&gt;"",COUNTIF($E$2:$E$798,E385)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21950,7 +26211,7 @@
       <c r="AA386" s="4"/>
       <c r="AB386" s="4"/>
       <c r="AC386" t="str">
-        <f t="shared" ref="AC386:AC400" si="6">IF(AND(E386&lt;&gt;"",COUNTIF($E$2:$E$800,E386)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E386&lt;&gt;"",COUNTIF($E$2:$E$798,E386)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21958,7 +26219,7 @@
       <c r="AA387" s="4"/>
       <c r="AB387" s="4"/>
       <c r="AC387" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E387&lt;&gt;"",COUNTIF($E$2:$E$798,E387)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21966,7 +26227,7 @@
       <c r="AA388" s="4"/>
       <c r="AB388" s="4"/>
       <c r="AC388" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E388&lt;&gt;"",COUNTIF($E$2:$E$798,E388)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21974,7 +26235,7 @@
       <c r="AA389" s="4"/>
       <c r="AB389" s="4"/>
       <c r="AC389" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E389&lt;&gt;"",COUNTIF($E$2:$E$798,E389)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21982,7 +26243,7 @@
       <c r="AA390" s="4"/>
       <c r="AB390" s="4"/>
       <c r="AC390" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E390&lt;&gt;"",COUNTIF($E$2:$E$798,E390)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21990,7 +26251,7 @@
       <c r="AA391" s="4"/>
       <c r="AB391" s="4"/>
       <c r="AC391" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E391&lt;&gt;"",COUNTIF($E$2:$E$798,E391)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21998,7 +26259,7 @@
       <c r="AA392" s="4"/>
       <c r="AB392" s="4"/>
       <c r="AC392" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E392&lt;&gt;"",COUNTIF($E$2:$E$798,E392)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -22006,7 +26267,7 @@
       <c r="AA393" s="4"/>
       <c r="AB393" s="4"/>
       <c r="AC393" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E393&lt;&gt;"",COUNTIF($E$2:$E$798,E393)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -22014,7 +26275,7 @@
       <c r="AA394" s="4"/>
       <c r="AB394" s="4"/>
       <c r="AC394" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E394&lt;&gt;"",COUNTIF($E$2:$E$798,E394)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -22022,7 +26283,7 @@
       <c r="AA395" s="4"/>
       <c r="AB395" s="4"/>
       <c r="AC395" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E395&lt;&gt;"",COUNTIF($E$2:$E$798,E395)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -22030,7 +26291,7 @@
       <c r="AA396" s="4"/>
       <c r="AB396" s="4"/>
       <c r="AC396" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E396&lt;&gt;"",COUNTIF($E$2:$E$798,E396)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -22038,7 +26299,7 @@
       <c r="AA397" s="4"/>
       <c r="AB397" s="4"/>
       <c r="AC397" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E397&lt;&gt;"",COUNTIF($E$2:$E$798,E397)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -22046,46 +26307,30 @@
       <c r="AA398" s="4"/>
       <c r="AB398" s="4"/>
       <c r="AC398" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="399" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA399" s="4"/>
-      <c r="AB399" s="4"/>
-      <c r="AC399" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="400" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA400" s="4"/>
-      <c r="AB400" s="4"/>
-      <c r="AC400" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(AND(E398&lt;&gt;"",COUNTIF($E$2:$E$798,E398)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E800">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($E2&lt;&gt;"",COUNTIF($E$2:$E$800,$E2)&gt;1)</formula>
+  <conditionalFormatting sqref="E2:E798">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>AND($E2&lt;&gt;"",COUNTIF($E$2:$E$798,$E2)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B800">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B798">
       <formula1>"Open,Closed,Hidden"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C800">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C798">
       <formula1>"Yes"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D800">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D798">
       <formula1>"Scholarship,Internship"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G800">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G798">
       <formula1>"Africa,Asia,Europe,North America,Latin America &amp; Caribbean,Oceania"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K800">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K798">
       <formula1>"Full,Stipend,Partial"</formula1>
     </dataValidation>
   </dataValidations>

--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4409" uniqueCount="2881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4945" uniqueCount="3240">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -7269,9 +7269,6 @@
     <t>Caribbean</t>
   </si>
   <si>
-    <t>United States, Canada, United Kingdom, Other accredited destinations</t>
-  </si>
-  <si>
     <t>National development priority fields</t>
   </si>
   <si>
@@ -7410,9 +7407,6 @@
     <t>Royal Civil Service Commission (RCSC), Bhutan</t>
   </si>
   <si>
-    <t>Bhutan, overseas destinations as specified in call</t>
-  </si>
-  <si>
     <t>Priority fields listed in annual announcement</t>
   </si>
   <si>
@@ -7455,9 +7449,6 @@
     <t>Bhutan King’s Scholarship</t>
   </si>
   <si>
-    <t>Bhutan, as specified by the annual award</t>
-  </si>
-  <si>
     <t>Priority fields according to annual call</t>
   </si>
   <si>
@@ -7503,9 +7494,6 @@
     <t>Government of Botswana — Placement Division</t>
   </si>
   <si>
-    <t>Botswana, approved regional and overseas institutions</t>
-  </si>
-  <si>
     <t>Bachelor, Diploma</t>
   </si>
   <si>
@@ -7602,9 +7590,6 @@
     <t>Ministry of Foreign Affairs, Brunei Darussalam</t>
   </si>
   <si>
-    <t>Brunei Darussalam</t>
-  </si>
-  <si>
     <t>Diploma, Bachelor, Master</t>
   </si>
   <si>
@@ -7743,9 +7728,6 @@
     <t>Government of Burkina Faso — Ministry responsible for higher education</t>
   </si>
   <si>
-    <t>Burkina Faso and destinations specified in official calls</t>
-  </si>
-  <si>
     <t>Bachelor, Master, PhD, Research</t>
   </si>
   <si>
@@ -7839,162 +7821,6 @@
     <t>Burkina Faso, Internship, Youth Employment, Local Opportunities</t>
   </si>
   <si>
-    <t>erasmus-mundus-joint-masters-global-scholarship</t>
-  </si>
-  <si>
-    <t>Erasmus Mundus Joint Masters Scholarships</t>
-  </si>
-  <si>
-    <t>European Union — Erasmus+; participating university consortia</t>
-  </si>
-  <si>
-    <t>Europe, Worldwide</t>
-  </si>
-  <si>
-    <t>Participating European and partner countries</t>
-  </si>
-  <si>
-    <t>Varies by joint master programme</t>
-  </si>
-  <si>
-    <t>Selected scholarships cover participation costs and contribute to travel, visa and living expenses.</t>
-  </si>
-  <si>
-    <t>Programme-specific; many courses accept applications between October and January for the following academic year.</t>
-  </si>
-  <si>
-    <t>Students worldwide may apply, subject to the chosen master’s admission criteria and any country-specific restrictions.</t>
-  </si>
-  <si>
-    <t>High: apply directly to each consortium; documents and selection criteria vary.</t>
-  </si>
-  <si>
-    <t>International applicants seeking a joint master’s degree across multiple universities</t>
-  </si>
-  <si>
-    <t>Erasmus Mundus Joint Masters are integrated programmes delivered by international university consortia. Selected programmes offer competitive scholarships to applicants from around the world.</t>
-  </si>
-  <si>
-    <t>Usually academic transcripts and degree certificate, CV, motivation statement, language evidence and references; check the individual programme.</t>
-  </si>
-  <si>
-    <t>Each consortium runs its own admissions and scholarship selection.</t>
-  </si>
-  <si>
-    <t>Use the official catalogue and link to the exact programme. Do not use one universal deadline for all courses.</t>
-  </si>
-  <si>
-    <t>https://erasmus-plus.ec.europa.eu/opportunities/individuals/students/erasmus-mundus-joint-masters</t>
-  </si>
-  <si>
-    <t>International, Europe, Master, Full Scholarship, Erasmus Mundus</t>
-  </si>
-  <si>
-    <t>unesco-internship-programme-global</t>
-  </si>
-  <si>
-    <t>UNESCO Internship Programme</t>
-  </si>
-  <si>
-    <t>United Nations Educational, Scientific and Cultural Organization (UNESCO)</t>
-  </si>
-  <si>
-    <t>Worldwide</t>
-  </si>
-  <si>
-    <t>UNESCO offices and participating locations</t>
-  </si>
-  <si>
-    <t>Bachelor, Master, PhD, Technical/Vocational</t>
-  </si>
-  <si>
-    <t>Education, culture, science, communication, administration and other advertised areas</t>
-  </si>
-  <si>
-    <t>Unpaid</t>
-  </si>
-  <si>
-    <t>Learning placement; applicants should check the official terms for insurance, travel and living costs.</t>
-  </si>
-  <si>
-    <t>No single deadline; vacancies are posted periodically on the official careers site.</t>
-  </si>
-  <si>
-    <t>Generally age 20 or older; applicants must meet the enrolment or recent-graduate criteria in UNESCO’s current internship rules.</t>
-  </si>
-  <si>
-    <t>Medium–High: apply to a posted opening and provide the required application materials.</t>
-  </si>
-  <si>
-    <t>Students and recent graduates interested in international development, culture, education or science</t>
-  </si>
-  <si>
-    <t>UNESCO’s internship programme offers practical learning assignments to eligible students and recent graduates. Eligibility and openings are governed by current official rules.</t>
-  </si>
-  <si>
-    <t>Apply through the official careers portal; prepare CV and any supporting documents requested by the vacancy.</t>
-  </si>
-  <si>
-    <t>Vacancy-specific competitive review.</t>
-  </si>
-  <si>
-    <t>Confirm the exact opening and whether costs are covered; do not describe it as a paid internship unless the official posting says so.</t>
-  </si>
-  <si>
-    <t>https://careers.unesco.org/content/Internship-Programme/</t>
-  </si>
-  <si>
-    <t>International, UNESCO, Internship, Unpaid, Students</t>
-  </si>
-  <si>
-    <t>united-nations-secretariat-internship-global</t>
-  </si>
-  <si>
-    <t>United Nations Secretariat Internship Programme</t>
-  </si>
-  <si>
-    <t>United Nations Secretariat</t>
-  </si>
-  <si>
-    <t>United Nations duty stations as advertised</t>
-  </si>
-  <si>
-    <t>Varies by vacancy: policy, communications, economics, law, administration, languages and more</t>
-  </si>
-  <si>
-    <t>Internship experience; the Secretariat internship programme is generally unpaid and costs are normally the intern’s responsibility.</t>
-  </si>
-  <si>
-    <t>No single deadline; apply to individual internship vacancies on UN Careers.</t>
-  </si>
-  <si>
-    <t>Generally enrolled in the final year of a first university degree, enrolled in a graduate programme, or graduated within the period stated in the vacancy. Language and other requirements vary.</t>
-  </si>
-  <si>
-    <t>Medium–High: online profile, application/cover letter and vacancy-specific information.</t>
-  </si>
-  <si>
-    <t>University students and recent graduates seeking UN experience</t>
-  </si>
-  <si>
-    <t>The UN Secretariat advertises internships through UN Careers. Applicants must meet the eligibility conditions in each vacancy; internship terms and location are specified in the posting.</t>
-  </si>
-  <si>
-    <t>Typically CV/profile and cover letter; follow the application instructions in the individual vacancy.</t>
-  </si>
-  <si>
-    <t>Vacancy-specific screening and selection.</t>
-  </si>
-  <si>
-    <t>Do not imply that the UN internship is paid. Check each vacancy for country, language, duration and cost conditions.</t>
-  </si>
-  <si>
-    <t>https://careers.un.org/internship?language=en</t>
-  </si>
-  <si>
-    <t>International, United Nations, Internship, Unpaid, Students</t>
-  </si>
-  <si>
     <t>benin-public-university-allowances-2026-2027</t>
   </si>
   <si>
@@ -8046,9 +7872,6 @@
     <t>National Institute of Culture and History (NICH), Belize</t>
   </si>
   <si>
-    <t>Central America</t>
-  </si>
-  <si>
     <t>Belize</t>
   </si>
   <si>
@@ -8100,9 +7923,6 @@
     <t>Government of Barbados, Ministry of Education Transformation</t>
   </si>
   <si>
-    <t>International; eligible accredited universities</t>
-  </si>
-  <si>
     <t>Undergraduate, Postgraduate</t>
   </si>
   <si>
@@ -8148,9 +7968,6 @@
     <t>Errol Walton Barrow Scholarships 2026</t>
   </si>
   <si>
-    <t>International; eligible institutions</t>
-  </si>
-  <si>
     <t>Marine Studies; Aeronautics; Culinary Arts</t>
   </si>
   <si>
@@ -8355,9 +8172,6 @@
     <t>Comoros Ministry of National Education</t>
   </si>
   <si>
-    <t>Indian Ocean</t>
-  </si>
-  <si>
     <t>Morocco</t>
   </si>
   <si>
@@ -8427,9 +8241,6 @@
     <t>Cyprus</t>
   </si>
   <si>
-    <t>Cyprus and eligible overseas destinations, depending on scheme</t>
-  </si>
-  <si>
     <t>Undergraduate; Master; PhD</t>
   </si>
   <si>
@@ -8520,9 +8331,6 @@
     <t>Ministry of Higher Education, Science and Technology (MESCyT), Dominican Republic</t>
   </si>
   <si>
-    <t>Multiple international destinations</t>
-  </si>
-  <si>
     <t>Undergraduate, Postgraduate; depends on published offer</t>
   </si>
   <si>
@@ -8671,6 +8479,1275 @@
   </si>
   <si>
     <t>Fiji; TSLS; tertiary education; scholarship; study loan; closed 2026</t>
+  </si>
+  <si>
+    <t>aga-khan-foundation-international-scholarship-programme</t>
+  </si>
+  <si>
+    <t>Aga Khan Foundation International Scholarship Programme (AKF ISP)</t>
+  </si>
+  <si>
+    <t>Aga Khan Foundation (AKF)</t>
+  </si>
+  <si>
+    <t>Afghanistan, Pakistan, India, Bangladesh, United Kingdom, United States, Canada, France</t>
+  </si>
+  <si>
+    <t>Tuition fees and living expenses (50% grant and 50% interest-free loan)</t>
+  </si>
+  <si>
+    <t>Mar 31 (annual cycle; local AKF office deadlines may be earlier)</t>
+  </si>
+  <si>
+    <t>Citizens of selected developing countries (including Afghanistan, Bangladesh, India, Pakistan, Syria, Tajikistan, Kyrgyz Republic, Egypt, Kenya, Tanzania, Uganda, Madagascar and Mozambique) residing in an eligible country; normally under 30; strong academic record and genuine financial need.</t>
+  </si>
+  <si>
+    <t>High: local AKF application form + university admission + financial need documentation + interview</t>
+  </si>
+  <si>
+    <t>High-achieving Master and PhD applicants from Afghanistan and other AKF partner countries with demonstrated financial need</t>
+  </si>
+  <si>
+    <t>The Aga Khan Foundation provides a limited number of scholarships each year for postgraduate studies to outstanding students from select developing countries who have no other means of financing their studies. Awards are structured as a 50% grant and 50% loan with a low service charge.</t>
+  </si>
+  <si>
+    <t>AKF application form | Official academic transcripts and degree certificates | Admission offer from a reputable university | Detailed household financial plan | Two recommendation letters | Passport or national ID copy</t>
+  </si>
+  <si>
+    <t>Local AKF National Committee review and interview followed by final selection by the international panel in Geneva</t>
+  </si>
+  <si>
+    <t>Contact your local AKF office in January or February to obtain the current application forms | Show a clear plan to contribute to your home region after graduation</t>
+  </si>
+  <si>
+    <t>https://the.akdn/en/what-we-do/developing-human-capacity/education/international-scholarships</t>
+  </si>
+  <si>
+    <t>albanian-government-bilateral-scholarships</t>
+  </si>
+  <si>
+    <t>Albanian Government Bilateral &amp; Western Balkans Scholarships</t>
+  </si>
+  <si>
+    <t>Ministry of Education and Sport of the Republic of Albania</t>
+  </si>
+  <si>
+    <t>Albania</t>
+  </si>
+  <si>
+    <t>Tuition waiver at public universities in Albania, monthly living stipend and free student dormitory accommodation</t>
+  </si>
+  <si>
+    <t>Jun - Jul (annual call via bilateral partner ministries and embassies)</t>
+  </si>
+  <si>
+    <t>Citizens of partner countries with active bilateral educational agreements with Albania and eligible regional candidates; high school diploma for Bachelor or Bachelor degree for Master; meets host university entry requirements.</t>
+  </si>
+  <si>
+    <t>Medium: home ministry or embassy nomination + transcripts + medical certificate</t>
+  </si>
+  <si>
+    <t>Students from partner countries seeking a state-funded degree in Albania or the Western Balkans</t>
+  </si>
+  <si>
+    <t>The Ministry of Education and Sport of Albania offers annual scholarship quotas under bilateral intergovernmental agreements for foreign students to pursue undergraduate, postgraduate or language studies at Albanian public higher education institutions.</t>
+  </si>
+  <si>
+    <t>Official application and nomination form | Certified high school or university transcripts | Birth certificate and passport copy | Medical certificate | Proof of language proficiency</t>
+  </si>
+  <si>
+    <t>Nomination by the sending country's Ministry of Education or embassy followed by placement confirmation by the Albanian Ministry of Education and Sport</t>
+  </si>
+  <si>
+    <t>Apply through your home country's Ministry of Education scholarship desk before the summer deadline | Check whether a preparatory Albanian language year is required for your track</t>
+  </si>
+  <si>
+    <t>https://arsimi.gov.al/</t>
+  </si>
+  <si>
+    <t>university-of-andorra-honours-and-national-study-grants</t>
+  </si>
+  <si>
+    <t>University of Andorra (UdA) Honours Waivers &amp; National Study Grants</t>
+  </si>
+  <si>
+    <t>Government of Andorra &amp; Universitat d'Andorra (UdA)</t>
+  </si>
+  <si>
+    <t>Andorra</t>
+  </si>
+  <si>
+    <t>Computer Science, Data &amp; AI, Business, Economics &amp; Management, Health &amp; Life Sciences, Education, Law, Governance &amp; Public Policy</t>
+  </si>
+  <si>
+    <t>100% first-year registration fee waiver (up to 60 European credits) for Honours qualification holders; government study grants for eligible residents covering tuition, materials, transport and living costs</t>
+  </si>
+  <si>
+    <t>Jul - Sep (pre-enrolment window; national grant calls run Sep - Oct)</t>
+  </si>
+  <si>
+    <t>International and domestic students admitted to full-time Bachelor, Master or PhD programmes at the University of Andorra who hold an Honours qualification from prior studies (or meet residency criteria for Andorran government financial aid).</t>
+  </si>
+  <si>
+    <t>Medium: UdA admission application + certified Honours transcript + grant form</t>
+  </si>
+  <si>
+    <t>Top-performing students seeking an affordable European Higher Education Area (EHEA) degree in Andorra</t>
+  </si>
+  <si>
+    <t>Universitat d'Andorra (UdA), the public university of the Principality of Andorra, grants full first-year credit fee exemptions to incoming students with an Honours mark in their previous studies, alongside national and international mobility grants.</t>
+  </si>
+  <si>
+    <t>UdA online admission form | Apostilled academic transcripts showing Honours distinction | Passport copy | Language proficiency certificate (Catalan, Spanish, French or English depending on track)</t>
+  </si>
+  <si>
+    <t>Verified during academic admission and financial aid review by Universitat d'Andorra and the Andorran Ministry of Education</t>
+  </si>
+  <si>
+    <t>Have your secondary or undergraduate diploma legalised with the Hague Apostille well before pre-enrolment closes | Check the English-taught modules and double-degree options</t>
+  </si>
+  <si>
+    <t>https://www.uda.ad/en/choose-the-uda/grants-discounts-and-prices/</t>
+  </si>
+  <si>
+    <t>inagbe-angola-national-and-international-scholarships</t>
+  </si>
+  <si>
+    <t>INAGBE National &amp; International Scholarships (Angola)</t>
+  </si>
+  <si>
+    <t>Instituto Nacional de Gestão de Bolsas de Estudo (INAGBE) — Government of Angola</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Health &amp; Life Sciences, Mathematics &amp; Natural Sciences, Agriculture &amp; Food Security, Education</t>
+  </si>
+  <si>
+    <t>Full tuition coverage, monthly maintenance allowance, research/book subsidy, health insurance and return airfare for external scholars</t>
+  </si>
+  <si>
+    <t>Apr - Aug (annual call announced on the INAGBE portal)</t>
+  </si>
+  <si>
+    <t>Citizens of Angola (and eligible bilateral exchange students in Angola); strong high school or university grade average; meets age cutoffs set in each annual call (typically under 22 for Bachelor and under 35 for Master).</t>
+  </si>
+  <si>
+    <t>Medium: online INAGBE portal application + academic certificates + university admission proof</t>
+  </si>
+  <si>
+    <t>Angolan students pursuing priority STEM, health and education degrees at home or abroad</t>
+  </si>
+  <si>
+    <t>Administered by Angola's Ministry of Higher Education, Science, Technology and Innovation, INAGBE funds thousands of undergraduate and postgraduate scholars annually at Angolan universities and international partner institutions.</t>
+  </si>
+  <si>
+    <t>Online INAGBE application form | National ID (Bilhete de Identidade) or passport | Certified academic transcripts and certificates | Proof of university enrolment or admission</t>
+  </si>
+  <si>
+    <t>Automated academic grade ranking, age verification and priority field weighting by INAGBE</t>
+  </si>
+  <si>
+    <t>Ensure all school and university certificates are properly authenticated before the INAGBE portal opens | Priority goes to STEM, medicine and teacher training tracks</t>
+  </si>
+  <si>
+    <t>https://www.inagbe.gov.ao/</t>
+  </si>
+  <si>
+    <t>uwi-five-islands-and-antigua-barbuda-scholarships</t>
+  </si>
+  <si>
+    <t>UWI Five Islands Campus &amp; Antigua and Barbuda Government Scholarships</t>
+  </si>
+  <si>
+    <t>The University of the West Indies (UWI) &amp; Government of Antigua and Barbuda</t>
+  </si>
+  <si>
+    <t>Tuition scholarships and bursaries (including USD 2,500/yr donor awards and government tuition grants for OECS and national students)</t>
+  </si>
+  <si>
+    <t>May 31 (annual cycle for Fall intake)</t>
+  </si>
+  <si>
+    <t>Citizens of Antigua and Barbuda, OECS member states and CARICOM nationals enrolled full-time at the UWI Five Islands Campus in Antigua (or sister UWI campuses); minimum GPA 3.0/4.0 and demonstrated financial need.</t>
+  </si>
+  <si>
+    <t>Medium: UWI admission + scholarship application form + financial need statement</t>
+  </si>
+  <si>
+    <t>Caribbean students seeking funded undergraduate or postgraduate degrees in Antigua and Barbuda</t>
+  </si>
+  <si>
+    <t>The University of the West Indies Five Islands Campus in Antigua, together with regional corporate donors and the Government of Antigua and Barbuda, offers merit and need-based scholarships across business, health, education and computer science.</t>
+  </si>
+  <si>
+    <t>UWI admission letter | Completed scholarship application form | Official CSEC/CAPE or university transcripts | Financial need declaration | Two academic or character references</t>
+  </si>
+  <si>
+    <t>Selected by the UWI Campus Committee on Undergraduate Awards and the Prime Minister's Scholarship Committee based on GPA and socioeconomic need</t>
+  </si>
+  <si>
+    <t>Submit your UWI Five Islands admission application early so you have your student ID number ready for the scholarship form</t>
+  </si>
+  <si>
+    <t>https://www.fiveislands.uwi.edu/</t>
+  </si>
+  <si>
+    <t>conicet-doctoral-fellowships-argentina</t>
+  </si>
+  <si>
+    <t>CONICET Doctoral &amp; Postdoctoral Research Fellowships (Argentina)</t>
+  </si>
+  <si>
+    <t>National Scientific and Technical Research Council (CONICET), Government of Argentina</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Monthly living stipend indexed to national research scales, workers' compensation and health coverage (public doctoral tuition in Argentina is commonly waived or low-cost)</t>
+  </si>
+  <si>
+    <t>Jul - Aug (annual call on the SIGEVA-CONICET portal)</t>
+  </si>
+  <si>
+    <t>Open to Argentine and international graduates worldwide (especially Latin American candidates); holds a university degree qualifying for doctoral admission; secured an eligible CONICET research director and accredited Argentine host institute.</t>
+  </si>
+  <si>
+    <t>High: research work plan + CONICET supervisor endorsement + SIGEVA portal submission</t>
+  </si>
+  <si>
+    <t>Researchers seeking a fully salaried PhD in science, engineering, medicine or social sciences in Argentina</t>
+  </si>
+  <si>
+    <t>CONICET is Argentina's premier scientific research council. Its annual doctoral fellowship call funds full-time PhD candidates of any nationality to conduct original doctoral research at Argentine universities and national laboratories.</t>
+  </si>
+  <si>
+    <t>SIGEVA online application | Doctoral research work plan | Certified university transcript showing class average and historical cohort average | CV of applicant and proposed director | Host institute endorsement</t>
+  </si>
+  <si>
+    <t>Peer review by CONICET disciplinary advisory committees scoring academic average (relative to university cohort), research plan quality and director track record</t>
+  </si>
+  <si>
+    <t>Contact a CONICET investigator 3 to 4 months before the July call to co-design your research plan | Obtain an official letter from your home university stating the historical average grade of your graduating class</t>
+  </si>
+  <si>
+    <t>https://convocatorias.conicet.gov.ar/</t>
+  </si>
+  <si>
+    <t>american-university-of-armenia-international-scholarships</t>
+  </si>
+  <si>
+    <t>American University of Armenia (AUA) International &amp; AGBU Scholarships</t>
+  </si>
+  <si>
+    <t>American University of Armenia (AUA) &amp; Armenian General Benevolent Union (AGBU)</t>
+  </si>
+  <si>
+    <t>Armenia</t>
+  </si>
+  <si>
+    <t>Computer Science, Data &amp; AI, Engineering &amp; Technology, Business, Economics &amp; Management, Health &amp; Life Sciences, Law, Governance &amp; Public Policy</t>
+  </si>
+  <si>
+    <t>Up to 50% to 100% tuition reduction for international and merit scholars; additional AGBU international scholarships available</t>
+  </si>
+  <si>
+    <t>Jan - May (Early, Regular and Rolling admission deadlines)</t>
+  </si>
+  <si>
+    <t>Open to international citizens and Armenian nationals admitted to US-accredited undergraduate or graduate degree programmes at AUA in Yerevan; strong GPA, English proficiency (TOEFL iBT or IELTS) and financial need/merit.</t>
+  </si>
+  <si>
+    <t>Medium: AUA admission application + financial aid/scholarship form + English &amp; math test scores</t>
+  </si>
+  <si>
+    <t>Students seeking an English-taught, US-accredited Bachelor or Master degree in Armenia</t>
+  </si>
+  <si>
+    <t>Affiliated with the University of California and accredited by WASC, the American University of Armenia offers generous merit and need-based tuition scholarships to international and local students across STEM, business, public health and law.</t>
+  </si>
+  <si>
+    <t>AUA online admission application | Official transcripts | TOEFL iBT or IELTS score report | SAT/ACT or GRE score (if required by track) | Financial Aid application and income documents</t>
+  </si>
+  <si>
+    <t>Evaluated on admissions test scores, cumulative GPA and verified household financial need</t>
+  </si>
+  <si>
+    <t>Apply by the Early or Regular deadline rather than Rolling admission to maximise scholarship funding availability</t>
+  </si>
+  <si>
+    <t>https://finaid.aua.am/</t>
+  </si>
+  <si>
+    <t>heydar-aliyev-international-education-grant-program-azerbaijan</t>
+  </si>
+  <si>
+    <t>Heydar Aliyev International Education Grant Program (Azerbaijan)</t>
+  </si>
+  <si>
+    <t>Ministry of Foreign Affairs &amp; Ministry of Science and Education of the Republic of Azerbaijan</t>
+  </si>
+  <si>
+    <t>Azerbaijan</t>
+  </si>
+  <si>
+    <t>100% tuition waiver (including preparatory course), monthly stipend of 800 AZN (~USD 470) for 10 months/yr covering accommodation and living costs, annual international round-trip flight, and 200 AZN/yr medical insurance</t>
+  </si>
+  <si>
+    <t>May 15 (Stage 1 home country nomination) / Jun 15 (Stage 2 SIACAS portal submission)</t>
+  </si>
+  <si>
+    <t>Citizens of OIC member states, Non-Aligned Movement (NAM) countries, Small Island Developing States (SIDS) and culturally linked partner countries; age under 35 for Bachelor/general medicine, under 40 for Master/residency, under 45 for PhD; GPA &gt;= 70%; IELTS 5.0 (Bachelor) or 5.5 (Master/PhD).</t>
+  </si>
+  <si>
+    <t>High: embassy or home ministry nomination + SIACAS online application + medical &amp; HIV/Hep certificates</t>
+  </si>
+  <si>
+    <t>Students from OIC, NAM and developing nations seeking a fully funded English, Russian or Turkish-taught degree in Azerbaijan</t>
+  </si>
+  <si>
+    <t>Established by Presidential Decree, the Heydar Aliyev International Education Grant funds 100 international scholars every year for preparatory, undergraduate, graduate, medical residency and doctoral studies at top universities in Azerbaijan (including ADA University, Baku State University and ASOIU).</t>
+  </si>
+  <si>
+    <t>Official Nomination Form from home Ministry or Embassy | Diplomas and transcripts (notarised) | Medical certificate (including HIV and Hepatitis B/C tests) | Valid passport | CV and Motivation Letter | Language certificate (IELTS/TOEFL)</t>
+  </si>
+  <si>
+    <t>Two-stage selection: official nomination by home government/embassy (Stage 1), followed by SIACAS portal review and online interviews with Azerbaijani universities and the Ministry (Stage 2)</t>
+  </si>
+  <si>
+    <t>Secure your home Ministry of Education or Embassy nomination first, as direct applications to the SIACAS portal without official nomination are not accepted</t>
+  </si>
+  <si>
+    <t>https://studyinazerbaijan.edu.az/</t>
+  </si>
+  <si>
+    <t>bahamas-ministry-of-education-national-and-ub-scholarships</t>
+  </si>
+  <si>
+    <t>Bahamas Ministry of Education National Scholarships &amp; University of The Bahamas Grants</t>
+  </si>
+  <si>
+    <t>Government of The Bahamas &amp; University of The Bahamas (UB)</t>
+  </si>
+  <si>
+    <t>Bahamas, United States, Canada, United Kingdom</t>
+  </si>
+  <si>
+    <t>Full tuition at University of The Bahamas or USD 7,500 to USD 35,000/yr for accredited overseas study (National Merit, All-Bahamian and National Technical Scholarships)</t>
+  </si>
+  <si>
+    <t>Mar - Apr (annual cycle via the Bahamas Scholarships portal)</t>
+  </si>
+  <si>
+    <t>Citizens of The Bahamas for national overseas/domestic awards (plus institutional merit scholarships for eligible students admitted to University of The Bahamas); minimum GPA 3.0 to 3.5+ and strong BGCSE/SAT or undergraduate grades.</t>
+  </si>
+  <si>
+    <t>High: online portal application + unconditional university offer + SAT/GRE scores + community service proof</t>
+  </si>
+  <si>
+    <t>Bahamian and regional students pursuing priority undergraduate and graduate degrees at UB or top international universities</t>
+  </si>
+  <si>
+    <t>The Ministry of Education and Technical and Vocational Training of The Bahamas, alongside the University of The Bahamas, awards multi-year national merit, technical and bursary scholarships for domestic and international higher education.</t>
+  </si>
+  <si>
+    <t>Bahamas Scholarship portal application | Proof of citizenship (passport) | Official BGCSE/high school or university transcripts | Unconditional acceptance letter from an accredited institution | Two recommendation letters</t>
+  </si>
+  <si>
+    <t>Evaluated by the Bahamas National Scholarship Advisory Committee based on GPA, standardised test scores, financial need and national human-resource priority areas</t>
+  </si>
+  <si>
+    <t>Take the SAT or GRE early in the year so official score reports reach the Ministry before the April deadline</t>
+  </si>
+  <si>
+    <t>https://www.bahamasscholarships.com/</t>
+  </si>
+  <si>
+    <t>bahrain-crown-prince-international-scholarship-program</t>
+  </si>
+  <si>
+    <t>Crown Prince's International Scholarship Program (CPISP) &amp; University of Bahrain Scholarships</t>
+  </si>
+  <si>
+    <t>Court of the Crown Prince of Bahrain &amp; Ministry of Education of Bahrain</t>
+  </si>
+  <si>
+    <t>Bahrain, United States, United Kingdom</t>
+  </si>
+  <si>
+    <t>Full ride covering 100% tuition, housing, monthly living stipend, books and return flights for CPISP; tuition exemptions for international bilateral scholars at the University of Bahrain</t>
+  </si>
+  <si>
+    <t>Mar (annual CPISP candidacy window; Ministry bilateral calls run May - Jul)</t>
+  </si>
+  <si>
+    <t>Citizens of Bahrain (and international students nominated via bilateral cultural agreements for University of Bahrain grants); minimum 97% cumulative secondary GPA for CPISP; strong English proficiency and leadership record.</t>
+  </si>
+  <si>
+    <t>High: academic transcripts + IELTS/SAT assessment + leadership training and selection interviews</t>
+  </si>
+  <si>
+    <t>Top-tier students from Bahrain and bilateral partner states seeking fully funded undergraduate or postgraduate degrees</t>
+  </si>
+  <si>
+    <t>Founded by HRH Prince Salman bin Hamad Al Khalifa, CPISP is Bahrain's flagship merit scholarship, providing summer leadership/SAT prep and full funding at top global universities, alongside Ministry of Education bilateral scholarships hosted at the University of Bahrain.</t>
+  </si>
+  <si>
+    <t>Official secondary school or university transcripts | Passport and CPR copy | IELTS/TOEFL score report | Personal statement and extracurricular portfolio | Recommendation letters</t>
+  </si>
+  <si>
+    <t>Shortlisting of top 60 candidates based on GPA and qualifying English/critical-thinking exams, followed by a year of leadership/SAT training before final selection of 10 scholars</t>
+  </si>
+  <si>
+    <t>Apply during Grade 11 (one year before high school graduation) for CPISP | International applicants to the University of Bahrain should apply through their home Ministry of Education bilateral desk</t>
+  </si>
+  <si>
+    <t>https://www.cpisp.bh/</t>
+  </si>
+  <si>
+    <t>Bhutan</t>
+  </si>
+  <si>
+    <t>Botswana</t>
+  </si>
+  <si>
+    <t>Brunei</t>
+  </si>
+  <si>
+    <t>Latin America</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Barbuda</t>
+  </si>
+  <si>
+    <t>content.xlsx</t>
+  </si>
+  <si>
+    <t>iceland-government-icelandic-language-scholarship</t>
+  </si>
+  <si>
+    <t>Icelandic Government Scholarships for Icelandic as a Second Language</t>
+  </si>
+  <si>
+    <t>Árni Magnússon Institute for Icelandic Studies; Government of Iceland</t>
+  </si>
+  <si>
+    <t>Iceland</t>
+  </si>
+  <si>
+    <t>Undergraduate; Icelandic language study</t>
+  </si>
+  <si>
+    <t>Icelandic language and culture</t>
+  </si>
+  <si>
+    <t>University registration fee and monthly living allowance; verify current amount</t>
+  </si>
+  <si>
+    <t>Annual deadline usually 1 December; confirm next call</t>
+  </si>
+  <si>
+    <t>Students from eligible countries who meet the language-study and prior-study requirements</t>
+  </si>
+  <si>
+    <t>Medium: application and academic documentation</t>
+  </si>
+  <si>
+    <t>International students wishing to study Icelandic language and culture</t>
+  </si>
+  <si>
+    <t>The Icelandic Government offers scholarships for eligible students studying Icelandic as a second language at the University of Iceland. Eligibility is restricted to specified nationalities and prior language-study requirements.</t>
+  </si>
+  <si>
+    <t>Check current call for required application form, CV, academic records and language-study evidence</t>
+  </si>
+  <si>
+    <t>Selection under the official scholarship criteria</t>
+  </si>
+  <si>
+    <t>Confirm eligible nationalities, stipend amount and application dates in the current call before publishing as Open.</t>
+  </si>
+  <si>
+    <t>https://arnastofnun.is/en/about-scholarship</t>
+  </si>
+  <si>
+    <t>Iceland; Icelandic language; government scholarship; language study</t>
+  </si>
+  <si>
+    <t>reykjavik-university-new-student-scholarship</t>
+  </si>
+  <si>
+    <t>Reykjavík University New Student Scholarship</t>
+  </si>
+  <si>
+    <t>Reykjavík University</t>
+  </si>
+  <si>
+    <t>Eligible undergraduate programmes</t>
+  </si>
+  <si>
+    <t>Tuition fee waiver</t>
+  </si>
+  <si>
+    <t>First-semester tuition fees; verify current terms</t>
+  </si>
+  <si>
+    <t>No separate application stated; confirm current admissions cycle</t>
+  </si>
+  <si>
+    <t>Incoming undergraduate applicants meeting the university's academic achievement criteria</t>
+  </si>
+  <si>
+    <t>Medium: university admission application</t>
+  </si>
+  <si>
+    <t>High-achieving secondary-school graduates applying to Reykjavík University</t>
+  </si>
+  <si>
+    <t>Reykjavík University describes scholarship support for outstanding incoming undergraduate students. Availability and eligibility must be checked against the current admissions and scholarship rules.</t>
+  </si>
+  <si>
+    <t>University admission application and academic transcripts</t>
+  </si>
+  <si>
+    <t>University selection based on academic achievement and current scholarship rules</t>
+  </si>
+  <si>
+    <t>Confirm that the scholarship is offered for the intended intake and whether nationality or programme restrictions apply.</t>
+  </si>
+  <si>
+    <t>https://www.ru.is/en/namid/um-namid/scholarships-and-grants</t>
+  </si>
+  <si>
+    <t>Iceland; Reykjavík University; undergraduate; tuition waiver</t>
+  </si>
+  <si>
+    <t>reykjavik-university-alan-turing-scholarship</t>
+  </si>
+  <si>
+    <t>Alan Turing Scholarship</t>
+  </si>
+  <si>
+    <t>Computer Science; verify eligible programme</t>
+  </si>
+  <si>
+    <t>Tuition fee support; confirm current terms</t>
+  </si>
+  <si>
+    <t>Amount and coverage must be confirmed with the university</t>
+  </si>
+  <si>
+    <t>Not confirmed; check official scholarship page</t>
+  </si>
+  <si>
+    <t>Eligible high-achieving applicants to the relevant master's programme; confirm current nationality and academic requirements</t>
+  </si>
+  <si>
+    <t>Medium: university admission application and academic documentation</t>
+  </si>
+  <si>
+    <t>Prospective master's students in Computer Science</t>
+  </si>
+  <si>
+    <t>Scholarship opportunity referenced in Reykjavík University's scholarship information. Confirm the current award, eligible programme, selection process and availability before publishing.</t>
+  </si>
+  <si>
+    <t>Admission application and academic records; confirm additional requirements</t>
+  </si>
+  <si>
+    <t>University selection under current award rules</t>
+  </si>
+  <si>
+    <t>Do not advertise a guaranteed award or specific tuition coverage until confirmed for the current intake.</t>
+  </si>
+  <si>
+    <t>Iceland; computer science; master's; scholarship</t>
+  </si>
+  <si>
+    <t>snorri-sturluson-fellowship</t>
+  </si>
+  <si>
+    <t>Fellowship</t>
+  </si>
+  <si>
+    <t>Snorri Sturluson Fellowship</t>
+  </si>
+  <si>
+    <t>Árni Magnússon Institute for Icelandic Studies</t>
+  </si>
+  <si>
+    <t>Research fellowship</t>
+  </si>
+  <si>
+    <t>Language; literature; Icelandic culture; humanities</t>
+  </si>
+  <si>
+    <t>Financial support for a research stay; verify current stipend and travel terms</t>
+  </si>
+  <si>
+    <t>Annual deadline usually 1 December; confirm current call</t>
+  </si>
+  <si>
+    <t>Foreign writers, translators and humanities scholars interested in Icelandic language, literature and culture; specific eligibility applies</t>
+  </si>
+  <si>
+    <t>Medium: fellowship application and research documentation</t>
+  </si>
+  <si>
+    <t>Researchers, writers and translators studying Icelandic culture</t>
+  </si>
+  <si>
+    <t>The Snorri Sturluson Fellowship supports eligible foreign scholars and cultural practitioners undertaking a research stay in Iceland. It is a fellowship rather than a degree scholarship.</t>
+  </si>
+  <si>
+    <t>Application form and supporting documents required by the current call</t>
+  </si>
+  <si>
+    <t>Selection by the administering institute under its published criteria</t>
+  </si>
+  <si>
+    <t>Confirm whether the next call is open and whether travel costs are covered.</t>
+  </si>
+  <si>
+    <t>https://arnastofnun.is/en/study-icelandic-language-culture</t>
+  </si>
+  <si>
+    <t>Iceland; research fellowship; humanities; writers; translators</t>
+  </si>
+  <si>
+    <t>lund-university-global-scholarship</t>
+  </si>
+  <si>
+    <t>Lund University Global Scholarship</t>
+  </si>
+  <si>
+    <t>Lund University</t>
+  </si>
+  <si>
+    <t>Master; selected undergraduate programmes</t>
+  </si>
+  <si>
+    <t>Eligible degree programmes at Lund University</t>
+  </si>
+  <si>
+    <t>Partial to full tuition waiver</t>
+  </si>
+  <si>
+    <t>Partial or full tuition fee grant; living expenses not covered</t>
+  </si>
+  <si>
+    <t>16 February 2026; closed for the 2026 round</t>
+  </si>
+  <si>
+    <t>High-achieving students from outside the EU/EEA who are liable for tuition fees and meet programme admission requirements</t>
+  </si>
+  <si>
+    <t>High: university application and scholarship motivation statement</t>
+  </si>
+  <si>
+    <t>High-achieving international degree applicants</t>
+  </si>
+  <si>
+    <t>The Lund University Global Scholarship is a competitive merit-based tuition scholarship. The university states that the 2026 application round has closed; monitor the official page for the next round.</t>
+  </si>
+  <si>
+    <t>University admission application and scholarship motivation statement; additional documents as specified</t>
+  </si>
+  <si>
+    <t>Selection based on academic merit and the university's assessment criteria</t>
+  </si>
+  <si>
+    <t>Do not mark the 2026 round Open. Check the next intake and eligible degree programmes.</t>
+  </si>
+  <si>
+    <t>https://www.lunduniversity.lu.se/study/admission-degree-studies/scholarships-and-awards/lund-university-global-scholarship</t>
+  </si>
+  <si>
+    <t>Sweden; Lund University; tuition scholarship; merit-based</t>
+  </si>
+  <si>
+    <t>aalto-university-excellence-scholarship</t>
+  </si>
+  <si>
+    <t>Aalto University Excellence Scholarship</t>
+  </si>
+  <si>
+    <t>Aalto University</t>
+  </si>
+  <si>
+    <t>Bachelor; Master; programme-dependent</t>
+  </si>
+  <si>
+    <t>Eligible degree programmes at Aalto University</t>
+  </si>
+  <si>
+    <t>Full tuition fee waiver</t>
+  </si>
+  <si>
+    <t>100% tuition fee; living expenses not covered</t>
+  </si>
+  <si>
+    <t>Apply during the relevant degree admission period; next dates to be confirmed</t>
+  </si>
+  <si>
+    <t>Applicants liable for tuition fees, generally non-EU/EEA citizens who do not qualify for an exemption; programme-specific conditions apply</t>
+  </si>
+  <si>
+    <t>High: degree application and scholarship selection</t>
+  </si>
+  <si>
+    <t>High-achieving international students applying to Aalto University</t>
+  </si>
+  <si>
+    <t>Aalto University Excellence Scholarships are competitive merit-based tuition waivers. They cover tuition fees but not living expenses, and some programmes may award no scholarships.</t>
+  </si>
+  <si>
+    <t>University admission application with scholarship selection indicated; supporting academic documents</t>
+  </si>
+  <si>
+    <t>Competitive academic assessment by the relevant degree programme and school</t>
+  </si>
+  <si>
+    <t>Verify the next admission period and whether the intended programme participates before publishing as Open.</t>
+  </si>
+  <si>
+    <t>https://www.aalto.fi/en/admission-services/scholarships-and-tuition-fees</t>
+  </si>
+  <si>
+    <t>Finland; Aalto University; tuition waiver; international students</t>
+  </si>
+  <si>
+    <t>university-helsinki-international-masters-tuition-waiver</t>
+  </si>
+  <si>
+    <t>University of Helsinki International Master's Tuition Fee Waiver</t>
+  </si>
+  <si>
+    <t>University of Helsinki</t>
+  </si>
+  <si>
+    <t>Eligible international master's programmes</t>
+  </si>
+  <si>
+    <t>Partial to full tuition fee waiver</t>
+  </si>
+  <si>
+    <t>50% or 100% tuition fee waiver; living expenses not covered</t>
+  </si>
+  <si>
+    <t>Apply alongside the relevant master's admission round</t>
+  </si>
+  <si>
+    <t>Eligible students liable for tuition fees from outside the EU/EEA and Switzerland, subject to programme and university requirements</t>
+  </si>
+  <si>
+    <t>High: master's admission application and scholarship application</t>
+  </si>
+  <si>
+    <t>High-achieving international master's applicants</t>
+  </si>
+  <si>
+    <t>The University of Helsinki offers competitive tuition fee waivers for eligible fee-paying master's students. Most awards cover 50% of tuition; a limited number cover 100%. Living expenses are not covered.</t>
+  </si>
+  <si>
+    <t>Master's application, academic transcripts and other documents required by the chosen programme</t>
+  </si>
+  <si>
+    <t>Academic assessment under the university's scholarship and admission criteria</t>
+  </si>
+  <si>
+    <t>Keep this as one record for the university-wide scheme. Check the next application window and programme-specific eligibility.</t>
+  </si>
+  <si>
+    <t>https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/tuition-fees-and-scholarship-programme</t>
+  </si>
+  <si>
+    <t>Finland; University of Helsinki; master's; tuition waiver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latin America </t>
+  </si>
+  <si>
+    <t>tu-delft-justus-and-louise-van-effen-excellence-scholarships</t>
+  </si>
+  <si>
+    <t>TU Delft Justus &amp; Louise van Effen Excellence Scholarships</t>
+  </si>
+  <si>
+    <t>Delft University of Technology (TU Delft) — Legacy of Justus &amp; Louise van Effen</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Computer Science, Data &amp; AI, Mathematics &amp; Natural Sciences, Architecture, Arts &amp; Design</t>
+  </si>
+  <si>
+    <t>Full tuition fee waiver (~EUR 21,500/yr) plus full monthly living expenses contribution (~EUR 11,500/yr) for 2 years</t>
+  </si>
+  <si>
+    <t>Dec 1, 2026 (annual cycle for September 2027 intake)</t>
+  </si>
+  <si>
+    <t>Excellent international applicants admitted to any 2-year Regular MSc programme at TU Delft with a cumulative Bachelor GPA of 80% or higher of the scale maximum from an internationally renowned university outside the Netherlands.</t>
+  </si>
+  <si>
+    <t>High: complete MSc admission application + Scholarship Application Form + 2 reference letters + English test</t>
+  </si>
+  <si>
+    <t>Top-tier engineering, architecture and STEM graduates seeking a full ride at TU Delft</t>
+  </si>
+  <si>
+    <t>Financed by the bequest of Justus and Louise van Effen, this flagship TU Delft scholarship supports outstanding international MSc students who wish to study technology and engineering in Delft. Two scholarships are typically awarded per TU Delft faculty each year.</t>
+  </si>
+  <si>
+    <t>TU Delft MSc admission application | Scholarship Application Form | Two reference letters (uploaded or submitted via osiaan.tudelft.nl) | Official Bachelor transcripts (GPA &gt;= 80%) | English proficiency certificate (TOEFL iBT 100+ or IELTS 7.0+)</t>
+  </si>
+  <si>
+    <t>Faculty selection committees shortlist top candidates in December/January based on GPA, university reputation and motivation; final results announced by late March</t>
+  </si>
+  <si>
+    <t>Submit your complete MSc application in Studielink and osiaan.tudelft.nl well before 1 December | Explain clearly how you discovered the scholarship and your research goals in the Scholarship Application Form</t>
+  </si>
+  <si>
+    <t>https://www.tudelft.nl/en/education/practical-matters/scholarships/justus-louise-van-effen-excellence-scholarships</t>
+  </si>
+  <si>
+    <t>maastricht-university-nl-high-potential-scholarship</t>
+  </si>
+  <si>
+    <t>Maastricht University NL-High Potential Scholarship</t>
+  </si>
+  <si>
+    <t>Maastricht University Scholarship Fund &amp; Dutch Ministry of Education (NL Scholarship)</t>
+  </si>
+  <si>
+    <t>Up to EUR 36,000+ per year covering full tuition fee waiver, living expenses (EUR 20,150 for 13 mos or EUR 38,750 for 25 mos), health &amp; liability insurance (EUR 700), visa costs and pre-academic training</t>
+  </si>
+  <si>
+    <t>Dec 10, 2026 (MSc admission registration) / Feb 1, 2027 (Scholarship application deadline)</t>
+  </si>
+  <si>
+    <t>Non-EU/EEA, non-Swiss and non-Surinamese citizens aged under 35 on 1 September 2027; never enrolled in a degree-seeking programme in the Netherlands; GPA of at least 7.5/10 in prior degree; applied to a participating full-time Master programme at Maastricht University.</t>
+  </si>
+  <si>
+    <t>High: Studielink MSc application + UM portal scholarship form + referee letter submitted directly by referee</t>
+  </si>
+  <si>
+    <t>High-GPA non-EU/EEA graduates seeking a comprehensive 21-seat full ride at Maastricht University</t>
+  </si>
+  <si>
+    <t>Combining the Maastricht University Scholarship Fund and the NL Scholarship, the UM NL-High Potential Scholarship awards 21 full scholarships annually to talented non-EU/EEA students admitted to participating 1-year or 2-year Master programmes at Maastricht University.</t>
+  </si>
+  <si>
+    <t>Studielink Master admission application (student ID required) | UM Scholarship Application Form | Proof of academic excellence (transcript showing GPA &gt;= 7.5/10) | Personal statement of financial need | Motivation letter | Contact details of 1 referee (professor or employer)</t>
+  </si>
+  <si>
+    <t>Faculty ranking of top 5% candidates in February -&gt; UM International Services Office verification in March -&gt; Final selection decision announced in April</t>
+  </si>
+  <si>
+    <t>Register for your Master programme in Studielink before 10 December so you receive your UM student ID in time | Remind your referee to submit their reference via the online form before 1 February</t>
+  </si>
+  <si>
+    <t>https://www.maastrichtuniversity.nl/support/your-studies-begin/coming-maastricht-university-abroad/um-scholarships-students-abroad</t>
+  </si>
+  <si>
+    <t>eric-bleumink-fund-scholarship-university-of-groningen</t>
+  </si>
+  <si>
+    <t>Eric Bleumink Fund (EBF) Fellowship — University of Groningen</t>
+  </si>
+  <si>
+    <t>University of Groningen (Eric Bleumink Fund)</t>
+  </si>
+  <si>
+    <t>Full tuition fee coverage, international travel costs, monthly subsistence allowance, books and health insurance for a 1-year or 2-year Master degree</t>
+  </si>
+  <si>
+    <t>Dec 1, 2026 (Master admission application deadline for automatic EBF consideration)</t>
+  </si>
+  <si>
+    <t>Citizens of eligible developing countries (including Afghanistan, Angola, Armenia, Bangladesh, Ethiopia, Ghana, India, Indonesia, Kenya, Morocco, Nepal, Nigeria, Pakistan, Sri Lanka, Tanzania, Uganda, Uzbekistan, Vietnam, Zambia, etc.); conditional/unconditional admission to a Groningen Master before 1 December; outstanding academic record and no other means of financing.</t>
+  </si>
+  <si>
+    <t>Medium: complete Groningen MSc/MA/LLM admission application before 1 December (nomination is automatic)</t>
+  </si>
+  <si>
+    <t>Top graduates from developing countries seeking a fully funded Master at the University of Groningen</t>
+  </si>
+  <si>
+    <t>The Eric Bleumink Fund awards full scholarships to talented students and young researchers from developing nations to pursue a 1-year or 2-year Master programme (MSc, MA or LL.M.) at the University of Groningen.</t>
+  </si>
+  <si>
+    <t>University of Groningen Master admission application | Official Bachelor transcripts and degree certificate | Two letters of recommendation confirming top academic standing | Motivation letter | CV | English proficiency score</t>
+  </si>
+  <si>
+    <t>University of Groningen Admission Office and Faculty Boards nominate top admitted candidates from eligible countries before 1 December; shortlisted nominees are notified directly</t>
+  </si>
+  <si>
+    <t>There is no separate scholarship application form—you must submit your Master admission application well before 1 December so the Admission Office can issue a provisional offer in time for nomination</t>
+  </si>
+  <si>
+    <t>https://www.rug.nl/education/scholarships/eric-bleumink-fellowship</t>
+  </si>
+  <si>
+    <t>wageningen-university-africa-scholarship-programme</t>
+  </si>
+  <si>
+    <t>Wageningen University Africa Scholarship Programme (ASP) &amp; Excellence Programme</t>
+  </si>
+  <si>
+    <t>Wageningen University &amp; Research (WUR)</t>
+  </si>
+  <si>
+    <t>Agriculture &amp; Food Security, Environment, Water &amp; Energy, Health &amp; Life Sciences, Mathematics &amp; Natural Sciences</t>
+  </si>
+  <si>
+    <t>Full tuition fee coverage (24 months), monthly living allowance, travel to/from the Netherlands, visa costs, health insurance and capacity-building seminar budget</t>
+  </si>
+  <si>
+    <t>Dec 1, 2026 (complete MSc admission application deadline for ASP; Feb 1, 2027 for WUR Excellence Programme)</t>
+  </si>
+  <si>
+    <t>Citizens of an African country (for ASP) or non-EU/EEA countries (for WUR Excellence Programme); First Class Honours Bachelor degree with GPA of 80% or higher; unconditionally admitted to a WUR MSc programme before the deadline; does not already hold a Master degree.</t>
+  </si>
+  <si>
+    <t>High: unconditional MSc admission before 1 December + invitation-only written assignment + online selection interview</t>
+  </si>
+  <si>
+    <t>First-Class Honours graduates in agriculture, food science, climate and environmental sciences</t>
+  </si>
+  <si>
+    <t>Wageningen University &amp; Research, ranked #1 globally in Agriculture and Forestry, funds talented students through the Africa Scholarship Programme (ASP) and the WUR Excellence Programme to build research and leadership capacity for a sustainable world.</t>
+  </si>
+  <si>
+    <t>Complete WUR MSc admission application | Uploaded Bachelor diploma and final transcript (GPA &gt;= 80%) | Official English proficiency certificate | CV and Motivation Letter</t>
+  </si>
+  <si>
+    <t>Automatic screening of unconditional MSc admits after 1 December -&gt; ~40 candidates invited in January to submit reference letters and a written assignment -&gt; Online interviews in March -&gt; Final selection in April</t>
+  </si>
+  <si>
+    <t>You must already hold your final Bachelor diploma and English test score before 1 December to receive unconditional admission in time for the ASP shortlist</t>
+  </si>
+  <si>
+    <t>https://www.wur.nl/en/education/master/study-expenses-masters/scholarships</t>
+  </si>
+  <si>
+    <t>tue-amandus-h-lundqvist-scholarship-program</t>
+  </si>
+  <si>
+    <t>Amandus H. Lundqvist Scholarship Program (ALSP) — TU Eindhoven</t>
+  </si>
+  <si>
+    <t>Eindhoven University of Technology (TU/e)</t>
+  </si>
+  <si>
+    <t>Full tuition fee waiver (EUR 16,000/yr waived for 2 years) plus EUR 5,000/yr towards living expenses (EUR 10,000 total over 2 years)</t>
+  </si>
+  <si>
+    <t>Feb 1, 2027 (annual deadline for September 2027 intake; applying before Jan 1 is strongly advised)</t>
+  </si>
+  <si>
+    <t>International students of any nationality (except Dutch) not eligible for Dutch student finance; applying to a full-time 2-year TU/e Master programme; cumulative GPA above 80% of the grading scale maximum from an internationally recognised university.</t>
+  </si>
+  <si>
+    <t>Medium: complete TU/e Master admission application + motivation letter detailing career plans (automatic consideration)</t>
+  </si>
+  <si>
+    <t>High-GPA engineering, AI and computer science applicants targeting Eindhoven's Brainport tech hub</t>
+  </si>
+  <si>
+    <t>The Amandus H. Lundqvist Scholarship Program (ALSP) at Eindhoven University of Technology supports outstanding international Master students with a full 2-year tuition waiver and annual living allowance in the heart of Europe's Brainport high-tech ecosystem.</t>
+  </si>
+  <si>
+    <t>Online TU/e Master admission application | Official Bachelor transcripts (GPA &gt;= 80%) | Motivation letter including post-graduation career plans | CV | Two recommendation letters | English proficiency certificate</t>
+  </si>
+  <si>
+    <t>All complete Master applications submitted before 1 February are automatically evaluated by department selection committees on academic excellence and motivation</t>
+  </si>
+  <si>
+    <t>No separate scholarship form is required—simply submit your complete TU/e MSc application before 1 February (ideally by 1 January) to be automatically entered into the ALSP selection</t>
+  </si>
+  <si>
+    <t>https://www.tue.nl/en/education/become-a-tue-student/scholarships-and-grants/amandus-h-lundqvist-scholarship-program</t>
+  </si>
+  <si>
+    <t>utrecht-excellence-scholarships</t>
+  </si>
+  <si>
+    <t>Utrecht Excellence Scholarships (UES)</t>
+  </si>
+  <si>
+    <t>Utrecht University (Utrecht Excellence Scholarship Fund)</t>
+  </si>
+  <si>
+    <t>Full tuition fee waiver OR full tuition fee waiver plus the IND-required annual living allowance for a study residence permit (renewable for Year 2)</t>
+  </si>
+  <si>
+    <t>Feb 1, 2027 (23:59 CET; submit MSc admission and UES application via OSIRIS before Jan 27 to allow document updates)</t>
+  </si>
+  <si>
+    <t>Non-EU/EEA citizens not eligible for Dutch student grants; graduated in the top 10% of their Bachelor class outside the Netherlands; applied to a participating international Master programme at Utrecht University starting 1 September.</t>
+  </si>
+  <si>
+    <t>High: OSIRIS Master admission application + separate UES dashboard application + official top 10% class ranking proof</t>
+  </si>
+  <si>
+    <t>Graduates with official proof of ranking in the top 10% of their undergraduate cohort</t>
+  </si>
+  <si>
+    <t>The Utrecht Excellence Scholarship (UES) offers a highly selective number of full tuition or tuition-plus-living grants to outstanding prospective non-EU/EEA Master students across Utrecht University's graduate schools.</t>
+  </si>
+  <si>
+    <t>OSIRIS Master admission application | Official statement/certificate from home university proving top 10% class ranking | UES application questions in OSIRIS dashboard | Academic transcripts | Motivation letter | Reference letters</t>
+  </si>
+  <si>
+    <t>Selected by Utrecht University Graduate School committees based on top 10% class standing, academic quality of previous institution, motivation letter and completeness of file; results announced in mid-April</t>
+  </si>
+  <si>
+    <t>Obtain a stamped, signed class-ranking certificate from your university registrar explicitly stating you belong to the top 10% of your graduating cohort | Submit before 27 January because applications sent between 27 Jan and 1 Feb cannot be edited if a document is missing</t>
+  </si>
+  <si>
+    <t>https://www.uu.nl/en/masters/general-information/application-and-admission/scholarships-and-grants/utrecht-excellence-scholarships</t>
+  </si>
+  <si>
+    <t>university-of-twente-scholarship-and-kipaji-fund</t>
+  </si>
+  <si>
+    <t>University of Twente Scholarship (UTS) &amp; Kipaji Scholarship</t>
+  </si>
+  <si>
+    <t>University of Twente (UT)</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Technology, Computer Science, Data &amp; AI, Mathematics &amp; Natural Sciences, Business, Economics &amp; Management, Social Sciences &amp; Humanities</t>
+  </si>
+  <si>
+    <t>EUR 3,000 to EUR 22,000 per year (renewable for Year 2 in 2-year MSc programmes); eligible developing-country UTS winners can receive up to an extra EUR 12,000 via the Kipaji Scholarship</t>
+  </si>
+  <si>
+    <t>Apr 1, 2027 (Round 1 opens Oct 15, 2026; Kipaji deadline May 1)</t>
+  </si>
+  <si>
+    <t>Non-EU/EEA students provisionally admitted to a qualifying UT Master programme (excluding ITC programmes); top 5-10% of graduating class; IELTS 6.5 (6.0 speaking) or TOEFL iBT 90; Kipaji top-up open to citizens of DAC/developing nations (including Afghanistan, Angola, Bangladesh, Pakistan, Nepal, Kenya, Nigeria, etc.).</t>
+  </si>
+  <si>
+    <t>Medium: first obtain provisional UT MSc admission (student number) + submit separate UTS online form</t>
+  </si>
+  <si>
+    <t>Top 5-10% STEM and social science graduates applying to the University of Twente</t>
+  </si>
+  <si>
+    <t>The University of Twente Scholarship (UTS) is a merit award for outstanding non-EU/EEA Master students. Recipients from developing economies with rising scientific potential can combine UTS with the Kipaji Scholarship (up to EUR 12,000 extra) to cover full study and living costs.</t>
+  </si>
+  <si>
+    <t>Provisional admission letter from University of Twente (student number required) | Bachelor transcripts showing top 5-10% standing | IELTS 6.5 or TOEFL iBT 90 certificate | UTS motivation letter (include a paragraph on entrepreneurship/scientific impact in your home country to be considered for Kipaji)</t>
+  </si>
+  <si>
+    <t>Evaluated by UT faculty scholarship panels on class rank, academic background and motivation; results announced within weeks of the deadline</t>
+  </si>
+  <si>
+    <t>Apply for UT Master admission at least 4 to 6 weeks before 1 April because you cannot open the UTS form without a provisional admission offer | Mention in your UTS motivation letter that you also wish to apply for the Kipaji Scholarship</t>
+  </si>
+  <si>
+    <t>https://www.utwente.nl/en/education/scholarship-finder/university-of-twente-scholarship/</t>
+  </si>
+  <si>
+    <t>vu-fellowship-programme-vrije-universiteit-amsterdam</t>
+  </si>
+  <si>
+    <t>VU Fellowship Programme (VUFP) — Vrije Universiteit Amsterdam</t>
+  </si>
+  <si>
+    <t>Vrije Universiteit Amsterdam (VU Amsterdam)</t>
+  </si>
+  <si>
+    <t>100% tuition fee waiver for a 1-year or 2-year Master programme (automatically combined with NL Scholarship consideration for an additional EUR 5,000 or EUR 10,000 Year-1 living grant)</t>
+  </si>
+  <si>
+    <t>Dec 1, 2026 (advised MSc admission application) / Feb 1, 2027 (VUFP scholarship deadline in VU dashboard)</t>
+  </si>
+  <si>
+    <t>Non-EU/EEA citizens not holding a Dutch degree; conditionally or unconditionally admitted to a full-time English-taught Master programme at VU Amsterdam starting in September 2027; Bachelor GPA equivalent to at least a Dutch 8.0/10.</t>
+  </si>
+  <si>
+    <t>High: Studielink MSc registration by 1 December + combined VUFP-NLS single PDF upload in VU dashboard by 1 February</t>
+  </si>
+  <si>
+    <t>Students with a GPA &gt;= 80% seeking a full tuition waiver (plus potential living grant) in Amsterdam</t>
+  </si>
+  <si>
+    <t>The VU Fellowship Programme (VUFP) awards 20 to 25 full tuition waivers each year to talented non-EU/EEA students at Vrije Universiteit Amsterdam. Applying for VUFP automatically enters candidates for the VU NL Scholarship towards first-year living expenses.</t>
+  </si>
+  <si>
+    <t>Official VUFP-NLS application form | Bachelor transcript and GPA proof (&gt;= 8.0/10 equivalent) | Official grading scale explanation | Conditional or unconditional VU Master admission confirmation (all merged into a single PDF file)</t>
+  </si>
+  <si>
+    <t>Faculties nominate top candidates in February -&gt; Central VUFP Committee selects recipients -&gt; Results announced in mid-March</t>
+  </si>
+  <si>
+    <t>Register for your Master programme in Studielink by 1 December so you are conditionally admitted before the 1 February VUFP deadline | Merge the VUFP-NLS form, GPA proof and grading scale into a single PDF as required</t>
+  </si>
+  <si>
+    <t>https://vu.nl/en/education/more-about/incoming-master-scholarships</t>
+  </si>
+  <si>
+    <t>radboud-scholarship-programme-netherlands</t>
+  </si>
+  <si>
+    <t>Radboud Scholarship Programme</t>
+  </si>
+  <si>
+    <t>Radboud University Nijmegen</t>
+  </si>
+  <si>
+    <t>Reduces institutional tuition fee (~EUR 18,000) to the statutory EEA tuition rate (~EUR 2,695/yr) PLUS full coverage of visa, residence permit, health insurance and liability insurance costs</t>
+  </si>
+  <si>
+    <t>Jan 31, 2027 (23:59 CET; OSIRIS Master admission and scholarship application deadline)</t>
+  </si>
+  <si>
+    <t>Non-EU/EEA passport holders who obtained their Bachelor degree outside the Netherlands; outstanding academic results; admitted to an eligible English-taught Master degree programme at Radboud University starting 1 September 2027.</t>
+  </si>
+  <si>
+    <t>Medium: indicate Radboud Scholarship interest inside the OSIRIS Master admission application + upload 2 reference letters + CV</t>
+  </si>
+  <si>
+    <t>Non-EU/EEA students seeking an 85% tuition reduction and free visa/insurance at a top Dutch research university</t>
+  </si>
+  <si>
+    <t>The Radboud Scholarship Programme offers approximately 28 selective scholarships across all seven faculties of Radboud University, reducing non-EEA tuition to the statutory European rate and paying all immigration and insurance fees for the full duration of the Master programme.</t>
+  </si>
+  <si>
+    <t>OSIRIS Master admission application (with Radboud Scholarship box ticked) | Two reference letters | Curriculum Vitae | Official Bachelor transcripts | English proficiency certificate</t>
+  </si>
+  <si>
+    <t>Faculty selection boards assess academic talent, ambition, reference letters and transcript quality; decisions announced before mid-April</t>
+  </si>
+  <si>
+    <t>You apply for admission and the Radboud Scholarship in the same OSIRIS workflow, but you must fully submit your OSIRIS application before 31 January (even if the normal course deadline is later)</t>
+  </si>
+  <si>
+    <t>https://www.ru.nl/en/education/scholarships/radboud-scholarship-programme</t>
+  </si>
+  <si>
+    <t>leiden-university-excellence-scholarship-lexs</t>
+  </si>
+  <si>
+    <t>Leiden University Excellence Scholarship (LExS)</t>
+  </si>
+  <si>
+    <t>Leiden University</t>
+  </si>
+  <si>
+    <t>Tuition fee waiver tiers of EUR 10,000, EUR 15,000, EUR 17,500, EUR 18,500 or EUR 19,000 per year for the official duration of the Master programme</t>
+  </si>
+  <si>
+    <t>Dec 1, 2026 (for February intake: Oct 1; for September 2027 intake: Dec 1, 2026)</t>
+  </si>
+  <si>
+    <t>Non-EEA/non-EFTA passport holders (including UK nationals not resident in NL before 2021) applying to a full-time Master programme at Leiden University; ranked in the top 10% of their previous graduating class.</t>
+  </si>
+  <si>
+    <t>Medium: online Leiden Master admission application + 500-word LExS motivation letter uploaded in the portal</t>
+  </si>
+  <si>
+    <t>Top 10% graduates in law, governance, humanities, medicine and science applying to Leiden University</t>
+  </si>
+  <si>
+    <t>The Leiden University Excellence Scholarship (LExS) is awarded to academically exceptional non-EEA Master students across Archaeology, Humanities, Medicine (LUMC), Governance and Global Affairs, Law, Science, and Social &amp; Behavioural Sciences.</t>
+  </si>
+  <si>
+    <t>Leiden University online Master admission application | Separate 500-word LExS motivation letter (PDF) | Official academic transcripts (top 10% standing) | CV | Language proficiency certificate</t>
+  </si>
+  <si>
+    <t>Faculty selection committees review applications within 10 weeks of the deadline; results communicated by late March</t>
+  </si>
+  <si>
+    <t>After submitting your Master admission application in the Leiden portal, return to the Scholarships section of your online application to upload your 500-word LExS motivation letter before 1 December</t>
+  </si>
+  <si>
+    <t>https://www.universiteitleiden.nl/en/scholarships/sea/leiden-university-excellence-scholarship-lexs</t>
+  </si>
+  <si>
+    <t>amsterdam-merit-scholarship-university-of-amsterdam</t>
+  </si>
+  <si>
+    <t>Amsterdam Merit Scholarship (AMS) — University of Amsterdam</t>
+  </si>
+  <si>
+    <t>University of Amsterdam (UvA)</t>
+  </si>
+  <si>
+    <t>EUR 6,000 up to full institutional tuition fee waiver (~EUR 18,000 to EUR 25,000/yr depending on the UvA faculty and Graduate School)</t>
+  </si>
+  <si>
+    <t>Jan 15, 2027 (varies between Jan 15 and Feb 1, 2027 depending on the UvA faculty)</t>
+  </si>
+  <si>
+    <t>Non-EU/EEA (and non-Swiss/non-UK where applicable) students admitted to an English-taught Bachelor or Master programme at the University of Amsterdam; ranked in the top 10% of their graduating class.</t>
+  </si>
+  <si>
+    <t>High: UvA programme admission application + faculty-specific AMS motivation letter + recommendation letters + extracurricular CV</t>
+  </si>
+  <si>
+    <t>Top 10% undergraduate and graduate applicants targeting the University of Amsterdam</t>
+  </si>
+  <si>
+    <t>The University of Amsterdam (UvA) offers the Amsterdam Merit Scholarship (AMS) through its individual faculties (Economics &amp; Business, Science, Social &amp; Behavioural Sciences, Humanities, Law, Medicine and Child Development) to attract the brightest non-EEA students.</t>
+  </si>
+  <si>
+    <t>Studielink &amp; MyInfo UvA admission application | Official transcripts (GPA in top 10%) | AMS motivation letter (300-500 words) | Recommendation letter from dean, teacher or academic supervisor | Description of extracurricular activities | English proficiency score</t>
+  </si>
+  <si>
+    <t>Decided by each UvA Faculty or Graduate School selection committee based on GPA, class rank, academic motivation and extracurricular profile</t>
+  </si>
+  <si>
+    <t>Check your exact UvA faculty page (e.g., Faculty of Science vs. Amsterdam Business School) because each faculty sets its own AMS deadline in January and its own application upload link</t>
+  </si>
+  <si>
+    <t>https://www.uva.nl/en/education/fees-and-funding/master-scholarships-and-loans/scholarships-and-loans.html</t>
+  </si>
+  <si>
+    <t>academictransfer-salaried-phd-positions-netherlands</t>
+  </si>
+  <si>
+    <t>Dutch Salaried PhD Fellowships (AcademicTransfer / NWO / 4TU)</t>
+  </si>
+  <si>
+    <t>Dutch Research Universities (UNL), NWO (Dutch Research Council) &amp; University Medical Centers</t>
+  </si>
+  <si>
+    <t>Full 4-year salaried employment contract (EUR 2,872/mo in Year 1 rising to EUR 3,670/mo in Year 4, plus 8% holiday allowance, 8.3% year-end bonus, zero tuition fees, pension and 30% tax ruling eligibility)</t>
+  </si>
+  <si>
+    <t>Year-round rolling deadlines (individual PhD vacancies close 3 to 6 weeks after posting on AcademicTransfer)</t>
+  </si>
+  <si>
+    <t>Open to all nationalities worldwide; holds (or is about to complete) a research-oriented Master degree (MSc/MA/MRes) in a relevant discipline; strong thesis research record and English proficiency.</t>
+  </si>
+  <si>
+    <t>High: tailored cover letter + academic CV + MSc thesis PDF/summary + 2-3 academic references + multi-round interviews</t>
+  </si>
+  <si>
+    <t>Master graduates worldwide seeking a fully salaried 4-year PhD employee position in the Netherlands with zero tuition</t>
+  </si>
+  <si>
+    <t>Unlike most countries, PhD candidates at Dutch research universities (TU Delft, UT, TU/e, WUR, UvA, Leiden, Utrecht, Groningen, Radboud, Maastricht, etc.) are hired as full-time paid university employees rather than fee-paying students. All official NWO, ERC and university-funded PhD vacancies are published centrally on AcademicTransfer.</t>
+  </si>
+  <si>
+    <t>Tailored academic CV | Motivation letter addressing the specific project description | Bachelor and Master transcripts | Master thesis (or draft/abstract) | Contact details for 2 to 3 academic referees</t>
+  </si>
+  <si>
+    <t>Direct recruitment by the Principal Investigator (PI) and HR committee: CV/thesis screening -&gt; 1st round online technical interview -&gt; 2nd round research presentation with the lab group</t>
+  </si>
+  <si>
+    <t>Set up weekly email alerts on AcademicTransfer.com for your exact subfield | Treat the application like a research job interview by referencing the PI's recent papers and the exact methodology in the vacancy text</t>
+  </si>
+  <si>
+    <t>https://www.academictransfer.com/en/jobs/?vacancy_type=scientific&amp;function_types=1</t>
   </si>
 </sst>
 </file>
@@ -9059,7 +10136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="150" style="5" customWidth="1"/>
@@ -9198,6 +10275,11 @@
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>2965</v>
       </c>
     </row>
   </sheetData>
@@ -9290,7 +10372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC398"/>
+  <dimension ref="A1:AC394"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" style="5" customWidth="1"/>
@@ -9472,7 +10554,7 @@
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
       <c r="AC2" s="6" t="str">
-        <f>IF(AND(E2&lt;&gt;"",COUNTIF($E$2:$E$798,E2)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E2&lt;&gt;"",COUNTIF($E$2:$E$794,E2)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9546,7 +10628,7 @@
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="6" t="str">
-        <f>IF(AND(E3&lt;&gt;"",COUNTIF($E$2:$E$798,E3)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E3&lt;&gt;"",COUNTIF($E$2:$E$794,E3)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9612,7 +10694,7 @@
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
       <c r="AC4" s="6" t="str">
-        <f>IF(AND(E4&lt;&gt;"",COUNTIF($E$2:$E$798,E4)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E4&lt;&gt;"",COUNTIF($E$2:$E$794,E4)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9678,7 +10760,7 @@
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="6" t="str">
-        <f>IF(AND(E5&lt;&gt;"",COUNTIF($E$2:$E$798,E5)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E5&lt;&gt;"",COUNTIF($E$2:$E$794,E5)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9742,7 +10824,7 @@
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="6" t="str">
-        <f>IF(AND(E6&lt;&gt;"",COUNTIF($E$2:$E$798,E6)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E6&lt;&gt;"",COUNTIF($E$2:$E$794,E6)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9818,7 +10900,7 @@
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="6" t="str">
-        <f>IF(AND(E7&lt;&gt;"",COUNTIF($E$2:$E$798,E7)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E7&lt;&gt;"",COUNTIF($E$2:$E$794,E7)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9892,7 +10974,7 @@
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
       <c r="AC8" s="6" t="str">
-        <f>IF(AND(E8&lt;&gt;"",COUNTIF($E$2:$E$798,E8)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E8&lt;&gt;"",COUNTIF($E$2:$E$794,E8)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -9956,7 +11038,7 @@
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
       <c r="AC9" s="6" t="str">
-        <f>IF(AND(E9&lt;&gt;"",COUNTIF($E$2:$E$798,E9)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E9&lt;&gt;"",COUNTIF($E$2:$E$794,E9)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10032,7 +11114,7 @@
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="6" t="str">
-        <f>IF(AND(E10&lt;&gt;"",COUNTIF($E$2:$E$798,E10)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E10&lt;&gt;"",COUNTIF($E$2:$E$794,E10)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10098,7 +11180,7 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="6" t="str">
-        <f>IF(AND(E11&lt;&gt;"",COUNTIF($E$2:$E$798,E11)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E11&lt;&gt;"",COUNTIF($E$2:$E$794,E11)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10164,7 +11246,7 @@
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="6" t="str">
-        <f>IF(AND(E12&lt;&gt;"",COUNTIF($E$2:$E$798,E12)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E12&lt;&gt;"",COUNTIF($E$2:$E$794,E12)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10240,7 +11322,7 @@
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="6" t="str">
-        <f>IF(AND(E13&lt;&gt;"",COUNTIF($E$2:$E$798,E13)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E13&lt;&gt;"",COUNTIF($E$2:$E$794,E13)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10306,7 +11388,7 @@
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="6" t="str">
-        <f>IF(AND(E14&lt;&gt;"",COUNTIF($E$2:$E$798,E14)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E14&lt;&gt;"",COUNTIF($E$2:$E$794,E14)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10372,7 +11454,7 @@
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="6" t="str">
-        <f>IF(AND(E15&lt;&gt;"",COUNTIF($E$2:$E$798,E15)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E15&lt;&gt;"",COUNTIF($E$2:$E$794,E15)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10436,7 +11518,7 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="6" t="str">
-        <f>IF(AND(E16&lt;&gt;"",COUNTIF($E$2:$E$798,E16)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E16&lt;&gt;"",COUNTIF($E$2:$E$794,E16)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10512,7 +11594,7 @@
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="6" t="str">
-        <f>IF(AND(E17&lt;&gt;"",COUNTIF($E$2:$E$798,E17)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E17&lt;&gt;"",COUNTIF($E$2:$E$794,E17)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10586,7 +11668,7 @@
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="6" t="str">
-        <f>IF(AND(E18&lt;&gt;"",COUNTIF($E$2:$E$798,E18)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E18&lt;&gt;"",COUNTIF($E$2:$E$794,E18)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10650,7 +11732,7 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="6" t="str">
-        <f>IF(AND(E19&lt;&gt;"",COUNTIF($E$2:$E$798,E19)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E19&lt;&gt;"",COUNTIF($E$2:$E$794,E19)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10714,7 +11796,7 @@
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="6" t="str">
-        <f>IF(AND(E20&lt;&gt;"",COUNTIF($E$2:$E$798,E20)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E20&lt;&gt;"",COUNTIF($E$2:$E$794,E20)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10788,7 +11870,7 @@
       <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="6" t="str">
-        <f>IF(AND(E21&lt;&gt;"",COUNTIF($E$2:$E$798,E21)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E21&lt;&gt;"",COUNTIF($E$2:$E$794,E21)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10864,7 +11946,7 @@
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="6" t="str">
-        <f>IF(AND(E22&lt;&gt;"",COUNTIF($E$2:$E$798,E22)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E22&lt;&gt;"",COUNTIF($E$2:$E$794,E22)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10930,7 +12012,7 @@
       <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="6" t="str">
-        <f>IF(AND(E23&lt;&gt;"",COUNTIF($E$2:$E$798,E23)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E23&lt;&gt;"",COUNTIF($E$2:$E$794,E23)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -10994,7 +12076,7 @@
       <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="6" t="str">
-        <f>IF(AND(E24&lt;&gt;"",COUNTIF($E$2:$E$798,E24)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E24&lt;&gt;"",COUNTIF($E$2:$E$794,E24)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11058,7 +12140,7 @@
       <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="6" t="str">
-        <f>IF(AND(E25&lt;&gt;"",COUNTIF($E$2:$E$798,E25)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E25&lt;&gt;"",COUNTIF($E$2:$E$794,E25)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11134,7 +12216,7 @@
       <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="6" t="str">
-        <f>IF(AND(E26&lt;&gt;"",COUNTIF($E$2:$E$798,E26)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E26&lt;&gt;"",COUNTIF($E$2:$E$794,E26)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11200,7 +12282,7 @@
       <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="6" t="str">
-        <f>IF(AND(E27&lt;&gt;"",COUNTIF($E$2:$E$798,E27)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E27&lt;&gt;"",COUNTIF($E$2:$E$794,E27)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11274,7 +12356,7 @@
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="6" t="str">
-        <f>IF(AND(E28&lt;&gt;"",COUNTIF($E$2:$E$798,E28)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E28&lt;&gt;"",COUNTIF($E$2:$E$794,E28)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11340,7 +12422,7 @@
       <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="6" t="str">
-        <f>IF(AND(E29&lt;&gt;"",COUNTIF($E$2:$E$798,E29)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E29&lt;&gt;"",COUNTIF($E$2:$E$794,E29)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11406,7 +12488,7 @@
       <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
       <c r="AC30" s="6" t="str">
-        <f>IF(AND(E30&lt;&gt;"",COUNTIF($E$2:$E$798,E30)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E30&lt;&gt;"",COUNTIF($E$2:$E$794,E30)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11470,7 +12552,7 @@
       <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
       <c r="AC31" s="6" t="str">
-        <f>IF(AND(E31&lt;&gt;"",COUNTIF($E$2:$E$798,E31)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E31&lt;&gt;"",COUNTIF($E$2:$E$794,E31)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11536,7 +12618,7 @@
       <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="6" t="str">
-        <f>IF(AND(E32&lt;&gt;"",COUNTIF($E$2:$E$798,E32)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E32&lt;&gt;"",COUNTIF($E$2:$E$794,E32)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11608,7 +12690,7 @@
       <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="6" t="str">
-        <f>IF(AND(E33&lt;&gt;"",COUNTIF($E$2:$E$798,E33)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E33&lt;&gt;"",COUNTIF($E$2:$E$794,E33)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11682,7 +12764,7 @@
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="6" t="str">
-        <f>IF(AND(E34&lt;&gt;"",COUNTIF($E$2:$E$798,E34)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E34&lt;&gt;"",COUNTIF($E$2:$E$794,E34)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11758,7 +12840,7 @@
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="6" t="str">
-        <f>IF(AND(E35&lt;&gt;"",COUNTIF($E$2:$E$798,E35)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E35&lt;&gt;"",COUNTIF($E$2:$E$794,E35)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11832,7 +12914,7 @@
       <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="6" t="str">
-        <f>IF(AND(E36&lt;&gt;"",COUNTIF($E$2:$E$798,E36)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E36&lt;&gt;"",COUNTIF($E$2:$E$794,E36)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11896,7 +12978,7 @@
       <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="6" t="str">
-        <f>IF(AND(E37&lt;&gt;"",COUNTIF($E$2:$E$798,E37)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E37&lt;&gt;"",COUNTIF($E$2:$E$794,E37)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -11962,7 +13044,7 @@
       <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="6" t="str">
-        <f>IF(AND(E38&lt;&gt;"",COUNTIF($E$2:$E$798,E38)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E38&lt;&gt;"",COUNTIF($E$2:$E$794,E38)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12036,7 +13118,7 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="6" t="str">
-        <f>IF(AND(E39&lt;&gt;"",COUNTIF($E$2:$E$798,E39)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E39&lt;&gt;"",COUNTIF($E$2:$E$794,E39)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12110,7 +13192,7 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="6" t="str">
-        <f>IF(AND(E40&lt;&gt;"",COUNTIF($E$2:$E$798,E40)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E40&lt;&gt;"",COUNTIF($E$2:$E$794,E40)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12176,7 +13258,7 @@
       <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
       <c r="AC41" s="6" t="str">
-        <f>IF(AND(E41&lt;&gt;"",COUNTIF($E$2:$E$798,E41)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E41&lt;&gt;"",COUNTIF($E$2:$E$794,E41)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12250,7 +13332,7 @@
       <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
       <c r="AC42" s="6" t="str">
-        <f>IF(AND(E42&lt;&gt;"",COUNTIF($E$2:$E$798,E42)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E42&lt;&gt;"",COUNTIF($E$2:$E$794,E42)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12316,7 +13398,7 @@
       <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
       <c r="AC43" s="6" t="str">
-        <f>IF(AND(E43&lt;&gt;"",COUNTIF($E$2:$E$798,E43)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E43&lt;&gt;"",COUNTIF($E$2:$E$794,E43)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12382,7 +13464,7 @@
       <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
       <c r="AC44" s="6" t="str">
-        <f>IF(AND(E44&lt;&gt;"",COUNTIF($E$2:$E$798,E44)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E44&lt;&gt;"",COUNTIF($E$2:$E$794,E44)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12446,7 +13528,7 @@
       <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
       <c r="AC45" s="6" t="str">
-        <f>IF(AND(E45&lt;&gt;"",COUNTIF($E$2:$E$798,E45)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E45&lt;&gt;"",COUNTIF($E$2:$E$794,E45)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12520,7 +13602,7 @@
       <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="6" t="str">
-        <f>IF(AND(E46&lt;&gt;"",COUNTIF($E$2:$E$798,E46)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E46&lt;&gt;"",COUNTIF($E$2:$E$794,E46)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12584,7 +13666,7 @@
       <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
       <c r="AC47" s="6" t="str">
-        <f>IF(AND(E47&lt;&gt;"",COUNTIF($E$2:$E$798,E47)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E47&lt;&gt;"",COUNTIF($E$2:$E$794,E47)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12650,7 +13732,7 @@
       <c r="AA48" s="3"/>
       <c r="AB48" s="3"/>
       <c r="AC48" s="6" t="str">
-        <f>IF(AND(E48&lt;&gt;"",COUNTIF($E$2:$E$798,E48)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E48&lt;&gt;"",COUNTIF($E$2:$E$794,E48)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12716,7 +13798,7 @@
       <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="6" t="str">
-        <f>IF(AND(E49&lt;&gt;"",COUNTIF($E$2:$E$798,E49)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E49&lt;&gt;"",COUNTIF($E$2:$E$794,E49)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12792,7 +13874,7 @@
       <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
       <c r="AC50" s="6" t="str">
-        <f>IF(AND(E50&lt;&gt;"",COUNTIF($E$2:$E$798,E50)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E50&lt;&gt;"",COUNTIF($E$2:$E$794,E50)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12858,7 +13940,7 @@
       <c r="AA51" s="3"/>
       <c r="AB51" s="3"/>
       <c r="AC51" s="6" t="str">
-        <f>IF(AND(E51&lt;&gt;"",COUNTIF($E$2:$E$798,E51)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E51&lt;&gt;"",COUNTIF($E$2:$E$794,E51)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12924,7 +14006,7 @@
       <c r="AA52" s="3"/>
       <c r="AB52" s="3"/>
       <c r="AC52" s="6" t="str">
-        <f>IF(AND(E52&lt;&gt;"",COUNTIF($E$2:$E$798,E52)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E52&lt;&gt;"",COUNTIF($E$2:$E$794,E52)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -12990,7 +14072,7 @@
       <c r="AA53" s="3"/>
       <c r="AB53" s="3"/>
       <c r="AC53" s="6" t="str">
-        <f>IF(AND(E53&lt;&gt;"",COUNTIF($E$2:$E$798,E53)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E53&lt;&gt;"",COUNTIF($E$2:$E$794,E53)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13054,7 +14136,7 @@
       <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
       <c r="AC54" s="6" t="str">
-        <f>IF(AND(E54&lt;&gt;"",COUNTIF($E$2:$E$798,E54)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E54&lt;&gt;"",COUNTIF($E$2:$E$794,E54)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13120,7 +14202,7 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="6" t="str">
-        <f>IF(AND(E55&lt;&gt;"",COUNTIF($E$2:$E$798,E55)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E55&lt;&gt;"",COUNTIF($E$2:$E$794,E55)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13192,7 +14274,7 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="6" t="str">
-        <f>IF(AND(E56&lt;&gt;"",COUNTIF($E$2:$E$798,E56)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E56&lt;&gt;"",COUNTIF($E$2:$E$794,E56)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13266,7 +14348,7 @@
       <c r="AA57" s="3"/>
       <c r="AB57" s="3"/>
       <c r="AC57" s="6" t="str">
-        <f>IF(AND(E57&lt;&gt;"",COUNTIF($E$2:$E$798,E57)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E57&lt;&gt;"",COUNTIF($E$2:$E$794,E57)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13330,7 +14412,7 @@
       <c r="AA58" s="3"/>
       <c r="AB58" s="3"/>
       <c r="AC58" s="6" t="str">
-        <f>IF(AND(E58&lt;&gt;"",COUNTIF($E$2:$E$798,E58)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E58&lt;&gt;"",COUNTIF($E$2:$E$794,E58)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13394,7 +14476,7 @@
       <c r="AA59" s="3"/>
       <c r="AB59" s="3"/>
       <c r="AC59" s="6" t="str">
-        <f>IF(AND(E59&lt;&gt;"",COUNTIF($E$2:$E$798,E59)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E59&lt;&gt;"",COUNTIF($E$2:$E$794,E59)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13460,7 +14542,7 @@
       <c r="AA60" s="3"/>
       <c r="AB60" s="3"/>
       <c r="AC60" s="6" t="str">
-        <f>IF(AND(E60&lt;&gt;"",COUNTIF($E$2:$E$798,E60)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E60&lt;&gt;"",COUNTIF($E$2:$E$794,E60)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13536,7 +14618,7 @@
       <c r="AA61" s="3"/>
       <c r="AB61" s="3"/>
       <c r="AC61" s="6" t="str">
-        <f>IF(AND(E61&lt;&gt;"",COUNTIF($E$2:$E$798,E61)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E61&lt;&gt;"",COUNTIF($E$2:$E$794,E61)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13600,7 +14682,7 @@
       <c r="AA62" s="3"/>
       <c r="AB62" s="3"/>
       <c r="AC62" s="6" t="str">
-        <f>IF(AND(E62&lt;&gt;"",COUNTIF($E$2:$E$798,E62)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E62&lt;&gt;"",COUNTIF($E$2:$E$794,E62)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13674,7 +14756,7 @@
       <c r="AA63" s="3"/>
       <c r="AB63" s="3"/>
       <c r="AC63" s="6" t="str">
-        <f>IF(AND(E63&lt;&gt;"",COUNTIF($E$2:$E$798,E63)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E63&lt;&gt;"",COUNTIF($E$2:$E$794,E63)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13738,7 +14820,7 @@
       <c r="AA64" s="3"/>
       <c r="AB64" s="3"/>
       <c r="AC64" s="6" t="str">
-        <f>IF(AND(E64&lt;&gt;"",COUNTIF($E$2:$E$798,E64)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E64&lt;&gt;"",COUNTIF($E$2:$E$794,E64)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13802,7 +14884,7 @@
       <c r="AA65" s="3"/>
       <c r="AB65" s="3"/>
       <c r="AC65" s="6" t="str">
-        <f>IF(AND(E65&lt;&gt;"",COUNTIF($E$2:$E$798,E65)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E65&lt;&gt;"",COUNTIF($E$2:$E$794,E65)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13878,7 +14960,7 @@
       <c r="AA66" s="3"/>
       <c r="AB66" s="3"/>
       <c r="AC66" s="6" t="str">
-        <f>IF(AND(E66&lt;&gt;"",COUNTIF($E$2:$E$798,E66)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E66&lt;&gt;"",COUNTIF($E$2:$E$794,E66)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -13942,7 +15024,7 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="6" t="str">
-        <f>IF(AND(E67&lt;&gt;"",COUNTIF($E$2:$E$798,E67)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E67&lt;&gt;"",COUNTIF($E$2:$E$794,E67)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14008,7 +15090,7 @@
       <c r="AA68" s="3"/>
       <c r="AB68" s="3"/>
       <c r="AC68" s="6" t="str">
-        <f>IF(AND(E68&lt;&gt;"",COUNTIF($E$2:$E$798,E68)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E68&lt;&gt;"",COUNTIF($E$2:$E$794,E68)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14072,7 +15154,7 @@
       <c r="AA69" s="3"/>
       <c r="AB69" s="3"/>
       <c r="AC69" s="6" t="str">
-        <f>IF(AND(E69&lt;&gt;"",COUNTIF($E$2:$E$798,E69)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E69&lt;&gt;"",COUNTIF($E$2:$E$794,E69)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14148,7 +15230,7 @@
       <c r="AA70" s="3"/>
       <c r="AB70" s="3"/>
       <c r="AC70" s="6" t="str">
-        <f>IF(AND(E70&lt;&gt;"",COUNTIF($E$2:$E$798,E70)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E70&lt;&gt;"",COUNTIF($E$2:$E$794,E70)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14214,7 +15296,7 @@
       <c r="AA71" s="3"/>
       <c r="AB71" s="3"/>
       <c r="AC71" s="6" t="str">
-        <f>IF(AND(E71&lt;&gt;"",COUNTIF($E$2:$E$798,E71)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E71&lt;&gt;"",COUNTIF($E$2:$E$794,E71)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14280,7 +15362,7 @@
       <c r="AA72" s="3"/>
       <c r="AB72" s="3"/>
       <c r="AC72" s="6" t="str">
-        <f>IF(AND(E72&lt;&gt;"",COUNTIF($E$2:$E$798,E72)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E72&lt;&gt;"",COUNTIF($E$2:$E$794,E72)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14354,7 +15436,7 @@
       <c r="AA73" s="3"/>
       <c r="AB73" s="3"/>
       <c r="AC73" s="6" t="str">
-        <f>IF(AND(E73&lt;&gt;"",COUNTIF($E$2:$E$798,E73)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E73&lt;&gt;"",COUNTIF($E$2:$E$794,E73)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14418,7 +15500,7 @@
       <c r="AA74" s="3"/>
       <c r="AB74" s="3"/>
       <c r="AC74" s="6" t="str">
-        <f>IF(AND(E74&lt;&gt;"",COUNTIF($E$2:$E$798,E74)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E74&lt;&gt;"",COUNTIF($E$2:$E$794,E74)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14482,7 +15564,7 @@
       <c r="AA75" s="3"/>
       <c r="AB75" s="3"/>
       <c r="AC75" s="6" t="str">
-        <f>IF(AND(E75&lt;&gt;"",COUNTIF($E$2:$E$798,E75)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E75&lt;&gt;"",COUNTIF($E$2:$E$794,E75)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14558,7 +15640,7 @@
       <c r="AA76" s="3"/>
       <c r="AB76" s="3"/>
       <c r="AC76" s="6" t="str">
-        <f>IF(AND(E76&lt;&gt;"",COUNTIF($E$2:$E$798,E76)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E76&lt;&gt;"",COUNTIF($E$2:$E$794,E76)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14624,7 +15706,7 @@
       <c r="AA77" s="3"/>
       <c r="AB77" s="3"/>
       <c r="AC77" s="6" t="str">
-        <f>IF(AND(E77&lt;&gt;"",COUNTIF($E$2:$E$798,E77)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E77&lt;&gt;"",COUNTIF($E$2:$E$794,E77)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14690,7 +15772,7 @@
       <c r="AA78" s="3"/>
       <c r="AB78" s="3"/>
       <c r="AC78" s="6" t="str">
-        <f>IF(AND(E78&lt;&gt;"",COUNTIF($E$2:$E$798,E78)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E78&lt;&gt;"",COUNTIF($E$2:$E$794,E78)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14764,7 +15846,7 @@
       <c r="AA79" s="3"/>
       <c r="AB79" s="3"/>
       <c r="AC79" s="6" t="str">
-        <f>IF(AND(E79&lt;&gt;"",COUNTIF($E$2:$E$798,E79)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E79&lt;&gt;"",COUNTIF($E$2:$E$794,E79)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14828,7 +15910,7 @@
       <c r="AA80" s="3"/>
       <c r="AB80" s="3"/>
       <c r="AC80" s="6" t="str">
-        <f>IF(AND(E80&lt;&gt;"",COUNTIF($E$2:$E$798,E80)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E80&lt;&gt;"",COUNTIF($E$2:$E$794,E80)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14892,7 +15974,7 @@
       <c r="AA81" s="3"/>
       <c r="AB81" s="3"/>
       <c r="AC81" s="6" t="str">
-        <f>IF(AND(E81&lt;&gt;"",COUNTIF($E$2:$E$798,E81)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E81&lt;&gt;"",COUNTIF($E$2:$E$794,E81)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -14967,7 +16049,7 @@
         <v>46312</v>
       </c>
       <c r="AC82" t="str">
-        <f>IF(AND(E82&lt;&gt;"",COUNTIF($E$2:$E$798,E82)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E82&lt;&gt;"",COUNTIF($E$2:$E$794,E82)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15042,7 +16124,7 @@
         <v>46312</v>
       </c>
       <c r="AC83" t="str">
-        <f>IF(AND(E83&lt;&gt;"",COUNTIF($E$2:$E$798,E83)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E83&lt;&gt;"",COUNTIF($E$2:$E$794,E83)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15117,7 +16199,7 @@
         <v>46312</v>
       </c>
       <c r="AC84" t="str">
-        <f>IF(AND(E84&lt;&gt;"",COUNTIF($E$2:$E$798,E84)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E84&lt;&gt;"",COUNTIF($E$2:$E$794,E84)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15189,7 +16271,7 @@
         <v>46312</v>
       </c>
       <c r="AC85" t="str">
-        <f>IF(AND(E85&lt;&gt;"",COUNTIF($E$2:$E$798,E85)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E85&lt;&gt;"",COUNTIF($E$2:$E$794,E85)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15264,7 +16346,7 @@
         <v>46312</v>
       </c>
       <c r="AC86" t="str">
-        <f>IF(AND(E86&lt;&gt;"",COUNTIF($E$2:$E$798,E86)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E86&lt;&gt;"",COUNTIF($E$2:$E$794,E86)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15339,7 +16421,7 @@
         <v>46312</v>
       </c>
       <c r="AC87" t="str">
-        <f>IF(AND(E87&lt;&gt;"",COUNTIF($E$2:$E$798,E87)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E87&lt;&gt;"",COUNTIF($E$2:$E$794,E87)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15411,7 +16493,7 @@
         <v>46312</v>
       </c>
       <c r="AC88" t="str">
-        <f>IF(AND(E88&lt;&gt;"",COUNTIF($E$2:$E$798,E88)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E88&lt;&gt;"",COUNTIF($E$2:$E$794,E88)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15483,7 +16565,7 @@
         <v>46312</v>
       </c>
       <c r="AC89" t="str">
-        <f>IF(AND(E89&lt;&gt;"",COUNTIF($E$2:$E$798,E89)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E89&lt;&gt;"",COUNTIF($E$2:$E$794,E89)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15558,7 +16640,7 @@
         <v>46312</v>
       </c>
       <c r="AC90" t="str">
-        <f>IF(AND(E90&lt;&gt;"",COUNTIF($E$2:$E$798,E90)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E90&lt;&gt;"",COUNTIF($E$2:$E$794,E90)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15633,7 +16715,7 @@
         <v>46312</v>
       </c>
       <c r="AC91" t="str">
-        <f>IF(AND(E91&lt;&gt;"",COUNTIF($E$2:$E$798,E91)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E91&lt;&gt;"",COUNTIF($E$2:$E$794,E91)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15705,7 +16787,7 @@
         <v>46312</v>
       </c>
       <c r="AC92" t="str">
-        <f>IF(AND(E92&lt;&gt;"",COUNTIF($E$2:$E$798,E92)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E92&lt;&gt;"",COUNTIF($E$2:$E$794,E92)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15780,7 +16862,7 @@
         <v>46312</v>
       </c>
       <c r="AC93" t="str">
-        <f>IF(AND(E93&lt;&gt;"",COUNTIF($E$2:$E$798,E93)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E93&lt;&gt;"",COUNTIF($E$2:$E$794,E93)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15855,7 +16937,7 @@
         <v>46312</v>
       </c>
       <c r="AC94" t="str">
-        <f>IF(AND(E94&lt;&gt;"",COUNTIF($E$2:$E$798,E94)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E94&lt;&gt;"",COUNTIF($E$2:$E$794,E94)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -15930,7 +17012,7 @@
         <v>46312</v>
       </c>
       <c r="AC95" t="str">
-        <f>IF(AND(E95&lt;&gt;"",COUNTIF($E$2:$E$798,E95)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E95&lt;&gt;"",COUNTIF($E$2:$E$794,E95)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16005,7 +17087,7 @@
         <v>46312</v>
       </c>
       <c r="AC96" t="str">
-        <f>IF(AND(E96&lt;&gt;"",COUNTIF($E$2:$E$798,E96)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E96&lt;&gt;"",COUNTIF($E$2:$E$794,E96)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16080,7 +17162,7 @@
         <v>46312</v>
       </c>
       <c r="AC97" t="str">
-        <f>IF(AND(E97&lt;&gt;"",COUNTIF($E$2:$E$798,E97)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E97&lt;&gt;"",COUNTIF($E$2:$E$794,E97)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16155,7 +17237,7 @@
         <v>46312</v>
       </c>
       <c r="AC98" t="str">
-        <f>IF(AND(E98&lt;&gt;"",COUNTIF($E$2:$E$798,E98)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E98&lt;&gt;"",COUNTIF($E$2:$E$794,E98)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16230,7 +17312,7 @@
         <v>46312</v>
       </c>
       <c r="AC99" t="str">
-        <f>IF(AND(E99&lt;&gt;"",COUNTIF($E$2:$E$798,E99)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E99&lt;&gt;"",COUNTIF($E$2:$E$794,E99)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16305,7 +17387,7 @@
         <v>46312</v>
       </c>
       <c r="AC100" t="str">
-        <f>IF(AND(E100&lt;&gt;"",COUNTIF($E$2:$E$798,E100)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E100&lt;&gt;"",COUNTIF($E$2:$E$794,E100)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16380,7 +17462,7 @@
         <v>46312</v>
       </c>
       <c r="AC101" t="str">
-        <f>IF(AND(E101&lt;&gt;"",COUNTIF($E$2:$E$798,E101)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E101&lt;&gt;"",COUNTIF($E$2:$E$794,E101)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16455,7 +17537,7 @@
         <v>46312</v>
       </c>
       <c r="AC102" t="str">
-        <f>IF(AND(E102&lt;&gt;"",COUNTIF($E$2:$E$798,E102)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E102&lt;&gt;"",COUNTIF($E$2:$E$794,E102)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16530,7 +17612,7 @@
         <v>46312</v>
       </c>
       <c r="AC103" t="str">
-        <f>IF(AND(E103&lt;&gt;"",COUNTIF($E$2:$E$798,E103)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E103&lt;&gt;"",COUNTIF($E$2:$E$794,E103)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16605,7 +17687,7 @@
         <v>46312</v>
       </c>
       <c r="AC104" t="str">
-        <f>IF(AND(E104&lt;&gt;"",COUNTIF($E$2:$E$798,E104)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E104&lt;&gt;"",COUNTIF($E$2:$E$794,E104)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16680,7 +17762,7 @@
         <v>46312</v>
       </c>
       <c r="AC105" t="str">
-        <f>IF(AND(E105&lt;&gt;"",COUNTIF($E$2:$E$798,E105)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E105&lt;&gt;"",COUNTIF($E$2:$E$794,E105)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16755,7 +17837,7 @@
         <v>46312</v>
       </c>
       <c r="AC106" t="str">
-        <f>IF(AND(E106&lt;&gt;"",COUNTIF($E$2:$E$798,E106)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E106&lt;&gt;"",COUNTIF($E$2:$E$794,E106)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16830,7 +17912,7 @@
         <v>46312</v>
       </c>
       <c r="AC107" t="str">
-        <f>IF(AND(E107&lt;&gt;"",COUNTIF($E$2:$E$798,E107)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E107&lt;&gt;"",COUNTIF($E$2:$E$794,E107)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16905,7 +17987,7 @@
         <v>46312</v>
       </c>
       <c r="AC108" t="str">
-        <f>IF(AND(E108&lt;&gt;"",COUNTIF($E$2:$E$798,E108)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E108&lt;&gt;"",COUNTIF($E$2:$E$794,E108)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -16980,7 +18062,7 @@
         <v>46312</v>
       </c>
       <c r="AC109" t="str">
-        <f>IF(AND(E109&lt;&gt;"",COUNTIF($E$2:$E$798,E109)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E109&lt;&gt;"",COUNTIF($E$2:$E$794,E109)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17055,7 +18137,7 @@
         <v>46312</v>
       </c>
       <c r="AC110" t="str">
-        <f>IF(AND(E110&lt;&gt;"",COUNTIF($E$2:$E$798,E110)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E110&lt;&gt;"",COUNTIF($E$2:$E$794,E110)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17130,7 +18212,7 @@
         <v>46312</v>
       </c>
       <c r="AC111" t="str">
-        <f>IF(AND(E111&lt;&gt;"",COUNTIF($E$2:$E$798,E111)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E111&lt;&gt;"",COUNTIF($E$2:$E$794,E111)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17205,7 +18287,7 @@
         <v>46312</v>
       </c>
       <c r="AC112" t="str">
-        <f>IF(AND(E112&lt;&gt;"",COUNTIF($E$2:$E$798,E112)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E112&lt;&gt;"",COUNTIF($E$2:$E$794,E112)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17280,7 +18362,7 @@
         <v>46312</v>
       </c>
       <c r="AC113" t="str">
-        <f>IF(AND(E113&lt;&gt;"",COUNTIF($E$2:$E$798,E113)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E113&lt;&gt;"",COUNTIF($E$2:$E$794,E113)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17355,7 +18437,7 @@
         <v>46312</v>
       </c>
       <c r="AC114" t="str">
-        <f>IF(AND(E114&lt;&gt;"",COUNTIF($E$2:$E$798,E114)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E114&lt;&gt;"",COUNTIF($E$2:$E$794,E114)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17430,7 +18512,7 @@
         <v>46312</v>
       </c>
       <c r="AC115" t="str">
-        <f>IF(AND(E115&lt;&gt;"",COUNTIF($E$2:$E$798,E115)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E115&lt;&gt;"",COUNTIF($E$2:$E$794,E115)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17505,7 +18587,7 @@
         <v>46313</v>
       </c>
       <c r="AC116" t="str">
-        <f>IF(AND(E116&lt;&gt;"",COUNTIF($E$2:$E$798,E116)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E116&lt;&gt;"",COUNTIF($E$2:$E$794,E116)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17580,7 +18662,7 @@
         <v>46313</v>
       </c>
       <c r="AC117" t="str">
-        <f>IF(AND(E117&lt;&gt;"",COUNTIF($E$2:$E$798,E117)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E117&lt;&gt;"",COUNTIF($E$2:$E$794,E117)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17655,7 +18737,7 @@
         <v>46313</v>
       </c>
       <c r="AC118" t="str">
-        <f>IF(AND(E118&lt;&gt;"",COUNTIF($E$2:$E$798,E118)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E118&lt;&gt;"",COUNTIF($E$2:$E$794,E118)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17730,7 +18812,7 @@
         <v>46313</v>
       </c>
       <c r="AC119" t="str">
-        <f>IF(AND(E119&lt;&gt;"",COUNTIF($E$2:$E$798,E119)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E119&lt;&gt;"",COUNTIF($E$2:$E$794,E119)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17805,7 +18887,7 @@
         <v>46313</v>
       </c>
       <c r="AC120" t="str">
-        <f>IF(AND(E120&lt;&gt;"",COUNTIF($E$2:$E$798,E120)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E120&lt;&gt;"",COUNTIF($E$2:$E$794,E120)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17880,7 +18962,7 @@
         <v>46313</v>
       </c>
       <c r="AC121" t="str">
-        <f>IF(AND(E121&lt;&gt;"",COUNTIF($E$2:$E$798,E121)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E121&lt;&gt;"",COUNTIF($E$2:$E$794,E121)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -17955,7 +19037,7 @@
         <v>46313</v>
       </c>
       <c r="AC122" t="str">
-        <f>IF(AND(E122&lt;&gt;"",COUNTIF($E$2:$E$798,E122)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E122&lt;&gt;"",COUNTIF($E$2:$E$794,E122)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18030,7 +19112,7 @@
         <v>46313</v>
       </c>
       <c r="AC123" t="str">
-        <f>IF(AND(E123&lt;&gt;"",COUNTIF($E$2:$E$798,E123)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E123&lt;&gt;"",COUNTIF($E$2:$E$794,E123)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18105,7 +19187,7 @@
         <v>46313</v>
       </c>
       <c r="AC124" t="str">
-        <f>IF(AND(E124&lt;&gt;"",COUNTIF($E$2:$E$798,E124)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E124&lt;&gt;"",COUNTIF($E$2:$E$794,E124)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18180,7 +19262,7 @@
         <v>46313</v>
       </c>
       <c r="AC125" t="str">
-        <f>IF(AND(E125&lt;&gt;"",COUNTIF($E$2:$E$798,E125)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E125&lt;&gt;"",COUNTIF($E$2:$E$794,E125)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18255,7 +19337,7 @@
         <v>46313</v>
       </c>
       <c r="AC126" t="str">
-        <f>IF(AND(E126&lt;&gt;"",COUNTIF($E$2:$E$798,E126)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E126&lt;&gt;"",COUNTIF($E$2:$E$794,E126)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18330,7 +19412,7 @@
         <v>46313</v>
       </c>
       <c r="AC127" t="str">
-        <f>IF(AND(E127&lt;&gt;"",COUNTIF($E$2:$E$798,E127)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E127&lt;&gt;"",COUNTIF($E$2:$E$794,E127)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18405,7 +19487,7 @@
         <v>46313</v>
       </c>
       <c r="AC128" t="str">
-        <f>IF(AND(E128&lt;&gt;"",COUNTIF($E$2:$E$798,E128)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E128&lt;&gt;"",COUNTIF($E$2:$E$794,E128)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18480,7 +19562,7 @@
         <v>46313</v>
       </c>
       <c r="AC129" t="str">
-        <f>IF(AND(E129&lt;&gt;"",COUNTIF($E$2:$E$798,E129)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E129&lt;&gt;"",COUNTIF($E$2:$E$794,E129)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18555,7 +19637,7 @@
         <v>46313</v>
       </c>
       <c r="AC130" t="str">
-        <f>IF(AND(E130&lt;&gt;"",COUNTIF($E$2:$E$798,E130)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E130&lt;&gt;"",COUNTIF($E$2:$E$794,E130)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18630,7 +19712,7 @@
         <v>46313</v>
       </c>
       <c r="AC131" t="str">
-        <f>IF(AND(E131&lt;&gt;"",COUNTIF($E$2:$E$798,E131)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E131&lt;&gt;"",COUNTIF($E$2:$E$794,E131)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18705,7 +19787,7 @@
         <v>46313</v>
       </c>
       <c r="AC132" t="str">
-        <f>IF(AND(E132&lt;&gt;"",COUNTIF($E$2:$E$798,E132)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E132&lt;&gt;"",COUNTIF($E$2:$E$794,E132)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18780,7 +19862,7 @@
         <v>46313</v>
       </c>
       <c r="AC133" t="str">
-        <f>IF(AND(E133&lt;&gt;"",COUNTIF($E$2:$E$798,E133)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E133&lt;&gt;"",COUNTIF($E$2:$E$794,E133)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18855,7 +19937,7 @@
         <v>46313</v>
       </c>
       <c r="AC134" t="str">
-        <f>IF(AND(E134&lt;&gt;"",COUNTIF($E$2:$E$798,E134)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E134&lt;&gt;"",COUNTIF($E$2:$E$794,E134)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -18930,7 +20012,7 @@
         <v>46313</v>
       </c>
       <c r="AC135" t="str">
-        <f>IF(AND(E135&lt;&gt;"",COUNTIF($E$2:$E$798,E135)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E135&lt;&gt;"",COUNTIF($E$2:$E$794,E135)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19005,7 +20087,7 @@
         <v>46313</v>
       </c>
       <c r="AC136" t="str">
-        <f>IF(AND(E136&lt;&gt;"",COUNTIF($E$2:$E$798,E136)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E136&lt;&gt;"",COUNTIF($E$2:$E$794,E136)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20162,7 @@
         <v>46313</v>
       </c>
       <c r="AC137" t="str">
-        <f>IF(AND(E137&lt;&gt;"",COUNTIF($E$2:$E$798,E137)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E137&lt;&gt;"",COUNTIF($E$2:$E$794,E137)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19155,7 +20237,7 @@
         <v>46313</v>
       </c>
       <c r="AC138" t="str">
-        <f>IF(AND(E138&lt;&gt;"",COUNTIF($E$2:$E$798,E138)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E138&lt;&gt;"",COUNTIF($E$2:$E$794,E138)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19230,7 +20312,7 @@
         <v>46313</v>
       </c>
       <c r="AC139" t="str">
-        <f>IF(AND(E139&lt;&gt;"",COUNTIF($E$2:$E$798,E139)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E139&lt;&gt;"",COUNTIF($E$2:$E$794,E139)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19305,7 +20387,7 @@
         <v>46313</v>
       </c>
       <c r="AC140" t="str">
-        <f>IF(AND(E140&lt;&gt;"",COUNTIF($E$2:$E$798,E140)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E140&lt;&gt;"",COUNTIF($E$2:$E$794,E140)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19380,7 +20462,7 @@
         <v>46313</v>
       </c>
       <c r="AC141" t="str">
-        <f>IF(AND(E141&lt;&gt;"",COUNTIF($E$2:$E$798,E141)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E141&lt;&gt;"",COUNTIF($E$2:$E$794,E141)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19455,7 +20537,7 @@
         <v>46313</v>
       </c>
       <c r="AC142" t="str">
-        <f>IF(AND(E142&lt;&gt;"",COUNTIF($E$2:$E$798,E142)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E142&lt;&gt;"",COUNTIF($E$2:$E$794,E142)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19530,7 +20612,7 @@
         <v>46313</v>
       </c>
       <c r="AC143" t="str">
-        <f>IF(AND(E143&lt;&gt;"",COUNTIF($E$2:$E$798,E143)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E143&lt;&gt;"",COUNTIF($E$2:$E$794,E143)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19605,7 +20687,7 @@
         <v>46313</v>
       </c>
       <c r="AC144" t="str">
-        <f>IF(AND(E144&lt;&gt;"",COUNTIF($E$2:$E$798,E144)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E144&lt;&gt;"",COUNTIF($E$2:$E$794,E144)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19680,7 +20762,7 @@
         <v>46313</v>
       </c>
       <c r="AC145" t="str">
-        <f>IF(AND(E145&lt;&gt;"",COUNTIF($E$2:$E$798,E145)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E145&lt;&gt;"",COUNTIF($E$2:$E$794,E145)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19755,7 +20837,7 @@
         <v>46313</v>
       </c>
       <c r="AC146" t="str">
-        <f>IF(AND(E146&lt;&gt;"",COUNTIF($E$2:$E$798,E146)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E146&lt;&gt;"",COUNTIF($E$2:$E$794,E146)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19830,7 +20912,7 @@
         <v>46313</v>
       </c>
       <c r="AC147" t="str">
-        <f>IF(AND(E147&lt;&gt;"",COUNTIF($E$2:$E$798,E147)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E147&lt;&gt;"",COUNTIF($E$2:$E$794,E147)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19905,7 +20987,7 @@
         <v>46313</v>
       </c>
       <c r="AC148" t="str">
-        <f>IF(AND(E148&lt;&gt;"",COUNTIF($E$2:$E$798,E148)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E148&lt;&gt;"",COUNTIF($E$2:$E$794,E148)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -19980,7 +21062,7 @@
         <v>46313</v>
       </c>
       <c r="AC149" t="str">
-        <f>IF(AND(E149&lt;&gt;"",COUNTIF($E$2:$E$798,E149)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E149&lt;&gt;"",COUNTIF($E$2:$E$794,E149)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20055,7 +21137,7 @@
         <v>46313</v>
       </c>
       <c r="AC150" t="str">
-        <f>IF(AND(E150&lt;&gt;"",COUNTIF($E$2:$E$798,E150)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E150&lt;&gt;"",COUNTIF($E$2:$E$794,E150)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20130,7 +21212,7 @@
         <v>46313</v>
       </c>
       <c r="AC151" t="str">
-        <f>IF(AND(E151&lt;&gt;"",COUNTIF($E$2:$E$798,E151)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E151&lt;&gt;"",COUNTIF($E$2:$E$794,E151)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20205,7 +21287,7 @@
         <v>46313</v>
       </c>
       <c r="AC152" t="str">
-        <f>IF(AND(E152&lt;&gt;"",COUNTIF($E$2:$E$798,E152)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E152&lt;&gt;"",COUNTIF($E$2:$E$794,E152)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20280,7 +21362,7 @@
         <v>46313</v>
       </c>
       <c r="AC153" t="str">
-        <f>IF(AND(E153&lt;&gt;"",COUNTIF($E$2:$E$798,E153)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E153&lt;&gt;"",COUNTIF($E$2:$E$794,E153)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20355,7 +21437,7 @@
         <v>46313</v>
       </c>
       <c r="AC154" t="str">
-        <f>IF(AND(E154&lt;&gt;"",COUNTIF($E$2:$E$798,E154)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E154&lt;&gt;"",COUNTIF($E$2:$E$794,E154)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20430,7 +21512,7 @@
         <v>46313</v>
       </c>
       <c r="AC155" t="str">
-        <f>IF(AND(E155&lt;&gt;"",COUNTIF($E$2:$E$798,E155)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E155&lt;&gt;"",COUNTIF($E$2:$E$794,E155)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20505,7 +21587,7 @@
         <v>46313</v>
       </c>
       <c r="AC156" t="str">
-        <f>IF(AND(E156&lt;&gt;"",COUNTIF($E$2:$E$798,E156)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E156&lt;&gt;"",COUNTIF($E$2:$E$794,E156)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20580,7 +21662,7 @@
         <v>46313</v>
       </c>
       <c r="AC157" t="str">
-        <f>IF(AND(E157&lt;&gt;"",COUNTIF($E$2:$E$798,E157)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E157&lt;&gt;"",COUNTIF($E$2:$E$794,E157)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20655,7 +21737,7 @@
         <v>46313</v>
       </c>
       <c r="AC158" t="str">
-        <f>IF(AND(E158&lt;&gt;"",COUNTIF($E$2:$E$798,E158)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E158&lt;&gt;"",COUNTIF($E$2:$E$794,E158)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20730,7 +21812,7 @@
         <v>46313</v>
       </c>
       <c r="AC159" t="str">
-        <f>IF(AND(E159&lt;&gt;"",COUNTIF($E$2:$E$798,E159)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E159&lt;&gt;"",COUNTIF($E$2:$E$794,E159)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20805,7 +21887,7 @@
         <v>46313</v>
       </c>
       <c r="AC160" t="str">
-        <f>IF(AND(E160&lt;&gt;"",COUNTIF($E$2:$E$798,E160)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E160&lt;&gt;"",COUNTIF($E$2:$E$794,E160)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20880,7 +21962,7 @@
         <v>46313</v>
       </c>
       <c r="AC161" t="str">
-        <f>IF(AND(E161&lt;&gt;"",COUNTIF($E$2:$E$798,E161)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E161&lt;&gt;"",COUNTIF($E$2:$E$794,E161)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -20955,7 +22037,7 @@
         <v>46313</v>
       </c>
       <c r="AC162" t="str">
-        <f>IF(AND(E162&lt;&gt;"",COUNTIF($E$2:$E$798,E162)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E162&lt;&gt;"",COUNTIF($E$2:$E$794,E162)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21030,7 +22112,7 @@
         <v>46313</v>
       </c>
       <c r="AC163" t="str">
-        <f>IF(AND(E163&lt;&gt;"",COUNTIF($E$2:$E$798,E163)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E163&lt;&gt;"",COUNTIF($E$2:$E$794,E163)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21105,7 +22187,7 @@
         <v>46313</v>
       </c>
       <c r="AC164" t="str">
-        <f>IF(AND(E164&lt;&gt;"",COUNTIF($E$2:$E$798,E164)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E164&lt;&gt;"",COUNTIF($E$2:$E$794,E164)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21180,7 +22262,7 @@
         <v>46313</v>
       </c>
       <c r="AC165" t="str">
-        <f>IF(AND(E165&lt;&gt;"",COUNTIF($E$2:$E$798,E165)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E165&lt;&gt;"",COUNTIF($E$2:$E$794,E165)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21255,7 +22337,7 @@
         <v>46313</v>
       </c>
       <c r="AC166" t="str">
-        <f>IF(AND(E166&lt;&gt;"",COUNTIF($E$2:$E$798,E166)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E166&lt;&gt;"",COUNTIF($E$2:$E$794,E166)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21317,7 +22399,7 @@
       <c r="AA167" s="4"/>
       <c r="AB167" s="4"/>
       <c r="AC167" t="str">
-        <f>IF(AND(E167&lt;&gt;"",COUNTIF($E$2:$E$798,E167)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E167&lt;&gt;"",COUNTIF($E$2:$E$794,E167)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21387,7 +22469,7 @@
       </c>
       <c r="AB168" s="4"/>
       <c r="AC168" t="str">
-        <f>IF(AND(E168&lt;&gt;"",COUNTIF($E$2:$E$798,E168)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E168&lt;&gt;"",COUNTIF($E$2:$E$794,E168)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21457,7 +22539,7 @@
       </c>
       <c r="AB169" s="4"/>
       <c r="AC169" t="str">
-        <f>IF(AND(E169&lt;&gt;"",COUNTIF($E$2:$E$798,E169)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E169&lt;&gt;"",COUNTIF($E$2:$E$794,E169)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21527,7 +22609,7 @@
       </c>
       <c r="AB170" s="4"/>
       <c r="AC170" t="str">
-        <f>IF(AND(E170&lt;&gt;"",COUNTIF($E$2:$E$798,E170)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E170&lt;&gt;"",COUNTIF($E$2:$E$794,E170)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21597,7 +22679,7 @@
       </c>
       <c r="AB171" s="4"/>
       <c r="AC171" t="str">
-        <f>IF(AND(E171&lt;&gt;"",COUNTIF($E$2:$E$798,E171)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E171&lt;&gt;"",COUNTIF($E$2:$E$794,E171)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21667,7 +22749,7 @@
       </c>
       <c r="AB172" s="4"/>
       <c r="AC172" t="str">
-        <f>IF(AND(E172&lt;&gt;"",COUNTIF($E$2:$E$798,E172)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E172&lt;&gt;"",COUNTIF($E$2:$E$794,E172)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21734,7 +22816,7 @@
       </c>
       <c r="AB173" s="4"/>
       <c r="AC173" t="str">
-        <f>IF(AND(E173&lt;&gt;"",COUNTIF($E$2:$E$798,E173)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E173&lt;&gt;"",COUNTIF($E$2:$E$794,E173)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21801,7 +22883,7 @@
       </c>
       <c r="AB174" s="4"/>
       <c r="AC174" t="str">
-        <f>IF(AND(E174&lt;&gt;"",COUNTIF($E$2:$E$798,E174)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E174&lt;&gt;"",COUNTIF($E$2:$E$794,E174)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21871,7 +22953,7 @@
       </c>
       <c r="AB175" s="4"/>
       <c r="AC175" t="str">
-        <f>IF(AND(E175&lt;&gt;"",COUNTIF($E$2:$E$798,E175)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E175&lt;&gt;"",COUNTIF($E$2:$E$794,E175)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -21941,7 +23023,7 @@
       </c>
       <c r="AB176" s="4"/>
       <c r="AC176" t="str">
-        <f>IF(AND(E176&lt;&gt;"",COUNTIF($E$2:$E$798,E176)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E176&lt;&gt;"",COUNTIF($E$2:$E$794,E176)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -22011,7 +23093,7 @@
       </c>
       <c r="AB177" s="4"/>
       <c r="AC177" t="str">
-        <f>IF(AND(E177&lt;&gt;"",COUNTIF($E$2:$E$798,E177)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E177&lt;&gt;"",COUNTIF($E$2:$E$794,E177)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -22644,66 +23726,66 @@
         <v>2412</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>2413</v>
+        <v>2427</v>
       </c>
       <c r="I187" s="6" t="s">
         <v>883</v>
       </c>
       <c r="J187" s="6" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="K187" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L187" s="6" t="s">
+        <v>2414</v>
+      </c>
+      <c r="M187" s="6" t="s">
         <v>2415</v>
       </c>
-      <c r="M187" s="6" t="s">
+      <c r="N187" s="6" t="s">
         <v>2416</v>
       </c>
-      <c r="N187" s="6" t="s">
+      <c r="O187" s="6" t="s">
         <v>2417</v>
       </c>
-      <c r="O187" s="6" t="s">
+      <c r="P187" s="6" t="s">
         <v>2418</v>
       </c>
-      <c r="P187" s="6" t="s">
+      <c r="Q187" s="6" t="s">
         <v>2419</v>
       </c>
-      <c r="Q187" s="6" t="s">
+      <c r="R187" s="6" t="s">
         <v>2420</v>
       </c>
-      <c r="R187" s="6" t="s">
+      <c r="S187" s="6" t="s">
         <v>2421</v>
-      </c>
-      <c r="S187" s="6" t="s">
-        <v>2422</v>
       </c>
       <c r="T187" s="6"/>
       <c r="U187" s="6" t="s">
+        <v>2422</v>
+      </c>
+      <c r="V187" s="6" t="s">
         <v>2423</v>
-      </c>
-      <c r="V187" s="6" t="s">
-        <v>2424</v>
       </c>
       <c r="W187" s="6"/>
       <c r="X187" s="6"/>
       <c r="Y187" s="6"/>
       <c r="Z187" s="6" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="AA187" s="6"/>
       <c r="AB187" s="3">
         <v>46313</v>
       </c>
       <c r="AC187" s="6" t="str">
-        <f>IF(AND(E187&lt;&gt;"",COUNTIF($E$2:$E$798,E187)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E187&lt;&gt;"",COUNTIF($E$2:$E$794,E187)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="188" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>2076</v>
@@ -22713,7 +23795,7 @@
         <v>58</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>2411</v>
@@ -22722,66 +23804,66 @@
         <v>2412</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="I188" s="6" t="s">
         <v>883</v>
       </c>
       <c r="J188" s="6" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="K188" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L188" s="6" t="s">
+        <v>2429</v>
+      </c>
+      <c r="M188" s="6" t="s">
         <v>2430</v>
       </c>
-      <c r="M188" s="6" t="s">
+      <c r="N188" s="6" t="s">
         <v>2431</v>
       </c>
-      <c r="N188" s="6" t="s">
+      <c r="O188" s="6" t="s">
         <v>2432</v>
       </c>
-      <c r="O188" s="6" t="s">
+      <c r="P188" s="6" t="s">
         <v>2433</v>
       </c>
-      <c r="P188" s="6" t="s">
+      <c r="Q188" s="6" t="s">
         <v>2434</v>
       </c>
-      <c r="Q188" s="6" t="s">
+      <c r="R188" s="6" t="s">
         <v>2435</v>
       </c>
-      <c r="R188" s="6" t="s">
+      <c r="S188" s="6" t="s">
         <v>2436</v>
-      </c>
-      <c r="S188" s="6" t="s">
-        <v>2437</v>
       </c>
       <c r="T188" s="6"/>
       <c r="U188" s="6" t="s">
+        <v>2437</v>
+      </c>
+      <c r="V188" s="6" t="s">
         <v>2438</v>
-      </c>
-      <c r="V188" s="6" t="s">
-        <v>2439</v>
       </c>
       <c r="W188" s="6"/>
       <c r="X188" s="6"/>
       <c r="Y188" s="6"/>
       <c r="Z188" s="6" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="AA188" s="6"/>
       <c r="AB188" s="3">
         <v>46313</v>
       </c>
       <c r="AC188" s="6" t="str">
-        <f>IF(AND(E188&lt;&gt;"",COUNTIF($E$2:$E$798,E188)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E188&lt;&gt;"",COUNTIF($E$2:$E$794,E188)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="189" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>57</v>
@@ -22791,75 +23873,75 @@
         <v>58</v>
       </c>
       <c r="E189" s="6" t="s">
+        <v>2441</v>
+      </c>
+      <c r="F189" s="6" t="s">
         <v>2442</v>
-      </c>
-      <c r="F189" s="6" t="s">
-        <v>2443</v>
       </c>
       <c r="G189" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="I189" s="6" t="s">
         <v>883</v>
       </c>
       <c r="J189" s="6" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="K189" s="6" t="s">
         <v>113</v>
       </c>
       <c r="L189" s="6" t="s">
+        <v>2445</v>
+      </c>
+      <c r="M189" s="6" t="s">
         <v>2446</v>
       </c>
-      <c r="M189" s="6" t="s">
+      <c r="N189" s="6" t="s">
         <v>2447</v>
       </c>
-      <c r="N189" s="6" t="s">
+      <c r="O189" s="6" t="s">
         <v>2448</v>
       </c>
-      <c r="O189" s="6" t="s">
+      <c r="P189" s="6" t="s">
         <v>2449</v>
       </c>
-      <c r="P189" s="6" t="s">
+      <c r="Q189" s="6" t="s">
         <v>2450</v>
       </c>
-      <c r="Q189" s="6" t="s">
+      <c r="R189" s="6" t="s">
         <v>2451</v>
       </c>
-      <c r="R189" s="6" t="s">
+      <c r="S189" s="6" t="s">
         <v>2452</v>
-      </c>
-      <c r="S189" s="6" t="s">
-        <v>2453</v>
       </c>
       <c r="T189" s="6"/>
       <c r="U189" s="6" t="s">
+        <v>2453</v>
+      </c>
+      <c r="V189" s="6" t="s">
         <v>2454</v>
-      </c>
-      <c r="V189" s="6" t="s">
-        <v>2455</v>
       </c>
       <c r="W189" s="6"/>
       <c r="X189" s="6"/>
       <c r="Y189" s="6"/>
       <c r="Z189" s="6" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="AA189" s="6"/>
       <c r="AB189" s="3">
         <v>46313</v>
       </c>
       <c r="AC189" s="6" t="str">
-        <f>IF(AND(E189&lt;&gt;"",COUNTIF($E$2:$E$798,E189)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E189&lt;&gt;"",COUNTIF($E$2:$E$794,E189)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="190" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>57</v>
@@ -22869,75 +23951,75 @@
         <v>58</v>
       </c>
       <c r="E190" s="6" t="s">
+        <v>2457</v>
+      </c>
+      <c r="F190" s="6" t="s">
         <v>2458</v>
-      </c>
-      <c r="F190" s="6" t="s">
-        <v>2459</v>
       </c>
       <c r="G190" s="6" t="s">
         <v>244</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>2460</v>
+        <v>2959</v>
       </c>
       <c r="I190" s="6" t="s">
         <v>63</v>
       </c>
       <c r="J190" s="6" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="K190" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L190" s="6" t="s">
+        <v>2460</v>
+      </c>
+      <c r="M190" s="6" t="s">
+        <v>2461</v>
+      </c>
+      <c r="N190" s="6" t="s">
         <v>2462</v>
       </c>
-      <c r="M190" s="6" t="s">
+      <c r="O190" s="6" t="s">
         <v>2463</v>
       </c>
-      <c r="N190" s="6" t="s">
+      <c r="P190" s="6" t="s">
         <v>2464</v>
       </c>
-      <c r="O190" s="6" t="s">
+      <c r="Q190" s="6" t="s">
         <v>2465</v>
       </c>
-      <c r="P190" s="6" t="s">
+      <c r="R190" s="6" t="s">
         <v>2466</v>
       </c>
-      <c r="Q190" s="6" t="s">
+      <c r="S190" s="6" t="s">
         <v>2467</v>
-      </c>
-      <c r="R190" s="6" t="s">
-        <v>2468</v>
-      </c>
-      <c r="S190" s="6" t="s">
-        <v>2469</v>
       </c>
       <c r="T190" s="6"/>
       <c r="U190" s="6" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="V190" s="6" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="W190" s="6"/>
       <c r="X190" s="6"/>
       <c r="Y190" s="6"/>
       <c r="Z190" s="6" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="AA190" s="6"/>
       <c r="AB190" s="3">
         <v>46313</v>
       </c>
       <c r="AC190" s="6" t="str">
-        <f>IF(AND(E190&lt;&gt;"",COUNTIF($E$2:$E$798,E190)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E190&lt;&gt;"",COUNTIF($E$2:$E$794,E190)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="191" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>57</v>
@@ -22947,75 +24029,75 @@
         <v>58</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="G191" s="6" t="s">
         <v>244</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>2475</v>
+        <v>2959</v>
       </c>
       <c r="I191" s="6" t="s">
         <v>63</v>
       </c>
       <c r="J191" s="6" t="s">
-        <v>2476</v>
+        <v>2473</v>
       </c>
       <c r="K191" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L191" s="6" t="s">
+        <v>2474</v>
+      </c>
+      <c r="M191" s="6" t="s">
+        <v>2475</v>
+      </c>
+      <c r="N191" s="6" t="s">
+        <v>2476</v>
+      </c>
+      <c r="O191" s="6" t="s">
         <v>2477</v>
       </c>
-      <c r="M191" s="6" t="s">
+      <c r="P191" s="6" t="s">
         <v>2478</v>
       </c>
-      <c r="N191" s="6" t="s">
+      <c r="Q191" s="6" t="s">
         <v>2479</v>
       </c>
-      <c r="O191" s="6" t="s">
+      <c r="R191" s="6" t="s">
         <v>2480</v>
       </c>
-      <c r="P191" s="6" t="s">
+      <c r="S191" s="6" t="s">
         <v>2481</v>
-      </c>
-      <c r="Q191" s="6" t="s">
-        <v>2482</v>
-      </c>
-      <c r="R191" s="6" t="s">
-        <v>2483</v>
-      </c>
-      <c r="S191" s="6" t="s">
-        <v>2484</v>
       </c>
       <c r="T191" s="6"/>
       <c r="U191" s="6" t="s">
-        <v>2485</v>
+        <v>2482</v>
       </c>
       <c r="V191" s="6" t="s">
-        <v>2486</v>
+        <v>2483</v>
       </c>
       <c r="W191" s="6"/>
       <c r="X191" s="6"/>
       <c r="Y191" s="6"/>
       <c r="Z191" s="6" t="s">
-        <v>2487</v>
+        <v>2484</v>
       </c>
       <c r="AA191" s="6"/>
       <c r="AB191" s="3">
         <v>46313</v>
       </c>
       <c r="AC191" s="6" t="str">
-        <f>IF(AND(E191&lt;&gt;"",COUNTIF($E$2:$E$798,E191)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E191&lt;&gt;"",COUNTIF($E$2:$E$794,E191)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="192" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
-        <v>2488</v>
+        <v>2485</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>57</v>
@@ -23025,75 +24107,75 @@
         <v>58</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>2489</v>
+        <v>2486</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>2490</v>
+        <v>2487</v>
       </c>
       <c r="G192" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>2491</v>
+        <v>2960</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>2492</v>
+        <v>2488</v>
       </c>
       <c r="J192" s="6" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
       <c r="K192" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L192" s="6" t="s">
+        <v>2490</v>
+      </c>
+      <c r="M192" s="6" t="s">
+        <v>2491</v>
+      </c>
+      <c r="N192" s="6" t="s">
+        <v>2492</v>
+      </c>
+      <c r="O192" s="6" t="s">
+        <v>2493</v>
+      </c>
+      <c r="P192" s="6" t="s">
         <v>2494</v>
       </c>
-      <c r="M192" s="6" t="s">
+      <c r="Q192" s="6" t="s">
         <v>2495</v>
       </c>
-      <c r="N192" s="6" t="s">
+      <c r="R192" s="6" t="s">
         <v>2496</v>
       </c>
-      <c r="O192" s="6" t="s">
+      <c r="S192" s="6" t="s">
         <v>2497</v>
-      </c>
-      <c r="P192" s="6" t="s">
-        <v>2498</v>
-      </c>
-      <c r="Q192" s="6" t="s">
-        <v>2499</v>
-      </c>
-      <c r="R192" s="6" t="s">
-        <v>2500</v>
-      </c>
-      <c r="S192" s="6" t="s">
-        <v>2501</v>
       </c>
       <c r="T192" s="6"/>
       <c r="U192" s="6" t="s">
-        <v>2502</v>
+        <v>2498</v>
       </c>
       <c r="V192" s="6" t="s">
-        <v>2503</v>
+        <v>2499</v>
       </c>
       <c r="W192" s="6"/>
       <c r="X192" s="6"/>
       <c r="Y192" s="6"/>
       <c r="Z192" s="6" t="s">
-        <v>2504</v>
+        <v>2500</v>
       </c>
       <c r="AA192" s="6"/>
       <c r="AB192" s="3">
         <v>46313</v>
       </c>
       <c r="AC192" s="6" t="str">
-        <f>IF(AND(E192&lt;&gt;"",COUNTIF($E$2:$E$798,E192)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E192&lt;&gt;"",COUNTIF($E$2:$E$794,E192)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="193" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>2505</v>
+        <v>2501</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>57</v>
@@ -23103,13 +24185,13 @@
         <v>58</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>2506</v>
+        <v>2502</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>2507</v>
+        <v>2503</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>2508</v>
+        <v>2504</v>
       </c>
       <c r="H193" s="6" t="s">
         <v>869</v>
@@ -23118,60 +24200,60 @@
         <v>883</v>
       </c>
       <c r="J193" s="6" t="s">
-        <v>2509</v>
+        <v>2505</v>
       </c>
       <c r="K193" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L193" s="6" t="s">
+        <v>2506</v>
+      </c>
+      <c r="M193" s="6" t="s">
+        <v>2507</v>
+      </c>
+      <c r="N193" s="6" t="s">
+        <v>2508</v>
+      </c>
+      <c r="O193" s="6" t="s">
+        <v>2509</v>
+      </c>
+      <c r="P193" s="6" t="s">
         <v>2510</v>
       </c>
-      <c r="M193" s="6" t="s">
+      <c r="Q193" s="6" t="s">
         <v>2511</v>
       </c>
-      <c r="N193" s="6" t="s">
+      <c r="R193" s="6" t="s">
         <v>2512</v>
       </c>
-      <c r="O193" s="6" t="s">
+      <c r="S193" s="6" t="s">
         <v>2513</v>
-      </c>
-      <c r="P193" s="6" t="s">
-        <v>2514</v>
-      </c>
-      <c r="Q193" s="6" t="s">
-        <v>2515</v>
-      </c>
-      <c r="R193" s="6" t="s">
-        <v>2516</v>
-      </c>
-      <c r="S193" s="6" t="s">
-        <v>2517</v>
       </c>
       <c r="T193" s="6"/>
       <c r="U193" s="6" t="s">
-        <v>2518</v>
+        <v>2514</v>
       </c>
       <c r="V193" s="6" t="s">
-        <v>2519</v>
+        <v>2515</v>
       </c>
       <c r="W193" s="6"/>
       <c r="X193" s="6"/>
       <c r="Y193" s="6"/>
       <c r="Z193" s="6" t="s">
-        <v>2520</v>
+        <v>2516</v>
       </c>
       <c r="AA193" s="6"/>
       <c r="AB193" s="3">
         <v>46313</v>
       </c>
       <c r="AC193" s="6" t="str">
-        <f>IF(AND(E193&lt;&gt;"",COUNTIF($E$2:$E$798,E193)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E193&lt;&gt;"",COUNTIF($E$2:$E$794,E193)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="194" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
-        <v>2521</v>
+        <v>2517</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>57</v>
@@ -23181,75 +24263,75 @@
         <v>58</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>2523</v>
+        <v>2519</v>
       </c>
       <c r="G194" s="6" t="s">
         <v>244</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>2524</v>
+        <v>2961</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="J194" s="6" t="s">
-        <v>2526</v>
+        <v>2521</v>
       </c>
       <c r="K194" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L194" s="6" t="s">
+        <v>2522</v>
+      </c>
+      <c r="M194" s="6" t="s">
+        <v>2523</v>
+      </c>
+      <c r="N194" s="6" t="s">
+        <v>2524</v>
+      </c>
+      <c r="O194" s="6" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P194" s="6" t="s">
+        <v>2526</v>
+      </c>
+      <c r="Q194" s="6" t="s">
         <v>2527</v>
       </c>
-      <c r="M194" s="6" t="s">
+      <c r="R194" s="6" t="s">
         <v>2528</v>
       </c>
-      <c r="N194" s="6" t="s">
+      <c r="S194" s="6" t="s">
         <v>2529</v>
-      </c>
-      <c r="O194" s="6" t="s">
-        <v>2530</v>
-      </c>
-      <c r="P194" s="6" t="s">
-        <v>2531</v>
-      </c>
-      <c r="Q194" s="6" t="s">
-        <v>2532</v>
-      </c>
-      <c r="R194" s="6" t="s">
-        <v>2533</v>
-      </c>
-      <c r="S194" s="6" t="s">
-        <v>2534</v>
       </c>
       <c r="T194" s="6"/>
       <c r="U194" s="6" t="s">
-        <v>2535</v>
+        <v>2530</v>
       </c>
       <c r="V194" s="6" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="W194" s="6"/>
       <c r="X194" s="6"/>
       <c r="Y194" s="6"/>
       <c r="Z194" s="6" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
       <c r="AA194" s="6"/>
       <c r="AB194" s="3">
         <v>46313</v>
       </c>
       <c r="AC194" s="6" t="str">
-        <f>IF(AND(E194&lt;&gt;"",COUNTIF($E$2:$E$798,E194)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E194&lt;&gt;"",COUNTIF($E$2:$E$794,E194)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="195" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
-        <v>2538</v>
+        <v>2533</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>57</v>
@@ -23259,75 +24341,75 @@
         <v>58</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
       <c r="G195" s="6" t="s">
-        <v>2541</v>
+        <v>2536</v>
       </c>
       <c r="H195" s="6" t="s">
         <v>521</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
       <c r="J195" s="6" t="s">
-        <v>2543</v>
+        <v>2538</v>
       </c>
       <c r="K195" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L195" s="6" t="s">
+        <v>2539</v>
+      </c>
+      <c r="M195" s="6" t="s">
+        <v>2540</v>
+      </c>
+      <c r="N195" s="6" t="s">
+        <v>2541</v>
+      </c>
+      <c r="O195" s="6" t="s">
+        <v>2542</v>
+      </c>
+      <c r="P195" s="6" t="s">
+        <v>2543</v>
+      </c>
+      <c r="Q195" s="6" t="s">
         <v>2544</v>
       </c>
-      <c r="M195" s="6" t="s">
+      <c r="R195" s="6" t="s">
         <v>2545</v>
       </c>
-      <c r="N195" s="6" t="s">
+      <c r="S195" s="6" t="s">
         <v>2546</v>
-      </c>
-      <c r="O195" s="6" t="s">
-        <v>2547</v>
-      </c>
-      <c r="P195" s="6" t="s">
-        <v>2548</v>
-      </c>
-      <c r="Q195" s="6" t="s">
-        <v>2549</v>
-      </c>
-      <c r="R195" s="6" t="s">
-        <v>2550</v>
-      </c>
-      <c r="S195" s="6" t="s">
-        <v>2551</v>
       </c>
       <c r="T195" s="6"/>
       <c r="U195" s="6" t="s">
-        <v>2552</v>
+        <v>2547</v>
       </c>
       <c r="V195" s="6" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
       <c r="W195" s="6"/>
       <c r="X195" s="6"/>
       <c r="Y195" s="6"/>
       <c r="Z195" s="6" t="s">
-        <v>2554</v>
+        <v>2549</v>
       </c>
       <c r="AA195" s="6"/>
       <c r="AB195" s="3">
         <v>46313</v>
       </c>
       <c r="AC195" s="6" t="str">
-        <f>IF(AND(E195&lt;&gt;"",COUNTIF($E$2:$E$798,E195)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E195&lt;&gt;"",COUNTIF($E$2:$E$794,E195)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="196" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>57</v>
@@ -23337,7 +24419,7 @@
         <v>58</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>2556</v>
+        <v>2551</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>457</v>
@@ -23352,60 +24434,60 @@
         <v>124</v>
       </c>
       <c r="J196" s="6" t="s">
-        <v>2557</v>
+        <v>2552</v>
       </c>
       <c r="K196" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L196" s="6" t="s">
+        <v>2553</v>
+      </c>
+      <c r="M196" s="6" t="s">
+        <v>2540</v>
+      </c>
+      <c r="N196" s="6" t="s">
+        <v>2554</v>
+      </c>
+      <c r="O196" s="6" t="s">
+        <v>2555</v>
+      </c>
+      <c r="P196" s="6" t="s">
+        <v>2556</v>
+      </c>
+      <c r="Q196" s="6" t="s">
+        <v>2557</v>
+      </c>
+      <c r="R196" s="6" t="s">
         <v>2558</v>
       </c>
-      <c r="M196" s="6" t="s">
-        <v>2545</v>
-      </c>
-      <c r="N196" s="6" t="s">
+      <c r="S196" s="6" t="s">
         <v>2559</v>
-      </c>
-      <c r="O196" s="6" t="s">
-        <v>2560</v>
-      </c>
-      <c r="P196" s="6" t="s">
-        <v>2561</v>
-      </c>
-      <c r="Q196" s="6" t="s">
-        <v>2562</v>
-      </c>
-      <c r="R196" s="6" t="s">
-        <v>2563</v>
-      </c>
-      <c r="S196" s="6" t="s">
-        <v>2564</v>
       </c>
       <c r="T196" s="6"/>
       <c r="U196" s="6" t="s">
-        <v>2565</v>
+        <v>2560</v>
       </c>
       <c r="V196" s="6" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
       <c r="W196" s="6"/>
       <c r="X196" s="6"/>
       <c r="Y196" s="6"/>
       <c r="Z196" s="6" t="s">
-        <v>2567</v>
+        <v>2562</v>
       </c>
       <c r="AA196" s="6"/>
       <c r="AB196" s="3">
         <v>46313</v>
       </c>
       <c r="AC196" s="6" t="str">
-        <f>IF(AND(E196&lt;&gt;"",COUNTIF($E$2:$E$798,E196)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E196&lt;&gt;"",COUNTIF($E$2:$E$794,E196)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="197" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
-        <v>2568</v>
+        <v>2563</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>57</v>
@@ -23415,75 +24497,75 @@
         <v>58</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>2569</v>
+        <v>2564</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>2570</v>
+        <v>2565</v>
       </c>
       <c r="G197" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H197" s="6" t="s">
+        <v>2583</v>
+      </c>
+      <c r="I197" s="6" t="s">
+        <v>2566</v>
+      </c>
+      <c r="J197" s="6" t="s">
+        <v>2567</v>
+      </c>
+      <c r="K197" s="6" t="s">
+        <v>2568</v>
+      </c>
+      <c r="L197" s="6" t="s">
+        <v>2569</v>
+      </c>
+      <c r="M197" s="6" t="s">
+        <v>2570</v>
+      </c>
+      <c r="N197" s="6" t="s">
         <v>2571</v>
       </c>
-      <c r="I197" s="6" t="s">
+      <c r="O197" s="6" t="s">
         <v>2572</v>
       </c>
-      <c r="J197" s="6" t="s">
+      <c r="P197" s="6" t="s">
         <v>2573</v>
       </c>
-      <c r="K197" s="6" t="s">
+      <c r="Q197" s="6" t="s">
         <v>2574</v>
       </c>
-      <c r="L197" s="6" t="s">
+      <c r="R197" s="6" t="s">
         <v>2575</v>
       </c>
-      <c r="M197" s="6" t="s">
+      <c r="S197" s="6" t="s">
         <v>2576</v>
-      </c>
-      <c r="N197" s="6" t="s">
-        <v>2577</v>
-      </c>
-      <c r="O197" s="6" t="s">
-        <v>2578</v>
-      </c>
-      <c r="P197" s="6" t="s">
-        <v>2579</v>
-      </c>
-      <c r="Q197" s="6" t="s">
-        <v>2580</v>
-      </c>
-      <c r="R197" s="6" t="s">
-        <v>2581</v>
-      </c>
-      <c r="S197" s="6" t="s">
-        <v>2582</v>
       </c>
       <c r="T197" s="6"/>
       <c r="U197" s="6" t="s">
-        <v>2583</v>
+        <v>2577</v>
       </c>
       <c r="V197" s="6" t="s">
-        <v>2584</v>
+        <v>2578</v>
       </c>
       <c r="W197" s="6"/>
       <c r="X197" s="6"/>
       <c r="Y197" s="6"/>
       <c r="Z197" s="6" t="s">
-        <v>2585</v>
+        <v>2579</v>
       </c>
       <c r="AA197" s="6"/>
       <c r="AB197" s="3">
         <v>46313</v>
       </c>
       <c r="AC197" s="6" t="str">
-        <f>IF(AND(E197&lt;&gt;"",COUNTIF($E$2:$E$798,E197)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E197&lt;&gt;"",COUNTIF($E$2:$E$794,E197)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="198" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
-        <v>2586</v>
+        <v>2580</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>57</v>
@@ -23493,309 +24575,291 @@
         <v>1339</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>2587</v>
+        <v>2581</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>2588</v>
+        <v>2582</v>
       </c>
       <c r="G198" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H198" s="6" t="s">
+        <v>2583</v>
+      </c>
+      <c r="I198" s="6" t="s">
+        <v>2584</v>
+      </c>
+      <c r="J198" s="6" t="s">
+        <v>2585</v>
+      </c>
+      <c r="K198" s="6" t="s">
+        <v>2568</v>
+      </c>
+      <c r="L198" s="6" t="s">
+        <v>2586</v>
+      </c>
+      <c r="M198" s="6" t="s">
+        <v>2587</v>
+      </c>
+      <c r="N198" s="6" t="s">
+        <v>2588</v>
+      </c>
+      <c r="O198" s="6" t="s">
         <v>2589</v>
       </c>
-      <c r="I198" s="6" t="s">
+      <c r="P198" s="6" t="s">
         <v>2590</v>
       </c>
-      <c r="J198" s="6" t="s">
+      <c r="Q198" s="6" t="s">
         <v>2591</v>
       </c>
-      <c r="K198" s="6" t="s">
-        <v>2574</v>
-      </c>
-      <c r="L198" s="6" t="s">
+      <c r="R198" s="6" t="s">
         <v>2592</v>
       </c>
-      <c r="M198" s="6" t="s">
+      <c r="S198" s="6" t="s">
         <v>2593</v>
-      </c>
-      <c r="N198" s="6" t="s">
-        <v>2594</v>
-      </c>
-      <c r="O198" s="6" t="s">
-        <v>2595</v>
-      </c>
-      <c r="P198" s="6" t="s">
-        <v>2596</v>
-      </c>
-      <c r="Q198" s="6" t="s">
-        <v>2597</v>
-      </c>
-      <c r="R198" s="6" t="s">
-        <v>2598</v>
-      </c>
-      <c r="S198" s="6" t="s">
-        <v>2599</v>
       </c>
       <c r="T198" s="6"/>
       <c r="U198" s="6" t="s">
-        <v>2600</v>
+        <v>2594</v>
       </c>
       <c r="V198" s="6" t="s">
-        <v>2601</v>
+        <v>2595</v>
       </c>
       <c r="W198" s="6"/>
       <c r="X198" s="6"/>
       <c r="Y198" s="6"/>
       <c r="Z198" s="6" t="s">
-        <v>2602</v>
+        <v>2596</v>
       </c>
       <c r="AA198" s="6"/>
       <c r="AB198" s="3">
         <v>46313</v>
       </c>
       <c r="AC198" s="6" t="str">
-        <f>IF(AND(E198&lt;&gt;"",COUNTIF($E$2:$E$798,E198)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="6" t="s">
+        <f>IF(AND(E198&lt;&gt;"",COUNTIF($E$2:$E$794,E198)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A199" s="5" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>2598</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>2599</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H199" s="5" t="s">
+        <v>2443</v>
+      </c>
+      <c r="I199" s="5" t="s">
+        <v>2600</v>
+      </c>
+      <c r="J199" s="5" t="s">
+        <v>2601</v>
+      </c>
+      <c r="K199" s="5" t="s">
+        <v>2602</v>
+      </c>
+      <c r="L199" s="5" t="s">
         <v>2603</v>
       </c>
-      <c r="B199" s="6" t="s">
+      <c r="M199" s="7">
+        <v>46423</v>
+      </c>
+      <c r="N199" s="5" t="s">
+        <v>2604</v>
+      </c>
+      <c r="O199" s="5" t="s">
+        <v>2605</v>
+      </c>
+      <c r="P199" s="5" t="s">
+        <v>2449</v>
+      </c>
+      <c r="Q199" s="5" t="s">
+        <v>2606</v>
+      </c>
+      <c r="R199" s="5" t="s">
+        <v>2607</v>
+      </c>
+      <c r="S199" s="5" t="s">
+        <v>2608</v>
+      </c>
+      <c r="U199" s="5" t="s">
+        <v>2609</v>
+      </c>
+      <c r="V199" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Z199" s="5" t="s">
+        <v>2610</v>
+      </c>
+      <c r="AA199" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB199" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC199"/>
+    </row>
+    <row r="200" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A200" s="5" t="s">
+        <v>2611</v>
+      </c>
+      <c r="B200" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C199" s="6"/>
-      <c r="D199" s="6" t="s">
+      <c r="D200" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>2613</v>
+      </c>
+      <c r="G200" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="H200" s="5" t="s">
+        <v>2614</v>
+      </c>
+      <c r="I200" s="5" t="s">
+        <v>2615</v>
+      </c>
+      <c r="J200" s="5" t="s">
+        <v>2616</v>
+      </c>
+      <c r="K200" s="5" t="s">
+        <v>2617</v>
+      </c>
+      <c r="L200" s="5" t="s">
+        <v>2618</v>
+      </c>
+      <c r="M200" s="5" t="s">
+        <v>2619</v>
+      </c>
+      <c r="N200" s="5" t="s">
+        <v>2620</v>
+      </c>
+      <c r="O200" s="5" t="s">
+        <v>2621</v>
+      </c>
+      <c r="P200" s="5" t="s">
+        <v>2622</v>
+      </c>
+      <c r="Q200" s="5" t="s">
+        <v>2623</v>
+      </c>
+      <c r="R200" s="5" t="s">
+        <v>2624</v>
+      </c>
+      <c r="S200" s="5" t="s">
+        <v>2625</v>
+      </c>
+      <c r="U200" s="5" t="s">
+        <v>2626</v>
+      </c>
+      <c r="V200" s="5" t="s">
+        <v>2627</v>
+      </c>
+      <c r="Z200" s="5" t="s">
+        <v>2628</v>
+      </c>
+      <c r="AA200" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB200" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC200"/>
+    </row>
+    <row r="201" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A201" s="5" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D201" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E199" s="6" t="s">
-        <v>2604</v>
-      </c>
-      <c r="F199" s="6" t="s">
-        <v>2605</v>
-      </c>
-      <c r="G199" s="6" t="s">
-        <v>2606</v>
-      </c>
-      <c r="H199" s="6" t="s">
-        <v>2607</v>
-      </c>
-      <c r="I199" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J199" s="6" t="s">
-        <v>2608</v>
-      </c>
-      <c r="K199" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="L199" s="6" t="s">
-        <v>2609</v>
-      </c>
-      <c r="M199" s="6" t="s">
-        <v>2610</v>
-      </c>
-      <c r="N199" s="6" t="s">
-        <v>2611</v>
-      </c>
-      <c r="O199" s="6" t="s">
-        <v>2612</v>
-      </c>
-      <c r="P199" s="6" t="s">
-        <v>2613</v>
-      </c>
-      <c r="Q199" s="6" t="s">
-        <v>2614</v>
-      </c>
-      <c r="R199" s="6" t="s">
-        <v>2615</v>
-      </c>
-      <c r="S199" s="6" t="s">
-        <v>2616</v>
-      </c>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6" t="s">
-        <v>2617</v>
-      </c>
-      <c r="V199" s="6" t="s">
-        <v>2618</v>
-      </c>
-      <c r="W199" s="6"/>
-      <c r="X199" s="6"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6" t="s">
-        <v>2619</v>
-      </c>
-      <c r="AA199" s="6"/>
-      <c r="AB199" s="3">
+      <c r="E201" s="5" t="s">
+        <v>2629</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>2630</v>
+      </c>
+      <c r="G201" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="H201" s="5" t="s">
+        <v>2963</v>
+      </c>
+      <c r="I201" s="5" t="s">
+        <v>2631</v>
+      </c>
+      <c r="J201" s="5" t="s">
+        <v>2632</v>
+      </c>
+      <c r="K201" s="5" t="s">
+        <v>2633</v>
+      </c>
+      <c r="L201" s="5" t="s">
+        <v>2634</v>
+      </c>
+      <c r="M201" s="5" t="s">
+        <v>2635</v>
+      </c>
+      <c r="N201" s="5" t="s">
+        <v>2636</v>
+      </c>
+      <c r="O201" s="5" t="s">
+        <v>2637</v>
+      </c>
+      <c r="P201" s="5" t="s">
+        <v>2638</v>
+      </c>
+      <c r="Q201" s="5" t="s">
+        <v>2639</v>
+      </c>
+      <c r="R201" s="5" t="s">
+        <v>2640</v>
+      </c>
+      <c r="S201" s="5" t="s">
+        <v>2641</v>
+      </c>
+      <c r="U201" s="5" t="s">
+        <v>2642</v>
+      </c>
+      <c r="V201" s="5" t="s">
+        <v>2423</v>
+      </c>
+      <c r="Z201" s="5" t="s">
+        <v>2643</v>
+      </c>
+      <c r="AA201" s="4">
         <v>46313</v>
       </c>
-      <c r="AC199" s="6" t="str">
-        <f>IF(AND(E199&lt;&gt;"",COUNTIF($E$2:$E$798,E199)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="6" t="s">
-        <v>2620</v>
-      </c>
-      <c r="B200" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C200" s="6"/>
-      <c r="D200" s="6" t="s">
-        <v>1339</v>
-      </c>
-      <c r="E200" s="6" t="s">
-        <v>2621</v>
-      </c>
-      <c r="F200" s="6" t="s">
-        <v>2622</v>
-      </c>
-      <c r="G200" s="6" t="s">
-        <v>2623</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>2624</v>
-      </c>
-      <c r="I200" s="6" t="s">
-        <v>2625</v>
-      </c>
-      <c r="J200" s="6" t="s">
-        <v>2626</v>
-      </c>
-      <c r="K200" s="6" t="s">
-        <v>2627</v>
-      </c>
-      <c r="L200" s="6" t="s">
-        <v>2628</v>
-      </c>
-      <c r="M200" s="6" t="s">
-        <v>2629</v>
-      </c>
-      <c r="N200" s="6" t="s">
-        <v>2630</v>
-      </c>
-      <c r="O200" s="6" t="s">
-        <v>2631</v>
-      </c>
-      <c r="P200" s="6" t="s">
-        <v>2632</v>
-      </c>
-      <c r="Q200" s="6" t="s">
-        <v>2633</v>
-      </c>
-      <c r="R200" s="6" t="s">
-        <v>2634</v>
-      </c>
-      <c r="S200" s="6" t="s">
-        <v>2635</v>
-      </c>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6" t="s">
-        <v>2636</v>
-      </c>
-      <c r="V200" s="6" t="s">
-        <v>2637</v>
-      </c>
-      <c r="W200" s="6"/>
-      <c r="X200" s="6"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6" t="s">
-        <v>2638</v>
-      </c>
-      <c r="AA200" s="6"/>
-      <c r="AB200" s="3">
+      <c r="AB201" s="4">
         <v>46313</v>
       </c>
-      <c r="AC200" s="6" t="str">
-        <f>IF(AND(E200&lt;&gt;"",COUNTIF($E$2:$E$798,E200)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="1:29" s="5" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="6" t="s">
-        <v>2639</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C201" s="6"/>
-      <c r="D201" s="6" t="s">
-        <v>1339</v>
-      </c>
-      <c r="E201" s="6" t="s">
-        <v>2640</v>
-      </c>
-      <c r="F201" s="6" t="s">
-        <v>2641</v>
-      </c>
-      <c r="G201" s="6" t="s">
-        <v>2623</v>
-      </c>
-      <c r="H201" s="6" t="s">
-        <v>2642</v>
-      </c>
-      <c r="I201" s="6" t="s">
-        <v>883</v>
-      </c>
-      <c r="J201" s="6" t="s">
-        <v>2643</v>
-      </c>
-      <c r="K201" s="6" t="s">
-        <v>2627</v>
-      </c>
-      <c r="L201" s="6" t="s">
-        <v>2644</v>
-      </c>
-      <c r="M201" s="6" t="s">
-        <v>2645</v>
-      </c>
-      <c r="N201" s="6" t="s">
-        <v>2646</v>
-      </c>
-      <c r="O201" s="6" t="s">
-        <v>2647</v>
-      </c>
-      <c r="P201" s="6" t="s">
-        <v>2648</v>
-      </c>
-      <c r="Q201" s="6" t="s">
-        <v>2649</v>
-      </c>
-      <c r="R201" s="6" t="s">
-        <v>2650</v>
-      </c>
-      <c r="S201" s="6" t="s">
-        <v>2651</v>
-      </c>
-      <c r="T201" s="6"/>
-      <c r="U201" s="6" t="s">
-        <v>2652</v>
-      </c>
-      <c r="V201" s="6" t="s">
-        <v>2653</v>
-      </c>
-      <c r="W201" s="6"/>
-      <c r="X201" s="6"/>
-      <c r="Y201" s="6"/>
-      <c r="Z201" s="6" t="s">
-        <v>2654</v>
-      </c>
-      <c r="AA201" s="6"/>
-      <c r="AB201" s="3">
-        <v>46313</v>
-      </c>
-      <c r="AC201" s="6" t="str">
-        <f>IF(AND(E201&lt;&gt;"",COUNTIF($E$2:$E$798,E201)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
+      <c r="AC201"/>
     </row>
     <row r="202" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A202" s="5" t="s">
-        <v>2655</v>
+        <v>2644</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>57</v>
@@ -23804,58 +24868,58 @@
         <v>58</v>
       </c>
       <c r="E202" s="5" t="s">
+        <v>2645</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>2630</v>
+      </c>
+      <c r="G202" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="H202" s="5" t="s">
+        <v>2963</v>
+      </c>
+      <c r="I202" s="5" t="s">
+        <v>2631</v>
+      </c>
+      <c r="J202" s="5" t="s">
+        <v>2646</v>
+      </c>
+      <c r="K202" s="5" t="s">
+        <v>2633</v>
+      </c>
+      <c r="L202" s="5" t="s">
+        <v>2647</v>
+      </c>
+      <c r="M202" s="5" t="s">
+        <v>2648</v>
+      </c>
+      <c r="N202" s="5" t="s">
+        <v>2649</v>
+      </c>
+      <c r="O202" s="5" t="s">
+        <v>2650</v>
+      </c>
+      <c r="P202" s="5" t="s">
+        <v>2651</v>
+      </c>
+      <c r="Q202" s="5" t="s">
+        <v>2652</v>
+      </c>
+      <c r="R202" s="5" t="s">
+        <v>2653</v>
+      </c>
+      <c r="S202" s="5" t="s">
+        <v>2654</v>
+      </c>
+      <c r="U202" s="5" t="s">
+        <v>2655</v>
+      </c>
+      <c r="V202" s="5" t="s">
+        <v>2438</v>
+      </c>
+      <c r="Z202" s="5" t="s">
         <v>2656</v>
-      </c>
-      <c r="F202" s="5" t="s">
-        <v>2657</v>
-      </c>
-      <c r="G202" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H202" s="5" t="s">
-        <v>2444</v>
-      </c>
-      <c r="I202" s="5" t="s">
-        <v>2658</v>
-      </c>
-      <c r="J202" s="5" t="s">
-        <v>2659</v>
-      </c>
-      <c r="K202" s="5" t="s">
-        <v>2660</v>
-      </c>
-      <c r="L202" s="5" t="s">
-        <v>2661</v>
-      </c>
-      <c r="M202" s="7">
-        <v>46423</v>
-      </c>
-      <c r="N202" s="5" t="s">
-        <v>2662</v>
-      </c>
-      <c r="O202" s="5" t="s">
-        <v>2663</v>
-      </c>
-      <c r="P202" s="5" t="s">
-        <v>2450</v>
-      </c>
-      <c r="Q202" s="5" t="s">
-        <v>2664</v>
-      </c>
-      <c r="R202" s="5" t="s">
-        <v>2665</v>
-      </c>
-      <c r="S202" s="5" t="s">
-        <v>2666</v>
-      </c>
-      <c r="U202" s="5" t="s">
-        <v>2667</v>
-      </c>
-      <c r="V202" s="5" t="s">
-        <v>2455</v>
-      </c>
-      <c r="Z202" s="5" t="s">
-        <v>2668</v>
       </c>
       <c r="AA202" s="4">
         <v>46313</v>
@@ -23867,67 +24931,67 @@
     </row>
     <row r="203" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A203" s="5" t="s">
-        <v>2669</v>
+        <v>2657</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>1339</v>
+        <v>58</v>
       </c>
       <c r="E203" s="5" t="s">
+        <v>2658</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>2659</v>
+      </c>
+      <c r="G203" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H203" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="I203" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="J203" s="5" t="s">
+        <v>2661</v>
+      </c>
+      <c r="K203" s="5" t="s">
+        <v>2662</v>
+      </c>
+      <c r="L203" s="5" t="s">
+        <v>2663</v>
+      </c>
+      <c r="M203" s="5" t="s">
+        <v>2664</v>
+      </c>
+      <c r="N203" s="5" t="s">
+        <v>2665</v>
+      </c>
+      <c r="O203" s="5" t="s">
+        <v>2666</v>
+      </c>
+      <c r="P203" s="5" t="s">
+        <v>2667</v>
+      </c>
+      <c r="Q203" s="5" t="s">
+        <v>2668</v>
+      </c>
+      <c r="R203" s="5" t="s">
+        <v>2669</v>
+      </c>
+      <c r="S203" s="5" t="s">
         <v>2670</v>
       </c>
-      <c r="F203" s="5" t="s">
+      <c r="U203" s="5" t="s">
         <v>2671</v>
       </c>
-      <c r="G203" s="5" t="s">
+      <c r="V203" s="5" t="s">
         <v>2672</v>
       </c>
-      <c r="H203" s="5" t="s">
+      <c r="Z203" s="5" t="s">
         <v>2673</v>
-      </c>
-      <c r="I203" s="5" t="s">
-        <v>2674</v>
-      </c>
-      <c r="J203" s="5" t="s">
-        <v>2675</v>
-      </c>
-      <c r="K203" s="5" t="s">
-        <v>2676</v>
-      </c>
-      <c r="L203" s="5" t="s">
-        <v>2677</v>
-      </c>
-      <c r="M203" s="5" t="s">
-        <v>2678</v>
-      </c>
-      <c r="N203" s="5" t="s">
-        <v>2679</v>
-      </c>
-      <c r="O203" s="5" t="s">
-        <v>2680</v>
-      </c>
-      <c r="P203" s="5" t="s">
-        <v>2681</v>
-      </c>
-      <c r="Q203" s="5" t="s">
-        <v>2682</v>
-      </c>
-      <c r="R203" s="5" t="s">
-        <v>2683</v>
-      </c>
-      <c r="S203" s="5" t="s">
-        <v>2684</v>
-      </c>
-      <c r="U203" s="5" t="s">
-        <v>2685</v>
-      </c>
-      <c r="V203" s="5" t="s">
-        <v>2686</v>
-      </c>
-      <c r="Z203" s="5" t="s">
-        <v>2687</v>
       </c>
       <c r="AA203" s="4">
         <v>46313</v>
@@ -23939,7 +25003,7 @@
     </row>
     <row r="204" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A204" s="5" t="s">
-        <v>2409</v>
+        <v>2674</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>57</v>
@@ -23948,70 +25012,64 @@
         <v>58</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>2688</v>
+        <v>2675</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>2689</v>
+        <v>2676</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>2412</v>
-      </c>
-      <c r="H204" s="5" t="s">
-        <v>2690</v>
+        <v>61</v>
       </c>
       <c r="I204" s="5" t="s">
-        <v>2691</v>
+        <v>2677</v>
       </c>
       <c r="J204" s="5" t="s">
-        <v>2692</v>
+        <v>2677</v>
       </c>
       <c r="K204" s="5" t="s">
-        <v>2693</v>
+        <v>2677</v>
       </c>
       <c r="L204" s="5" t="s">
-        <v>2694</v>
+        <v>2677</v>
       </c>
       <c r="M204" s="5" t="s">
-        <v>2695</v>
+        <v>2678</v>
       </c>
       <c r="N204" s="5" t="s">
-        <v>2696</v>
+        <v>2679</v>
       </c>
       <c r="O204" s="5" t="s">
-        <v>2697</v>
+        <v>2680</v>
       </c>
       <c r="P204" s="5" t="s">
-        <v>2698</v>
+        <v>2681</v>
       </c>
       <c r="Q204" s="5" t="s">
-        <v>2699</v>
+        <v>2682</v>
       </c>
       <c r="R204" s="5" t="s">
-        <v>2700</v>
+        <v>2683</v>
       </c>
       <c r="S204" s="5" t="s">
-        <v>2701</v>
+        <v>2683</v>
       </c>
       <c r="U204" s="5" t="s">
-        <v>2702</v>
+        <v>2684</v>
       </c>
       <c r="V204" s="5" t="s">
-        <v>2424</v>
-      </c>
-      <c r="Z204" s="5" t="s">
-        <v>2703</v>
-      </c>
-      <c r="AA204" s="4">
-        <v>46313</v>
-      </c>
+        <v>2685</v>
+      </c>
+      <c r="AA204" s="4"/>
       <c r="AB204" s="4">
         <v>46313</v>
       </c>
-      <c r="AC204"/>
+      <c r="AC204" s="8">
+        <v>46313</v>
+      </c>
     </row>
     <row r="205" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
-        <v>2704</v>
+        <v>2686</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>57</v>
@@ -24020,142 +25078,136 @@
         <v>58</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>2705</v>
+        <v>2687</v>
       </c>
       <c r="F205" s="5" t="s">
+        <v>2688</v>
+      </c>
+      <c r="G205" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H205" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="I205" s="5" t="s">
         <v>2689</v>
       </c>
-      <c r="G205" s="5" t="s">
-        <v>2412</v>
-      </c>
-      <c r="H205" s="5" t="s">
-        <v>2706</v>
-      </c>
-      <c r="I205" s="5" t="s">
+      <c r="J205" s="5" t="s">
+        <v>2677</v>
+      </c>
+      <c r="K205" s="5" t="s">
+        <v>2677</v>
+      </c>
+      <c r="L205" s="5" t="s">
+        <v>2677</v>
+      </c>
+      <c r="M205" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="N205" s="5" t="s">
         <v>2691</v>
       </c>
-      <c r="J205" s="5" t="s">
-        <v>2707</v>
-      </c>
-      <c r="K205" s="5" t="s">
+      <c r="O205" s="5" t="s">
+        <v>2680</v>
+      </c>
+      <c r="P205" s="5" t="s">
+        <v>2692</v>
+      </c>
+      <c r="Q205" s="5" t="s">
         <v>2693</v>
       </c>
-      <c r="L205" s="5" t="s">
-        <v>2708</v>
-      </c>
-      <c r="M205" s="5" t="s">
-        <v>2709</v>
-      </c>
-      <c r="N205" s="5" t="s">
-        <v>2710</v>
-      </c>
-      <c r="O205" s="5" t="s">
-        <v>2711</v>
-      </c>
-      <c r="P205" s="5" t="s">
-        <v>2712</v>
-      </c>
-      <c r="Q205" s="5" t="s">
-        <v>2713</v>
-      </c>
       <c r="R205" s="5" t="s">
-        <v>2714</v>
+        <v>2683</v>
       </c>
       <c r="S205" s="5" t="s">
-        <v>2715</v>
+        <v>2683</v>
       </c>
       <c r="U205" s="5" t="s">
-        <v>2716</v>
+        <v>2694</v>
       </c>
       <c r="V205" s="5" t="s">
-        <v>2439</v>
-      </c>
-      <c r="Z205" s="5" t="s">
-        <v>2717</v>
-      </c>
-      <c r="AA205" s="4">
-        <v>46313</v>
-      </c>
+        <v>2695</v>
+      </c>
+      <c r="AA205" s="4"/>
       <c r="AB205" s="4">
         <v>46313</v>
       </c>
-      <c r="AC205"/>
+      <c r="AC205" s="8">
+        <v>46313</v>
+      </c>
     </row>
     <row r="206" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A206" s="5" t="s">
-        <v>2718</v>
+        <v>2696</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>58</v>
+        <v>1339</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>2719</v>
+        <v>2697</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>2720</v>
+        <v>2698</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>372</v>
+        <v>606</v>
       </c>
       <c r="H206" s="5" t="s">
-        <v>373</v>
+        <v>2699</v>
       </c>
       <c r="I206" s="5" t="s">
-        <v>2721</v>
+        <v>2700</v>
       </c>
       <c r="J206" s="5" t="s">
-        <v>2722</v>
+        <v>2701</v>
       </c>
       <c r="K206" s="5" t="s">
-        <v>2723</v>
+        <v>2677</v>
       </c>
       <c r="L206" s="5" t="s">
-        <v>2724</v>
+        <v>2702</v>
       </c>
       <c r="M206" s="5" t="s">
-        <v>2725</v>
+        <v>2703</v>
       </c>
       <c r="N206" s="5" t="s">
-        <v>2726</v>
+        <v>2704</v>
       </c>
       <c r="O206" s="5" t="s">
-        <v>2727</v>
+        <v>2705</v>
       </c>
       <c r="P206" s="5" t="s">
-        <v>2728</v>
+        <v>2706</v>
       </c>
       <c r="Q206" s="5" t="s">
-        <v>2729</v>
+        <v>2707</v>
       </c>
       <c r="R206" s="5" t="s">
-        <v>2730</v>
+        <v>2708</v>
       </c>
       <c r="S206" s="5" t="s">
-        <v>2731</v>
+        <v>2708</v>
       </c>
       <c r="U206" s="5" t="s">
-        <v>2732</v>
+        <v>2709</v>
       </c>
       <c r="V206" s="5" t="s">
-        <v>2733</v>
-      </c>
-      <c r="Z206" s="5" t="s">
-        <v>2734</v>
-      </c>
-      <c r="AA206" s="4">
-        <v>46313</v>
-      </c>
+        <v>2710</v>
+      </c>
+      <c r="AA206" s="4"/>
       <c r="AB206" s="4">
         <v>46313</v>
       </c>
-      <c r="AC206"/>
+      <c r="AC206" s="8">
+        <v>46313</v>
+      </c>
     </row>
     <row r="207" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A207" s="5" t="s">
-        <v>2735</v>
+        <v>2711</v>
       </c>
       <c r="B207" s="5" t="s">
         <v>57</v>
@@ -24164,55 +25216,55 @@
         <v>58</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>2736</v>
+        <v>2712</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>2737</v>
+        <v>2713</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>61</v>
+        <v>606</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>2738</v>
+        <v>2714</v>
       </c>
       <c r="I207" s="5" t="s">
-        <v>2738</v>
+        <v>2677</v>
       </c>
       <c r="J207" s="5" t="s">
-        <v>2738</v>
+        <v>2677</v>
       </c>
       <c r="K207" s="5" t="s">
-        <v>2738</v>
+        <v>2677</v>
       </c>
       <c r="L207" s="5" t="s">
-        <v>2738</v>
+        <v>2677</v>
       </c>
       <c r="M207" s="5" t="s">
-        <v>2739</v>
+        <v>2715</v>
       </c>
       <c r="N207" s="5" t="s">
-        <v>2740</v>
+        <v>2716</v>
       </c>
       <c r="O207" s="5" t="s">
-        <v>2741</v>
+        <v>2680</v>
       </c>
       <c r="P207" s="5" t="s">
-        <v>2742</v>
+        <v>2717</v>
       </c>
       <c r="Q207" s="5" t="s">
-        <v>2743</v>
+        <v>2718</v>
       </c>
       <c r="R207" s="5" t="s">
-        <v>2744</v>
+        <v>2683</v>
       </c>
       <c r="S207" s="5" t="s">
-        <v>2744</v>
+        <v>2683</v>
       </c>
       <c r="U207" s="5" t="s">
-        <v>2745</v>
+        <v>2719</v>
       </c>
       <c r="V207" s="5" t="s">
-        <v>2746</v>
+        <v>2720</v>
       </c>
       <c r="AA207" s="4"/>
       <c r="AB207" s="4">
@@ -24224,7 +25276,7 @@
     </row>
     <row r="208" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A208" s="5" t="s">
-        <v>2747</v>
+        <v>2721</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>57</v>
@@ -24233,55 +25285,55 @@
         <v>58</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>2748</v>
+        <v>2722</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>2749</v>
+        <v>2723</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>61</v>
+        <v>372</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>647</v>
+        <v>2724</v>
       </c>
       <c r="I208" s="5" t="s">
-        <v>2750</v>
+        <v>2725</v>
       </c>
       <c r="J208" s="5" t="s">
-        <v>2738</v>
+        <v>2726</v>
       </c>
       <c r="K208" s="5" t="s">
-        <v>2738</v>
+        <v>2677</v>
       </c>
       <c r="L208" s="5" t="s">
-        <v>2738</v>
-      </c>
-      <c r="M208" s="5" t="s">
-        <v>2751</v>
+        <v>2727</v>
+      </c>
+      <c r="M208" s="8">
+        <v>46122</v>
       </c>
       <c r="N208" s="5" t="s">
-        <v>2752</v>
+        <v>2728</v>
       </c>
       <c r="O208" s="5" t="s">
-        <v>2741</v>
+        <v>2680</v>
       </c>
       <c r="P208" s="5" t="s">
-        <v>2753</v>
+        <v>2729</v>
       </c>
       <c r="Q208" s="5" t="s">
-        <v>2754</v>
+        <v>2730</v>
       </c>
       <c r="R208" s="5" t="s">
-        <v>2744</v>
+        <v>2708</v>
       </c>
       <c r="S208" s="5" t="s">
-        <v>2744</v>
+        <v>2708</v>
       </c>
       <c r="U208" s="5" t="s">
-        <v>2755</v>
+        <v>2731</v>
       </c>
       <c r="V208" s="5" t="s">
-        <v>2756</v>
+        <v>2732</v>
       </c>
       <c r="AA208" s="4"/>
       <c r="AB208" s="4">
@@ -24293,64 +25345,64 @@
     </row>
     <row r="209" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A209" s="5" t="s">
-        <v>2757</v>
+        <v>2733</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>1339</v>
+        <v>58</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>2758</v>
+        <v>2734</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>2759</v>
+        <v>2735</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>606</v>
+        <v>2736</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>2760</v>
+        <v>2736</v>
       </c>
       <c r="I209" s="5" t="s">
-        <v>2761</v>
+        <v>2737</v>
       </c>
       <c r="J209" s="5" t="s">
-        <v>2762</v>
+        <v>2738</v>
       </c>
       <c r="K209" s="5" t="s">
-        <v>2738</v>
+        <v>2677</v>
       </c>
       <c r="L209" s="5" t="s">
-        <v>2763</v>
-      </c>
-      <c r="M209" s="5" t="s">
-        <v>2764</v>
+        <v>2739</v>
+      </c>
+      <c r="M209" s="8">
+        <v>46120</v>
       </c>
       <c r="N209" s="5" t="s">
-        <v>2765</v>
+        <v>2740</v>
       </c>
       <c r="O209" s="5" t="s">
-        <v>2766</v>
+        <v>2680</v>
       </c>
       <c r="P209" s="5" t="s">
-        <v>2767</v>
+        <v>2741</v>
       </c>
       <c r="Q209" s="5" t="s">
-        <v>2768</v>
+        <v>2742</v>
       </c>
       <c r="R209" s="5" t="s">
-        <v>2769</v>
+        <v>2743</v>
       </c>
       <c r="S209" s="5" t="s">
-        <v>2769</v>
+        <v>2743</v>
       </c>
       <c r="U209" s="5" t="s">
-        <v>2770</v>
+        <v>2744</v>
       </c>
       <c r="V209" s="5" t="s">
-        <v>2771</v>
+        <v>2745</v>
       </c>
       <c r="AA209" s="4"/>
       <c r="AB209" s="4">
@@ -24362,214 +25414,220 @@
     </row>
     <row r="210" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A210" s="5" t="s">
-        <v>2772</v>
+        <v>2746</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>57</v>
+        <v>2076</v>
       </c>
       <c r="D210" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>2773</v>
+        <v>2747</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>2774</v>
+        <v>2748</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>2775</v>
+        <v>606</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>2776</v>
+        <v>2749</v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>2738</v>
+        <v>2750</v>
       </c>
       <c r="J210" s="5" t="s">
-        <v>2738</v>
+        <v>2751</v>
       </c>
       <c r="K210" s="5" t="s">
-        <v>2738</v>
+        <v>2752</v>
       </c>
       <c r="L210" s="5" t="s">
-        <v>2738</v>
+        <v>2753</v>
       </c>
       <c r="M210" s="5" t="s">
-        <v>2777</v>
+        <v>2754</v>
       </c>
       <c r="N210" s="5" t="s">
-        <v>2778</v>
+        <v>2755</v>
       </c>
       <c r="O210" s="5" t="s">
-        <v>2741</v>
+        <v>2756</v>
       </c>
       <c r="P210" s="5" t="s">
-        <v>2779</v>
+        <v>2757</v>
       </c>
       <c r="Q210" s="5" t="s">
-        <v>2780</v>
+        <v>2758</v>
       </c>
       <c r="R210" s="5" t="s">
-        <v>2744</v>
+        <v>2759</v>
       </c>
       <c r="S210" s="5" t="s">
-        <v>2744</v>
+        <v>2760</v>
       </c>
       <c r="U210" s="5" t="s">
-        <v>2781</v>
+        <v>2761</v>
       </c>
       <c r="V210" s="5" t="s">
-        <v>2782</v>
-      </c>
-      <c r="AA210" s="4"/>
+        <v>2762</v>
+      </c>
+      <c r="Z210" s="5" t="s">
+        <v>2763</v>
+      </c>
+      <c r="AA210" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB210" s="4">
         <v>46313</v>
       </c>
-      <c r="AC210" s="8">
-        <v>46313</v>
-      </c>
+      <c r="AC210"/>
     </row>
     <row r="211" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
-        <v>2783</v>
+        <v>2764</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>57</v>
+        <v>2076</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>2784</v>
+        <v>2765</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>2785</v>
+        <v>2766</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="H211" s="5" t="s">
-        <v>2786</v>
+        <v>606</v>
       </c>
       <c r="I211" s="5" t="s">
-        <v>2787</v>
+        <v>2767</v>
       </c>
       <c r="J211" s="5" t="s">
-        <v>2788</v>
+        <v>2768</v>
       </c>
       <c r="K211" s="5" t="s">
-        <v>2738</v>
+        <v>2769</v>
       </c>
       <c r="L211" s="5" t="s">
-        <v>2789</v>
-      </c>
-      <c r="M211" s="8">
-        <v>46122</v>
+        <v>2770</v>
+      </c>
+      <c r="M211" s="5" t="s">
+        <v>2771</v>
       </c>
       <c r="N211" s="5" t="s">
-        <v>2790</v>
+        <v>2772</v>
       </c>
       <c r="O211" s="5" t="s">
-        <v>2741</v>
+        <v>2773</v>
       </c>
       <c r="P211" s="5" t="s">
-        <v>2791</v>
+        <v>2774</v>
       </c>
       <c r="Q211" s="5" t="s">
-        <v>2792</v>
+        <v>2775</v>
       </c>
       <c r="R211" s="5" t="s">
-        <v>2769</v>
+        <v>2776</v>
       </c>
       <c r="S211" s="5" t="s">
-        <v>2769</v>
+        <v>2777</v>
       </c>
       <c r="U211" s="5" t="s">
-        <v>2793</v>
+        <v>2778</v>
       </c>
       <c r="V211" s="5" t="s">
-        <v>2794</v>
-      </c>
-      <c r="AA211" s="4"/>
+        <v>2779</v>
+      </c>
+      <c r="Z211" s="5" t="s">
+        <v>2780</v>
+      </c>
+      <c r="AA211" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB211" s="4">
         <v>46313</v>
       </c>
-      <c r="AC211" s="8">
-        <v>46313</v>
-      </c>
+      <c r="AC211"/>
     </row>
     <row r="212" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
-        <v>2795</v>
+        <v>2781</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>57</v>
+        <v>2076</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E212" s="5" t="s">
+        <v>2782</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>2783</v>
+      </c>
+      <c r="G212" s="5" t="s">
+        <v>2784</v>
+      </c>
+      <c r="H212" s="5" t="s">
+        <v>2785</v>
+      </c>
+      <c r="I212" s="5" t="s">
+        <v>2786</v>
+      </c>
+      <c r="J212" s="5" t="s">
+        <v>2787</v>
+      </c>
+      <c r="K212" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L212" s="5" t="s">
+        <v>2788</v>
+      </c>
+      <c r="M212" s="5" t="s">
+        <v>2789</v>
+      </c>
+      <c r="N212" s="5" t="s">
+        <v>2790</v>
+      </c>
+      <c r="O212" s="5" t="s">
+        <v>2791</v>
+      </c>
+      <c r="P212" s="5" t="s">
+        <v>2792</v>
+      </c>
+      <c r="Q212" s="5" t="s">
+        <v>2793</v>
+      </c>
+      <c r="R212" s="5" t="s">
+        <v>2794</v>
+      </c>
+      <c r="S212" s="5" t="s">
+        <v>2795</v>
+      </c>
+      <c r="U212" s="5" t="s">
         <v>2796</v>
       </c>
-      <c r="F212" s="5" t="s">
+      <c r="V212" s="5" t="s">
         <v>2797</v>
       </c>
-      <c r="G212" s="5" t="s">
+      <c r="Z212" s="5" t="s">
         <v>2798</v>
       </c>
-      <c r="H212" s="5" t="s">
-        <v>2799</v>
-      </c>
-      <c r="I212" s="5" t="s">
-        <v>2800</v>
-      </c>
-      <c r="J212" s="5" t="s">
-        <v>2801</v>
-      </c>
-      <c r="K212" s="5" t="s">
-        <v>2738</v>
-      </c>
-      <c r="L212" s="5" t="s">
-        <v>2802</v>
-      </c>
-      <c r="M212" s="8">
-        <v>46120</v>
-      </c>
-      <c r="N212" s="5" t="s">
-        <v>2803</v>
-      </c>
-      <c r="O212" s="5" t="s">
-        <v>2741</v>
-      </c>
-      <c r="P212" s="5" t="s">
-        <v>2804</v>
-      </c>
-      <c r="Q212" s="5" t="s">
-        <v>2805</v>
-      </c>
-      <c r="R212" s="5" t="s">
-        <v>2806</v>
-      </c>
-      <c r="S212" s="5" t="s">
-        <v>2806</v>
-      </c>
-      <c r="U212" s="5" t="s">
-        <v>2807</v>
-      </c>
-      <c r="V212" s="5" t="s">
-        <v>2808</v>
-      </c>
-      <c r="AA212" s="4"/>
+      <c r="AA212" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB212" s="4">
         <v>46313</v>
       </c>
-      <c r="AC212" s="8">
-        <v>46313</v>
-      </c>
+      <c r="AC212"/>
     </row>
     <row r="213" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
-        <v>2809</v>
+        <v>2799</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>2076</v>
@@ -24578,58 +25636,58 @@
         <v>58</v>
       </c>
       <c r="E213" s="5" t="s">
+        <v>2800</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>2801</v>
+      </c>
+      <c r="G213" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="H213" s="5" t="s">
+        <v>2802</v>
+      </c>
+      <c r="I213" s="5" t="s">
+        <v>2803</v>
+      </c>
+      <c r="J213" s="5" t="s">
+        <v>2804</v>
+      </c>
+      <c r="K213" s="5" t="s">
+        <v>2805</v>
+      </c>
+      <c r="L213" s="5" t="s">
+        <v>2806</v>
+      </c>
+      <c r="M213" s="5" t="s">
+        <v>2807</v>
+      </c>
+      <c r="N213" s="5" t="s">
+        <v>2808</v>
+      </c>
+      <c r="O213" s="5" t="s">
+        <v>2809</v>
+      </c>
+      <c r="P213" s="5" t="s">
         <v>2810</v>
       </c>
-      <c r="F213" s="5" t="s">
+      <c r="Q213" s="5" t="s">
         <v>2811</v>
       </c>
-      <c r="G213" s="5" t="s">
-        <v>2412</v>
-      </c>
-      <c r="H213" s="5" t="s">
+      <c r="R213" s="5" t="s">
         <v>2812</v>
       </c>
-      <c r="I213" s="5" t="s">
+      <c r="S213" s="5" t="s">
         <v>2813</v>
       </c>
-      <c r="J213" s="5" t="s">
+      <c r="U213" s="5" t="s">
         <v>2814</v>
       </c>
-      <c r="K213" s="5" t="s">
+      <c r="V213" s="5" t="s">
         <v>2815</v>
       </c>
-      <c r="L213" s="5" t="s">
+      <c r="Z213" s="5" t="s">
         <v>2816</v>
-      </c>
-      <c r="M213" s="5" t="s">
-        <v>2817</v>
-      </c>
-      <c r="N213" s="5" t="s">
-        <v>2818</v>
-      </c>
-      <c r="O213" s="5" t="s">
-        <v>2819</v>
-      </c>
-      <c r="P213" s="5" t="s">
-        <v>2820</v>
-      </c>
-      <c r="Q213" s="5" t="s">
-        <v>2821</v>
-      </c>
-      <c r="R213" s="5" t="s">
-        <v>2822</v>
-      </c>
-      <c r="S213" s="5" t="s">
-        <v>2823</v>
-      </c>
-      <c r="U213" s="5" t="s">
-        <v>2824</v>
-      </c>
-      <c r="V213" s="5" t="s">
-        <v>2825</v>
-      </c>
-      <c r="Z213" s="5" t="s">
-        <v>2826</v>
       </c>
       <c r="AA213" s="4">
         <v>46313</v>
@@ -24641,537 +25699,2196 @@
     </row>
     <row r="214" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A214" s="5" t="s">
-        <v>2827</v>
+        <v>2817</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>2076</v>
+        <v>57</v>
       </c>
       <c r="D214" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E214" s="5" t="s">
+        <v>2818</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>2819</v>
+      </c>
+      <c r="G214" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H214" s="5" t="s">
+        <v>2820</v>
+      </c>
+      <c r="I214" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="J214" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K214" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L214" s="5" t="s">
+        <v>2821</v>
+      </c>
+      <c r="M214" s="5" t="s">
+        <v>2822</v>
+      </c>
+      <c r="N214" s="5" t="s">
+        <v>2823</v>
+      </c>
+      <c r="O214" s="5" t="s">
+        <v>2824</v>
+      </c>
+      <c r="P214" s="5" t="s">
+        <v>2825</v>
+      </c>
+      <c r="Q214" s="5" t="s">
+        <v>2826</v>
+      </c>
+      <c r="R214" s="5" t="s">
+        <v>2827</v>
+      </c>
+      <c r="S214" s="5" t="s">
         <v>2828</v>
       </c>
-      <c r="F214" s="5" t="s">
+      <c r="U214" s="5" t="s">
         <v>2829</v>
       </c>
-      <c r="G214" s="5" t="s">
-        <v>2412</v>
-      </c>
-      <c r="H214" s="5" t="s">
+      <c r="V214" s="5" t="s">
         <v>2830</v>
       </c>
-      <c r="I214" s="5" t="s">
-        <v>2831</v>
-      </c>
-      <c r="J214" s="5" t="s">
-        <v>2832</v>
-      </c>
-      <c r="K214" s="5" t="s">
-        <v>2833</v>
-      </c>
-      <c r="L214" s="5" t="s">
-        <v>2834</v>
-      </c>
-      <c r="M214" s="5" t="s">
-        <v>2835</v>
-      </c>
-      <c r="N214" s="5" t="s">
-        <v>2836</v>
-      </c>
-      <c r="O214" s="5" t="s">
-        <v>2837</v>
-      </c>
-      <c r="P214" s="5" t="s">
-        <v>2838</v>
-      </c>
-      <c r="Q214" s="5" t="s">
-        <v>2839</v>
-      </c>
-      <c r="R214" s="5" t="s">
-        <v>2840</v>
-      </c>
-      <c r="S214" s="5" t="s">
-        <v>2841</v>
-      </c>
-      <c r="U214" s="5" t="s">
-        <v>2842</v>
-      </c>
-      <c r="V214" s="5" t="s">
-        <v>2843</v>
-      </c>
       <c r="Z214" s="5" t="s">
-        <v>2844</v>
+        <v>74</v>
       </c>
       <c r="AA214" s="4">
         <v>46313</v>
       </c>
-      <c r="AB214" s="4">
-        <v>46313</v>
-      </c>
-      <c r="AC214"/>
+      <c r="AB214" s="4"/>
+      <c r="AC214" t="str">
+        <f>IF(AND(E214&lt;&gt;"",COUNTIF($E$2:$E$794,E214)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
     </row>
     <row r="215" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A215" s="5" t="s">
-        <v>2845</v>
+        <v>2831</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>2076</v>
+        <v>57</v>
       </c>
       <c r="D215" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>2846</v>
+        <v>2832</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>2847</v>
+        <v>2833</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>2848</v>
+        <v>372</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>2849</v>
+        <v>2834</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>2850</v>
+        <v>896</v>
       </c>
       <c r="J215" s="5" t="s">
-        <v>2851</v>
+        <v>64</v>
       </c>
       <c r="K215" s="5" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="L215" s="5" t="s">
-        <v>2852</v>
+        <v>2835</v>
       </c>
       <c r="M215" s="5" t="s">
-        <v>2853</v>
+        <v>2836</v>
       </c>
       <c r="N215" s="5" t="s">
-        <v>2854</v>
+        <v>2837</v>
       </c>
       <c r="O215" s="5" t="s">
-        <v>2855</v>
+        <v>2838</v>
       </c>
       <c r="P215" s="5" t="s">
-        <v>2856</v>
+        <v>2839</v>
       </c>
       <c r="Q215" s="5" t="s">
-        <v>2857</v>
+        <v>2840</v>
       </c>
       <c r="R215" s="5" t="s">
-        <v>2858</v>
+        <v>2841</v>
       </c>
       <c r="S215" s="5" t="s">
-        <v>2859</v>
+        <v>2842</v>
       </c>
       <c r="U215" s="5" t="s">
-        <v>2860</v>
+        <v>2843</v>
       </c>
       <c r="V215" s="5" t="s">
-        <v>2861</v>
-      </c>
-      <c r="Z215" s="5" t="s">
-        <v>2862</v>
+        <v>2844</v>
       </c>
       <c r="AA215" s="4">
         <v>46313</v>
       </c>
-      <c r="AB215" s="4">
-        <v>46313</v>
-      </c>
-      <c r="AC215"/>
+      <c r="AB215" s="4"/>
+      <c r="AC215" t="str">
+        <f>IF(AND(E215&lt;&gt;"",COUNTIF($E$2:$E$794,E215)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
     </row>
     <row r="216" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A216" s="5" t="s">
-        <v>2863</v>
+        <v>2845</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>2076</v>
+        <v>57</v>
       </c>
       <c r="D216" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>2864</v>
+        <v>2846</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>2865</v>
+        <v>2847</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>703</v>
+        <v>372</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>2866</v>
+        <v>2848</v>
       </c>
       <c r="I216" s="5" t="s">
-        <v>2867</v>
+        <v>883</v>
       </c>
       <c r="J216" s="5" t="s">
-        <v>2868</v>
+        <v>2849</v>
       </c>
       <c r="K216" s="5" t="s">
-        <v>2869</v>
+        <v>113</v>
       </c>
       <c r="L216" s="5" t="s">
-        <v>2870</v>
+        <v>2850</v>
       </c>
       <c r="M216" s="5" t="s">
-        <v>2871</v>
+        <v>2851</v>
       </c>
       <c r="N216" s="5" t="s">
-        <v>2872</v>
+        <v>2852</v>
       </c>
       <c r="O216" s="5" t="s">
-        <v>2873</v>
+        <v>2853</v>
       </c>
       <c r="P216" s="5" t="s">
-        <v>2874</v>
+        <v>2854</v>
       </c>
       <c r="Q216" s="5" t="s">
-        <v>2875</v>
+        <v>2855</v>
       </c>
       <c r="R216" s="5" t="s">
-        <v>2876</v>
+        <v>2856</v>
       </c>
       <c r="S216" s="5" t="s">
-        <v>2877</v>
+        <v>2857</v>
       </c>
       <c r="U216" s="5" t="s">
-        <v>2878</v>
+        <v>2858</v>
       </c>
       <c r="V216" s="5" t="s">
-        <v>2879</v>
+        <v>2859</v>
       </c>
       <c r="Z216" s="5" t="s">
-        <v>2880</v>
+        <v>74</v>
       </c>
       <c r="AA216" s="4">
         <v>46313</v>
       </c>
-      <c r="AB216" s="4">
+      <c r="AB216" s="4"/>
+      <c r="AC216" t="str">
+        <f>IF(AND(E216&lt;&gt;"",COUNTIF($E$2:$E$794,E216)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A217" s="5" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E217" s="5" t="s">
+        <v>2861</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>2862</v>
+      </c>
+      <c r="G217" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H217" s="5" t="s">
+        <v>2863</v>
+      </c>
+      <c r="I217" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="J217" s="5" t="s">
+        <v>2864</v>
+      </c>
+      <c r="K217" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L217" s="5" t="s">
+        <v>2865</v>
+      </c>
+      <c r="M217" s="5" t="s">
+        <v>2866</v>
+      </c>
+      <c r="N217" s="5" t="s">
+        <v>2867</v>
+      </c>
+      <c r="O217" s="5" t="s">
+        <v>2868</v>
+      </c>
+      <c r="P217" s="5" t="s">
+        <v>2869</v>
+      </c>
+      <c r="Q217" s="5" t="s">
+        <v>2870</v>
+      </c>
+      <c r="R217" s="5" t="s">
+        <v>2871</v>
+      </c>
+      <c r="S217" s="5" t="s">
+        <v>2872</v>
+      </c>
+      <c r="U217" s="5" t="s">
+        <v>2873</v>
+      </c>
+      <c r="V217" s="5" t="s">
+        <v>2874</v>
+      </c>
+      <c r="Z217" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA217" s="4">
         <v>46313</v>
       </c>
-      <c r="AC216"/>
-    </row>
-    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA217" s="4"/>
       <c r="AB217" s="4"/>
       <c r="AC217" t="str">
-        <f>IF(AND(E217&lt;&gt;"",COUNTIF($E$2:$E$798,E217)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E217&lt;&gt;"",COUNTIF($E$2:$E$794,E217)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="218" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA218" s="4"/>
+      <c r="A218" s="5" t="s">
+        <v>2875</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E218" s="5" t="s">
+        <v>2876</v>
+      </c>
+      <c r="F218" s="5" t="s">
+        <v>2877</v>
+      </c>
+      <c r="G218" s="5" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H218" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="I218" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="J218" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K218" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L218" s="5" t="s">
+        <v>2878</v>
+      </c>
+      <c r="M218" s="5" t="s">
+        <v>2879</v>
+      </c>
+      <c r="N218" s="5" t="s">
+        <v>2880</v>
+      </c>
+      <c r="O218" s="5" t="s">
+        <v>2881</v>
+      </c>
+      <c r="P218" s="5" t="s">
+        <v>2882</v>
+      </c>
+      <c r="Q218" s="5" t="s">
+        <v>2883</v>
+      </c>
+      <c r="R218" s="5" t="s">
+        <v>2884</v>
+      </c>
+      <c r="S218" s="5" t="s">
+        <v>2885</v>
+      </c>
+      <c r="U218" s="5" t="s">
+        <v>2886</v>
+      </c>
+      <c r="V218" s="5" t="s">
+        <v>2887</v>
+      </c>
+      <c r="Z218" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA218" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB218" s="4"/>
       <c r="AC218" t="str">
-        <f>IF(AND(E218&lt;&gt;"",COUNTIF($E$2:$E$798,E218)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E218&lt;&gt;"",COUNTIF($E$2:$E$794,E218)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="219" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA219" s="4"/>
+      <c r="A219" s="5" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>2889</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>2890</v>
+      </c>
+      <c r="G219" s="5" t="s">
+        <v>3080</v>
+      </c>
+      <c r="H219" s="5" t="s">
+        <v>2891</v>
+      </c>
+      <c r="I219" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="J219" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K219" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L219" s="5" t="s">
+        <v>2892</v>
+      </c>
+      <c r="M219" s="5" t="s">
+        <v>2893</v>
+      </c>
+      <c r="N219" s="5" t="s">
+        <v>2894</v>
+      </c>
+      <c r="O219" s="5" t="s">
+        <v>2895</v>
+      </c>
+      <c r="P219" s="5" t="s">
+        <v>2896</v>
+      </c>
+      <c r="Q219" s="5" t="s">
+        <v>2897</v>
+      </c>
+      <c r="R219" s="5" t="s">
+        <v>2898</v>
+      </c>
+      <c r="S219" s="5" t="s">
+        <v>2899</v>
+      </c>
+      <c r="U219" s="5" t="s">
+        <v>2900</v>
+      </c>
+      <c r="V219" s="5" t="s">
+        <v>2901</v>
+      </c>
+      <c r="Z219" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA219" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB219" s="4"/>
       <c r="AC219" t="str">
-        <f>IF(AND(E219&lt;&gt;"",COUNTIF($E$2:$E$798,E219)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E219&lt;&gt;"",COUNTIF($E$2:$E$794,E219)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="220" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA220" s="4"/>
+      <c r="A220" s="5" t="s">
+        <v>2902</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D220" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>2903</v>
+      </c>
+      <c r="F220" s="5" t="s">
+        <v>2904</v>
+      </c>
+      <c r="G220" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H220" s="5" t="s">
+        <v>2905</v>
+      </c>
+      <c r="I220" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="J220" s="5" t="s">
+        <v>2906</v>
+      </c>
+      <c r="K220" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L220" s="5" t="s">
+        <v>2907</v>
+      </c>
+      <c r="M220" s="5" t="s">
+        <v>2908</v>
+      </c>
+      <c r="N220" s="5" t="s">
+        <v>2909</v>
+      </c>
+      <c r="O220" s="5" t="s">
+        <v>2910</v>
+      </c>
+      <c r="P220" s="5" t="s">
+        <v>2911</v>
+      </c>
+      <c r="Q220" s="5" t="s">
+        <v>2912</v>
+      </c>
+      <c r="R220" s="5" t="s">
+        <v>2913</v>
+      </c>
+      <c r="S220" s="5" t="s">
+        <v>2914</v>
+      </c>
+      <c r="U220" s="5" t="s">
+        <v>2915</v>
+      </c>
+      <c r="V220" s="5" t="s">
+        <v>2916</v>
+      </c>
+      <c r="Z220" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA220" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB220" s="4"/>
       <c r="AC220" t="str">
-        <f>IF(AND(E220&lt;&gt;"",COUNTIF($E$2:$E$798,E220)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E220&lt;&gt;"",COUNTIF($E$2:$E$794,E220)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="221" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA221" s="4"/>
+      <c r="A221" s="5" t="s">
+        <v>2917</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>2918</v>
+      </c>
+      <c r="F221" s="5" t="s">
+        <v>2919</v>
+      </c>
+      <c r="G221" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H221" s="5" t="s">
+        <v>2920</v>
+      </c>
+      <c r="I221" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="J221" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K221" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L221" s="5" t="s">
+        <v>2921</v>
+      </c>
+      <c r="M221" s="5" t="s">
+        <v>2922</v>
+      </c>
+      <c r="N221" s="5" t="s">
+        <v>2923</v>
+      </c>
+      <c r="O221" s="5" t="s">
+        <v>2924</v>
+      </c>
+      <c r="P221" s="5" t="s">
+        <v>2925</v>
+      </c>
+      <c r="Q221" s="5" t="s">
+        <v>2926</v>
+      </c>
+      <c r="R221" s="5" t="s">
+        <v>2927</v>
+      </c>
+      <c r="S221" s="5" t="s">
+        <v>2928</v>
+      </c>
+      <c r="U221" s="5" t="s">
+        <v>2929</v>
+      </c>
+      <c r="V221" s="5" t="s">
+        <v>2930</v>
+      </c>
+      <c r="AA221" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB221" s="4"/>
       <c r="AC221" t="str">
-        <f>IF(AND(E221&lt;&gt;"",COUNTIF($E$2:$E$798,E221)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E221&lt;&gt;"",COUNTIF($E$2:$E$794,E221)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="222" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA222" s="4"/>
+      <c r="A222" s="5" t="s">
+        <v>2931</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>2932</v>
+      </c>
+      <c r="F222" s="5" t="s">
+        <v>2933</v>
+      </c>
+      <c r="G222" s="5" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H222" s="5" t="s">
+        <v>2934</v>
+      </c>
+      <c r="I222" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="J222" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K222" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L222" s="5" t="s">
+        <v>2935</v>
+      </c>
+      <c r="M222" s="5" t="s">
+        <v>2936</v>
+      </c>
+      <c r="N222" s="5" t="s">
+        <v>2937</v>
+      </c>
+      <c r="O222" s="5" t="s">
+        <v>2938</v>
+      </c>
+      <c r="P222" s="5" t="s">
+        <v>2939</v>
+      </c>
+      <c r="Q222" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="R222" s="5" t="s">
+        <v>2941</v>
+      </c>
+      <c r="S222" s="5" t="s">
+        <v>2942</v>
+      </c>
+      <c r="U222" s="5" t="s">
+        <v>2943</v>
+      </c>
+      <c r="V222" s="5" t="s">
+        <v>2944</v>
+      </c>
+      <c r="AA222" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB222" s="4"/>
       <c r="AC222" t="str">
-        <f>IF(AND(E222&lt;&gt;"",COUNTIF($E$2:$E$798,E222)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E222&lt;&gt;"",COUNTIF($E$2:$E$794,E222)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="223" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA223" s="4"/>
+      <c r="A223" s="5" t="s">
+        <v>2945</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D223" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>2946</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>2947</v>
+      </c>
+      <c r="G223" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H223" s="5" t="s">
+        <v>2948</v>
+      </c>
+      <c r="I223" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="J223" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K223" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L223" s="5" t="s">
+        <v>2949</v>
+      </c>
+      <c r="M223" s="5" t="s">
+        <v>2950</v>
+      </c>
+      <c r="N223" s="5" t="s">
+        <v>2951</v>
+      </c>
+      <c r="O223" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="P223" s="5" t="s">
+        <v>2953</v>
+      </c>
+      <c r="Q223" s="5" t="s">
+        <v>2954</v>
+      </c>
+      <c r="R223" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="S223" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="U223" s="5" t="s">
+        <v>2957</v>
+      </c>
+      <c r="V223" s="5" t="s">
+        <v>2958</v>
+      </c>
+      <c r="AA223" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB223" s="4"/>
       <c r="AC223" t="str">
-        <f>IF(AND(E223&lt;&gt;"",COUNTIF($E$2:$E$798,E223)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E223&lt;&gt;"",COUNTIF($E$2:$E$794,E223)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
     <row r="224" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AA224" s="4"/>
-      <c r="AB224" s="4"/>
-      <c r="AC224" t="str">
-        <f>IF(AND(E224&lt;&gt;"",COUNTIF($E$2:$E$798,E224)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA225" s="4"/>
-      <c r="AB225" s="4"/>
-      <c r="AC225" t="str">
-        <f>IF(AND(E225&lt;&gt;"",COUNTIF($E$2:$E$798,E225)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA226" s="4"/>
-      <c r="AB226" s="4"/>
-      <c r="AC226" t="str">
-        <f>IF(AND(E226&lt;&gt;"",COUNTIF($E$2:$E$798,E226)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA227" s="4"/>
-      <c r="AB227" s="4"/>
-      <c r="AC227" t="str">
-        <f>IF(AND(E227&lt;&gt;"",COUNTIF($E$2:$E$798,E227)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA228" s="4"/>
-      <c r="AB228" s="4"/>
-      <c r="AC228" t="str">
-        <f>IF(AND(E228&lt;&gt;"",COUNTIF($E$2:$E$798,E228)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA229" s="4"/>
-      <c r="AB229" s="4"/>
-      <c r="AC229" t="str">
-        <f>IF(AND(E229&lt;&gt;"",COUNTIF($E$2:$E$798,E229)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA230" s="4"/>
-      <c r="AB230" s="4"/>
-      <c r="AC230" t="str">
-        <f>IF(AND(E230&lt;&gt;"",COUNTIF($E$2:$E$798,E230)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA231" s="4"/>
+      <c r="A224" s="5" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E224" s="5" t="s">
+        <v>2967</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>2968</v>
+      </c>
+      <c r="G224" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H224" s="5" t="s">
+        <v>2969</v>
+      </c>
+      <c r="I224" s="5" t="s">
+        <v>2970</v>
+      </c>
+      <c r="J224" s="5" t="s">
+        <v>2971</v>
+      </c>
+      <c r="K224" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L224" s="5" t="s">
+        <v>2972</v>
+      </c>
+      <c r="M224" s="5" t="s">
+        <v>2973</v>
+      </c>
+      <c r="N224" s="5" t="s">
+        <v>2974</v>
+      </c>
+      <c r="O224" s="5" t="s">
+        <v>2975</v>
+      </c>
+      <c r="P224" s="5" t="s">
+        <v>2976</v>
+      </c>
+      <c r="Q224" s="5" t="s">
+        <v>2977</v>
+      </c>
+      <c r="R224" s="5" t="s">
+        <v>2978</v>
+      </c>
+      <c r="S224" s="5" t="s">
+        <v>2979</v>
+      </c>
+      <c r="U224" s="5" t="s">
+        <v>2980</v>
+      </c>
+      <c r="V224" s="5" t="s">
+        <v>2981</v>
+      </c>
+      <c r="Z224" s="5" t="s">
+        <v>2982</v>
+      </c>
+      <c r="AA224" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB224" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC224"/>
+    </row>
+    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A225" s="5" t="s">
+        <v>2983</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D225" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>2984</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>2985</v>
+      </c>
+      <c r="G225" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H225" s="5" t="s">
+        <v>2969</v>
+      </c>
+      <c r="I225" s="5" t="s">
+        <v>2750</v>
+      </c>
+      <c r="J225" s="5" t="s">
+        <v>2986</v>
+      </c>
+      <c r="K225" s="5" t="s">
+        <v>2987</v>
+      </c>
+      <c r="L225" s="5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="M225" s="5" t="s">
+        <v>2989</v>
+      </c>
+      <c r="N225" s="5" t="s">
+        <v>2990</v>
+      </c>
+      <c r="O225" s="5" t="s">
+        <v>2991</v>
+      </c>
+      <c r="P225" s="5" t="s">
+        <v>2992</v>
+      </c>
+      <c r="Q225" s="5" t="s">
+        <v>2993</v>
+      </c>
+      <c r="R225" s="5" t="s">
+        <v>2994</v>
+      </c>
+      <c r="S225" s="5" t="s">
+        <v>2995</v>
+      </c>
+      <c r="U225" s="5" t="s">
+        <v>2996</v>
+      </c>
+      <c r="V225" s="5" t="s">
+        <v>2997</v>
+      </c>
+      <c r="Z225" s="5" t="s">
+        <v>2998</v>
+      </c>
+      <c r="AA225" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB225" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC225"/>
+    </row>
+    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A226" s="5" t="s">
+        <v>2999</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>3000</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>2985</v>
+      </c>
+      <c r="G226" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H226" s="5" t="s">
+        <v>2969</v>
+      </c>
+      <c r="I226" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J226" s="5" t="s">
+        <v>3001</v>
+      </c>
+      <c r="K226" s="5" t="s">
+        <v>3002</v>
+      </c>
+      <c r="L226" s="5" t="s">
+        <v>3003</v>
+      </c>
+      <c r="M226" s="5" t="s">
+        <v>3004</v>
+      </c>
+      <c r="N226" s="5" t="s">
+        <v>3005</v>
+      </c>
+      <c r="O226" s="5" t="s">
+        <v>3006</v>
+      </c>
+      <c r="P226" s="5" t="s">
+        <v>3007</v>
+      </c>
+      <c r="Q226" s="5" t="s">
+        <v>3008</v>
+      </c>
+      <c r="R226" s="5" t="s">
+        <v>3009</v>
+      </c>
+      <c r="S226" s="5" t="s">
+        <v>3010</v>
+      </c>
+      <c r="U226" s="5" t="s">
+        <v>3011</v>
+      </c>
+      <c r="V226" s="5" t="s">
+        <v>2997</v>
+      </c>
+      <c r="Z226" s="5" t="s">
+        <v>3012</v>
+      </c>
+      <c r="AA226" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB226" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC226"/>
+    </row>
+    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A227" s="5" t="s">
+        <v>3013</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>3014</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>3015</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>3016</v>
+      </c>
+      <c r="G227" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H227" s="5" t="s">
+        <v>2969</v>
+      </c>
+      <c r="I227" s="5" t="s">
+        <v>3017</v>
+      </c>
+      <c r="J227" s="5" t="s">
+        <v>3018</v>
+      </c>
+      <c r="K227" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L227" s="5" t="s">
+        <v>3019</v>
+      </c>
+      <c r="M227" s="5" t="s">
+        <v>3020</v>
+      </c>
+      <c r="N227" s="5" t="s">
+        <v>3021</v>
+      </c>
+      <c r="O227" s="5" t="s">
+        <v>3022</v>
+      </c>
+      <c r="P227" s="5" t="s">
+        <v>3023</v>
+      </c>
+      <c r="Q227" s="5" t="s">
+        <v>3024</v>
+      </c>
+      <c r="R227" s="5" t="s">
+        <v>3025</v>
+      </c>
+      <c r="S227" s="5" t="s">
+        <v>3026</v>
+      </c>
+      <c r="U227" s="5" t="s">
+        <v>3027</v>
+      </c>
+      <c r="V227" s="5" t="s">
+        <v>3028</v>
+      </c>
+      <c r="Z227" s="5" t="s">
+        <v>3029</v>
+      </c>
+      <c r="AA227" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB227" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC227"/>
+    </row>
+    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A228" s="5" t="s">
+        <v>3030</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D228" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E228" s="5" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F228" s="5" t="s">
+        <v>3032</v>
+      </c>
+      <c r="G228" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H228" s="5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I228" s="5" t="s">
+        <v>3033</v>
+      </c>
+      <c r="J228" s="5" t="s">
+        <v>3034</v>
+      </c>
+      <c r="K228" s="5" t="s">
+        <v>3035</v>
+      </c>
+      <c r="L228" s="5" t="s">
+        <v>3036</v>
+      </c>
+      <c r="M228" s="5" t="s">
+        <v>3037</v>
+      </c>
+      <c r="N228" s="5" t="s">
+        <v>3038</v>
+      </c>
+      <c r="O228" s="5" t="s">
+        <v>3039</v>
+      </c>
+      <c r="P228" s="5" t="s">
+        <v>3040</v>
+      </c>
+      <c r="Q228" s="5" t="s">
+        <v>3041</v>
+      </c>
+      <c r="R228" s="5" t="s">
+        <v>3042</v>
+      </c>
+      <c r="S228" s="5" t="s">
+        <v>3043</v>
+      </c>
+      <c r="U228" s="5" t="s">
+        <v>3044</v>
+      </c>
+      <c r="V228" s="5" t="s">
+        <v>3045</v>
+      </c>
+      <c r="Z228" s="5" t="s">
+        <v>3046</v>
+      </c>
+      <c r="AA228" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB228" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC228"/>
+    </row>
+    <row r="229" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A229" s="5" t="s">
+        <v>3047</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D229" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E229" s="5" t="s">
+        <v>3048</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>3049</v>
+      </c>
+      <c r="G229" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H229" s="5" t="s">
+        <v>1646</v>
+      </c>
+      <c r="I229" s="5" t="s">
+        <v>3050</v>
+      </c>
+      <c r="J229" s="5" t="s">
+        <v>3051</v>
+      </c>
+      <c r="K229" s="5" t="s">
+        <v>3052</v>
+      </c>
+      <c r="L229" s="5" t="s">
+        <v>3053</v>
+      </c>
+      <c r="M229" s="5" t="s">
+        <v>3054</v>
+      </c>
+      <c r="N229" s="5" t="s">
+        <v>3055</v>
+      </c>
+      <c r="O229" s="5" t="s">
+        <v>3056</v>
+      </c>
+      <c r="P229" s="5" t="s">
+        <v>3057</v>
+      </c>
+      <c r="Q229" s="5" t="s">
+        <v>3058</v>
+      </c>
+      <c r="R229" s="5" t="s">
+        <v>3059</v>
+      </c>
+      <c r="S229" s="5" t="s">
+        <v>3060</v>
+      </c>
+      <c r="U229" s="5" t="s">
+        <v>3061</v>
+      </c>
+      <c r="V229" s="5" t="s">
+        <v>3062</v>
+      </c>
+      <c r="Z229" s="5" t="s">
+        <v>3063</v>
+      </c>
+      <c r="AA229" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB229" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC229"/>
+    </row>
+    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A230" s="5" t="s">
+        <v>3064</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D230" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E230" s="5" t="s">
+        <v>3065</v>
+      </c>
+      <c r="F230" s="5" t="s">
+        <v>3066</v>
+      </c>
+      <c r="G230" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H230" s="5" t="s">
+        <v>1646</v>
+      </c>
+      <c r="I230" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J230" s="5" t="s">
+        <v>3067</v>
+      </c>
+      <c r="K230" s="5" t="s">
+        <v>3068</v>
+      </c>
+      <c r="L230" s="5" t="s">
+        <v>3069</v>
+      </c>
+      <c r="M230" s="5" t="s">
+        <v>3070</v>
+      </c>
+      <c r="N230" s="5" t="s">
+        <v>3071</v>
+      </c>
+      <c r="O230" s="5" t="s">
+        <v>3072</v>
+      </c>
+      <c r="P230" s="5" t="s">
+        <v>3073</v>
+      </c>
+      <c r="Q230" s="5" t="s">
+        <v>3074</v>
+      </c>
+      <c r="R230" s="5" t="s">
+        <v>3075</v>
+      </c>
+      <c r="S230" s="5" t="s">
+        <v>3076</v>
+      </c>
+      <c r="U230" s="5" t="s">
+        <v>3077</v>
+      </c>
+      <c r="V230" s="5" t="s">
+        <v>3078</v>
+      </c>
+      <c r="Z230" s="5" t="s">
+        <v>3079</v>
+      </c>
+      <c r="AA230" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AB230" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AC230"/>
+    </row>
+    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A231" s="5" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>3082</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>3083</v>
+      </c>
+      <c r="G231" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H231" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I231" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J231" s="5" t="s">
+        <v>3084</v>
+      </c>
+      <c r="K231" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L231" s="5" t="s">
+        <v>3085</v>
+      </c>
+      <c r="M231" s="5" t="s">
+        <v>3086</v>
+      </c>
+      <c r="N231" s="5" t="s">
+        <v>3087</v>
+      </c>
+      <c r="O231" s="5" t="s">
+        <v>3088</v>
+      </c>
+      <c r="P231" s="5" t="s">
+        <v>3089</v>
+      </c>
+      <c r="Q231" s="5" t="s">
+        <v>3090</v>
+      </c>
+      <c r="R231" s="5" t="s">
+        <v>3091</v>
+      </c>
+      <c r="S231" s="5" t="s">
+        <v>3092</v>
+      </c>
+      <c r="U231" s="5" t="s">
+        <v>3093</v>
+      </c>
+      <c r="V231" s="5" t="s">
+        <v>3094</v>
+      </c>
+      <c r="Z231" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA231" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB231" s="4"/>
       <c r="AC231" t="str">
-        <f>IF(AND(E231&lt;&gt;"",COUNTIF($E$2:$E$798,E231)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA232" s="4"/>
+        <f>IF(AND(E231&lt;&gt;"",COUNTIF($E$2:$E$794,E231)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A232" s="5" t="s">
+        <v>3095</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E232" s="5" t="s">
+        <v>3096</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>3097</v>
+      </c>
+      <c r="G232" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H232" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I232" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J232" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K232" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L232" s="5" t="s">
+        <v>3098</v>
+      </c>
+      <c r="M232" s="5" t="s">
+        <v>3099</v>
+      </c>
+      <c r="N232" s="5" t="s">
+        <v>3100</v>
+      </c>
+      <c r="O232" s="5" t="s">
+        <v>3101</v>
+      </c>
+      <c r="P232" s="5" t="s">
+        <v>3102</v>
+      </c>
+      <c r="Q232" s="5" t="s">
+        <v>3103</v>
+      </c>
+      <c r="R232" s="5" t="s">
+        <v>3104</v>
+      </c>
+      <c r="S232" s="5" t="s">
+        <v>3105</v>
+      </c>
+      <c r="U232" s="5" t="s">
+        <v>3106</v>
+      </c>
+      <c r="V232" s="5" t="s">
+        <v>3107</v>
+      </c>
+      <c r="Z232" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA232" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB232" s="4"/>
       <c r="AC232" t="str">
-        <f>IF(AND(E232&lt;&gt;"",COUNTIF($E$2:$E$798,E232)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA233" s="4"/>
+        <f>IF(AND(E232&lt;&gt;"",COUNTIF($E$2:$E$794,E232)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A233" s="5" t="s">
+        <v>3108</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E233" s="5" t="s">
+        <v>3109</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>3110</v>
+      </c>
+      <c r="G233" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H233" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I233" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J233" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K233" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L233" s="5" t="s">
+        <v>3111</v>
+      </c>
+      <c r="M233" s="5" t="s">
+        <v>3112</v>
+      </c>
+      <c r="N233" s="5" t="s">
+        <v>3113</v>
+      </c>
+      <c r="O233" s="5" t="s">
+        <v>3114</v>
+      </c>
+      <c r="P233" s="5" t="s">
+        <v>3115</v>
+      </c>
+      <c r="Q233" s="5" t="s">
+        <v>3116</v>
+      </c>
+      <c r="R233" s="5" t="s">
+        <v>3117</v>
+      </c>
+      <c r="S233" s="5" t="s">
+        <v>3118</v>
+      </c>
+      <c r="U233" s="5" t="s">
+        <v>3119</v>
+      </c>
+      <c r="V233" s="5" t="s">
+        <v>3120</v>
+      </c>
+      <c r="Z233" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA233" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB233" s="4"/>
       <c r="AC233" t="str">
-        <f>IF(AND(E233&lt;&gt;"",COUNTIF($E$2:$E$798,E233)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA234" s="4"/>
+        <f>IF(AND(E233&lt;&gt;"",COUNTIF($E$2:$E$794,E233)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A234" s="5" t="s">
+        <v>3121</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E234" s="5" t="s">
+        <v>3122</v>
+      </c>
+      <c r="F234" s="5" t="s">
+        <v>3123</v>
+      </c>
+      <c r="G234" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H234" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I234" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J234" s="5" t="s">
+        <v>3124</v>
+      </c>
+      <c r="K234" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L234" s="5" t="s">
+        <v>3125</v>
+      </c>
+      <c r="M234" s="5" t="s">
+        <v>3126</v>
+      </c>
+      <c r="N234" s="5" t="s">
+        <v>3127</v>
+      </c>
+      <c r="O234" s="5" t="s">
+        <v>3128</v>
+      </c>
+      <c r="P234" s="5" t="s">
+        <v>3129</v>
+      </c>
+      <c r="Q234" s="5" t="s">
+        <v>3130</v>
+      </c>
+      <c r="R234" s="5" t="s">
+        <v>3131</v>
+      </c>
+      <c r="S234" s="5" t="s">
+        <v>3132</v>
+      </c>
+      <c r="U234" s="5" t="s">
+        <v>3133</v>
+      </c>
+      <c r="V234" s="5" t="s">
+        <v>3134</v>
+      </c>
+      <c r="Z234" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA234" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB234" s="4"/>
       <c r="AC234" t="str">
-        <f>IF(AND(E234&lt;&gt;"",COUNTIF($E$2:$E$798,E234)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA235" s="4"/>
+        <f>IF(AND(E234&lt;&gt;"",COUNTIF($E$2:$E$794,E234)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A235" s="5" t="s">
+        <v>3135</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D235" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E235" s="5" t="s">
+        <v>3136</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>3137</v>
+      </c>
+      <c r="G235" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H235" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I235" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J235" s="5" t="s">
+        <v>3084</v>
+      </c>
+      <c r="K235" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L235" s="5" t="s">
+        <v>3138</v>
+      </c>
+      <c r="M235" s="5" t="s">
+        <v>3139</v>
+      </c>
+      <c r="N235" s="5" t="s">
+        <v>3140</v>
+      </c>
+      <c r="O235" s="5" t="s">
+        <v>3141</v>
+      </c>
+      <c r="P235" s="5" t="s">
+        <v>3142</v>
+      </c>
+      <c r="Q235" s="5" t="s">
+        <v>3143</v>
+      </c>
+      <c r="R235" s="5" t="s">
+        <v>3144</v>
+      </c>
+      <c r="S235" s="5" t="s">
+        <v>3145</v>
+      </c>
+      <c r="U235" s="5" t="s">
+        <v>3146</v>
+      </c>
+      <c r="V235" s="5" t="s">
+        <v>3147</v>
+      </c>
+      <c r="Z235" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA235" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB235" s="4"/>
       <c r="AC235" t="str">
-        <f>IF(AND(E235&lt;&gt;"",COUNTIF($E$2:$E$798,E235)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA236" s="4"/>
+        <f>IF(AND(E235&lt;&gt;"",COUNTIF($E$2:$E$794,E235)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A236" s="5" t="s">
+        <v>3148</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D236" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E236" s="5" t="s">
+        <v>3149</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>3150</v>
+      </c>
+      <c r="G236" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H236" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I236" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J236" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K236" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L236" s="5" t="s">
+        <v>3151</v>
+      </c>
+      <c r="M236" s="5" t="s">
+        <v>3152</v>
+      </c>
+      <c r="N236" s="5" t="s">
+        <v>3153</v>
+      </c>
+      <c r="O236" s="5" t="s">
+        <v>3154</v>
+      </c>
+      <c r="P236" s="5" t="s">
+        <v>3155</v>
+      </c>
+      <c r="Q236" s="5" t="s">
+        <v>3156</v>
+      </c>
+      <c r="R236" s="5" t="s">
+        <v>3157</v>
+      </c>
+      <c r="S236" s="5" t="s">
+        <v>3158</v>
+      </c>
+      <c r="U236" s="5" t="s">
+        <v>3159</v>
+      </c>
+      <c r="V236" s="5" t="s">
+        <v>3160</v>
+      </c>
+      <c r="AA236" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB236" s="4"/>
       <c r="AC236" t="str">
-        <f>IF(AND(E236&lt;&gt;"",COUNTIF($E$2:$E$798,E236)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA237" s="4"/>
+        <f>IF(AND(E236&lt;&gt;"",COUNTIF($E$2:$E$794,E236)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A237" s="5" t="s">
+        <v>3161</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E237" s="5" t="s">
+        <v>3162</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>3163</v>
+      </c>
+      <c r="G237" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H237" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I237" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J237" s="5" t="s">
+        <v>3164</v>
+      </c>
+      <c r="K237" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L237" s="5" t="s">
+        <v>3165</v>
+      </c>
+      <c r="M237" s="5" t="s">
+        <v>3166</v>
+      </c>
+      <c r="N237" s="5" t="s">
+        <v>3167</v>
+      </c>
+      <c r="O237" s="5" t="s">
+        <v>3168</v>
+      </c>
+      <c r="P237" s="5" t="s">
+        <v>3169</v>
+      </c>
+      <c r="Q237" s="5" t="s">
+        <v>3170</v>
+      </c>
+      <c r="R237" s="5" t="s">
+        <v>3171</v>
+      </c>
+      <c r="S237" s="5" t="s">
+        <v>3172</v>
+      </c>
+      <c r="U237" s="5" t="s">
+        <v>3173</v>
+      </c>
+      <c r="V237" s="5" t="s">
+        <v>3174</v>
+      </c>
+      <c r="Z237" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA237" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB237" s="4"/>
       <c r="AC237" t="str">
-        <f>IF(AND(E237&lt;&gt;"",COUNTIF($E$2:$E$798,E237)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA238" s="4"/>
+        <f>IF(AND(E237&lt;&gt;"",COUNTIF($E$2:$E$794,E237)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A238" s="5" t="s">
+        <v>3175</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D238" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E238" s="5" t="s">
+        <v>3176</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>3177</v>
+      </c>
+      <c r="G238" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H238" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I238" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J238" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K238" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L238" s="5" t="s">
+        <v>3178</v>
+      </c>
+      <c r="M238" s="5" t="s">
+        <v>3179</v>
+      </c>
+      <c r="N238" s="5" t="s">
+        <v>3180</v>
+      </c>
+      <c r="O238" s="5" t="s">
+        <v>3181</v>
+      </c>
+      <c r="P238" s="5" t="s">
+        <v>3182</v>
+      </c>
+      <c r="Q238" s="5" t="s">
+        <v>3183</v>
+      </c>
+      <c r="R238" s="5" t="s">
+        <v>3184</v>
+      </c>
+      <c r="S238" s="5" t="s">
+        <v>3185</v>
+      </c>
+      <c r="U238" s="5" t="s">
+        <v>3186</v>
+      </c>
+      <c r="V238" s="5" t="s">
+        <v>3187</v>
+      </c>
+      <c r="AA238" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB238" s="4"/>
       <c r="AC238" t="str">
-        <f>IF(AND(E238&lt;&gt;"",COUNTIF($E$2:$E$798,E238)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA239" s="4"/>
+        <f>IF(AND(E238&lt;&gt;"",COUNTIF($E$2:$E$794,E238)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A239" s="5" t="s">
+        <v>3188</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E239" s="5" t="s">
+        <v>3189</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>3190</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H239" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I239" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J239" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K239" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L239" s="5" t="s">
+        <v>3191</v>
+      </c>
+      <c r="M239" s="5" t="s">
+        <v>3192</v>
+      </c>
+      <c r="N239" s="5" t="s">
+        <v>3193</v>
+      </c>
+      <c r="O239" s="5" t="s">
+        <v>3194</v>
+      </c>
+      <c r="P239" s="5" t="s">
+        <v>3195</v>
+      </c>
+      <c r="Q239" s="5" t="s">
+        <v>3196</v>
+      </c>
+      <c r="R239" s="5" t="s">
+        <v>3197</v>
+      </c>
+      <c r="S239" s="5" t="s">
+        <v>3198</v>
+      </c>
+      <c r="U239" s="5" t="s">
+        <v>3199</v>
+      </c>
+      <c r="V239" s="5" t="s">
+        <v>3200</v>
+      </c>
+      <c r="AA239" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB239" s="4"/>
       <c r="AC239" t="str">
-        <f>IF(AND(E239&lt;&gt;"",COUNTIF($E$2:$E$798,E239)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA240" s="4"/>
+        <f>IF(AND(E239&lt;&gt;"",COUNTIF($E$2:$E$794,E239)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A240" s="5" t="s">
+        <v>3201</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E240" s="5" t="s">
+        <v>3202</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>3203</v>
+      </c>
+      <c r="G240" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H240" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I240" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J240" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K240" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L240" s="5" t="s">
+        <v>3204</v>
+      </c>
+      <c r="M240" s="5" t="s">
+        <v>3205</v>
+      </c>
+      <c r="N240" s="5" t="s">
+        <v>3206</v>
+      </c>
+      <c r="O240" s="5" t="s">
+        <v>3207</v>
+      </c>
+      <c r="P240" s="5" t="s">
+        <v>3208</v>
+      </c>
+      <c r="Q240" s="5" t="s">
+        <v>3209</v>
+      </c>
+      <c r="R240" s="5" t="s">
+        <v>3210</v>
+      </c>
+      <c r="S240" s="5" t="s">
+        <v>3211</v>
+      </c>
+      <c r="U240" s="5" t="s">
+        <v>3212</v>
+      </c>
+      <c r="V240" s="5" t="s">
+        <v>3213</v>
+      </c>
+      <c r="AA240" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB240" s="4"/>
       <c r="AC240" t="str">
-        <f>IF(AND(E240&lt;&gt;"",COUNTIF($E$2:$E$798,E240)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA241" s="4"/>
+        <f>IF(AND(E240&lt;&gt;"",COUNTIF($E$2:$E$794,E240)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A241" s="5" t="s">
+        <v>3214</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D241" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E241" s="5" t="s">
+        <v>3215</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>3216</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H241" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I241" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="J241" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K241" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L241" s="5" t="s">
+        <v>3217</v>
+      </c>
+      <c r="M241" s="5" t="s">
+        <v>3218</v>
+      </c>
+      <c r="N241" s="5" t="s">
+        <v>3219</v>
+      </c>
+      <c r="O241" s="5" t="s">
+        <v>3220</v>
+      </c>
+      <c r="P241" s="5" t="s">
+        <v>3221</v>
+      </c>
+      <c r="Q241" s="5" t="s">
+        <v>3222</v>
+      </c>
+      <c r="R241" s="5" t="s">
+        <v>3223</v>
+      </c>
+      <c r="S241" s="5" t="s">
+        <v>3224</v>
+      </c>
+      <c r="U241" s="5" t="s">
+        <v>3225</v>
+      </c>
+      <c r="V241" s="5" t="s">
+        <v>3226</v>
+      </c>
+      <c r="AA241" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB241" s="4"/>
       <c r="AC241" t="str">
-        <f>IF(AND(E241&lt;&gt;"",COUNTIF($E$2:$E$798,E241)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA242" s="4"/>
+        <f>IF(AND(E241&lt;&gt;"",COUNTIF($E$2:$E$794,E241)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A242" s="5" t="s">
+        <v>3227</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D242" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E242" s="5" t="s">
+        <v>3228</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>3229</v>
+      </c>
+      <c r="G242" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H242" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I242" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="J242" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K242" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L242" s="5" t="s">
+        <v>3230</v>
+      </c>
+      <c r="M242" s="5" t="s">
+        <v>3231</v>
+      </c>
+      <c r="N242" s="5" t="s">
+        <v>3232</v>
+      </c>
+      <c r="O242" s="5" t="s">
+        <v>3233</v>
+      </c>
+      <c r="P242" s="5" t="s">
+        <v>3234</v>
+      </c>
+      <c r="Q242" s="5" t="s">
+        <v>3235</v>
+      </c>
+      <c r="R242" s="5" t="s">
+        <v>3236</v>
+      </c>
+      <c r="S242" s="5" t="s">
+        <v>3237</v>
+      </c>
+      <c r="U242" s="5" t="s">
+        <v>3238</v>
+      </c>
+      <c r="V242" s="5" t="s">
+        <v>3239</v>
+      </c>
+      <c r="Z242" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA242" s="4">
+        <v>46313</v>
+      </c>
       <c r="AB242" s="4"/>
       <c r="AC242" t="str">
-        <f>IF(AND(E242&lt;&gt;"",COUNTIF($E$2:$E$798,E242)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E242&lt;&gt;"",COUNTIF($E$2:$E$794,E242)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA243" s="4"/>
       <c r="AB243" s="4"/>
       <c r="AC243" t="str">
-        <f>IF(AND(E243&lt;&gt;"",COUNTIF($E$2:$E$798,E243)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E243&lt;&gt;"",COUNTIF($E$2:$E$794,E243)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA244" s="4"/>
       <c r="AB244" s="4"/>
       <c r="AC244" t="str">
-        <f>IF(AND(E244&lt;&gt;"",COUNTIF($E$2:$E$798,E244)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E244&lt;&gt;"",COUNTIF($E$2:$E$794,E244)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA245" s="4"/>
       <c r="AB245" s="4"/>
       <c r="AC245" t="str">
-        <f>IF(AND(E245&lt;&gt;"",COUNTIF($E$2:$E$798,E245)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E245&lt;&gt;"",COUNTIF($E$2:$E$794,E245)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA246" s="4"/>
       <c r="AB246" s="4"/>
       <c r="AC246" t="str">
-        <f>IF(AND(E246&lt;&gt;"",COUNTIF($E$2:$E$798,E246)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E246&lt;&gt;"",COUNTIF($E$2:$E$794,E246)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA247" s="4"/>
       <c r="AB247" s="4"/>
       <c r="AC247" t="str">
-        <f>IF(AND(E247&lt;&gt;"",COUNTIF($E$2:$E$798,E247)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E247&lt;&gt;"",COUNTIF($E$2:$E$794,E247)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA248" s="4"/>
       <c r="AB248" s="4"/>
       <c r="AC248" t="str">
-        <f>IF(AND(E248&lt;&gt;"",COUNTIF($E$2:$E$798,E248)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E248&lt;&gt;"",COUNTIF($E$2:$E$794,E248)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA249" s="4"/>
       <c r="AB249" s="4"/>
       <c r="AC249" t="str">
-        <f>IF(AND(E249&lt;&gt;"",COUNTIF($E$2:$E$798,E249)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E249&lt;&gt;"",COUNTIF($E$2:$E$794,E249)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA250" s="4"/>
       <c r="AB250" s="4"/>
       <c r="AC250" t="str">
-        <f>IF(AND(E250&lt;&gt;"",COUNTIF($E$2:$E$798,E250)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E250&lt;&gt;"",COUNTIF($E$2:$E$794,E250)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA251" s="4"/>
       <c r="AB251" s="4"/>
       <c r="AC251" t="str">
-        <f>IF(AND(E251&lt;&gt;"",COUNTIF($E$2:$E$798,E251)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E251&lt;&gt;"",COUNTIF($E$2:$E$794,E251)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA252" s="4"/>
       <c r="AB252" s="4"/>
       <c r="AC252" t="str">
-        <f>IF(AND(E252&lt;&gt;"",COUNTIF($E$2:$E$798,E252)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E252&lt;&gt;"",COUNTIF($E$2:$E$794,E252)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA253" s="4"/>
       <c r="AB253" s="4"/>
       <c r="AC253" t="str">
-        <f>IF(AND(E253&lt;&gt;"",COUNTIF($E$2:$E$798,E253)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E253&lt;&gt;"",COUNTIF($E$2:$E$794,E253)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA254" s="4"/>
       <c r="AB254" s="4"/>
       <c r="AC254" t="str">
-        <f>IF(AND(E254&lt;&gt;"",COUNTIF($E$2:$E$798,E254)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E254&lt;&gt;"",COUNTIF($E$2:$E$794,E254)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA255" s="4"/>
       <c r="AB255" s="4"/>
       <c r="AC255" t="str">
-        <f>IF(AND(E255&lt;&gt;"",COUNTIF($E$2:$E$798,E255)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="27:29" x14ac:dyDescent="0.3">
+        <f>IF(AND(E255&lt;&gt;"",COUNTIF($E$2:$E$794,E255)&gt;1),"DUPLICATE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
       <c r="AA256" s="4"/>
       <c r="AB256" s="4"/>
       <c r="AC256" t="str">
-        <f>IF(AND(E256&lt;&gt;"",COUNTIF($E$2:$E$798,E256)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E256&lt;&gt;"",COUNTIF($E$2:$E$794,E256)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25179,7 +27896,7 @@
       <c r="AA257" s="4"/>
       <c r="AB257" s="4"/>
       <c r="AC257" t="str">
-        <f>IF(AND(E257&lt;&gt;"",COUNTIF($E$2:$E$798,E257)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E257&lt;&gt;"",COUNTIF($E$2:$E$794,E257)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25187,7 +27904,7 @@
       <c r="AA258" s="4"/>
       <c r="AB258" s="4"/>
       <c r="AC258" t="str">
-        <f>IF(AND(E258&lt;&gt;"",COUNTIF($E$2:$E$798,E258)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E258&lt;&gt;"",COUNTIF($E$2:$E$794,E258)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25195,7 +27912,7 @@
       <c r="AA259" s="4"/>
       <c r="AB259" s="4"/>
       <c r="AC259" t="str">
-        <f>IF(AND(E259&lt;&gt;"",COUNTIF($E$2:$E$798,E259)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E259&lt;&gt;"",COUNTIF($E$2:$E$794,E259)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25203,7 +27920,7 @@
       <c r="AA260" s="4"/>
       <c r="AB260" s="4"/>
       <c r="AC260" t="str">
-        <f>IF(AND(E260&lt;&gt;"",COUNTIF($E$2:$E$798,E260)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E260&lt;&gt;"",COUNTIF($E$2:$E$794,E260)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25211,7 +27928,7 @@
       <c r="AA261" s="4"/>
       <c r="AB261" s="4"/>
       <c r="AC261" t="str">
-        <f>IF(AND(E261&lt;&gt;"",COUNTIF($E$2:$E$798,E261)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E261&lt;&gt;"",COUNTIF($E$2:$E$794,E261)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25219,7 +27936,7 @@
       <c r="AA262" s="4"/>
       <c r="AB262" s="4"/>
       <c r="AC262" t="str">
-        <f>IF(AND(E262&lt;&gt;"",COUNTIF($E$2:$E$798,E262)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E262&lt;&gt;"",COUNTIF($E$2:$E$794,E262)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25227,7 +27944,7 @@
       <c r="AA263" s="4"/>
       <c r="AB263" s="4"/>
       <c r="AC263" t="str">
-        <f>IF(AND(E263&lt;&gt;"",COUNTIF($E$2:$E$798,E263)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E263&lt;&gt;"",COUNTIF($E$2:$E$794,E263)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25235,7 +27952,7 @@
       <c r="AA264" s="4"/>
       <c r="AB264" s="4"/>
       <c r="AC264" t="str">
-        <f>IF(AND(E264&lt;&gt;"",COUNTIF($E$2:$E$798,E264)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E264&lt;&gt;"",COUNTIF($E$2:$E$794,E264)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25243,7 +27960,7 @@
       <c r="AA265" s="4"/>
       <c r="AB265" s="4"/>
       <c r="AC265" t="str">
-        <f>IF(AND(E265&lt;&gt;"",COUNTIF($E$2:$E$798,E265)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E265&lt;&gt;"",COUNTIF($E$2:$E$794,E265)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25251,7 +27968,7 @@
       <c r="AA266" s="4"/>
       <c r="AB266" s="4"/>
       <c r="AC266" t="str">
-        <f>IF(AND(E266&lt;&gt;"",COUNTIF($E$2:$E$798,E266)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E266&lt;&gt;"",COUNTIF($E$2:$E$794,E266)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25259,7 +27976,7 @@
       <c r="AA267" s="4"/>
       <c r="AB267" s="4"/>
       <c r="AC267" t="str">
-        <f>IF(AND(E267&lt;&gt;"",COUNTIF($E$2:$E$798,E267)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E267&lt;&gt;"",COUNTIF($E$2:$E$794,E267)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25267,7 +27984,7 @@
       <c r="AA268" s="4"/>
       <c r="AB268" s="4"/>
       <c r="AC268" t="str">
-        <f>IF(AND(E268&lt;&gt;"",COUNTIF($E$2:$E$798,E268)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E268&lt;&gt;"",COUNTIF($E$2:$E$794,E268)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25275,7 +27992,7 @@
       <c r="AA269" s="4"/>
       <c r="AB269" s="4"/>
       <c r="AC269" t="str">
-        <f>IF(AND(E269&lt;&gt;"",COUNTIF($E$2:$E$798,E269)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E269&lt;&gt;"",COUNTIF($E$2:$E$794,E269)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25283,7 +28000,7 @@
       <c r="AA270" s="4"/>
       <c r="AB270" s="4"/>
       <c r="AC270" t="str">
-        <f>IF(AND(E270&lt;&gt;"",COUNTIF($E$2:$E$798,E270)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E270&lt;&gt;"",COUNTIF($E$2:$E$794,E270)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25291,7 +28008,7 @@
       <c r="AA271" s="4"/>
       <c r="AB271" s="4"/>
       <c r="AC271" t="str">
-        <f>IF(AND(E271&lt;&gt;"",COUNTIF($E$2:$E$798,E271)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E271&lt;&gt;"",COUNTIF($E$2:$E$794,E271)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25299,7 +28016,7 @@
       <c r="AA272" s="4"/>
       <c r="AB272" s="4"/>
       <c r="AC272" t="str">
-        <f>IF(AND(E272&lt;&gt;"",COUNTIF($E$2:$E$798,E272)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E272&lt;&gt;"",COUNTIF($E$2:$E$794,E272)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25307,7 +28024,7 @@
       <c r="AA273" s="4"/>
       <c r="AB273" s="4"/>
       <c r="AC273" t="str">
-        <f>IF(AND(E273&lt;&gt;"",COUNTIF($E$2:$E$798,E273)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E273&lt;&gt;"",COUNTIF($E$2:$E$794,E273)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25315,7 +28032,7 @@
       <c r="AA274" s="4"/>
       <c r="AB274" s="4"/>
       <c r="AC274" t="str">
-        <f>IF(AND(E274&lt;&gt;"",COUNTIF($E$2:$E$798,E274)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E274&lt;&gt;"",COUNTIF($E$2:$E$794,E274)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25323,7 +28040,7 @@
       <c r="AA275" s="4"/>
       <c r="AB275" s="4"/>
       <c r="AC275" t="str">
-        <f>IF(AND(E275&lt;&gt;"",COUNTIF($E$2:$E$798,E275)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E275&lt;&gt;"",COUNTIF($E$2:$E$794,E275)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25331,7 +28048,7 @@
       <c r="AA276" s="4"/>
       <c r="AB276" s="4"/>
       <c r="AC276" t="str">
-        <f>IF(AND(E276&lt;&gt;"",COUNTIF($E$2:$E$798,E276)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E276&lt;&gt;"",COUNTIF($E$2:$E$794,E276)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25339,7 +28056,7 @@
       <c r="AA277" s="4"/>
       <c r="AB277" s="4"/>
       <c r="AC277" t="str">
-        <f>IF(AND(E277&lt;&gt;"",COUNTIF($E$2:$E$798,E277)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E277&lt;&gt;"",COUNTIF($E$2:$E$794,E277)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25347,7 +28064,7 @@
       <c r="AA278" s="4"/>
       <c r="AB278" s="4"/>
       <c r="AC278" t="str">
-        <f>IF(AND(E278&lt;&gt;"",COUNTIF($E$2:$E$798,E278)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E278&lt;&gt;"",COUNTIF($E$2:$E$794,E278)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25355,7 +28072,7 @@
       <c r="AA279" s="4"/>
       <c r="AB279" s="4"/>
       <c r="AC279" t="str">
-        <f>IF(AND(E279&lt;&gt;"",COUNTIF($E$2:$E$798,E279)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E279&lt;&gt;"",COUNTIF($E$2:$E$794,E279)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25363,7 +28080,7 @@
       <c r="AA280" s="4"/>
       <c r="AB280" s="4"/>
       <c r="AC280" t="str">
-        <f>IF(AND(E280&lt;&gt;"",COUNTIF($E$2:$E$798,E280)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E280&lt;&gt;"",COUNTIF($E$2:$E$794,E280)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25371,7 +28088,7 @@
       <c r="AA281" s="4"/>
       <c r="AB281" s="4"/>
       <c r="AC281" t="str">
-        <f>IF(AND(E281&lt;&gt;"",COUNTIF($E$2:$E$798,E281)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E281&lt;&gt;"",COUNTIF($E$2:$E$794,E281)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25379,7 +28096,7 @@
       <c r="AA282" s="4"/>
       <c r="AB282" s="4"/>
       <c r="AC282" t="str">
-        <f>IF(AND(E282&lt;&gt;"",COUNTIF($E$2:$E$798,E282)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E282&lt;&gt;"",COUNTIF($E$2:$E$794,E282)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25387,7 +28104,7 @@
       <c r="AA283" s="4"/>
       <c r="AB283" s="4"/>
       <c r="AC283" t="str">
-        <f>IF(AND(E283&lt;&gt;"",COUNTIF($E$2:$E$798,E283)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E283&lt;&gt;"",COUNTIF($E$2:$E$794,E283)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25395,7 +28112,7 @@
       <c r="AA284" s="4"/>
       <c r="AB284" s="4"/>
       <c r="AC284" t="str">
-        <f>IF(AND(E284&lt;&gt;"",COUNTIF($E$2:$E$798,E284)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E284&lt;&gt;"",COUNTIF($E$2:$E$794,E284)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25403,7 +28120,7 @@
       <c r="AA285" s="4"/>
       <c r="AB285" s="4"/>
       <c r="AC285" t="str">
-        <f>IF(AND(E285&lt;&gt;"",COUNTIF($E$2:$E$798,E285)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E285&lt;&gt;"",COUNTIF($E$2:$E$794,E285)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25411,7 +28128,7 @@
       <c r="AA286" s="4"/>
       <c r="AB286" s="4"/>
       <c r="AC286" t="str">
-        <f>IF(AND(E286&lt;&gt;"",COUNTIF($E$2:$E$798,E286)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E286&lt;&gt;"",COUNTIF($E$2:$E$794,E286)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25419,7 +28136,7 @@
       <c r="AA287" s="4"/>
       <c r="AB287" s="4"/>
       <c r="AC287" t="str">
-        <f>IF(AND(E287&lt;&gt;"",COUNTIF($E$2:$E$798,E287)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E287&lt;&gt;"",COUNTIF($E$2:$E$794,E287)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25427,7 +28144,7 @@
       <c r="AA288" s="4"/>
       <c r="AB288" s="4"/>
       <c r="AC288" t="str">
-        <f>IF(AND(E288&lt;&gt;"",COUNTIF($E$2:$E$798,E288)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E288&lt;&gt;"",COUNTIF($E$2:$E$794,E288)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25435,7 +28152,7 @@
       <c r="AA289" s="4"/>
       <c r="AB289" s="4"/>
       <c r="AC289" t="str">
-        <f>IF(AND(E289&lt;&gt;"",COUNTIF($E$2:$E$798,E289)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E289&lt;&gt;"",COUNTIF($E$2:$E$794,E289)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25443,7 +28160,7 @@
       <c r="AA290" s="4"/>
       <c r="AB290" s="4"/>
       <c r="AC290" t="str">
-        <f>IF(AND(E290&lt;&gt;"",COUNTIF($E$2:$E$798,E290)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E290&lt;&gt;"",COUNTIF($E$2:$E$794,E290)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25451,7 +28168,7 @@
       <c r="AA291" s="4"/>
       <c r="AB291" s="4"/>
       <c r="AC291" t="str">
-        <f>IF(AND(E291&lt;&gt;"",COUNTIF($E$2:$E$798,E291)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E291&lt;&gt;"",COUNTIF($E$2:$E$794,E291)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25459,7 +28176,7 @@
       <c r="AA292" s="4"/>
       <c r="AB292" s="4"/>
       <c r="AC292" t="str">
-        <f>IF(AND(E292&lt;&gt;"",COUNTIF($E$2:$E$798,E292)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E292&lt;&gt;"",COUNTIF($E$2:$E$794,E292)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25467,7 +28184,7 @@
       <c r="AA293" s="4"/>
       <c r="AB293" s="4"/>
       <c r="AC293" t="str">
-        <f>IF(AND(E293&lt;&gt;"",COUNTIF($E$2:$E$798,E293)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E293&lt;&gt;"",COUNTIF($E$2:$E$794,E293)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25475,7 +28192,7 @@
       <c r="AA294" s="4"/>
       <c r="AB294" s="4"/>
       <c r="AC294" t="str">
-        <f>IF(AND(E294&lt;&gt;"",COUNTIF($E$2:$E$798,E294)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E294&lt;&gt;"",COUNTIF($E$2:$E$794,E294)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25483,7 +28200,7 @@
       <c r="AA295" s="4"/>
       <c r="AB295" s="4"/>
       <c r="AC295" t="str">
-        <f>IF(AND(E295&lt;&gt;"",COUNTIF($E$2:$E$798,E295)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E295&lt;&gt;"",COUNTIF($E$2:$E$794,E295)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25491,7 +28208,7 @@
       <c r="AA296" s="4"/>
       <c r="AB296" s="4"/>
       <c r="AC296" t="str">
-        <f>IF(AND(E296&lt;&gt;"",COUNTIF($E$2:$E$798,E296)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E296&lt;&gt;"",COUNTIF($E$2:$E$794,E296)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25499,7 +28216,7 @@
       <c r="AA297" s="4"/>
       <c r="AB297" s="4"/>
       <c r="AC297" t="str">
-        <f>IF(AND(E297&lt;&gt;"",COUNTIF($E$2:$E$798,E297)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E297&lt;&gt;"",COUNTIF($E$2:$E$794,E297)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25507,7 +28224,7 @@
       <c r="AA298" s="4"/>
       <c r="AB298" s="4"/>
       <c r="AC298" t="str">
-        <f>IF(AND(E298&lt;&gt;"",COUNTIF($E$2:$E$798,E298)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E298&lt;&gt;"",COUNTIF($E$2:$E$794,E298)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25515,7 +28232,7 @@
       <c r="AA299" s="4"/>
       <c r="AB299" s="4"/>
       <c r="AC299" t="str">
-        <f>IF(AND(E299&lt;&gt;"",COUNTIF($E$2:$E$798,E299)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E299&lt;&gt;"",COUNTIF($E$2:$E$794,E299)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25523,7 +28240,7 @@
       <c r="AA300" s="4"/>
       <c r="AB300" s="4"/>
       <c r="AC300" t="str">
-        <f>IF(AND(E300&lt;&gt;"",COUNTIF($E$2:$E$798,E300)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E300&lt;&gt;"",COUNTIF($E$2:$E$794,E300)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25531,7 +28248,7 @@
       <c r="AA301" s="4"/>
       <c r="AB301" s="4"/>
       <c r="AC301" t="str">
-        <f>IF(AND(E301&lt;&gt;"",COUNTIF($E$2:$E$798,E301)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E301&lt;&gt;"",COUNTIF($E$2:$E$794,E301)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25539,7 +28256,7 @@
       <c r="AA302" s="4"/>
       <c r="AB302" s="4"/>
       <c r="AC302" t="str">
-        <f>IF(AND(E302&lt;&gt;"",COUNTIF($E$2:$E$798,E302)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E302&lt;&gt;"",COUNTIF($E$2:$E$794,E302)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25547,7 +28264,7 @@
       <c r="AA303" s="4"/>
       <c r="AB303" s="4"/>
       <c r="AC303" t="str">
-        <f>IF(AND(E303&lt;&gt;"",COUNTIF($E$2:$E$798,E303)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E303&lt;&gt;"",COUNTIF($E$2:$E$794,E303)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25555,7 +28272,7 @@
       <c r="AA304" s="4"/>
       <c r="AB304" s="4"/>
       <c r="AC304" t="str">
-        <f>IF(AND(E304&lt;&gt;"",COUNTIF($E$2:$E$798,E304)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E304&lt;&gt;"",COUNTIF($E$2:$E$794,E304)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25563,7 +28280,7 @@
       <c r="AA305" s="4"/>
       <c r="AB305" s="4"/>
       <c r="AC305" t="str">
-        <f>IF(AND(E305&lt;&gt;"",COUNTIF($E$2:$E$798,E305)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E305&lt;&gt;"",COUNTIF($E$2:$E$794,E305)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25571,7 +28288,7 @@
       <c r="AA306" s="4"/>
       <c r="AB306" s="4"/>
       <c r="AC306" t="str">
-        <f>IF(AND(E306&lt;&gt;"",COUNTIF($E$2:$E$798,E306)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E306&lt;&gt;"",COUNTIF($E$2:$E$794,E306)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25579,7 +28296,7 @@
       <c r="AA307" s="4"/>
       <c r="AB307" s="4"/>
       <c r="AC307" t="str">
-        <f>IF(AND(E307&lt;&gt;"",COUNTIF($E$2:$E$798,E307)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E307&lt;&gt;"",COUNTIF($E$2:$E$794,E307)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25587,7 +28304,7 @@
       <c r="AA308" s="4"/>
       <c r="AB308" s="4"/>
       <c r="AC308" t="str">
-        <f>IF(AND(E308&lt;&gt;"",COUNTIF($E$2:$E$798,E308)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E308&lt;&gt;"",COUNTIF($E$2:$E$794,E308)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25595,7 +28312,7 @@
       <c r="AA309" s="4"/>
       <c r="AB309" s="4"/>
       <c r="AC309" t="str">
-        <f>IF(AND(E309&lt;&gt;"",COUNTIF($E$2:$E$798,E309)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E309&lt;&gt;"",COUNTIF($E$2:$E$794,E309)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25603,7 +28320,7 @@
       <c r="AA310" s="4"/>
       <c r="AB310" s="4"/>
       <c r="AC310" t="str">
-        <f>IF(AND(E310&lt;&gt;"",COUNTIF($E$2:$E$798,E310)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E310&lt;&gt;"",COUNTIF($E$2:$E$794,E310)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25611,7 +28328,7 @@
       <c r="AA311" s="4"/>
       <c r="AB311" s="4"/>
       <c r="AC311" t="str">
-        <f>IF(AND(E311&lt;&gt;"",COUNTIF($E$2:$E$798,E311)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E311&lt;&gt;"",COUNTIF($E$2:$E$794,E311)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25619,7 +28336,7 @@
       <c r="AA312" s="4"/>
       <c r="AB312" s="4"/>
       <c r="AC312" t="str">
-        <f>IF(AND(E312&lt;&gt;"",COUNTIF($E$2:$E$798,E312)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E312&lt;&gt;"",COUNTIF($E$2:$E$794,E312)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25627,7 +28344,7 @@
       <c r="AA313" s="4"/>
       <c r="AB313" s="4"/>
       <c r="AC313" t="str">
-        <f>IF(AND(E313&lt;&gt;"",COUNTIF($E$2:$E$798,E313)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E313&lt;&gt;"",COUNTIF($E$2:$E$794,E313)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25635,7 +28352,7 @@
       <c r="AA314" s="4"/>
       <c r="AB314" s="4"/>
       <c r="AC314" t="str">
-        <f>IF(AND(E314&lt;&gt;"",COUNTIF($E$2:$E$798,E314)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E314&lt;&gt;"",COUNTIF($E$2:$E$794,E314)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25643,7 +28360,7 @@
       <c r="AA315" s="4"/>
       <c r="AB315" s="4"/>
       <c r="AC315" t="str">
-        <f>IF(AND(E315&lt;&gt;"",COUNTIF($E$2:$E$798,E315)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E315&lt;&gt;"",COUNTIF($E$2:$E$794,E315)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25651,7 +28368,7 @@
       <c r="AA316" s="4"/>
       <c r="AB316" s="4"/>
       <c r="AC316" t="str">
-        <f>IF(AND(E316&lt;&gt;"",COUNTIF($E$2:$E$798,E316)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E316&lt;&gt;"",COUNTIF($E$2:$E$794,E316)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25659,7 +28376,7 @@
       <c r="AA317" s="4"/>
       <c r="AB317" s="4"/>
       <c r="AC317" t="str">
-        <f>IF(AND(E317&lt;&gt;"",COUNTIF($E$2:$E$798,E317)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E317&lt;&gt;"",COUNTIF($E$2:$E$794,E317)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25667,7 +28384,7 @@
       <c r="AA318" s="4"/>
       <c r="AB318" s="4"/>
       <c r="AC318" t="str">
-        <f>IF(AND(E318&lt;&gt;"",COUNTIF($E$2:$E$798,E318)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E318&lt;&gt;"",COUNTIF($E$2:$E$794,E318)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25675,7 +28392,7 @@
       <c r="AA319" s="4"/>
       <c r="AB319" s="4"/>
       <c r="AC319" t="str">
-        <f>IF(AND(E319&lt;&gt;"",COUNTIF($E$2:$E$798,E319)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E319&lt;&gt;"",COUNTIF($E$2:$E$794,E319)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25683,7 +28400,7 @@
       <c r="AA320" s="4"/>
       <c r="AB320" s="4"/>
       <c r="AC320" t="str">
-        <f>IF(AND(E320&lt;&gt;"",COUNTIF($E$2:$E$798,E320)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E320&lt;&gt;"",COUNTIF($E$2:$E$794,E320)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25691,7 +28408,7 @@
       <c r="AA321" s="4"/>
       <c r="AB321" s="4"/>
       <c r="AC321" t="str">
-        <f>IF(AND(E321&lt;&gt;"",COUNTIF($E$2:$E$798,E321)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E321&lt;&gt;"",COUNTIF($E$2:$E$794,E321)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25699,7 +28416,7 @@
       <c r="AA322" s="4"/>
       <c r="AB322" s="4"/>
       <c r="AC322" t="str">
-        <f>IF(AND(E322&lt;&gt;"",COUNTIF($E$2:$E$798,E322)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E322&lt;&gt;"",COUNTIF($E$2:$E$794,E322)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25707,7 +28424,7 @@
       <c r="AA323" s="4"/>
       <c r="AB323" s="4"/>
       <c r="AC323" t="str">
-        <f>IF(AND(E323&lt;&gt;"",COUNTIF($E$2:$E$798,E323)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E323&lt;&gt;"",COUNTIF($E$2:$E$794,E323)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25715,7 +28432,7 @@
       <c r="AA324" s="4"/>
       <c r="AB324" s="4"/>
       <c r="AC324" t="str">
-        <f>IF(AND(E324&lt;&gt;"",COUNTIF($E$2:$E$798,E324)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E324&lt;&gt;"",COUNTIF($E$2:$E$794,E324)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25723,7 +28440,7 @@
       <c r="AA325" s="4"/>
       <c r="AB325" s="4"/>
       <c r="AC325" t="str">
-        <f>IF(AND(E325&lt;&gt;"",COUNTIF($E$2:$E$798,E325)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E325&lt;&gt;"",COUNTIF($E$2:$E$794,E325)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25731,7 +28448,7 @@
       <c r="AA326" s="4"/>
       <c r="AB326" s="4"/>
       <c r="AC326" t="str">
-        <f>IF(AND(E326&lt;&gt;"",COUNTIF($E$2:$E$798,E326)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E326&lt;&gt;"",COUNTIF($E$2:$E$794,E326)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25739,7 +28456,7 @@
       <c r="AA327" s="4"/>
       <c r="AB327" s="4"/>
       <c r="AC327" t="str">
-        <f>IF(AND(E327&lt;&gt;"",COUNTIF($E$2:$E$798,E327)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E327&lt;&gt;"",COUNTIF($E$2:$E$794,E327)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25747,7 +28464,7 @@
       <c r="AA328" s="4"/>
       <c r="AB328" s="4"/>
       <c r="AC328" t="str">
-        <f>IF(AND(E328&lt;&gt;"",COUNTIF($E$2:$E$798,E328)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E328&lt;&gt;"",COUNTIF($E$2:$E$794,E328)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25755,7 +28472,7 @@
       <c r="AA329" s="4"/>
       <c r="AB329" s="4"/>
       <c r="AC329" t="str">
-        <f>IF(AND(E329&lt;&gt;"",COUNTIF($E$2:$E$798,E329)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E329&lt;&gt;"",COUNTIF($E$2:$E$794,E329)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25763,7 +28480,7 @@
       <c r="AA330" s="4"/>
       <c r="AB330" s="4"/>
       <c r="AC330" t="str">
-        <f>IF(AND(E330&lt;&gt;"",COUNTIF($E$2:$E$798,E330)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E330&lt;&gt;"",COUNTIF($E$2:$E$794,E330)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25771,7 +28488,7 @@
       <c r="AA331" s="4"/>
       <c r="AB331" s="4"/>
       <c r="AC331" t="str">
-        <f>IF(AND(E331&lt;&gt;"",COUNTIF($E$2:$E$798,E331)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E331&lt;&gt;"",COUNTIF($E$2:$E$794,E331)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25779,7 +28496,7 @@
       <c r="AA332" s="4"/>
       <c r="AB332" s="4"/>
       <c r="AC332" t="str">
-        <f>IF(AND(E332&lt;&gt;"",COUNTIF($E$2:$E$798,E332)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E332&lt;&gt;"",COUNTIF($E$2:$E$794,E332)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25787,7 +28504,7 @@
       <c r="AA333" s="4"/>
       <c r="AB333" s="4"/>
       <c r="AC333" t="str">
-        <f>IF(AND(E333&lt;&gt;"",COUNTIF($E$2:$E$798,E333)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E333&lt;&gt;"",COUNTIF($E$2:$E$794,E333)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25795,7 +28512,7 @@
       <c r="AA334" s="4"/>
       <c r="AB334" s="4"/>
       <c r="AC334" t="str">
-        <f>IF(AND(E334&lt;&gt;"",COUNTIF($E$2:$E$798,E334)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E334&lt;&gt;"",COUNTIF($E$2:$E$794,E334)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25803,7 +28520,7 @@
       <c r="AA335" s="4"/>
       <c r="AB335" s="4"/>
       <c r="AC335" t="str">
-        <f>IF(AND(E335&lt;&gt;"",COUNTIF($E$2:$E$798,E335)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E335&lt;&gt;"",COUNTIF($E$2:$E$794,E335)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25811,7 +28528,7 @@
       <c r="AA336" s="4"/>
       <c r="AB336" s="4"/>
       <c r="AC336" t="str">
-        <f>IF(AND(E336&lt;&gt;"",COUNTIF($E$2:$E$798,E336)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E336&lt;&gt;"",COUNTIF($E$2:$E$794,E336)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25819,7 +28536,7 @@
       <c r="AA337" s="4"/>
       <c r="AB337" s="4"/>
       <c r="AC337" t="str">
-        <f>IF(AND(E337&lt;&gt;"",COUNTIF($E$2:$E$798,E337)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E337&lt;&gt;"",COUNTIF($E$2:$E$794,E337)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25827,7 +28544,7 @@
       <c r="AA338" s="4"/>
       <c r="AB338" s="4"/>
       <c r="AC338" t="str">
-        <f>IF(AND(E338&lt;&gt;"",COUNTIF($E$2:$E$798,E338)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E338&lt;&gt;"",COUNTIF($E$2:$E$794,E338)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25835,7 +28552,7 @@
       <c r="AA339" s="4"/>
       <c r="AB339" s="4"/>
       <c r="AC339" t="str">
-        <f>IF(AND(E339&lt;&gt;"",COUNTIF($E$2:$E$798,E339)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E339&lt;&gt;"",COUNTIF($E$2:$E$794,E339)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25843,7 +28560,7 @@
       <c r="AA340" s="4"/>
       <c r="AB340" s="4"/>
       <c r="AC340" t="str">
-        <f>IF(AND(E340&lt;&gt;"",COUNTIF($E$2:$E$798,E340)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E340&lt;&gt;"",COUNTIF($E$2:$E$794,E340)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25851,7 +28568,7 @@
       <c r="AA341" s="4"/>
       <c r="AB341" s="4"/>
       <c r="AC341" t="str">
-        <f>IF(AND(E341&lt;&gt;"",COUNTIF($E$2:$E$798,E341)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E341&lt;&gt;"",COUNTIF($E$2:$E$794,E341)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25859,7 +28576,7 @@
       <c r="AA342" s="4"/>
       <c r="AB342" s="4"/>
       <c r="AC342" t="str">
-        <f>IF(AND(E342&lt;&gt;"",COUNTIF($E$2:$E$798,E342)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E342&lt;&gt;"",COUNTIF($E$2:$E$794,E342)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25867,7 +28584,7 @@
       <c r="AA343" s="4"/>
       <c r="AB343" s="4"/>
       <c r="AC343" t="str">
-        <f>IF(AND(E343&lt;&gt;"",COUNTIF($E$2:$E$798,E343)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E343&lt;&gt;"",COUNTIF($E$2:$E$794,E343)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25875,7 +28592,7 @@
       <c r="AA344" s="4"/>
       <c r="AB344" s="4"/>
       <c r="AC344" t="str">
-        <f>IF(AND(E344&lt;&gt;"",COUNTIF($E$2:$E$798,E344)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E344&lt;&gt;"",COUNTIF($E$2:$E$794,E344)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25883,7 +28600,7 @@
       <c r="AA345" s="4"/>
       <c r="AB345" s="4"/>
       <c r="AC345" t="str">
-        <f>IF(AND(E345&lt;&gt;"",COUNTIF($E$2:$E$798,E345)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E345&lt;&gt;"",COUNTIF($E$2:$E$794,E345)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25891,7 +28608,7 @@
       <c r="AA346" s="4"/>
       <c r="AB346" s="4"/>
       <c r="AC346" t="str">
-        <f>IF(AND(E346&lt;&gt;"",COUNTIF($E$2:$E$798,E346)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E346&lt;&gt;"",COUNTIF($E$2:$E$794,E346)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25899,7 +28616,7 @@
       <c r="AA347" s="4"/>
       <c r="AB347" s="4"/>
       <c r="AC347" t="str">
-        <f>IF(AND(E347&lt;&gt;"",COUNTIF($E$2:$E$798,E347)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E347&lt;&gt;"",COUNTIF($E$2:$E$794,E347)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25907,7 +28624,7 @@
       <c r="AA348" s="4"/>
       <c r="AB348" s="4"/>
       <c r="AC348" t="str">
-        <f>IF(AND(E348&lt;&gt;"",COUNTIF($E$2:$E$798,E348)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E348&lt;&gt;"",COUNTIF($E$2:$E$794,E348)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25915,7 +28632,7 @@
       <c r="AA349" s="4"/>
       <c r="AB349" s="4"/>
       <c r="AC349" t="str">
-        <f>IF(AND(E349&lt;&gt;"",COUNTIF($E$2:$E$798,E349)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E349&lt;&gt;"",COUNTIF($E$2:$E$794,E349)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25923,7 +28640,7 @@
       <c r="AA350" s="4"/>
       <c r="AB350" s="4"/>
       <c r="AC350" t="str">
-        <f>IF(AND(E350&lt;&gt;"",COUNTIF($E$2:$E$798,E350)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E350&lt;&gt;"",COUNTIF($E$2:$E$794,E350)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25931,7 +28648,7 @@
       <c r="AA351" s="4"/>
       <c r="AB351" s="4"/>
       <c r="AC351" t="str">
-        <f>IF(AND(E351&lt;&gt;"",COUNTIF($E$2:$E$798,E351)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E351&lt;&gt;"",COUNTIF($E$2:$E$794,E351)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25939,7 +28656,7 @@
       <c r="AA352" s="4"/>
       <c r="AB352" s="4"/>
       <c r="AC352" t="str">
-        <f>IF(AND(E352&lt;&gt;"",COUNTIF($E$2:$E$798,E352)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E352&lt;&gt;"",COUNTIF($E$2:$E$794,E352)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25947,7 +28664,7 @@
       <c r="AA353" s="4"/>
       <c r="AB353" s="4"/>
       <c r="AC353" t="str">
-        <f>IF(AND(E353&lt;&gt;"",COUNTIF($E$2:$E$798,E353)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E353&lt;&gt;"",COUNTIF($E$2:$E$794,E353)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25955,7 +28672,7 @@
       <c r="AA354" s="4"/>
       <c r="AB354" s="4"/>
       <c r="AC354" t="str">
-        <f>IF(AND(E354&lt;&gt;"",COUNTIF($E$2:$E$798,E354)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E354&lt;&gt;"",COUNTIF($E$2:$E$794,E354)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25963,7 +28680,7 @@
       <c r="AA355" s="4"/>
       <c r="AB355" s="4"/>
       <c r="AC355" t="str">
-        <f>IF(AND(E355&lt;&gt;"",COUNTIF($E$2:$E$798,E355)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E355&lt;&gt;"",COUNTIF($E$2:$E$794,E355)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25971,7 +28688,7 @@
       <c r="AA356" s="4"/>
       <c r="AB356" s="4"/>
       <c r="AC356" t="str">
-        <f>IF(AND(E356&lt;&gt;"",COUNTIF($E$2:$E$798,E356)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E356&lt;&gt;"",COUNTIF($E$2:$E$794,E356)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25979,7 +28696,7 @@
       <c r="AA357" s="4"/>
       <c r="AB357" s="4"/>
       <c r="AC357" t="str">
-        <f>IF(AND(E357&lt;&gt;"",COUNTIF($E$2:$E$798,E357)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E357&lt;&gt;"",COUNTIF($E$2:$E$794,E357)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25987,7 +28704,7 @@
       <c r="AA358" s="4"/>
       <c r="AB358" s="4"/>
       <c r="AC358" t="str">
-        <f>IF(AND(E358&lt;&gt;"",COUNTIF($E$2:$E$798,E358)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E358&lt;&gt;"",COUNTIF($E$2:$E$794,E358)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -25995,7 +28712,7 @@
       <c r="AA359" s="4"/>
       <c r="AB359" s="4"/>
       <c r="AC359" t="str">
-        <f>IF(AND(E359&lt;&gt;"",COUNTIF($E$2:$E$798,E359)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E359&lt;&gt;"",COUNTIF($E$2:$E$794,E359)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26003,7 +28720,7 @@
       <c r="AA360" s="4"/>
       <c r="AB360" s="4"/>
       <c r="AC360" t="str">
-        <f>IF(AND(E360&lt;&gt;"",COUNTIF($E$2:$E$798,E360)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E360&lt;&gt;"",COUNTIF($E$2:$E$794,E360)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26011,7 +28728,7 @@
       <c r="AA361" s="4"/>
       <c r="AB361" s="4"/>
       <c r="AC361" t="str">
-        <f>IF(AND(E361&lt;&gt;"",COUNTIF($E$2:$E$798,E361)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E361&lt;&gt;"",COUNTIF($E$2:$E$794,E361)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26019,7 +28736,7 @@
       <c r="AA362" s="4"/>
       <c r="AB362" s="4"/>
       <c r="AC362" t="str">
-        <f>IF(AND(E362&lt;&gt;"",COUNTIF($E$2:$E$798,E362)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E362&lt;&gt;"",COUNTIF($E$2:$E$794,E362)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26027,7 +28744,7 @@
       <c r="AA363" s="4"/>
       <c r="AB363" s="4"/>
       <c r="AC363" t="str">
-        <f>IF(AND(E363&lt;&gt;"",COUNTIF($E$2:$E$798,E363)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E363&lt;&gt;"",COUNTIF($E$2:$E$794,E363)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26035,7 +28752,7 @@
       <c r="AA364" s="4"/>
       <c r="AB364" s="4"/>
       <c r="AC364" t="str">
-        <f>IF(AND(E364&lt;&gt;"",COUNTIF($E$2:$E$798,E364)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E364&lt;&gt;"",COUNTIF($E$2:$E$794,E364)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26043,7 +28760,7 @@
       <c r="AA365" s="4"/>
       <c r="AB365" s="4"/>
       <c r="AC365" t="str">
-        <f>IF(AND(E365&lt;&gt;"",COUNTIF($E$2:$E$798,E365)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E365&lt;&gt;"",COUNTIF($E$2:$E$794,E365)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26051,7 +28768,7 @@
       <c r="AA366" s="4"/>
       <c r="AB366" s="4"/>
       <c r="AC366" t="str">
-        <f>IF(AND(E366&lt;&gt;"",COUNTIF($E$2:$E$798,E366)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E366&lt;&gt;"",COUNTIF($E$2:$E$794,E366)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26059,7 +28776,7 @@
       <c r="AA367" s="4"/>
       <c r="AB367" s="4"/>
       <c r="AC367" t="str">
-        <f>IF(AND(E367&lt;&gt;"",COUNTIF($E$2:$E$798,E367)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E367&lt;&gt;"",COUNTIF($E$2:$E$794,E367)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26067,7 +28784,7 @@
       <c r="AA368" s="4"/>
       <c r="AB368" s="4"/>
       <c r="AC368" t="str">
-        <f>IF(AND(E368&lt;&gt;"",COUNTIF($E$2:$E$798,E368)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E368&lt;&gt;"",COUNTIF($E$2:$E$794,E368)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26075,7 +28792,7 @@
       <c r="AA369" s="4"/>
       <c r="AB369" s="4"/>
       <c r="AC369" t="str">
-        <f>IF(AND(E369&lt;&gt;"",COUNTIF($E$2:$E$798,E369)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E369&lt;&gt;"",COUNTIF($E$2:$E$794,E369)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26083,7 +28800,7 @@
       <c r="AA370" s="4"/>
       <c r="AB370" s="4"/>
       <c r="AC370" t="str">
-        <f>IF(AND(E370&lt;&gt;"",COUNTIF($E$2:$E$798,E370)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E370&lt;&gt;"",COUNTIF($E$2:$E$794,E370)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26091,7 +28808,7 @@
       <c r="AA371" s="4"/>
       <c r="AB371" s="4"/>
       <c r="AC371" t="str">
-        <f>IF(AND(E371&lt;&gt;"",COUNTIF($E$2:$E$798,E371)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E371&lt;&gt;"",COUNTIF($E$2:$E$794,E371)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26099,7 +28816,7 @@
       <c r="AA372" s="4"/>
       <c r="AB372" s="4"/>
       <c r="AC372" t="str">
-        <f>IF(AND(E372&lt;&gt;"",COUNTIF($E$2:$E$798,E372)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E372&lt;&gt;"",COUNTIF($E$2:$E$794,E372)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26107,7 +28824,7 @@
       <c r="AA373" s="4"/>
       <c r="AB373" s="4"/>
       <c r="AC373" t="str">
-        <f>IF(AND(E373&lt;&gt;"",COUNTIF($E$2:$E$798,E373)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E373&lt;&gt;"",COUNTIF($E$2:$E$794,E373)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26115,7 +28832,7 @@
       <c r="AA374" s="4"/>
       <c r="AB374" s="4"/>
       <c r="AC374" t="str">
-        <f>IF(AND(E374&lt;&gt;"",COUNTIF($E$2:$E$798,E374)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E374&lt;&gt;"",COUNTIF($E$2:$E$794,E374)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26123,7 +28840,7 @@
       <c r="AA375" s="4"/>
       <c r="AB375" s="4"/>
       <c r="AC375" t="str">
-        <f>IF(AND(E375&lt;&gt;"",COUNTIF($E$2:$E$798,E375)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E375&lt;&gt;"",COUNTIF($E$2:$E$794,E375)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26131,7 +28848,7 @@
       <c r="AA376" s="4"/>
       <c r="AB376" s="4"/>
       <c r="AC376" t="str">
-        <f>IF(AND(E376&lt;&gt;"",COUNTIF($E$2:$E$798,E376)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E376&lt;&gt;"",COUNTIF($E$2:$E$794,E376)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26139,7 +28856,7 @@
       <c r="AA377" s="4"/>
       <c r="AB377" s="4"/>
       <c r="AC377" t="str">
-        <f>IF(AND(E377&lt;&gt;"",COUNTIF($E$2:$E$798,E377)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E377&lt;&gt;"",COUNTIF($E$2:$E$794,E377)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26147,7 +28864,7 @@
       <c r="AA378" s="4"/>
       <c r="AB378" s="4"/>
       <c r="AC378" t="str">
-        <f>IF(AND(E378&lt;&gt;"",COUNTIF($E$2:$E$798,E378)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E378&lt;&gt;"",COUNTIF($E$2:$E$794,E378)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26155,7 +28872,7 @@
       <c r="AA379" s="4"/>
       <c r="AB379" s="4"/>
       <c r="AC379" t="str">
-        <f>IF(AND(E379&lt;&gt;"",COUNTIF($E$2:$E$798,E379)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E379&lt;&gt;"",COUNTIF($E$2:$E$794,E379)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26163,7 +28880,7 @@
       <c r="AA380" s="4"/>
       <c r="AB380" s="4"/>
       <c r="AC380" t="str">
-        <f>IF(AND(E380&lt;&gt;"",COUNTIF($E$2:$E$798,E380)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E380&lt;&gt;"",COUNTIF($E$2:$E$794,E380)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26171,7 +28888,7 @@
       <c r="AA381" s="4"/>
       <c r="AB381" s="4"/>
       <c r="AC381" t="str">
-        <f>IF(AND(E381&lt;&gt;"",COUNTIF($E$2:$E$798,E381)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E381&lt;&gt;"",COUNTIF($E$2:$E$794,E381)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26179,7 +28896,7 @@
       <c r="AA382" s="4"/>
       <c r="AB382" s="4"/>
       <c r="AC382" t="str">
-        <f>IF(AND(E382&lt;&gt;"",COUNTIF($E$2:$E$798,E382)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E382&lt;&gt;"",COUNTIF($E$2:$E$794,E382)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26187,7 +28904,7 @@
       <c r="AA383" s="4"/>
       <c r="AB383" s="4"/>
       <c r="AC383" t="str">
-        <f>IF(AND(E383&lt;&gt;"",COUNTIF($E$2:$E$798,E383)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E383&lt;&gt;"",COUNTIF($E$2:$E$794,E383)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26195,7 +28912,7 @@
       <c r="AA384" s="4"/>
       <c r="AB384" s="4"/>
       <c r="AC384" t="str">
-        <f>IF(AND(E384&lt;&gt;"",COUNTIF($E$2:$E$798,E384)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E384&lt;&gt;"",COUNTIF($E$2:$E$794,E384)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26203,7 +28920,7 @@
       <c r="AA385" s="4"/>
       <c r="AB385" s="4"/>
       <c r="AC385" t="str">
-        <f>IF(AND(E385&lt;&gt;"",COUNTIF($E$2:$E$798,E385)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E385&lt;&gt;"",COUNTIF($E$2:$E$794,E385)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26211,7 +28928,7 @@
       <c r="AA386" s="4"/>
       <c r="AB386" s="4"/>
       <c r="AC386" t="str">
-        <f>IF(AND(E386&lt;&gt;"",COUNTIF($E$2:$E$798,E386)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E386&lt;&gt;"",COUNTIF($E$2:$E$794,E386)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26219,7 +28936,7 @@
       <c r="AA387" s="4"/>
       <c r="AB387" s="4"/>
       <c r="AC387" t="str">
-        <f>IF(AND(E387&lt;&gt;"",COUNTIF($E$2:$E$798,E387)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E387&lt;&gt;"",COUNTIF($E$2:$E$794,E387)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26227,7 +28944,7 @@
       <c r="AA388" s="4"/>
       <c r="AB388" s="4"/>
       <c r="AC388" t="str">
-        <f>IF(AND(E388&lt;&gt;"",COUNTIF($E$2:$E$798,E388)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E388&lt;&gt;"",COUNTIF($E$2:$E$794,E388)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26235,7 +28952,7 @@
       <c r="AA389" s="4"/>
       <c r="AB389" s="4"/>
       <c r="AC389" t="str">
-        <f>IF(AND(E389&lt;&gt;"",COUNTIF($E$2:$E$798,E389)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E389&lt;&gt;"",COUNTIF($E$2:$E$794,E389)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26243,7 +28960,7 @@
       <c r="AA390" s="4"/>
       <c r="AB390" s="4"/>
       <c r="AC390" t="str">
-        <f>IF(AND(E390&lt;&gt;"",COUNTIF($E$2:$E$798,E390)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E390&lt;&gt;"",COUNTIF($E$2:$E$794,E390)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26251,7 +28968,7 @@
       <c r="AA391" s="4"/>
       <c r="AB391" s="4"/>
       <c r="AC391" t="str">
-        <f>IF(AND(E391&lt;&gt;"",COUNTIF($E$2:$E$798,E391)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E391&lt;&gt;"",COUNTIF($E$2:$E$794,E391)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26259,7 +28976,7 @@
       <c r="AA392" s="4"/>
       <c r="AB392" s="4"/>
       <c r="AC392" t="str">
-        <f>IF(AND(E392&lt;&gt;"",COUNTIF($E$2:$E$798,E392)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E392&lt;&gt;"",COUNTIF($E$2:$E$794,E392)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26267,7 +28984,7 @@
       <c r="AA393" s="4"/>
       <c r="AB393" s="4"/>
       <c r="AC393" t="str">
-        <f>IF(AND(E393&lt;&gt;"",COUNTIF($E$2:$E$798,E393)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E393&lt;&gt;"",COUNTIF($E$2:$E$794,E393)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -26275,62 +28992,30 @@
       <c r="AA394" s="4"/>
       <c r="AB394" s="4"/>
       <c r="AC394" t="str">
-        <f>IF(AND(E394&lt;&gt;"",COUNTIF($E$2:$E$798,E394)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="395" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA395" s="4"/>
-      <c r="AB395" s="4"/>
-      <c r="AC395" t="str">
-        <f>IF(AND(E395&lt;&gt;"",COUNTIF($E$2:$E$798,E395)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="396" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA396" s="4"/>
-      <c r="AB396" s="4"/>
-      <c r="AC396" t="str">
-        <f>IF(AND(E396&lt;&gt;"",COUNTIF($E$2:$E$798,E396)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="397" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA397" s="4"/>
-      <c r="AB397" s="4"/>
-      <c r="AC397" t="str">
-        <f>IF(AND(E397&lt;&gt;"",COUNTIF($E$2:$E$798,E397)&gt;1),"DUPLICATE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="398" spans="27:29" x14ac:dyDescent="0.3">
-      <c r="AA398" s="4"/>
-      <c r="AB398" s="4"/>
-      <c r="AC398" t="str">
-        <f>IF(AND(E398&lt;&gt;"",COUNTIF($E$2:$E$798,E398)&gt;1),"DUPLICATE","")</f>
+        <f>IF(AND(E394&lt;&gt;"",COUNTIF($E$2:$E$794,E394)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E798">
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>AND($E2&lt;&gt;"",COUNTIF($E$2:$E$798,$E2)&gt;1)</formula>
+  <conditionalFormatting sqref="E2:E794">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>AND($E2&lt;&gt;"",COUNTIF($E$2:$E$794,$E2)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B798">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B794">
       <formula1>"Open,Closed,Hidden"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C798">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C794">
       <formula1>"Yes"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D798">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D794">
       <formula1>"Scholarship,Internship"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G798">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G794">
       <formula1>"Africa,Asia,Europe,North America,Latin America &amp; Caribbean,Oceania"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K798">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K794">
       <formula1>"Full,Stipend,Partial"</formula1>
     </dataValidation>
   </dataValidations>

--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -29599,7 +29599,7 @@
         <v>46313</v>
       </c>
       <c r="AC130" t="str">
-        <f t="shared" ref="AC130:AC193" si="2">IF(AND(E130&lt;&gt;"",COUNTIF($E$2:$E$800,E130)&gt;1),"DUPLICATE","")</f>
+        <f t="shared" ref="AC130:AC167" si="2">IF(AND(E130&lt;&gt;"",COUNTIF($E$2:$E$800,E130)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>
@@ -32431,7 +32431,7 @@
       </c>
       <c r="AB168" s="4"/>
       <c r="AC168" s="5" t="str">
-        <f t="shared" ref="AC168:AC183" si="3">IF(AND(E168&lt;&gt;"",COUNTIF($E$2:$E$778,E168)&gt;1),"DUPLICATE","")</f>
+        <f t="shared" ref="AC168:AC177" si="3">IF(AND(E168&lt;&gt;"",COUNTIF($E$2:$E$778,E168)&gt;1),"DUPLICATE","")</f>
         <v/>
       </c>
     </row>

--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9980" uniqueCount="6553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9980" uniqueCount="6554">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -19689,6 +19689,9 @@
   </si>
   <si>
     <t>content.xlsx</t>
+  </si>
+  <si>
+    <t>France | Spain | Netherlands</t>
   </si>
 </sst>
 </file>
@@ -55329,7 +55332,7 @@
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
       <c r="O4" s="5" t="s">
-        <v>6537</v>
+        <v>6553</v>
       </c>
       <c r="P4" s="10" t="s">
         <v>6547</v>

--- a/content.xlsx
+++ b/content.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9980" uniqueCount="6554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9995" uniqueCount="6564">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -19664,9 +19664,6 @@
     <t>Won an Erasmus Mundus Joint Master scholarship | Helped more than 50 students during their applications</t>
   </si>
   <si>
-    <t>English and Bangla</t>
-  </si>
-  <si>
     <t>Enschede, Netherlands</t>
   </si>
   <si>
@@ -19692,6 +19689,39 @@
   </si>
   <si>
     <t>France | Spain | Netherlands</t>
+  </si>
+  <si>
+    <t>Mahfuja Fariha Mim</t>
+  </si>
+  <si>
+    <t>I have completed my bachelor degree from Materials Science and Engineering, University of Rajshahi. I am currently enrolled Erasmus Mundus joint Master Program in Advanced Structural Analysis and Design using Composite Materials (FRP++). I would be happy if I help to those student who has the enthusiam to study abroad specially who are in the field of engineering and guide them to be on the right track.</t>
+  </si>
+  <si>
+    <t>Erasmus Mundus Scholarship Awardee</t>
+  </si>
+  <si>
+    <t>Won an Erasmus Mundus Joint Master scholarship</t>
+  </si>
+  <si>
+    <t>Girona, Spain</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ mahfujafarihamim</t>
+  </si>
+  <si>
+    <t>Motivation letter | Recommendation letters | IELTS or TOEFL preparation | Visa guidance</t>
+  </si>
+  <si>
+    <t>Mentor, Master's Student</t>
+  </si>
+  <si>
+    <t>mahfuja-fariha-mim.png</t>
+  </si>
+  <si>
+    <t>BSc in Materials Science and Engineeirng, University of Rajshahi | EMJMD in FRP++, University of Girona</t>
+  </si>
+  <si>
+    <t>University of Girona, Spain | University of Toulouse/ INSA Toulouse</t>
   </si>
 </sst>
 </file>
@@ -20287,7 +20317,7 @@
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>6552</v>
+        <v>6551</v>
       </c>
     </row>
   </sheetData>
@@ -55130,7 +55160,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" style="5" customWidth="1"/>
@@ -55223,7 +55253,7 @@
         <v>2165</v>
       </c>
       <c r="G2" t="s">
-        <v>6551</v>
+        <v>6550</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>6536</v>
@@ -55300,7 +55330,7 @@
         <v>6539</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>6549</v>
+        <v>6548</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>6540</v>
@@ -55312,33 +55342,33 @@
         <v>6542</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>6550</v>
+        <v>6549</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>6536</v>
+        <v>6562</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>6543</v>
       </c>
       <c r="J4" s="10" t="s">
+        <v>2175</v>
+      </c>
+      <c r="K4" s="10" t="s">
         <v>6544</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="L4" s="11" t="s">
         <v>6545</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>6546</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
       <c r="O4" s="5" t="s">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="P4" s="10" t="s">
+        <v>6546</v>
+      </c>
+      <c r="Q4" s="12" t="s">
         <v>6547</v>
-      </c>
-      <c r="Q4" s="12" t="s">
-        <v>6548</v>
       </c>
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
@@ -55350,9 +55380,67 @@
       <c r="Y4" s="10"/>
       <c r="Z4" s="10"/>
     </row>
+    <row r="5" spans="1:26" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>6553</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>6560</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>6554</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>6561</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>6555</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>6549</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>6536</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>6556</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>2175</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>6557</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>6558</v>
+      </c>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>6563</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>6559</v>
+      </c>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="N2:N3 N5:N300">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N3 N6:N300">
       <formula1>"Published,Hidden"</formula1>
     </dataValidation>
   </dataValidations>

--- a/content.xlsx
+++ b/content.xlsx
@@ -19715,13 +19715,13 @@
     <t>Mentor, Master's Student</t>
   </si>
   <si>
-    <t>mahfuja-fariha-mim.png</t>
-  </si>
-  <si>
     <t>BSc in Materials Science and Engineeirng, University of Rajshahi | EMJMD in FRP++, University of Girona</t>
   </si>
   <si>
     <t>University of Girona, Spain | University of Toulouse/ INSA Toulouse</t>
+  </si>
+  <si>
+    <t>mahfuja-fariha-mim.jpeg</t>
   </si>
 </sst>
 </file>
@@ -55345,7 +55345,7 @@
         <v>6549</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>6562</v>
+        <v>6561</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>6543</v>
@@ -55394,7 +55394,7 @@
         <v>6554</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>6561</v>
+        <v>6563</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>6555</v>
@@ -55423,7 +55423,7 @@
         <v>696</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>6563</v>
+        <v>6562</v>
       </c>
       <c r="Q5" s="12" t="s">
         <v>6559</v>

--- a/content.xlsx
+++ b/content.xlsx
@@ -55345,7 +55345,7 @@
         <v>6549</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>6561</v>
+        <v>6536</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>6543</v>
@@ -55403,7 +55403,7 @@
         <v>6549</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>6536</v>
+        <v>6561</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>6556</v>

--- a/content.xlsx
+++ b/content.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10009" uniqueCount="6575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10039" uniqueCount="6599">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -19755,6 +19755,79 @@
   </si>
   <si>
     <t>grishika-arora.png</t>
+  </si>
+  <si>
+    <t>Jakirul Islam</t>
+  </si>
+  <si>
+    <t>Currently I'm pursuing a master's program at Roskilde University, Denmark. 
+I can help future students choose the right country and university based on their goals. I can also provide guidance on the visa application process, which might be very helpful for students who planning to study abroad.</t>
+  </si>
+  <si>
+    <t>jakirul-islam.jpg</t>
+  </si>
+  <si>
+    <t>Bangla | English</t>
+  </si>
+  <si>
+    <t>Copenhagen, Denmark</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jakirul-islam-0948b1291?utm_source=share_via&amp;utm_content=profile&amp;utm_medium=member_android</t>
+  </si>
+  <si>
+    <t>Roskilde University, Denmark</t>
+  </si>
+  <si>
+    <t>University and course selection | Visa guidance | Life abroad and housing</t>
+  </si>
+  <si>
+    <t>Msc Student in Denmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc in Global and Development Studies, Roskilde University </t>
+  </si>
+  <si>
+    <t>Helped students to select suitable country and university.</t>
+  </si>
+  <si>
+    <t>Rakibul Hasan</t>
+  </si>
+  <si>
+    <t>I am a researcher in Materials Science, happy to share what I have learned along the way. Before coming to Europe, I completed my BSc in Materials Science and Engineering at the University of Rajshahi in Bangladesh. I then studied the Erasmus Mundus Joint Master (EMJM) FRP++ programme at UT3 in France and UdG in Spain, where my thesis focused on the microstructural analysis of materials for liquid H₂ storage tanks. After that, I was fortunate to join REFFRACTEUR, an MSCA industrial doctoral network on sustainable refractory materials. I am now a PhD candidate at the Institute of Research for Ceramics – IRCER under the University of Limoges, working jointly with Imerys. I remember how confusing the application process felt at the start, so I am glad to help students with choosing programmes, writing CVs and motivation letters, and preparing for scholarship interviews.</t>
+  </si>
+  <si>
+    <t>EMJM Graduate &amp; MSCA PhD Candidate</t>
+  </si>
+  <si>
+    <t>EMJM | MSCA</t>
+  </si>
+  <si>
+    <t>PhD, DEM Modelling of Microcracks for Refractory Materials, IRCER and Imerys, France (2026 - now) | MSc, EMJM FRP++, France and Spain (2025 - 2026) | BSc, Materials Science and Engineering, Bangladesh (2018-2024)</t>
+  </si>
+  <si>
+    <t>Helping students throughout the application process, like CV-making-to-application-submission for various scholarships</t>
+  </si>
+  <si>
+    <t>Bengali | English | Hindi | Urdu</t>
+  </si>
+  <si>
+    <t>Limoges, France</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/rhcontact</t>
+  </si>
+  <si>
+    <t>France | Spain | Portugal</t>
+  </si>
+  <si>
+    <t>University of Toulouse | University of Girona | University of Minho</t>
+  </si>
+  <si>
+    <t>Scholarship search and shortlist | SOP review | Motivation letter | CV review | Recommendation letters | IELTS or TOEFL preparation | University and course selection | Interview preparation | Visa guidance | Life abroad and housing | Financial planning for life abroad</t>
+  </si>
+  <si>
+    <t>rakibul-hasan.jpeg</t>
   </si>
 </sst>
 </file>
@@ -55193,7 +55266,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" style="5" customWidth="1"/>
@@ -55527,16 +55600,134 @@
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
     </row>
+    <row r="7" spans="1:26" ht="80.400000000000006" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>6575</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>6567</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>6576</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>6577</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>6583</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
+        <v>6584</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6585</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>6578</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>6579</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>6580</v>
+      </c>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10" t="s">
+        <v>5224</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>6581</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>6582</v>
+      </c>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+    </row>
+    <row r="8" spans="1:26" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>6586</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>6566</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>6587</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>6598</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>6588</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>6589</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>6590</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>6591</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>6592</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>6593</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>6594</v>
+      </c>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10" t="s">
+        <v>2177</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>6595</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>6596</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>6597</v>
+      </c>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="N2:N3 N7:N300">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N3 N9:N300">
       <formula1>"Published,Hidden"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="L4" r:id="rId1"/>
+    <hyperlink ref="L7" r:id="rId2"/>
+    <hyperlink ref="L8" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/content.xlsx
+++ b/content.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10039" uniqueCount="6599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10038" uniqueCount="6599">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -55600,7 +55600,7 @@
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
     </row>
-    <row r="7" spans="1:26" ht="80.400000000000006" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>365</v>
       </c>
@@ -55656,7 +55656,7 @@
       <c r="Y7" s="10"/>
       <c r="Z7" s="10"/>
     </row>
-    <row r="8" spans="1:26" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>2161</v>
       </c>
@@ -55694,9 +55694,7 @@
         <v>6594</v>
       </c>
       <c r="M8" s="10"/>
-      <c r="N8" s="10" t="s">
-        <v>2177</v>
-      </c>
+      <c r="N8" s="10"/>
       <c r="O8" s="10" t="s">
         <v>6595</v>
       </c>

--- a/content.xlsx
+++ b/content.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10038" uniqueCount="6599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10052" uniqueCount="6612">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -19828,6 +19828,45 @@
   </si>
   <si>
     <t>rakibul-hasan.jpeg</t>
+  </si>
+  <si>
+    <t>Akash Roy</t>
+  </si>
+  <si>
+    <t>I am an Erasmus Mundus scholarship recipient and a PhD researcher at CNRS, France, with a background in Chemical Engineering and Materials Science. Having experienced the journey of studying abroad firsthand, I understand the challenges of securing scholarships and research opportunities. I aim to help students with Erasmus Mundus applications, university selection, motivation letters, CV preparation, and approaching professors. Through my experience, I hope to guide aspiring students toward achieving their international academic dreams.</t>
+  </si>
+  <si>
+    <t>Erasmus Mundus | CNRS PhD Position</t>
+  </si>
+  <si>
+    <t>PhD , Chemical Engineering 2026-Current | EMJMD , Bioref 2024-2026</t>
+  </si>
+  <si>
+    <t>Strasbourg, France</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/akash-roy-54316a217?utm_source=share_via&amp;utm_content=profile&amp;utm_medium=member_ios</t>
+  </si>
+  <si>
+    <t>France Poland Italy</t>
+  </si>
+  <si>
+    <t>Scholarship search and shortlist | SOP review | Motivation letter | CV review | Recommendation letters | IELTS or TOEFL preparation | Interview preparation | Visa guidance | Life abroad and housing</t>
+  </si>
+  <si>
+    <t>PhD Researcher</t>
+  </si>
+  <si>
+    <t>Erasmus Mundus and Several PhD Positions Winner</t>
+  </si>
+  <si>
+    <t>Won EMJM for a Master</t>
+  </si>
+  <si>
+    <t>Bangla | English | French</t>
+  </si>
+  <si>
+    <t>akash-roy.png</t>
   </si>
 </sst>
 </file>
@@ -55266,7 +55305,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" style="5" customWidth="1"/>
@@ -55714,9 +55753,65 @@
       <c r="Y8" s="10"/>
       <c r="Z8" s="10"/>
     </row>
+    <row r="9" spans="1:26" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>6599</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>6607</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>6600</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>6611</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>6608</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>6601</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>6602</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>6609</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>6610</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>6603</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>6604</v>
+      </c>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="12" t="s">
+        <v>6605</v>
+      </c>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="12" t="s">
+        <v>6606</v>
+      </c>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="10"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="N2:N3 N9:N300">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N3 N10:N300">
       <formula1>"Published,Hidden"</formula1>
     </dataValidation>
   </dataValidations>
@@ -55724,8 +55819,9 @@
     <hyperlink ref="L4" r:id="rId1"/>
     <hyperlink ref="L7" r:id="rId2"/>
     <hyperlink ref="L8" r:id="rId3"/>
+    <hyperlink ref="L9" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/content.xlsx
+++ b/content.xlsx
@@ -19848,9 +19848,6 @@
     <t>https://www.linkedin.com/in/akash-roy-54316a217?utm_source=share_via&amp;utm_content=profile&amp;utm_medium=member_ios</t>
   </si>
   <si>
-    <t>France Poland Italy</t>
-  </si>
-  <si>
     <t>Scholarship search and shortlist | SOP review | Motivation letter | CV review | Recommendation letters | IELTS or TOEFL preparation | Interview preparation | Visa guidance | Life abroad and housing</t>
   </si>
   <si>
@@ -19867,6 +19864,9 @@
   </si>
   <si>
     <t>akash-roy.png</t>
+  </si>
+  <si>
+    <t>France | Poland | Italy</t>
   </si>
 </sst>
 </file>
@@ -55761,16 +55761,16 @@
         <v>6599</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>6607</v>
+        <v>6606</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>6600</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>6611</v>
+        <v>6610</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>6608</v>
+        <v>6607</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>6601</v>
@@ -55779,10 +55779,10 @@
         <v>6602</v>
       </c>
       <c r="I9" s="10" t="s">
+        <v>6608</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>6609</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>6610</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>6603</v>
@@ -55793,11 +55793,11 @@
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
       <c r="O9" s="12" t="s">
-        <v>6605</v>
+        <v>6611</v>
       </c>
       <c r="P9" s="10"/>
       <c r="Q9" s="12" t="s">
-        <v>6606</v>
+        <v>6605</v>
       </c>
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>

--- a/content.xlsx
+++ b/content.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10052" uniqueCount="6612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10067" uniqueCount="6624">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -19867,6 +19867,42 @@
   </si>
   <si>
     <t>France | Poland | Italy</t>
+  </si>
+  <si>
+    <t>MD Hasibul Hoque</t>
+  </si>
+  <si>
+    <t>I have completed my MSc IT with Data Analytics course at the University of the West of Scotland, London Campus, and received confirmation of course completion from my university. During my journey, I received a 30% university tuition fee discount and learned the importance of choosing a university that fits both academic goals and budget. I researched UK universities, compared tuition fees and funding opportunities, prepared application documents, and navigated the student visa process. Having helped friends and family, both formally and informally, I understand some of the questions prospective international students face when planning to study in the UK. I aim to help students explore suitable universities and courses, understand admission requirements, prepare application documents, research scholarships, and navigate the transition to UK student life.</t>
+  </si>
+  <si>
+    <t>md-hasibul-hoque.jpg</t>
+  </si>
+  <si>
+    <t>Completed MSc IT with Data Analytics course requirements at the University of the West of Scotland in 2026 | Received a 30% university tuition fee discount | Independently researched UK university options, tuition fees, funding opportunities, admission requirements, application documents and the student visa process</t>
+  </si>
+  <si>
+    <t>Bangla | English | Hindi | Urdu</t>
+  </si>
+  <si>
+    <t>London, United Kingdom</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/hasibul-hoque-1272751a7</t>
+  </si>
+  <si>
+    <t>Bangladesh | United Kingdom</t>
+  </si>
+  <si>
+    <t>University of the West of Scotland, London Campus | Noakhali Science and Technology University</t>
+  </si>
+  <si>
+    <t>Scholarship search and shortlist | SOP review | Motivation letter | CV review | Recommendation letters | IELTS or TOEFL preparation | University and course selection | Interview preparation | Visa guidance | Life abroad and housing</t>
+  </si>
+  <si>
+    <t>UK Higher Education Mentor</t>
+  </si>
+  <si>
+    <t>MSc, IT with Data Analytics, University of the West of Scotland, London Campus | BSC, Electrical &amp; Electronic Engineering, Noakhali Science &amp; Technology University</t>
   </si>
 </sst>
 </file>
@@ -55305,7 +55341,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" style="5" customWidth="1"/>
@@ -55809,9 +55845,67 @@
       <c r="Y9" s="10"/>
       <c r="Z9" s="10"/>
     </row>
+    <row r="10" spans="1:26" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>6612</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>6567</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>6613</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>6614</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>6622</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>6623</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>6615</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>6616</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>6617</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>6618</v>
+      </c>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10" t="s">
+        <v>2177</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>6619</v>
+      </c>
+      <c r="P10" s="10" t="s">
+        <v>6620</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>6621</v>
+      </c>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="N2:N3 N10:N300">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N3 N11:N300">
       <formula1>"Published,Hidden"</formula1>
     </dataValidation>
   </dataValidations>
@@ -55820,8 +55914,9 @@
     <hyperlink ref="L7" r:id="rId2"/>
     <hyperlink ref="L8" r:id="rId3"/>
     <hyperlink ref="L9" r:id="rId4"/>
+    <hyperlink ref="L10" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10067" uniqueCount="6624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10066" uniqueCount="6624">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -55845,7 +55845,7 @@
       <c r="Y9" s="10"/>
       <c r="Z9" s="10"/>
     </row>
-    <row r="10" spans="1:26" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>2217</v>
       </c>
@@ -55881,9 +55881,7 @@
         <v>6618</v>
       </c>
       <c r="M10" s="10"/>
-      <c r="N10" s="10" t="s">
-        <v>2177</v>
-      </c>
+      <c r="N10" s="10"/>
       <c r="O10" s="10" t="s">
         <v>6619</v>
       </c>

--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11856" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10066" uniqueCount="6624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10074" uniqueCount="6624">
   <si>
     <t>UNIPILOT GLOBAL: your website's content file</t>
   </si>
@@ -55448,6 +55448,9 @@
       <c r="K2" s="5" t="s">
         <v>6533</v>
       </c>
+      <c r="N2" s="5" t="s">
+        <v>2177</v>
+      </c>
       <c r="O2" s="5" t="s">
         <v>6535</v>
       </c>
@@ -55541,7 +55544,9 @@
         <v>6543</v>
       </c>
       <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+      <c r="N4" s="5" t="s">
+        <v>2177</v>
+      </c>
       <c r="O4" s="5" t="s">
         <v>6549</v>
       </c>
@@ -55599,7 +55604,9 @@
         <v>6555</v>
       </c>
       <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
+      <c r="N5" s="5" t="s">
+        <v>2177</v>
+      </c>
       <c r="O5" s="10" t="s">
         <v>696</v>
       </c>
@@ -55655,7 +55662,9 @@
       </c>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
+      <c r="N6" s="5" t="s">
+        <v>2177</v>
+      </c>
       <c r="O6" s="12" t="s">
         <v>6572</v>
       </c>
@@ -55711,7 +55720,9 @@
         <v>6580</v>
       </c>
       <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
+      <c r="N7" s="5" t="s">
+        <v>2177</v>
+      </c>
       <c r="O7" s="10" t="s">
         <v>5224</v>
       </c>
@@ -55769,7 +55780,9 @@
         <v>6594</v>
       </c>
       <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
+      <c r="N8" s="5" t="s">
+        <v>2177</v>
+      </c>
       <c r="O8" s="10" t="s">
         <v>6595</v>
       </c>
@@ -55827,7 +55840,9 @@
         <v>6604</v>
       </c>
       <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
+      <c r="N9" s="5" t="s">
+        <v>2177</v>
+      </c>
       <c r="O9" s="12" t="s">
         <v>6611</v>
       </c>
@@ -55881,7 +55896,9 @@
         <v>6618</v>
       </c>
       <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
+      <c r="N10" s="5" t="s">
+        <v>2177</v>
+      </c>
       <c r="O10" s="10" t="s">
         <v>6619</v>
       </c>
@@ -55903,7 +55920,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="N2:N3 N11:N300">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N300">
       <formula1>"Published,Hidden"</formula1>
     </dataValidation>
   </dataValidations>

--- a/content.xlsx
+++ b/content.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" firstSheet="1" activeTab="10"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
